--- a/data/france/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
+++ b/data/france/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:BP1"/>
+  <dimension ref="A1:BP17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -764,6 +768,3154 @@
           <t>sum_pot_player_miss_away</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>zkPwWhT1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>45522.65625</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millot b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>29778</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="M2" t="n">
+        <v>48</v>
+      </c>
+      <c r="N2" t="n">
+        <v>52</v>
+      </c>
+      <c r="O2" t="n">
+        <v>22</v>
+      </c>
+      <c r="P2" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>8</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S2" t="n">
+        <v>13</v>
+      </c>
+      <c r="T2" t="n">
+        <v>12</v>
+      </c>
+      <c r="U2" t="n">
+        <v>8</v>
+      </c>
+      <c r="V2" t="n">
+        <v>11</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="n">
+        <v>25.875</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>75.625</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>9475000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>79.25</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>76.33333333333333</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>10111111.11111111</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>24.23076923076923</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>181.9230769230769</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.538461538461539</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>73.07692307692308</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>8578846.153846154</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>77.53846153846153</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>23.81818181818182</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1.681818181818182</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>73.18181818181819</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>5522727.272727272</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>78.81818181818181</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>189</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>72</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>78</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>31</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>173.5</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>159</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>33000000</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>2NocJFqd</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45522.5</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leonard t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>18752</v>
+      </c>
+      <c r="F3" t="n">
+        <v>14811</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="M3" t="n">
+        <v>44</v>
+      </c>
+      <c r="N3" t="n">
+        <v>56</v>
+      </c>
+      <c r="O3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
+        <v>5</v>
+      </c>
+      <c r="S3" t="n">
+        <v>6</v>
+      </c>
+      <c r="T3" t="n">
+        <v>10</v>
+      </c>
+      <c r="U3" t="n">
+        <v>10</v>
+      </c>
+      <c r="V3" t="n">
+        <v>11</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>68</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1587500</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>27.63636363636364</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>179.8181818181818</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>77</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>12381818.18181818</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>78.72727272727273</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>66.45</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1278750</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>71.84999999999999</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>23.90909090909091</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>179.9545454545455</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>72.90909090909091</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>6081818.181818182</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>78.13636363636364</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>179.25</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>266</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>5725000</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>290</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>25</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>179</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>298</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>28600000</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>M5VGwpVA</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45522.5</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vernice m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>20484</v>
+      </c>
+      <c r="F4" t="n">
+        <v>15706</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M4" t="n">
+        <v>43</v>
+      </c>
+      <c r="N4" t="n">
+        <v>57</v>
+      </c>
+      <c r="O4" t="n">
+        <v>7</v>
+      </c>
+      <c r="P4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="n">
+        <v>18</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
+      </c>
+      <c r="V4" t="n">
+        <v>9</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>6330000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>21.22222222222222</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>185.4444444444445</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>70.77777777777777</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>4402777.777777778</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>79.88888888888889</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>23.375</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>182</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3787500</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>76.625</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>21.875</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>178.75</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>67.1875</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>2412500</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>76</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>31</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>186</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>147</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>147</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>19</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>176</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>70</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>6ehlLyFq</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45522.5</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F5" t="n">
+        <v>25491</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M5" t="n">
+        <v>53</v>
+      </c>
+      <c r="N5" t="n">
+        <v>47</v>
+      </c>
+      <c r="O5" t="n">
+        <v>7</v>
+      </c>
+      <c r="P5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="n">
+        <v>8</v>
+      </c>
+      <c r="U5" t="n">
+        <v>8</v>
+      </c>
+      <c r="V5" t="n">
+        <v>3</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>181.1</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>182</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>5310000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>178.375</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>69.8125</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2631250</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>75.4375</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>25.76470588235294</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>182.8235294117647</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.411764705882353</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>71.76470588235294</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>3450000</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>74.58823529411765</v>
+      </c>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
+      <c r="BO5" t="inlineStr"/>
+      <c r="BP5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>ripawyyS</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45522.41666666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lissorgue r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>17924</v>
+      </c>
+      <c r="F6" t="n">
+        <v>16354</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M6" t="n">
+        <v>46</v>
+      </c>
+      <c r="N6" t="n">
+        <v>54</v>
+      </c>
+      <c r="O6" t="n">
+        <v>16</v>
+      </c>
+      <c r="P6" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>7</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" t="n">
+        <v>11</v>
+      </c>
+      <c r="T6" t="n">
+        <v>17</v>
+      </c>
+      <c r="U6" t="n">
+        <v>7</v>
+      </c>
+      <c r="V6" t="n">
+        <v>8</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>68.22222222222223</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1708333.333333333</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>184</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>9280000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>25.08333333333333</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>180.8333333333333</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>65.08333333333333</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1062500</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>69.25</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>5470000</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>192</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>69</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>74</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>177</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>307</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>53500000</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>fHYrsJy3</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45521.66666666666</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">turpin c 
+  fra </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F7" t="n">
+        <v>14250</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M7" t="n">
+        <v>61</v>
+      </c>
+      <c r="N7" t="n">
+        <v>39</v>
+      </c>
+      <c r="O7" t="n">
+        <v>13</v>
+      </c>
+      <c r="P7" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>4</v>
+      </c>
+      <c r="S7" t="n">
+        <v>13</v>
+      </c>
+      <c r="T7" t="n">
+        <v>14</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
+      </c>
+      <c r="V7" t="n">
+        <v>17</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>182.9</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>12650000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="n">
+        <v>20.86666666666667</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>183.6666666666667</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>72.73333333333333</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>9083333.333333334</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>82</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>22.72727272727273</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>182.1818181818182</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>65.81818181818181</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1463636.363636364</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>74.27272727272727</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>190</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>78</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>20500000</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>84</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>24</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>176</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>71</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>jqSiuc6F</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45521.58333333334</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wattellier e 
+  fra </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F8" t="n">
+        <v>14755</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M8" t="n">
+        <v>29</v>
+      </c>
+      <c r="N8" t="n">
+        <v>71</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6</v>
+      </c>
+      <c r="S8" t="n">
+        <v>6</v>
+      </c>
+      <c r="T8" t="n">
+        <v>13</v>
+      </c>
+      <c r="U8" t="n">
+        <v>12</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="n">
+        <v>24.875</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>180.25</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>75.875</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>10312500</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>181.6666666666667</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>68</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3266666.666666667</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>178.6111111111111</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>72.38888888888889</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>8463888.888888888</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>79.88888888888889</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>182.6666666666667</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>221</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>29200000</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>238</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>180.6</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>386</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>55800000</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>0js8u60b</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45521.5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F9" t="n">
+        <v>14962</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="M9" t="n">
+        <v>51</v>
+      </c>
+      <c r="N9" t="n">
+        <v>49</v>
+      </c>
+      <c r="O9" t="n">
+        <v>7</v>
+      </c>
+      <c r="P9" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="n">
+        <v>8</v>
+      </c>
+      <c r="U9" t="n">
+        <v>10</v>
+      </c>
+      <c r="V9" t="n">
+        <v>12</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
+      <c r="AE9" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>5460000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="n">
+        <v>22.78571428571428</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>178.1428571428571</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.285714285714286</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>67.71428571428571</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>4185714.285714286</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>74.42857142857143</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>24.36363636363636</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>180.0909090909091</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>75.18181818181819</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>10490909.09090909</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>79.18181818181819</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>172</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>74</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>77</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>183.75</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>296</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>dvUee9dD</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45521.39583333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gaillouste p 
+  fra </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade michel d ornano
+  caen </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>20300</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>GjLn2QoH</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0OEHEprs</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>36</v>
+      </c>
+      <c r="N10" t="n">
+        <v>64</v>
+      </c>
+      <c r="O10" t="n">
+        <v>9</v>
+      </c>
+      <c r="P10" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>5</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="n">
+        <v>13</v>
+      </c>
+      <c r="U10" t="n">
+        <v>10</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Q9EVqFe4</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>zB2j3YvM</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="n">
+        <v>25.44444444444444</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>181</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>67.55555555555556</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1638888.888888889</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>74</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>177.8888888888889</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>67.22222222222223</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1697222.222222222</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>71.55555555555556</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>22.07142857142857</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>179.7857142857143</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>64.21428571428571</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1037500</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>74.07142857142857</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>181.8</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1083750</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>69.15000000000001</v>
+      </c>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+      <c r="BO10" t="inlineStr"/>
+      <c r="BP10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>SOLVXEbk</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45520.65625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delajod w 
+  fra </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>25178</v>
+      </c>
+      <c r="F11" t="n">
+        <v>23167</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="M11" t="n">
+        <v>26</v>
+      </c>
+      <c r="N11" t="n">
+        <v>74</v>
+      </c>
+      <c r="O11" t="n">
+        <v>5</v>
+      </c>
+      <c r="P11" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>9</v>
+      </c>
+      <c r="S11" t="n">
+        <v>9</v>
+      </c>
+      <c r="T11" t="n">
+        <v>9</v>
+      </c>
+      <c r="U11" t="n">
+        <v>8</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="n">
+        <v>25.18181818181818</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>185.2727272727273</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>71.36363636363636</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>2945454.545454545</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="n">
+        <v>22.5625</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>180.0625</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1389062.5</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>23.69230769230769</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>183.5384615384615</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>2.307692307692307</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>80.38461538461539</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>42061538.46153846</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>84.76923076923077</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>188</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>64</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>74</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>27</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>165</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>68000000</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>EeC5phre</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">valnet a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">michel moretti stadium
+  ajaccio </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>8470</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2aeoANM8</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0pOdQOCg</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>99</v>
+      </c>
+      <c r="O12" t="n">
+        <v>8</v>
+      </c>
+      <c r="P12" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>8tmnzqxe</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>OQuqpG7i</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>178.2</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>872500</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1090625</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>26.38888888888889</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>180</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>65.05555555555556</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>751388.8888888889</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>69.61111111111111</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>830000</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>71</v>
+      </c>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr"/>
+      <c r="BO12" t="inlineStr"/>
+      <c r="BP12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>2Hh06Z4E</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rosier e 
+  fra </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la licorne
+  amiens </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>12097</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4918</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>lKkBAsxF</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2kM6ufaS</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>51</v>
+      </c>
+      <c r="N13" t="n">
+        <v>49</v>
+      </c>
+      <c r="O13" t="n">
+        <v>17</v>
+      </c>
+      <c r="P13" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>6</v>
+      </c>
+      <c r="R13" t="n">
+        <v>3</v>
+      </c>
+      <c r="S13" t="n">
+        <v>11</v>
+      </c>
+      <c r="T13" t="n">
+        <v>13</v>
+      </c>
+      <c r="U13" t="n">
+        <v>11</v>
+      </c>
+      <c r="V13" t="n">
+        <v>13</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>dS1CBple</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>SzfSpYcf</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1205000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>63.0625</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>751562.5</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>71.4375</v>
+      </c>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr"/>
+      <c r="BO13" t="inlineStr"/>
+      <c r="BP13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>6V8cnEDr</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">landry r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade gabriel montpied
+  clermont ferrand </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>10800</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5582</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>IRuMRua1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>56</v>
+      </c>
+      <c r="N14" t="n">
+        <v>44</v>
+      </c>
+      <c r="O14" t="n">
+        <v>13</v>
+      </c>
+      <c r="P14" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>14</v>
+      </c>
+      <c r="T14" t="n">
+        <v>12</v>
+      </c>
+      <c r="U14" t="n">
+        <v>14</v>
+      </c>
+      <c r="V14" t="n">
+        <v>16</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>4G9MhScS</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>fm0Qb28B</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="n">
+        <v>23.88888888888889</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>180</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>66.44444444444444</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1436111.111111111</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>73.77777777777777</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>183.7</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>962500</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>20.85714285714286</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>176</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>65.28571428571429</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1614285.714285714</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>75.28571428571429</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>182.7272727272727</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>64.54545454545455</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>709090.9090909091</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>70.27272727272727</v>
+      </c>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="inlineStr"/>
+      <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="inlineStr"/>
+      <c r="BM14" t="inlineStr"/>
+      <c r="BN14" t="inlineStr"/>
+      <c r="BO14" t="inlineStr"/>
+      <c r="BP14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>zB0ErWC7</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kubler g 
+  fra </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade marcel tribut
+  dunkerque </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4933</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>tAAobNse</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>25dB6Eto</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>48</v>
+      </c>
+      <c r="N15" t="n">
+        <v>52</v>
+      </c>
+      <c r="O15" t="n">
+        <v>12</v>
+      </c>
+      <c r="P15" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>6</v>
+      </c>
+      <c r="R15" t="n">
+        <v>4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="n">
+        <v>15</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>SIiBpBrs</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="n">
+        <v>26.44444444444444</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>182.5555555555555</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>64.55555555555556</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>833333.3333333334</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>67.77777777777777</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>22.83333333333333</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>176.8333333333333</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>63.25</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>804166.6666666666</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>21.66666666666667</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>61.83333333333334</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>708333.3333333334</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>69.33333333333333</v>
+      </c>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="inlineStr"/>
+      <c r="BJ15" t="inlineStr"/>
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="inlineStr"/>
+      <c r="BM15" t="inlineStr"/>
+      <c r="BN15" t="inlineStr"/>
+      <c r="BO15" t="inlineStr"/>
+      <c r="BP15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>dGo94DZQ</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kherradji a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade des alpes
+  grenoble </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>20068</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>E1wDrLsJ</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>6</v>
+      </c>
+      <c r="P16" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Ys1Pb7ws</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="n">
+        <v>25.72727272727273</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>182.8181818181818</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>67.63636363636364</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1495454.545454545</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>71.36363636363636</v>
+      </c>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="n">
+        <v>29.66666666666667</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>185.1666666666667</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1937500</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>24.8125</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>64.3125</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>958750</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>71.3125</v>
+      </c>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="inlineStr"/>
+      <c r="BI16" t="inlineStr"/>
+      <c r="BJ16" t="inlineStr"/>
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="inlineStr"/>
+      <c r="BM16" t="inlineStr"/>
+      <c r="BN16" t="inlineStr"/>
+      <c r="BO16" t="inlineStr"/>
+      <c r="BP16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>b15XX7Nt</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de roudourou
+  guingamp </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>19060</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>QDfKl36E</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fsfAHubD</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
+        <v>49</v>
+      </c>
+      <c r="N17" t="n">
+        <v>51</v>
+      </c>
+      <c r="O17" t="n">
+        <v>16</v>
+      </c>
+      <c r="P17" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>9</v>
+      </c>
+      <c r="T17" t="n">
+        <v>12</v>
+      </c>
+      <c r="U17" t="n">
+        <v>9</v>
+      </c>
+      <c r="V17" t="n">
+        <v>14</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>QNSJnsB5</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>4vG8dmrf</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>179.9</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1025000</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>27.625</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>177.625</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>67.375</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1275000</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>70.375</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>179.7</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>950000</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>20.41666666666667</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>179.6666666666667</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>912500</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>70.91666666666667</v>
+      </c>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
+      <c r="BI17" t="inlineStr"/>
+      <c r="BJ17" t="inlineStr"/>
+      <c r="BK17" t="inlineStr"/>
+      <c r="BL17" t="inlineStr"/>
+      <c r="BM17" t="inlineStr"/>
+      <c r="BN17" t="inlineStr"/>
+      <c r="BO17" t="inlineStr"/>
+      <c r="BP17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
+++ b/data/france/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:BP1"/>
+  <dimension ref="A1:BP19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -764,6 +768,3506 @@
           <t>sum_pot_player_miss_away</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>lEQmcVR0</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>45523.65625</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">petit a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade saint symphorien
+  metz </t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>28786</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>AZwK8L6R</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>67</v>
+      </c>
+      <c r="N2" t="n">
+        <v>33</v>
+      </c>
+      <c r="O2" t="n">
+        <v>18</v>
+      </c>
+      <c r="P2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>3</v>
+      </c>
+      <c r="S2" t="n">
+        <v>13</v>
+      </c>
+      <c r="T2" t="n">
+        <v>15</v>
+      </c>
+      <c r="U2" t="n">
+        <v>12</v>
+      </c>
+      <c r="V2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>h89kUbu5</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>fo8nHfg4</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="n">
+        <v>24.90909090909091</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>177.8181818181818</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>68.90909090909091</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1677272.727272727</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>75.27272727272727</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>179.625</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>63.625</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>723125</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>68.375</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>181.0909090909091</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>67.81818181818181</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1718181.818181818</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>180</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>679166.6666666666</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>68.16666666666667</v>
+      </c>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>OA5YizjL</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45523.65625</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thual o 
+  fra </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>67394</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ADl76OZP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>jgNAYRGi</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>33</v>
+      </c>
+      <c r="N3" t="n">
+        <v>67</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P3" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S3" t="n">
+        <v>8</v>
+      </c>
+      <c r="T3" t="n">
+        <v>13</v>
+      </c>
+      <c r="U3" t="n">
+        <v>16</v>
+      </c>
+      <c r="V3" t="n">
+        <v>6</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>EwpPg8iH</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Cp0gM1r4</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="n">
+        <v>24.44444444444444</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>178.1111111111111</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>71.77777777777777</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>4622222.222222222</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>77.11111111111111</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="n">
+        <v>21.73333333333333</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>177.4</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>69.06666666666666</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>2781666.666666667</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>77.53333333333333</v>
+      </c>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
+      <c r="BO3" t="inlineStr"/>
+      <c r="BP3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>zkPwWhT1</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45522.65625</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millot b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>29778</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="M4" t="n">
+        <v>48</v>
+      </c>
+      <c r="N4" t="n">
+        <v>52</v>
+      </c>
+      <c r="O4" t="n">
+        <v>22</v>
+      </c>
+      <c r="P4" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>8</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>13</v>
+      </c>
+      <c r="T4" t="n">
+        <v>12</v>
+      </c>
+      <c r="U4" t="n">
+        <v>8</v>
+      </c>
+      <c r="V4" t="n">
+        <v>11</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="n">
+        <v>25.875</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>75.625</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>9475000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>79.25</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>76.33333333333333</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>10111111.11111111</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>80</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>24.23076923076923</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>181.9230769230769</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.538461538461539</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>73.07692307692308</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>8578846.153846154</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>77.53846153846153</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>23.81818181818182</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.681818181818182</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>73.18181818181819</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>5522727.272727272</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>78.81818181818181</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>189</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>72</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>78</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>31</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>173.5</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>159</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>33000000</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>6ehlLyFq</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45522.5</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F5" t="n">
+        <v>25491</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M5" t="n">
+        <v>53</v>
+      </c>
+      <c r="N5" t="n">
+        <v>47</v>
+      </c>
+      <c r="O5" t="n">
+        <v>7</v>
+      </c>
+      <c r="P5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="n">
+        <v>8</v>
+      </c>
+      <c r="U5" t="n">
+        <v>8</v>
+      </c>
+      <c r="V5" t="n">
+        <v>3</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>181.1</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>182</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>5310000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>178.375</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>69.8125</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2631250</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>75.4375</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>25.76470588235294</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>182.8235294117647</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.411764705882353</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>71.76470588235294</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>3450000</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>74.58823529411765</v>
+      </c>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
+      <c r="BO5" t="inlineStr"/>
+      <c r="BP5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2NocJFqd</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45522.5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leonard t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>18752</v>
+      </c>
+      <c r="F6" t="n">
+        <v>14811</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="M6" t="n">
+        <v>44</v>
+      </c>
+      <c r="N6" t="n">
+        <v>56</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4</v>
+      </c>
+      <c r="P6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>5</v>
+      </c>
+      <c r="S6" t="n">
+        <v>6</v>
+      </c>
+      <c r="T6" t="n">
+        <v>10</v>
+      </c>
+      <c r="U6" t="n">
+        <v>10</v>
+      </c>
+      <c r="V6" t="n">
+        <v>11</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>68</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1587500</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>27.63636363636364</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>179.8181818181818</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>77</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>12381818.18181818</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>78.72727272727273</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>66.45</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1278750</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>71.84999999999999</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>23.90909090909091</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>179.9545454545455</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>72.90909090909091</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>6081818.181818182</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>78.13636363636364</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>179.25</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>266</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>5725000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>290</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>25</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>179</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>298</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>28600000</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>M5VGwpVA</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45522.5</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vernice m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>20484</v>
+      </c>
+      <c r="F7" t="n">
+        <v>15706</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M7" t="n">
+        <v>43</v>
+      </c>
+      <c r="N7" t="n">
+        <v>57</v>
+      </c>
+      <c r="O7" t="n">
+        <v>7</v>
+      </c>
+      <c r="P7" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>4</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="n">
+        <v>18</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" t="n">
+        <v>9</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>6330000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>21.22222222222222</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>185.4444444444445</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>70.77777777777777</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>4402777.777777778</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>79.88888888888889</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>23.375</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>182</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3787500</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>76.625</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>21.875</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>178.75</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>67.1875</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>2412500</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>76</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>31</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>186</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>147</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>147</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>19</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>176</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>70</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>ripawyyS</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45522.41666666666</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lissorgue r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>17924</v>
+      </c>
+      <c r="F8" t="n">
+        <v>16354</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M8" t="n">
+        <v>46</v>
+      </c>
+      <c r="N8" t="n">
+        <v>54</v>
+      </c>
+      <c r="O8" t="n">
+        <v>16</v>
+      </c>
+      <c r="P8" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>7</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>11</v>
+      </c>
+      <c r="T8" t="n">
+        <v>17</v>
+      </c>
+      <c r="U8" t="n">
+        <v>7</v>
+      </c>
+      <c r="V8" t="n">
+        <v>8</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="AE8" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>68.22222222222223</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1708333.333333333</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>184</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>9280000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>25.08333333333333</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>180.8333333333333</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>65.08333333333333</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1062500</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>69.25</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>5470000</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>192</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>69</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>74</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>177</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>307</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>53500000</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>fHYrsJy3</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45521.66666666666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">turpin c 
+  fra </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F9" t="n">
+        <v>14250</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M9" t="n">
+        <v>61</v>
+      </c>
+      <c r="N9" t="n">
+        <v>39</v>
+      </c>
+      <c r="O9" t="n">
+        <v>13</v>
+      </c>
+      <c r="P9" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>6</v>
+      </c>
+      <c r="R9" t="n">
+        <v>4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>13</v>
+      </c>
+      <c r="T9" t="n">
+        <v>14</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
+      </c>
+      <c r="V9" t="n">
+        <v>17</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>182.9</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>12650000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="n">
+        <v>20.86666666666667</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>183.6666666666667</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>72.73333333333333</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>9083333.333333334</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>82</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>22.72727272727273</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>182.1818181818182</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>65.81818181818181</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1463636.363636364</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>74.27272727272727</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>190</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>78</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>20500000</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>84</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>24</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>176</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>71</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>jqSiuc6F</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45521.58333333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wattellier e 
+  fra </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F10" t="n">
+        <v>14755</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M10" t="n">
+        <v>29</v>
+      </c>
+      <c r="N10" t="n">
+        <v>71</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2</v>
+      </c>
+      <c r="P10" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6</v>
+      </c>
+      <c r="S10" t="n">
+        <v>6</v>
+      </c>
+      <c r="T10" t="n">
+        <v>13</v>
+      </c>
+      <c r="U10" t="n">
+        <v>12</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="n">
+        <v>24.875</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>180.25</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>75.875</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>10312500</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>181.6666666666667</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>68</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3266666.666666667</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>178.6111111111111</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>72.38888888888889</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>8463888.888888888</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>79.88888888888889</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>182.6666666666667</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>221</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>29200000</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>238</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>180.6</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>386</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>55800000</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>0js8u60b</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45521.5</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F11" t="n">
+        <v>14962</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="M11" t="n">
+        <v>51</v>
+      </c>
+      <c r="N11" t="n">
+        <v>49</v>
+      </c>
+      <c r="O11" t="n">
+        <v>7</v>
+      </c>
+      <c r="P11" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="n">
+        <v>8</v>
+      </c>
+      <c r="U11" t="n">
+        <v>10</v>
+      </c>
+      <c r="V11" t="n">
+        <v>12</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
+      <c r="AE11" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>5460000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="n">
+        <v>22.78571428571428</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>178.1428571428571</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.285714285714286</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>67.71428571428571</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>4185714.285714286</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>74.42857142857143</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>24.36363636363636</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>180.0909090909091</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>75.18181818181819</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>10490909.09090909</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>79.18181818181819</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>172</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>74</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>77</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>183.75</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>296</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>dvUee9dD</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45521.39583333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gaillouste p 
+  fra </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade michel d ornano
+  caen </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>20300</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>GjLn2QoH</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0OEHEprs</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>36</v>
+      </c>
+      <c r="N12" t="n">
+        <v>64</v>
+      </c>
+      <c r="O12" t="n">
+        <v>9</v>
+      </c>
+      <c r="P12" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="n">
+        <v>13</v>
+      </c>
+      <c r="U12" t="n">
+        <v>10</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Q9EVqFe4</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>zB2j3YvM</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="n">
+        <v>25.44444444444444</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>181</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>67.55555555555556</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1638888.888888889</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>74</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>177.8888888888889</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>67.22222222222223</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1697222.222222222</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>71.55555555555556</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>22.07142857142857</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>179.7857142857143</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>64.21428571428571</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1037500</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>74.07142857142857</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>181.8</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1083750</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>69.15000000000001</v>
+      </c>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr"/>
+      <c r="BO12" t="inlineStr"/>
+      <c r="BP12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SOLVXEbk</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45520.65625</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delajod w 
+  fra </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>25178</v>
+      </c>
+      <c r="F13" t="n">
+        <v>23167</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="M13" t="n">
+        <v>26</v>
+      </c>
+      <c r="N13" t="n">
+        <v>74</v>
+      </c>
+      <c r="O13" t="n">
+        <v>5</v>
+      </c>
+      <c r="P13" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>9</v>
+      </c>
+      <c r="S13" t="n">
+        <v>9</v>
+      </c>
+      <c r="T13" t="n">
+        <v>9</v>
+      </c>
+      <c r="U13" t="n">
+        <v>8</v>
+      </c>
+      <c r="V13" t="n">
+        <v>4</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="n">
+        <v>25.18181818181818</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>185.2727272727273</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>71.36363636363636</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>2945454.545454545</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="n">
+        <v>22.5625</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>180.0625</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1389062.5</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>23.69230769230769</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>183.5384615384615</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>2.307692307692307</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>80.38461538461539</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>42061538.46153846</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>84.76923076923077</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>188</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>64</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>74</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>27</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>165</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>68000000</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>EeC5phre</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">valnet a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">michel moretti stadium
+  ajaccio </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>8470</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2aeoANM8</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0pOdQOCg</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>99</v>
+      </c>
+      <c r="O14" t="n">
+        <v>8</v>
+      </c>
+      <c r="P14" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>8tmnzqxe</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>OQuqpG7i</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>178.2</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>872500</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1090625</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>26.38888888888889</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>180</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>65.05555555555556</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>751388.8888888889</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>69.61111111111111</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>830000</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>71</v>
+      </c>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="inlineStr"/>
+      <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="inlineStr"/>
+      <c r="BM14" t="inlineStr"/>
+      <c r="BN14" t="inlineStr"/>
+      <c r="BO14" t="inlineStr"/>
+      <c r="BP14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>2Hh06Z4E</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rosier e 
+  fra </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la licorne
+  amiens </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>12097</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4918</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>lKkBAsxF</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2kM6ufaS</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>51</v>
+      </c>
+      <c r="N15" t="n">
+        <v>49</v>
+      </c>
+      <c r="O15" t="n">
+        <v>17</v>
+      </c>
+      <c r="P15" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>6</v>
+      </c>
+      <c r="R15" t="n">
+        <v>3</v>
+      </c>
+      <c r="S15" t="n">
+        <v>11</v>
+      </c>
+      <c r="T15" t="n">
+        <v>13</v>
+      </c>
+      <c r="U15" t="n">
+        <v>11</v>
+      </c>
+      <c r="V15" t="n">
+        <v>13</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>dS1CBple</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>SzfSpYcf</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1205000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>63.0625</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>751562.5</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>71.4375</v>
+      </c>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="inlineStr"/>
+      <c r="BJ15" t="inlineStr"/>
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="inlineStr"/>
+      <c r="BM15" t="inlineStr"/>
+      <c r="BN15" t="inlineStr"/>
+      <c r="BO15" t="inlineStr"/>
+      <c r="BP15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>6V8cnEDr</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">landry r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade gabriel montpied
+  clermont ferrand </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>10800</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5582</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>IRuMRua1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>56</v>
+      </c>
+      <c r="N16" t="n">
+        <v>44</v>
+      </c>
+      <c r="O16" t="n">
+        <v>13</v>
+      </c>
+      <c r="P16" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>14</v>
+      </c>
+      <c r="T16" t="n">
+        <v>12</v>
+      </c>
+      <c r="U16" t="n">
+        <v>14</v>
+      </c>
+      <c r="V16" t="n">
+        <v>16</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>4G9MhScS</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>fm0Qb28B</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="n">
+        <v>23.88888888888889</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>180</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>66.44444444444444</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1436111.111111111</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>73.77777777777777</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>183.7</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>962500</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>20.85714285714286</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>176</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>65.28571428571429</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1614285.714285714</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>75.28571428571429</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>182.7272727272727</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>64.54545454545455</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>709090.9090909091</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>70.27272727272727</v>
+      </c>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="inlineStr"/>
+      <c r="BI16" t="inlineStr"/>
+      <c r="BJ16" t="inlineStr"/>
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="inlineStr"/>
+      <c r="BM16" t="inlineStr"/>
+      <c r="BN16" t="inlineStr"/>
+      <c r="BO16" t="inlineStr"/>
+      <c r="BP16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>zB0ErWC7</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kubler g 
+  fra </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade marcel tribut
+  dunkerque </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4933</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>tAAobNse</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>25dB6Eto</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
+        <v>48</v>
+      </c>
+      <c r="N17" t="n">
+        <v>52</v>
+      </c>
+      <c r="O17" t="n">
+        <v>12</v>
+      </c>
+      <c r="P17" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="n">
+        <v>15</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>SIiBpBrs</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="n">
+        <v>26.44444444444444</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>182.5555555555555</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>64.55555555555556</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>833333.3333333334</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>67.77777777777777</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>22.83333333333333</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>176.8333333333333</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>63.25</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>804166.6666666666</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>21.66666666666667</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>61.83333333333334</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>708333.3333333334</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>69.33333333333333</v>
+      </c>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
+      <c r="BI17" t="inlineStr"/>
+      <c r="BJ17" t="inlineStr"/>
+      <c r="BK17" t="inlineStr"/>
+      <c r="BL17" t="inlineStr"/>
+      <c r="BM17" t="inlineStr"/>
+      <c r="BN17" t="inlineStr"/>
+      <c r="BO17" t="inlineStr"/>
+      <c r="BP17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>dGo94DZQ</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kherradji a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade des alpes
+  grenoble </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>20068</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>E1wDrLsJ</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>6</v>
+      </c>
+      <c r="P18" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Ys1Pb7ws</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="n">
+        <v>25.72727272727273</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>182.8181818181818</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>67.63636363636364</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1495454.545454545</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>71.36363636363636</v>
+      </c>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="n">
+        <v>29.66666666666667</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>185.1666666666667</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1937500</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>24.8125</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>64.3125</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>958750</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>71.3125</v>
+      </c>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="inlineStr"/>
+      <c r="BI18" t="inlineStr"/>
+      <c r="BJ18" t="inlineStr"/>
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="inlineStr"/>
+      <c r="BM18" t="inlineStr"/>
+      <c r="BN18" t="inlineStr"/>
+      <c r="BO18" t="inlineStr"/>
+      <c r="BP18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>b15XX7Nt</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de roudourou
+  guingamp </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>19060</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>QDfKl36E</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fsfAHubD</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>49</v>
+      </c>
+      <c r="N19" t="n">
+        <v>51</v>
+      </c>
+      <c r="O19" t="n">
+        <v>16</v>
+      </c>
+      <c r="P19" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>5</v>
+      </c>
+      <c r="R19" t="n">
+        <v>3</v>
+      </c>
+      <c r="S19" t="n">
+        <v>9</v>
+      </c>
+      <c r="T19" t="n">
+        <v>12</v>
+      </c>
+      <c r="U19" t="n">
+        <v>9</v>
+      </c>
+      <c r="V19" t="n">
+        <v>14</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>QNSJnsB5</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>4vG8dmrf</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>179.9</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1025000</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>27.625</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>177.625</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>67.375</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1275000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>70.375</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>179.7</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>950000</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>20.41666666666667</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>179.6666666666667</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>912500</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>70.91666666666667</v>
+      </c>
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="inlineStr"/>
+      <c r="BI19" t="inlineStr"/>
+      <c r="BJ19" t="inlineStr"/>
+      <c r="BK19" t="inlineStr"/>
+      <c r="BL19" t="inlineStr"/>
+      <c r="BM19" t="inlineStr"/>
+      <c r="BN19" t="inlineStr"/>
+      <c r="BO19" t="inlineStr"/>
+      <c r="BP19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
+++ b/data/france/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP19"/>
+  <dimension ref="A1:BP30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,46 +772,50 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>lEQmcVR0</t>
+          <t>CKcVGr7E</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45523.65625</v>
+        <v>45528.58333333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">petit a 
+          <t xml:space="preserve">kherradji a 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade saint symphorien
-  metz </t>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>28786</v>
+        <v>50186</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4v0yqlWc</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>AZwK8L6R</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.6</v>
+      </c>
       <c r="M2" t="n">
         <v>67</v>
       </c>
@@ -819,44 +823,40 @@
         <v>33</v>
       </c>
       <c r="O2" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="P2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T2" t="n">
-        <v>15</v>
-      </c>
-      <c r="U2" t="n">
-        <v>12</v>
-      </c>
-      <c r="V2" t="n">
-        <v>6</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
-          <t>h89kUbu5</t>
+          <t>nVS1TlC4</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>fo8nHfg4</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
       <c r="Y2" t="n">
         <v>55</v>
       </c>
       <c r="Z2" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -866,185 +866,215 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>24.90909090909091</v>
+        <v>22.625</v>
       </c>
       <c r="AF2" t="n">
-        <v>177.8181818181818</v>
+        <v>181.75</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.090909090909091</v>
+        <v>1.375</v>
       </c>
       <c r="AH2" t="n">
-        <v>68.90909090909091</v>
+        <v>74.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>1677272.727272727</v>
+        <v>11625000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>75.27272727272727</v>
+        <v>81.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>25.375</v>
+        <v>25.1</v>
       </c>
       <c r="AL2" t="n">
-        <v>179.625</v>
+        <v>185.4</v>
       </c>
       <c r="AM2" t="n">
         <v>1</v>
       </c>
       <c r="AN2" t="n">
-        <v>63.625</v>
+        <v>67.3</v>
       </c>
       <c r="AO2" t="n">
-        <v>723125</v>
+        <v>1507500</v>
       </c>
       <c r="AP2" t="n">
-        <v>68.375</v>
+        <v>73</v>
       </c>
       <c r="AQ2" t="n">
-        <v>24</v>
+        <v>25.07142857142857</v>
       </c>
       <c r="AR2" t="n">
-        <v>181.0909090909091</v>
+        <v>179.3571428571429</v>
       </c>
       <c r="AS2" t="n">
-        <v>1</v>
+        <v>1.357142857142857</v>
       </c>
       <c r="AT2" t="n">
-        <v>67.81818181818181</v>
+        <v>73</v>
       </c>
       <c r="AU2" t="n">
-        <v>1718181.818181818</v>
+        <v>6525000</v>
       </c>
       <c r="AV2" t="n">
-        <v>75</v>
+        <v>78.64285714285714</v>
       </c>
       <c r="AW2" t="n">
-        <v>23.25</v>
+        <v>25</v>
       </c>
       <c r="AX2" t="n">
-        <v>180</v>
+        <v>181.1739130434783</v>
       </c>
       <c r="AY2" t="n">
         <v>1</v>
       </c>
       <c r="AZ2" t="n">
-        <v>61.5</v>
+        <v>66.34782608695652</v>
       </c>
       <c r="BA2" t="n">
-        <v>679166.6666666666</v>
+        <v>1292391.304347826</v>
       </c>
       <c r="BB2" t="n">
-        <v>68.16666666666667</v>
-      </c>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="inlineStr"/>
-      <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="inlineStr"/>
+        <v>71.95652173913044</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>178</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>461</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>66800000</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>471</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>23</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>176</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>131</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>2325000</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>144</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>OA5YizjL</t>
+          <t>pSpI7vU0</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45523.65625</v>
+        <v>45528.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">thual o 
+          <t xml:space="preserve">frappart s 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade velodrome
-  marseille </t>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>67394</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>59186</v>
+      </c>
+      <c r="F3" t="n">
+        <v>54392</v>
+      </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ADl76OZP</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>jgNAYRGi</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.82</v>
+      </c>
       <c r="M3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N3" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
+        <v>4</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="n">
         <v>7</v>
       </c>
-      <c r="S3" t="n">
-        <v>8</v>
-      </c>
-      <c r="T3" t="n">
-        <v>13</v>
-      </c>
-      <c r="U3" t="n">
-        <v>16</v>
-      </c>
-      <c r="V3" t="n">
-        <v>6</v>
-      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
-          <t>EwpPg8iH</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Cp0gM1r4</t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
       <c r="Y3" t="n">
         <v>55</v>
       </c>
       <c r="Z3" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -1055,56 +1085,80 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>179.7777777777778</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>75.66666666666667</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>10300000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>79.77777777777777</v>
+      </c>
       <c r="AK3" t="n">
-        <v>24.44444444444444</v>
+        <v>23.9</v>
       </c>
       <c r="AL3" t="n">
-        <v>178.1111111111111</v>
+        <v>183.4</v>
       </c>
       <c r="AM3" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AN3" t="n">
-        <v>71.77777777777777</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AO3" t="n">
-        <v>4622222.222222222</v>
+        <v>11600000</v>
       </c>
       <c r="AP3" t="n">
-        <v>77.11111111111111</v>
-      </c>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
+        <v>80.8</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>24.95652173913043</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>180.7391304347826</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.739130434782609</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>74.39130434782609</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7004347.826086956</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>79.47826086956522</v>
+      </c>
       <c r="AW3" t="n">
-        <v>21.73333333333333</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="AX3" t="n">
-        <v>177.4</v>
+        <v>183.1666666666667</v>
       </c>
       <c r="AY3" t="n">
-        <v>1</v>
+        <v>1.222222222222222</v>
       </c>
       <c r="AZ3" t="n">
-        <v>69.06666666666666</v>
+        <v>73.72222222222223</v>
       </c>
       <c r="BA3" t="n">
-        <v>2781666.666666667</v>
+        <v>11236111.11111111</v>
       </c>
       <c r="BB3" t="n">
-        <v>77.53333333333333</v>
+        <v>82</v>
       </c>
       <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="inlineStr"/>
@@ -1113,106 +1167,116 @@
       <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="inlineStr"/>
-      <c r="BN3" t="inlineStr"/>
-      <c r="BO3" t="inlineStr"/>
-      <c r="BP3" t="inlineStr"/>
+      <c r="BJ3" t="n">
+        <v>18</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>173</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>66</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>2yXIHV57</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45522.65625</v>
+        <v>45528.39583333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">millot b 
+          <t xml:space="preserve">benchabane f 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">roazhon park
-  rennes </t>
+          <t xml:space="preserve">stade du moustoir
+  lorient </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>29778</v>
+        <v>16787</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>jgNAYRGi</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.64</v>
-      </c>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
+        <v>52</v>
+      </c>
+      <c r="N4" t="n">
         <v>48</v>
       </c>
-      <c r="N4" t="n">
-        <v>52</v>
-      </c>
       <c r="O4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="P4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Q4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="U4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>pCcFFE7M</t>
+          <t>Cp0gM1r4</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>YHU1oFVQ</t>
+          <t>WrQARdPN</t>
         </is>
       </c>
       <c r="Y4" t="n">
         <v>55</v>
       </c>
       <c r="Z4" t="n">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1222,212 +1286,178 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>25.875</v>
+        <v>24.44444444444444</v>
       </c>
       <c r="AF4" t="n">
-        <v>180.5</v>
+        <v>178.1111111111111</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="AH4" t="n">
-        <v>75.625</v>
+        <v>71.77777777777777</v>
       </c>
       <c r="AI4" t="n">
-        <v>9475000</v>
+        <v>4622222.222222222</v>
       </c>
       <c r="AJ4" t="n">
-        <v>79.25</v>
+        <v>77.11111111111111</v>
       </c>
       <c r="AK4" t="n">
-        <v>25.66666666666667</v>
+        <v>26</v>
       </c>
       <c r="AL4" t="n">
-        <v>182.3333333333333</v>
+        <v>182.6363636363636</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.666666666666667</v>
+        <v>1</v>
       </c>
       <c r="AN4" t="n">
-        <v>76.33333333333333</v>
+        <v>66.72727272727273</v>
       </c>
       <c r="AO4" t="n">
-        <v>10111111.11111111</v>
+        <v>1343181.818181818</v>
       </c>
       <c r="AP4" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AQ4" t="n">
-        <v>24.23076923076923</v>
+        <v>20.92857142857143</v>
       </c>
       <c r="AR4" t="n">
-        <v>181.9230769230769</v>
+        <v>178.5714285714286</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.538461538461539</v>
+        <v>1</v>
       </c>
       <c r="AT4" t="n">
-        <v>73.07692307692308</v>
+        <v>68.28571428571429</v>
       </c>
       <c r="AU4" t="n">
-        <v>8578846.153846154</v>
+        <v>2466071.428571429</v>
       </c>
       <c r="AV4" t="n">
-        <v>77.53846153846153</v>
+        <v>78.42857142857143</v>
       </c>
       <c r="AW4" t="n">
-        <v>23.81818181818182</v>
+        <v>26.38461538461538</v>
       </c>
       <c r="AX4" t="n">
-        <v>179.5</v>
+        <v>184.3076923076923</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.681818181818182</v>
+        <v>1.153846153846154</v>
       </c>
       <c r="AZ4" t="n">
-        <v>73.18181818181819</v>
+        <v>66.38461538461539</v>
       </c>
       <c r="BA4" t="n">
-        <v>5522727.272727272</v>
+        <v>1365384.615384615</v>
       </c>
       <c r="BB4" t="n">
-        <v>78.81818181818181</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>189</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>72</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>78</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>31</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>173.5</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>159</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>33000000</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>159</v>
-      </c>
+        <v>71.69230769230769</v>
+      </c>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
+      <c r="BO4" t="inlineStr"/>
+      <c r="BP4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>ppvl45N8</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45522.5</v>
+        <v>45527.65625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stinat j 
+          <t xml:space="preserve">bollengier m 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
+          <t xml:space="preserve">parc des princes
+  paris </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>33150</v>
-      </c>
-      <c r="F5" t="n">
-        <v>25491</v>
-      </c>
+        <v>48229</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="L5" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="M5" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="N5" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="O5" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="P5" t="n">
         <v>6</v>
       </c>
       <c r="Q5" t="n">
+        <v>10</v>
+      </c>
+      <c r="R5" t="n">
         <v>3</v>
       </c>
-      <c r="R5" t="n">
-        <v>2</v>
-      </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="n">
-        <v>8</v>
-      </c>
-      <c r="U5" t="n">
-        <v>8</v>
-      </c>
-      <c r="V5" t="n">
-        <v>3</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
-          <t>UapruDaf</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>YTLwacK1</t>
+          <t>vVQcGxl1</t>
         </is>
       </c>
       <c r="Y5" t="n">
@@ -1445,123 +1475,137 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="AE5" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>181.1</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>5200000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>78.7</v>
-      </c>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="n">
-        <v>24.8</v>
+        <v>26.45454545454545</v>
       </c>
       <c r="AL5" t="n">
-        <v>182</v>
+        <v>180.2727272727273</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.4</v>
+        <v>1.454545454545455</v>
       </c>
       <c r="AN5" t="n">
-        <v>72.8</v>
+        <v>73.90909090909091</v>
       </c>
       <c r="AO5" t="n">
-        <v>5310000</v>
+        <v>5527272.727272728</v>
       </c>
       <c r="AP5" t="n">
-        <v>76.2</v>
+        <v>77.27272727272727</v>
       </c>
       <c r="AQ5" t="n">
-        <v>24</v>
+        <v>22.2</v>
       </c>
       <c r="AR5" t="n">
-        <v>178.375</v>
+        <v>184</v>
       </c>
       <c r="AS5" t="n">
-        <v>1</v>
+        <v>1.866666666666667</v>
       </c>
       <c r="AT5" t="n">
-        <v>69.8125</v>
+        <v>77.93333333333334</v>
       </c>
       <c r="AU5" t="n">
-        <v>2631250</v>
+        <v>27520000</v>
       </c>
       <c r="AV5" t="n">
-        <v>75.4375</v>
+        <v>84.33333333333333</v>
       </c>
       <c r="AW5" t="n">
-        <v>25.76470588235294</v>
+        <v>25.08333333333333</v>
       </c>
       <c r="AX5" t="n">
-        <v>182.8235294117647</v>
+        <v>181.75</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.411764705882353</v>
+        <v>1.25</v>
       </c>
       <c r="AZ5" t="n">
-        <v>71.76470588235294</v>
+        <v>71.33333333333333</v>
       </c>
       <c r="BA5" t="n">
-        <v>3450000</v>
+        <v>5383333.333333333</v>
       </c>
       <c r="BB5" t="n">
-        <v>74.58823529411765</v>
-      </c>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="inlineStr"/>
-      <c r="BM5" t="inlineStr"/>
-      <c r="BN5" t="inlineStr"/>
-      <c r="BO5" t="inlineStr"/>
-      <c r="BP5" t="inlineStr"/>
+        <v>76.33333333333333</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>27.71428571428572</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>183.7142857142857</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>2.571428571428572</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>563</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>162500000</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>568</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>30</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>196</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>74</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>4rrRVcF7</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45522.5</v>
+        <v>45527.625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">leonard t 
+          <t xml:space="preserve">chapapria r 
   fra </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
+          <t xml:space="preserve">stade de l aube
+  troyes </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>18752</v>
-      </c>
-      <c r="F6" t="n">
-        <v>14811</v>
-      </c>
+        <v>20420</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
         <v>0</v>
       </c>
@@ -1570,65 +1614,61 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>fsfAHubD</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.92</v>
-      </c>
+          <t>IRuMRua1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="N6" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="P6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
         <v>5</v>
       </c>
-      <c r="S6" t="n">
-        <v>6</v>
-      </c>
       <c r="T6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="U6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V6" t="n">
         <v>11</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>6FKPxxgf</t>
+          <t>4vG8dmrf</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>K6b7RoBp</t>
+          <t>4G9MhScS</t>
         </is>
       </c>
       <c r="Y6" t="n">
         <v>55</v>
       </c>
       <c r="Z6" t="n">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1637,220 +1677,182 @@
         <v>20242025</v>
       </c>
       <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="n">
-        <v>25.7</v>
+        <v>24.22222222222222</v>
       </c>
       <c r="AF6" t="n">
-        <v>184.5</v>
+        <v>177.7777777777778</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AH6" t="n">
-        <v>68</v>
+        <v>64.66666666666667</v>
       </c>
       <c r="AI6" t="n">
-        <v>1587500</v>
+        <v>1072222.222222222</v>
       </c>
       <c r="AJ6" t="n">
-        <v>72.8</v>
+        <v>70.66666666666667</v>
       </c>
       <c r="AK6" t="n">
-        <v>27.63636363636364</v>
+        <v>24.375</v>
       </c>
       <c r="AL6" t="n">
-        <v>179.8181818181818</v>
+        <v>180.625</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.454545454545455</v>
+        <v>1.125</v>
       </c>
       <c r="AN6" t="n">
-        <v>77</v>
+        <v>67.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>12381818.18181818</v>
+        <v>1553125</v>
       </c>
       <c r="AP6" t="n">
-        <v>78.72727272727273</v>
+        <v>74</v>
       </c>
       <c r="AQ6" t="n">
-        <v>25.7</v>
+        <v>27.05882352941176</v>
       </c>
       <c r="AR6" t="n">
-        <v>183.9</v>
+        <v>179.3529411764706</v>
       </c>
       <c r="AS6" t="n">
-        <v>1</v>
+        <v>1.176470588235294</v>
       </c>
       <c r="AT6" t="n">
-        <v>66.45</v>
+        <v>67.35294117647059</v>
       </c>
       <c r="AU6" t="n">
-        <v>1278750</v>
+        <v>1388235.294117647</v>
       </c>
       <c r="AV6" t="n">
-        <v>71.84999999999999</v>
+        <v>70.70588235294117</v>
       </c>
       <c r="AW6" t="n">
-        <v>23.90909090909091</v>
+        <v>23</v>
       </c>
       <c r="AX6" t="n">
-        <v>179.9545454545455</v>
+        <v>178.625</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.090909090909091</v>
+        <v>1</v>
       </c>
       <c r="AZ6" t="n">
-        <v>72.90909090909091</v>
+        <v>65.625</v>
       </c>
       <c r="BA6" t="n">
-        <v>6081818.181818182</v>
+        <v>1637500</v>
       </c>
       <c r="BB6" t="n">
-        <v>78.13636363636364</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>179.25</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>266</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>5725000</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>290</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>25</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>179</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>298</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>28600000</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>310</v>
-      </c>
+        <v>72.875</v>
+      </c>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>UsP4uZcE</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45522.5</v>
+        <v>45527.625</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">vernice m 
+          <t xml:space="preserve">landry r 
   fra </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la mosson
-  montpellier </t>
+          <t xml:space="preserve">stade paul lignon
+  rodez </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>20484</v>
-      </c>
-      <c r="F7" t="n">
-        <v>15706</v>
-      </c>
+        <v>5955</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>0pOdQOCg</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.23</v>
-      </c>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="N7" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="O7" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="P7" t="n">
         <v>11</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
         <v>4</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="T7" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="U7" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="V7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>vVQcGxl1</t>
+          <t>OQuqpG7i</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>4fMAHvLm</t>
+          <t>h89kUbu5</t>
         </is>
       </c>
       <c r="Y7" t="n">
         <v>55</v>
       </c>
       <c r="Z7" t="n">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1858,225 +1860,175 @@
       <c r="AB7" t="n">
         <v>20242025</v>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4v0yqlWc</t>
-        </is>
-      </c>
-      <c r="AE7" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>180.5</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>6330000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>78.2</v>
-      </c>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="n">
-        <v>21.22222222222222</v>
+        <v>26.81818181818182</v>
       </c>
       <c r="AL7" t="n">
-        <v>185.4444444444445</v>
+        <v>176.8181818181818</v>
       </c>
       <c r="AM7" t="n">
-        <v>1</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="AN7" t="n">
-        <v>70.77777777777777</v>
+        <v>70.54545454545455</v>
       </c>
       <c r="AO7" t="n">
-        <v>4402777.777777778</v>
+        <v>1861363.636363636</v>
       </c>
       <c r="AP7" t="n">
-        <v>79.88888888888889</v>
+        <v>73.90909090909091</v>
       </c>
       <c r="AQ7" t="n">
-        <v>23.375</v>
+        <v>20.9375</v>
       </c>
       <c r="AR7" t="n">
-        <v>182</v>
+        <v>182.75</v>
       </c>
       <c r="AS7" t="n">
         <v>1</v>
       </c>
       <c r="AT7" t="n">
-        <v>70.75</v>
+        <v>62.3125</v>
       </c>
       <c r="AU7" t="n">
-        <v>3787500</v>
+        <v>829687.5</v>
       </c>
       <c r="AV7" t="n">
-        <v>76.625</v>
+        <v>72.4375</v>
       </c>
       <c r="AW7" t="n">
-        <v>21.875</v>
+        <v>20.375</v>
       </c>
       <c r="AX7" t="n">
-        <v>178.75</v>
+        <v>181.25</v>
       </c>
       <c r="AY7" t="n">
         <v>1</v>
       </c>
       <c r="AZ7" t="n">
-        <v>67.1875</v>
+        <v>65.75</v>
       </c>
       <c r="BA7" t="n">
-        <v>2412500</v>
+        <v>1696875</v>
       </c>
       <c r="BB7" t="n">
-        <v>76</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>31</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>186</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>147</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>147</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>19</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>176</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>70</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>3800000</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>84</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
+      <c r="BM7" t="inlineStr"/>
+      <c r="BN7" t="inlineStr"/>
+      <c r="BO7" t="inlineStr"/>
+      <c r="BP7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>nsErYjjl</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45522.41666666666</v>
+        <v>45527.625</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">lissorgue r 
+          <t xml:space="preserve">leleu m 
   fra </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de l abbe deschamps
-  auxerre </t>
+          <t xml:space="preserve">nouste camp
+  pau </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>17924</v>
-      </c>
-      <c r="F8" t="n">
-        <v>16354</v>
-      </c>
+        <v>4031</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>GjLn2QoH</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>32</v>
+      </c>
+      <c r="N8" t="n">
+        <v>68</v>
+      </c>
+      <c r="O8" t="n">
+        <v>7</v>
+      </c>
+      <c r="P8" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q8" t="n">
         <v>2</v>
       </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="M8" t="n">
-        <v>46</v>
-      </c>
-      <c r="N8" t="n">
-        <v>54</v>
-      </c>
-      <c r="O8" t="n">
-        <v>16</v>
-      </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
+        <v>4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>12</v>
+      </c>
+      <c r="T8" t="n">
+        <v>20</v>
+      </c>
+      <c r="U8" t="n">
         <v>9</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>7</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>11</v>
-      </c>
-      <c r="T8" t="n">
-        <v>17</v>
-      </c>
-      <c r="U8" t="n">
-        <v>7</v>
       </c>
       <c r="V8" t="n">
         <v>8</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>OpNm82MB</t>
+          <t>fm0Qb28B</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>d0X3cO3I</t>
+          <t>Q9EVqFe4</t>
         </is>
       </c>
       <c r="Y8" t="n">
         <v>55</v>
       </c>
       <c r="Z8" t="n">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -2085,220 +2037,182 @@
         <v>20242025</v>
       </c>
       <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="n">
-        <v>25.66666666666667</v>
+        <v>23.33333333333333</v>
       </c>
       <c r="AF8" t="n">
-        <v>182.3333333333333</v>
+        <v>185.3333333333333</v>
       </c>
       <c r="AG8" t="n">
         <v>1</v>
       </c>
       <c r="AH8" t="n">
-        <v>68.22222222222223</v>
+        <v>64.88888888888889</v>
       </c>
       <c r="AI8" t="n">
-        <v>1708333.333333333</v>
+        <v>1066666.666666667</v>
       </c>
       <c r="AJ8" t="n">
-        <v>71.66666666666667</v>
+        <v>73</v>
       </c>
       <c r="AK8" t="n">
-        <v>23.8</v>
+        <v>26.375</v>
       </c>
       <c r="AL8" t="n">
-        <v>184</v>
+        <v>180.5</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AN8" t="n">
-        <v>73.7</v>
+        <v>68.25</v>
       </c>
       <c r="AO8" t="n">
-        <v>9280000</v>
+        <v>1643750</v>
       </c>
       <c r="AP8" t="n">
-        <v>78.90000000000001</v>
+        <v>73.25</v>
       </c>
       <c r="AQ8" t="n">
-        <v>25.08333333333333</v>
+        <v>26.84615384615385</v>
       </c>
       <c r="AR8" t="n">
-        <v>180.8333333333333</v>
+        <v>181.3076923076923</v>
       </c>
       <c r="AS8" t="n">
         <v>1</v>
       </c>
       <c r="AT8" t="n">
-        <v>65.08333333333333</v>
+        <v>65.46153846153847</v>
       </c>
       <c r="AU8" t="n">
-        <v>1062500</v>
+        <v>786538.4615384615</v>
       </c>
       <c r="AV8" t="n">
-        <v>69.25</v>
+        <v>70.92307692307692</v>
       </c>
       <c r="AW8" t="n">
-        <v>22.7</v>
+        <v>20.23076923076923</v>
       </c>
       <c r="AX8" t="n">
-        <v>179.5</v>
+        <v>181.4615384615385</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AZ8" t="n">
-        <v>72.7</v>
+        <v>62.53846153846154</v>
       </c>
       <c r="BA8" t="n">
-        <v>5470000</v>
+        <v>875000</v>
       </c>
       <c r="BB8" t="n">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>192</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>69</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>74</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>23.75</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>177</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>307</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>53500000</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>321</v>
-      </c>
+        <v>75.38461538461539</v>
+      </c>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
+      <c r="BM8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr"/>
+      <c r="BO8" t="inlineStr"/>
+      <c r="BP8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>WUmnhCsK</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45521.66666666666</v>
+        <v>45527.625</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">turpin c 
+          <t xml:space="preserve">taleb a 
   fra </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
+          <t xml:space="preserve">stade de la licorne
+  amiens </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>18523</v>
-      </c>
-      <c r="F9" t="n">
-        <v>14250</v>
-      </c>
+        <v>12097</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>0OEHEprs</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.6899999999999999</v>
-      </c>
+          <t>tAAobNse</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="N9" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="O9" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="P9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T9" t="n">
+        <v>17</v>
+      </c>
+      <c r="U9" t="n">
         <v>14</v>
       </c>
-      <c r="U9" t="n">
-        <v>4</v>
-      </c>
       <c r="V9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>CWxpUrtf</t>
+          <t>zB2j3YvM</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>tAufB9Mi</t>
+          <t>lb31RXzP</t>
         </is>
       </c>
       <c r="Y9" t="n">
         <v>55</v>
       </c>
       <c r="Z9" t="n">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -2306,29 +2220,25 @@
       <c r="AB9" t="n">
         <v>20242025</v>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="n">
-        <v>23.9</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="AF9" t="n">
-        <v>182.9</v>
+        <v>178.8888888888889</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.4</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="AH9" t="n">
-        <v>76.2</v>
+        <v>67.33333333333333</v>
       </c>
       <c r="AI9" t="n">
-        <v>12650000</v>
+        <v>1747222.222222222</v>
       </c>
       <c r="AJ9" t="n">
-        <v>80.8</v>
+        <v>71.66666666666667</v>
       </c>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
@@ -2337,178 +2247,144 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="n">
-        <v>20.86666666666667</v>
+        <v>26.17647058823529</v>
       </c>
       <c r="AR9" t="n">
-        <v>183.6666666666667</v>
+        <v>177.1764705882353</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AT9" t="n">
-        <v>72.73333333333333</v>
+        <v>66.17647058823529</v>
       </c>
       <c r="AU9" t="n">
-        <v>9083333.333333334</v>
+        <v>1182352.941176471</v>
       </c>
       <c r="AV9" t="n">
-        <v>82</v>
+        <v>69.23529411764706</v>
       </c>
       <c r="AW9" t="n">
-        <v>22.72727272727273</v>
+        <v>22.25</v>
       </c>
       <c r="AX9" t="n">
-        <v>182.1818181818182</v>
+        <v>179.5833333333333</v>
       </c>
       <c r="AY9" t="n">
         <v>1</v>
       </c>
       <c r="AZ9" t="n">
-        <v>65.81818181818181</v>
+        <v>63.83333333333334</v>
       </c>
       <c r="BA9" t="n">
-        <v>1463636.363636364</v>
+        <v>931250</v>
       </c>
       <c r="BB9" t="n">
-        <v>74.27272727272727</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>190</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>78</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>20500000</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>84</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>24</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>176</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>71</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>74</v>
-      </c>
+        <v>72.91666666666667</v>
+      </c>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+      <c r="BO9" t="inlineStr"/>
+      <c r="BP9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>MaSQpUZg</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45521.58333333334</v>
+        <v>45527.625</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">wattellier e 
+          <t xml:space="preserve">thual o 
   fra </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
+          <t xml:space="preserve">stade francis le basser
+  laval </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>21029</v>
-      </c>
-      <c r="F10" t="n">
-        <v>14755</v>
-      </c>
+        <v>11017</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>E1wDrLsJ</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.66</v>
-      </c>
+          <t>QDfKl36E</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="N10" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="P10" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="T10" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="U10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V10" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>25Wk0Fko</t>
+          <t>Ys1Pb7ws</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>nVS1TlC4</t>
+          <t>QNSJnsB5</t>
         </is>
       </c>
       <c r="Y10" t="n">
         <v>55</v>
       </c>
       <c r="Z10" t="n">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -2517,208 +2393,182 @@
         <v>20242025</v>
       </c>
       <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>181.125</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>66.75</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1281250</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>72.625</v>
+      </c>
       <c r="AK10" t="n">
-        <v>24.875</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="AL10" t="n">
-        <v>180.25</v>
+        <v>179.8888888888889</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>75.875</v>
+        <v>65.33333333333333</v>
       </c>
       <c r="AO10" t="n">
-        <v>10312500</v>
+        <v>1077777.777777778</v>
       </c>
       <c r="AP10" t="n">
-        <v>80.5</v>
+        <v>70.44444444444444</v>
       </c>
       <c r="AQ10" t="n">
-        <v>20.25</v>
+        <v>27.25</v>
       </c>
       <c r="AR10" t="n">
-        <v>181.6666666666667</v>
+        <v>177.75</v>
       </c>
       <c r="AS10" t="n">
         <v>1</v>
       </c>
       <c r="AT10" t="n">
-        <v>68</v>
+        <v>64.58333333333333</v>
       </c>
       <c r="AU10" t="n">
-        <v>3266666.666666667</v>
+        <v>832500</v>
       </c>
       <c r="AV10" t="n">
-        <v>78.75</v>
+        <v>71</v>
       </c>
       <c r="AW10" t="n">
-        <v>23.33333333333333</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="AX10" t="n">
-        <v>178.6111111111111</v>
+        <v>180.7777777777778</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.444444444444444</v>
+        <v>1</v>
       </c>
       <c r="AZ10" t="n">
-        <v>72.38888888888889</v>
+        <v>60.33333333333334</v>
       </c>
       <c r="BA10" t="n">
-        <v>8463888.888888888</v>
+        <v>686111.1111111111</v>
       </c>
       <c r="BB10" t="n">
-        <v>79.88888888888889</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>182.6666666666667</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>221</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>29200000</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>238</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>180.6</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>386</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>55800000</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>389</v>
-      </c>
+        <v>69.77777777777777</v>
+      </c>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+      <c r="BO10" t="inlineStr"/>
+      <c r="BP10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>r97iWUK0</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45521.5</v>
+        <v>45527.625</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">bastien b 
+          <t xml:space="preserve">lesage m 
   fra </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
+          <t xml:space="preserve">stade armand cesari
+  bastia </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>15220</v>
-      </c>
-      <c r="F11" t="n">
-        <v>14962</v>
-      </c>
+        <v>16048</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>AZwK8L6R</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2.58</v>
-      </c>
+          <t>lKkBAsxF</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="N11" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="O11" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="P11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="U11" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="V11" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0tIbS515</t>
+          <t>fo8nHfg4</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>pYizckpN</t>
+          <t>dS1CBple</t>
         </is>
       </c>
       <c r="Y11" t="n">
         <v>55</v>
       </c>
       <c r="Z11" t="n">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -2727,195 +2577,163 @@
         <v>20242025</v>
       </c>
       <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lhUkVMh2</t>
-        </is>
-      </c>
-      <c r="AE11" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>181.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>5460000</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1205000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>71.09999999999999</v>
+      </c>
       <c r="AQ11" t="n">
-        <v>22.78571428571428</v>
+        <v>24.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>178.1428571428571</v>
+        <v>180.8571428571429</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.285714285714286</v>
+        <v>1</v>
       </c>
       <c r="AT11" t="n">
-        <v>67.71428571428571</v>
+        <v>63.78571428571428</v>
       </c>
       <c r="AU11" t="n">
-        <v>4185714.285714286</v>
+        <v>832142.8571428572</v>
       </c>
       <c r="AV11" t="n">
-        <v>74.42857142857143</v>
+        <v>67.57142857142857</v>
       </c>
       <c r="AW11" t="n">
-        <v>24.36363636363636</v>
+        <v>24</v>
       </c>
       <c r="AX11" t="n">
-        <v>180.0909090909091</v>
+        <v>181.0666666666667</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.454545454545455</v>
+        <v>1.2</v>
       </c>
       <c r="AZ11" t="n">
-        <v>75.18181818181819</v>
+        <v>62.6</v>
       </c>
       <c r="BA11" t="n">
-        <v>10490909.09090909</v>
+        <v>728333.3333333334</v>
       </c>
       <c r="BB11" t="n">
-        <v>79.18181818181819</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>172</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>74</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>77</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>23.75</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>183.75</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>4</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>296</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>48000000</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>318</v>
-      </c>
+        <v>71.53333333333333</v>
+      </c>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr"/>
+      <c r="BO11" t="inlineStr"/>
+      <c r="BP11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>dvUee9dD</t>
+          <t>GM5aU8kD</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45521.39583333334</v>
+        <v>45527.625</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">gaillouste p 
+          <t xml:space="preserve">bastien b 
   fra </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade michel d ornano
-  caen </t>
+          <t xml:space="preserve">parc des sports
+  annecy </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>20300</v>
+        <v>15660</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>GjLn2QoH</t>
+          <t>25dB6Eto</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0OEHEprs</t>
+          <t>ADl76OZP</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="N12" t="n">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="O12" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="P12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R12" t="n">
         <v>5</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
         <v>13</v>
       </c>
       <c r="U12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V12" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Q9EVqFe4</t>
+          <t>SIiBpBrs</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>zB2j3YvM</t>
+          <t>EwpPg8iH</t>
         </is>
       </c>
       <c r="Y12" t="n">
@@ -2933,77 +2751,53 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="n">
-        <v>25.44444444444444</v>
+        <v>26</v>
       </c>
       <c r="AF12" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG12" t="n">
         <v>1</v>
       </c>
       <c r="AH12" t="n">
-        <v>67.55555555555556</v>
+        <v>64.44444444444444</v>
       </c>
       <c r="AI12" t="n">
-        <v>1638888.888888889</v>
+        <v>841666.6666666666</v>
       </c>
       <c r="AJ12" t="n">
-        <v>74</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>24.66666666666667</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>177.8888888888889</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.111111111111111</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>67.22222222222223</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>1697222.222222222</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>71.55555555555556</v>
-      </c>
+        <v>68.11111111111111</v>
+      </c>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="n">
-        <v>22.07142857142857</v>
+        <v>24.81818181818182</v>
       </c>
       <c r="AR12" t="n">
-        <v>179.7857142857143</v>
+        <v>181.2727272727273</v>
       </c>
       <c r="AS12" t="n">
         <v>1</v>
       </c>
       <c r="AT12" t="n">
-        <v>64.21428571428571</v>
+        <v>64.36363636363636</v>
       </c>
       <c r="AU12" t="n">
-        <v>1037500</v>
+        <v>881818.1818181818</v>
       </c>
       <c r="AV12" t="n">
-        <v>74.07142857142857</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>24.95</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>181.8</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>1083750</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>69.15000000000001</v>
-      </c>
+        <v>70.36363636363636</v>
+      </c>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
       <c r="BC12" t="inlineStr"/>
       <c r="BD12" t="inlineStr"/>
       <c r="BE12" t="inlineStr"/>
@@ -3022,97 +2816,91 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>OA5YizjL</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45520.65625</v>
+        <v>45523.65625</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">thual o 
   fra </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>25178</v>
-      </c>
-      <c r="F13" t="n">
-        <v>23167</v>
-      </c>
+        <v>67394</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>ADl76OZP</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.89</v>
-      </c>
+          <t>jgNAYRGi</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="N13" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="O13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T13" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="U13" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>dWZTBmVT</t>
+          <t>EwpPg8iH</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>8MdrBIUb</t>
+          <t>Cp0gM1r4</t>
         </is>
       </c>
       <c r="Y13" t="n">
         <v>55</v>
       </c>
       <c r="Z13" t="n">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -3121,187 +2909,155 @@
         <v>20242025</v>
       </c>
       <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="n">
-        <v>25.18181818181818</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>185.2727272727273</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>71.36363636363636</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>2945454.545454545</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="inlineStr"/>
-      <c r="AQ13" t="n">
-        <v>22.5625</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>180.0625</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>1389062.5</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>72.75</v>
-      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="n">
+        <v>24.44444444444444</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>178.1111111111111</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>71.77777777777777</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>4622222.222222222</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>77.11111111111111</v>
+      </c>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
       <c r="AW13" t="n">
-        <v>23.69230769230769</v>
+        <v>21.73333333333333</v>
       </c>
       <c r="AX13" t="n">
-        <v>183.5384615384615</v>
+        <v>177.4</v>
       </c>
       <c r="AY13" t="n">
-        <v>2.307692307692307</v>
+        <v>1</v>
       </c>
       <c r="AZ13" t="n">
-        <v>80.38461538461539</v>
+        <v>69.06666666666666</v>
       </c>
       <c r="BA13" t="n">
-        <v>42061538.46153846</v>
+        <v>2781666.666666667</v>
       </c>
       <c r="BB13" t="n">
-        <v>84.76923076923077</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>188</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>64</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>1300000</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>74</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>27</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>186.5</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>165</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>68000000</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>167</v>
-      </c>
+        <v>77.53333333333333</v>
+      </c>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr"/>
+      <c r="BO13" t="inlineStr"/>
+      <c r="BP13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>EeC5phre</t>
+          <t>lEQmcVR0</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45520.625</v>
+        <v>45523.65625</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">valnet a 
+          <t xml:space="preserve">petit a 
   fra </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">michel moretti stadium
-  ajaccio </t>
+          <t xml:space="preserve">stade saint symphorien
+  metz </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>8470</v>
+        <v>28786</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2aeoANM8</t>
+          <t>4v0yqlWc</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0pOdQOCg</t>
+          <t>AZwK8L6R</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="N14" t="n">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="O14" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="P14" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q14" t="n">
         <v>5</v>
       </c>
-      <c r="Q14" t="n">
-        <v>4</v>
-      </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="U14" t="n">
+        <v>12</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6</v>
+      </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>8tmnzqxe</t>
+          <t>h89kUbu5</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>OQuqpG7i</t>
+          <t>fo8nHfg4</t>
         </is>
       </c>
       <c r="Y14" t="n">
@@ -3316,79 +3072,83 @@
       <c r="AB14" t="n">
         <v>20242025</v>
       </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="n">
-        <v>24.9</v>
+        <v>24.90909090909091</v>
       </c>
       <c r="AF14" t="n">
-        <v>178.2</v>
+        <v>177.8181818181818</v>
       </c>
       <c r="AG14" t="n">
-        <v>1</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="AH14" t="n">
-        <v>64.40000000000001</v>
+        <v>68.90909090909091</v>
       </c>
       <c r="AI14" t="n">
-        <v>872500</v>
+        <v>1677272.727272727</v>
       </c>
       <c r="AJ14" t="n">
-        <v>70.3</v>
+        <v>75.27272727272727</v>
       </c>
       <c r="AK14" t="n">
-        <v>22.5</v>
+        <v>25.375</v>
       </c>
       <c r="AL14" t="n">
-        <v>182.5</v>
+        <v>179.625</v>
       </c>
       <c r="AM14" t="n">
         <v>1</v>
       </c>
       <c r="AN14" t="n">
-        <v>64.75</v>
+        <v>63.625</v>
       </c>
       <c r="AO14" t="n">
-        <v>1090625</v>
+        <v>723125</v>
       </c>
       <c r="AP14" t="n">
-        <v>70.75</v>
+        <v>68.375</v>
       </c>
       <c r="AQ14" t="n">
-        <v>26.38888888888889</v>
+        <v>24</v>
       </c>
       <c r="AR14" t="n">
+        <v>181.0909090909091</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>67.81818181818181</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1718181.818181818</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="AX14" t="n">
         <v>180</v>
       </c>
-      <c r="AS14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>65.05555555555556</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>751388.8888888889</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>69.61111111111111</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>182.2</v>
-      </c>
       <c r="AY14" t="n">
         <v>1</v>
       </c>
       <c r="AZ14" t="n">
-        <v>62.7</v>
+        <v>61.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>830000</v>
+        <v>679166.6666666666</v>
       </c>
       <c r="BB14" t="n">
-        <v>71</v>
+        <v>68.16666666666667</v>
       </c>
       <c r="BC14" t="inlineStr"/>
       <c r="BD14" t="inlineStr"/>
@@ -3408,30 +3168,28 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2Hh06Z4E</t>
+          <t>zkPwWhT1</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45520.625</v>
+        <v>45522.65625</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">rosier e 
+          <t xml:space="preserve">millot b 
   fra </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la licorne
-  amiens </t>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>12097</v>
-      </c>
-      <c r="F15" t="n">
-        <v>4918</v>
-      </c>
+        <v>29778</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
         <v>3</v>
       </c>
@@ -3440,61 +3198,65 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>lKkBAsxF</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2kM6ufaS</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.64</v>
+      </c>
       <c r="M15" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="N15" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O15" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="P15" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>8</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2</v>
+      </c>
+      <c r="S15" t="n">
         <v>13</v>
       </c>
-      <c r="Q15" t="n">
-        <v>6</v>
-      </c>
-      <c r="R15" t="n">
-        <v>3</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
+        <v>12</v>
+      </c>
+      <c r="U15" t="n">
+        <v>8</v>
+      </c>
+      <c r="V15" t="n">
         <v>11</v>
       </c>
-      <c r="T15" t="n">
-        <v>13</v>
-      </c>
-      <c r="U15" t="n">
-        <v>11</v>
-      </c>
-      <c r="V15" t="n">
-        <v>13</v>
-      </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>dS1CBple</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>SzfSpYcf</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
       <c r="Y15" t="n">
         <v>55</v>
       </c>
       <c r="Z15" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -3502,161 +3264,221 @@
       <c r="AB15" t="n">
         <v>20242025</v>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="n">
-        <v>26.1</v>
+        <v>25.875</v>
       </c>
       <c r="AF15" t="n">
-        <v>181.2</v>
+        <v>180.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="AH15" t="n">
-        <v>67.09999999999999</v>
+        <v>75.625</v>
       </c>
       <c r="AI15" t="n">
-        <v>1205000</v>
+        <v>9475000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>71.09999999999999</v>
-      </c>
-      <c r="AK15" t="inlineStr"/>
-      <c r="AL15" t="inlineStr"/>
-      <c r="AM15" t="inlineStr"/>
-      <c r="AN15" t="inlineStr"/>
-      <c r="AO15" t="inlineStr"/>
-      <c r="AP15" t="inlineStr"/>
+        <v>79.25</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>76.33333333333333</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>10111111.11111111</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>80</v>
+      </c>
       <c r="AQ15" t="n">
-        <v>24.5</v>
+        <v>24.23076923076923</v>
       </c>
       <c r="AR15" t="n">
-        <v>180.75</v>
+        <v>181.9230769230769</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.1875</v>
+        <v>1.538461538461539</v>
       </c>
       <c r="AT15" t="n">
-        <v>63.0625</v>
+        <v>73.07692307692308</v>
       </c>
       <c r="AU15" t="n">
-        <v>751562.5</v>
+        <v>8578846.153846154</v>
       </c>
       <c r="AV15" t="n">
-        <v>71.4375</v>
-      </c>
-      <c r="AW15" t="inlineStr"/>
-      <c r="AX15" t="inlineStr"/>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr"/>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
-      <c r="BI15" t="inlineStr"/>
-      <c r="BJ15" t="inlineStr"/>
-      <c r="BK15" t="inlineStr"/>
-      <c r="BL15" t="inlineStr"/>
-      <c r="BM15" t="inlineStr"/>
-      <c r="BN15" t="inlineStr"/>
-      <c r="BO15" t="inlineStr"/>
-      <c r="BP15" t="inlineStr"/>
+        <v>77.53846153846153</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>23.81818181818182</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.681818181818182</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>73.18181818181819</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>5522727.272727272</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>78.81818181818181</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>189</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>72</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>78</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>31</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>173.5</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>159</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>33000000</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>6V8cnEDr</t>
+          <t>2NocJFqd</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45520.625</v>
+        <v>45522.5</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">landry r 
+          <t xml:space="preserve">leonard t 
   fra </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade gabriel montpied
-  clermont ferrand </t>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>10800</v>
+        <v>18752</v>
       </c>
       <c r="F16" t="n">
-        <v>5582</v>
+        <v>14811</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>IRuMRua1</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>6NOhR4cm</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.92</v>
+      </c>
       <c r="M16" t="n">
+        <v>44</v>
+      </c>
+      <c r="N16" t="n">
         <v>56</v>
       </c>
-      <c r="N16" t="n">
-        <v>44</v>
-      </c>
       <c r="O16" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="P16" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>5</v>
+      </c>
+      <c r="S16" t="n">
+        <v>6</v>
+      </c>
+      <c r="T16" t="n">
+        <v>10</v>
+      </c>
+      <c r="U16" t="n">
+        <v>10</v>
+      </c>
+      <c r="V16" t="n">
         <v>11</v>
       </c>
-      <c r="Q16" t="n">
-        <v>5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>4</v>
-      </c>
-      <c r="S16" t="n">
-        <v>14</v>
-      </c>
-      <c r="T16" t="n">
-        <v>12</v>
-      </c>
-      <c r="U16" t="n">
-        <v>14</v>
-      </c>
-      <c r="V16" t="n">
-        <v>16</v>
-      </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>4G9MhScS</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>fm0Qb28B</t>
+          <t>K6b7RoBp</t>
         </is>
       </c>
       <c r="Y16" t="n">
         <v>55</v>
       </c>
       <c r="Z16" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -3665,178 +3487,220 @@
         <v>20242025</v>
       </c>
       <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
       <c r="AE16" t="n">
-        <v>23.88888888888889</v>
+        <v>25.7</v>
       </c>
       <c r="AF16" t="n">
-        <v>180</v>
+        <v>184.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.111111111111111</v>
+        <v>1.1</v>
       </c>
       <c r="AH16" t="n">
-        <v>66.44444444444444</v>
+        <v>68</v>
       </c>
       <c r="AI16" t="n">
-        <v>1436111.111111111</v>
+        <v>1587500</v>
       </c>
       <c r="AJ16" t="n">
-        <v>73.77777777777777</v>
+        <v>72.8</v>
       </c>
       <c r="AK16" t="n">
-        <v>25.4</v>
+        <v>27.63636363636364</v>
       </c>
       <c r="AL16" t="n">
-        <v>183.7</v>
+        <v>179.8181818181818</v>
       </c>
       <c r="AM16" t="n">
-        <v>1</v>
+        <v>1.454545454545455</v>
       </c>
       <c r="AN16" t="n">
-        <v>65.5</v>
+        <v>77</v>
       </c>
       <c r="AO16" t="n">
-        <v>962500</v>
+        <v>12381818.18181818</v>
       </c>
       <c r="AP16" t="n">
-        <v>70.7</v>
+        <v>78.72727272727273</v>
       </c>
       <c r="AQ16" t="n">
-        <v>20.85714285714286</v>
+        <v>25.7</v>
       </c>
       <c r="AR16" t="n">
-        <v>176</v>
+        <v>183.9</v>
       </c>
       <c r="AS16" t="n">
         <v>1</v>
       </c>
       <c r="AT16" t="n">
-        <v>65.28571428571429</v>
+        <v>66.45</v>
       </c>
       <c r="AU16" t="n">
-        <v>1614285.714285714</v>
+        <v>1278750</v>
       </c>
       <c r="AV16" t="n">
-        <v>75.28571428571429</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="AW16" t="n">
-        <v>26</v>
+        <v>23.90909090909091</v>
       </c>
       <c r="AX16" t="n">
-        <v>182.7272727272727</v>
+        <v>179.9545454545455</v>
       </c>
       <c r="AY16" t="n">
-        <v>1</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="AZ16" t="n">
-        <v>64.54545454545455</v>
+        <v>72.90909090909091</v>
       </c>
       <c r="BA16" t="n">
-        <v>709090.9090909091</v>
+        <v>6081818.181818182</v>
       </c>
       <c r="BB16" t="n">
-        <v>70.27272727272727</v>
-      </c>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
-      <c r="BI16" t="inlineStr"/>
-      <c r="BJ16" t="inlineStr"/>
-      <c r="BK16" t="inlineStr"/>
-      <c r="BL16" t="inlineStr"/>
-      <c r="BM16" t="inlineStr"/>
-      <c r="BN16" t="inlineStr"/>
-      <c r="BO16" t="inlineStr"/>
-      <c r="BP16" t="inlineStr"/>
+        <v>78.13636363636364</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>179.25</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>266</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>5725000</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>290</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>25</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>179</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>298</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>28600000</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>310</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>zB0ErWC7</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45520.625</v>
+        <v>45522.5</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">kubler g 
+          <t xml:space="preserve">stinat j 
   fra </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade marcel tribut
-  dunkerque </t>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4933</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
+        <v>33150</v>
+      </c>
+      <c r="F17" t="n">
+        <v>25491</v>
+      </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M17" t="n">
+        <v>53</v>
+      </c>
+      <c r="N17" t="n">
+        <v>47</v>
+      </c>
+      <c r="O17" t="n">
+        <v>7</v>
+      </c>
+      <c r="P17" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3</v>
+      </c>
+      <c r="R17" t="n">
         <v>2</v>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>tAAobNse</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>25dB6Eto</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="n">
-        <v>48</v>
-      </c>
-      <c r="N17" t="n">
-        <v>52</v>
-      </c>
-      <c r="O17" t="n">
-        <v>12</v>
-      </c>
-      <c r="P17" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>6</v>
-      </c>
-      <c r="R17" t="n">
-        <v>4</v>
-      </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="n">
-        <v>15</v>
-      </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="U17" t="n">
+        <v>8</v>
+      </c>
+      <c r="V17" t="n">
+        <v>3</v>
+      </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>lb31RXzP</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>SIiBpBrs</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
       <c r="Y17" t="n">
         <v>55</v>
       </c>
       <c r="Z17" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -3845,66 +3709,82 @@
         <v>20242025</v>
       </c>
       <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="AE17" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>181.1</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>78.7</v>
+      </c>
       <c r="AK17" t="n">
-        <v>26.44444444444444</v>
+        <v>24.8</v>
       </c>
       <c r="AL17" t="n">
-        <v>182.5555555555555</v>
+        <v>182</v>
       </c>
       <c r="AM17" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AN17" t="n">
-        <v>64.55555555555556</v>
+        <v>72.8</v>
       </c>
       <c r="AO17" t="n">
-        <v>833333.3333333334</v>
+        <v>5310000</v>
       </c>
       <c r="AP17" t="n">
-        <v>67.77777777777777</v>
+        <v>76.2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>22.83333333333333</v>
+        <v>24</v>
       </c>
       <c r="AR17" t="n">
-        <v>176.8333333333333</v>
+        <v>178.375</v>
       </c>
       <c r="AS17" t="n">
         <v>1</v>
       </c>
       <c r="AT17" t="n">
-        <v>63.25</v>
+        <v>69.8125</v>
       </c>
       <c r="AU17" t="n">
-        <v>804166.6666666666</v>
+        <v>2631250</v>
       </c>
       <c r="AV17" t="n">
-        <v>70.75</v>
+        <v>75.4375</v>
       </c>
       <c r="AW17" t="n">
-        <v>21.66666666666667</v>
+        <v>25.76470588235294</v>
       </c>
       <c r="AX17" t="n">
-        <v>180.6666666666667</v>
+        <v>182.8235294117647</v>
       </c>
       <c r="AY17" t="n">
-        <v>1</v>
+        <v>1.411764705882353</v>
       </c>
       <c r="AZ17" t="n">
-        <v>61.83333333333334</v>
+        <v>71.76470588235294</v>
       </c>
       <c r="BA17" t="n">
-        <v>708333.3333333334</v>
+        <v>3450000</v>
       </c>
       <c r="BB17" t="n">
-        <v>69.33333333333333</v>
+        <v>74.58823529411765</v>
       </c>
       <c r="BC17" t="inlineStr"/>
       <c r="BD17" t="inlineStr"/>
@@ -3924,83 +3804,97 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>dGo94DZQ</t>
+          <t>M5VGwpVA</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45520.625</v>
+        <v>45522.5</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">kherradji a 
+          <t xml:space="preserve">vernice m 
   fra </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade des alpes
-  grenoble </t>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>20068</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
+        <v>20484</v>
+      </c>
+      <c r="F18" t="n">
+        <v>15706</v>
+      </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>UgPj1p1N</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>E1wDrLsJ</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M18" t="n">
+        <v>43</v>
+      </c>
+      <c r="N18" t="n">
+        <v>57</v>
+      </c>
       <c r="O18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P18" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>4</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="n">
+        <v>18</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
+      </c>
+      <c r="V18" t="n">
         <v>9</v>
       </c>
-      <c r="Q18" t="n">
-        <v>4</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
-          <t>WrQARdPN</t>
+          <t>vVQcGxl1</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Ys1Pb7ws</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
       <c r="Y18" t="n">
         <v>55</v>
       </c>
       <c r="Z18" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -4008,266 +3902,2416 @@
       <c r="AB18" t="n">
         <v>20242025</v>
       </c>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
       <c r="AE18" t="n">
-        <v>25.72727272727273</v>
+        <v>25.6</v>
       </c>
       <c r="AF18" t="n">
-        <v>182.8181818181818</v>
+        <v>180.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AH18" t="n">
-        <v>67.63636363636364</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AI18" t="n">
-        <v>1495454.545454545</v>
+        <v>6330000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>71.36363636363636</v>
-      </c>
-      <c r="AK18" t="inlineStr"/>
-      <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="inlineStr"/>
-      <c r="AN18" t="inlineStr"/>
-      <c r="AO18" t="inlineStr"/>
-      <c r="AP18" t="inlineStr"/>
+        <v>78.2</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>21.22222222222222</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>185.4444444444445</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>70.77777777777777</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>4402777.777777778</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>79.88888888888889</v>
+      </c>
       <c r="AQ18" t="n">
-        <v>29.66666666666667</v>
+        <v>23.375</v>
       </c>
       <c r="AR18" t="n">
-        <v>185.1666666666667</v>
+        <v>182</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AT18" t="n">
-        <v>70.5</v>
+        <v>70.75</v>
       </c>
       <c r="AU18" t="n">
-        <v>1937500</v>
+        <v>3787500</v>
       </c>
       <c r="AV18" t="n">
-        <v>72.5</v>
+        <v>76.625</v>
       </c>
       <c r="AW18" t="n">
-        <v>24.8125</v>
+        <v>21.875</v>
       </c>
       <c r="AX18" t="n">
-        <v>181.5</v>
+        <v>178.75</v>
       </c>
       <c r="AY18" t="n">
         <v>1</v>
       </c>
       <c r="AZ18" t="n">
-        <v>64.3125</v>
+        <v>67.1875</v>
       </c>
       <c r="BA18" t="n">
-        <v>958750</v>
+        <v>2412500</v>
       </c>
       <c r="BB18" t="n">
-        <v>71.3125</v>
-      </c>
-      <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="inlineStr"/>
-      <c r="BF18" t="inlineStr"/>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
-      <c r="BI18" t="inlineStr"/>
-      <c r="BJ18" t="inlineStr"/>
-      <c r="BK18" t="inlineStr"/>
-      <c r="BL18" t="inlineStr"/>
-      <c r="BM18" t="inlineStr"/>
-      <c r="BN18" t="inlineStr"/>
-      <c r="BO18" t="inlineStr"/>
-      <c r="BP18" t="inlineStr"/>
+        <v>76</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>31</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>186</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>147</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>147</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>19</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>176</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>70</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
+          <t>ripawyyS</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45522.41666666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lissorgue r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>17924</v>
+      </c>
+      <c r="F19" t="n">
+        <v>16354</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M19" t="n">
+        <v>46</v>
+      </c>
+      <c r="N19" t="n">
+        <v>54</v>
+      </c>
+      <c r="O19" t="n">
+        <v>16</v>
+      </c>
+      <c r="P19" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>7</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2</v>
+      </c>
+      <c r="S19" t="n">
+        <v>11</v>
+      </c>
+      <c r="T19" t="n">
+        <v>17</v>
+      </c>
+      <c r="U19" t="n">
+        <v>7</v>
+      </c>
+      <c r="V19" t="n">
+        <v>8</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="AE19" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>68.22222222222223</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1708333.333333333</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>184</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>9280000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>25.08333333333333</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>180.8333333333333</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>65.08333333333333</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1062500</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>69.25</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>5470000</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>192</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>69</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>74</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>177</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>307</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>53500000</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>fHYrsJy3</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45521.66666666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">turpin c 
+  fra </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F20" t="n">
+        <v>14250</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M20" t="n">
+        <v>61</v>
+      </c>
+      <c r="N20" t="n">
+        <v>39</v>
+      </c>
+      <c r="O20" t="n">
+        <v>13</v>
+      </c>
+      <c r="P20" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>6</v>
+      </c>
+      <c r="R20" t="n">
+        <v>4</v>
+      </c>
+      <c r="S20" t="n">
+        <v>13</v>
+      </c>
+      <c r="T20" t="n">
+        <v>14</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4</v>
+      </c>
+      <c r="V20" t="n">
+        <v>17</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>182.9</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>12650000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="n">
+        <v>20.86666666666667</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>183.6666666666667</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>72.73333333333333</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>9083333.333333334</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>82</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>22.72727272727273</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>182.1818181818182</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>65.81818181818181</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1463636.363636364</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>74.27272727272727</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>190</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>78</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>20500000</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>84</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>24</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>176</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>71</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>jqSiuc6F</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45521.58333333334</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wattellier e 
+  fra </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F21" t="n">
+        <v>14755</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M21" t="n">
+        <v>29</v>
+      </c>
+      <c r="N21" t="n">
+        <v>71</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2</v>
+      </c>
+      <c r="P21" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6</v>
+      </c>
+      <c r="S21" t="n">
+        <v>6</v>
+      </c>
+      <c r="T21" t="n">
+        <v>13</v>
+      </c>
+      <c r="U21" t="n">
+        <v>12</v>
+      </c>
+      <c r="V21" t="n">
+        <v>6</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="n">
+        <v>24.875</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>180.25</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>75.875</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>10312500</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>181.6666666666667</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>68</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3266666.666666667</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>178.6111111111111</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>72.38888888888889</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>8463888.888888888</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>79.88888888888889</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>182.6666666666667</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>221</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>29200000</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>238</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>180.6</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>386</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>55800000</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>0js8u60b</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45521.5</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F22" t="n">
+        <v>14962</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>5</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="M22" t="n">
+        <v>51</v>
+      </c>
+      <c r="N22" t="n">
+        <v>49</v>
+      </c>
+      <c r="O22" t="n">
+        <v>7</v>
+      </c>
+      <c r="P22" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>5</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="n">
+        <v>8</v>
+      </c>
+      <c r="U22" t="n">
+        <v>10</v>
+      </c>
+      <c r="V22" t="n">
+        <v>12</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
+      <c r="AE22" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>5460000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="n">
+        <v>22.78571428571428</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>178.1428571428571</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.285714285714286</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>67.71428571428571</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>4185714.285714286</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>74.42857142857143</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>24.36363636363636</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>180.0909090909091</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>75.18181818181819</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>10490909.09090909</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>79.18181818181819</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>172</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>74</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>77</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>183.75</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>296</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>dvUee9dD</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45521.39583333334</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gaillouste p 
+  fra </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade michel d ornano
+  caen </t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>20300</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>GjLn2QoH</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0OEHEprs</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="n">
+        <v>36</v>
+      </c>
+      <c r="N23" t="n">
+        <v>64</v>
+      </c>
+      <c r="O23" t="n">
+        <v>9</v>
+      </c>
+      <c r="P23" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>5</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="n">
+        <v>13</v>
+      </c>
+      <c r="U23" t="n">
+        <v>10</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Q9EVqFe4</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>zB2j3YvM</t>
+        </is>
+      </c>
+      <c r="Y23" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="n">
+        <v>25.44444444444444</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>181</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>67.55555555555556</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1638888.888888889</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>74</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>177.8888888888889</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>67.22222222222223</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1697222.222222222</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>71.55555555555556</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>22.07142857142857</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>179.7857142857143</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>64.21428571428571</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1037500</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>74.07142857142857</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>181.8</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1083750</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>69.15000000000001</v>
+      </c>
+      <c r="BC23" t="inlineStr"/>
+      <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr"/>
+      <c r="BF23" t="inlineStr"/>
+      <c r="BG23" t="inlineStr"/>
+      <c r="BH23" t="inlineStr"/>
+      <c r="BI23" t="inlineStr"/>
+      <c r="BJ23" t="inlineStr"/>
+      <c r="BK23" t="inlineStr"/>
+      <c r="BL23" t="inlineStr"/>
+      <c r="BM23" t="inlineStr"/>
+      <c r="BN23" t="inlineStr"/>
+      <c r="BO23" t="inlineStr"/>
+      <c r="BP23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>SOLVXEbk</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45520.65625</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delajod w 
+  fra </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>25178</v>
+      </c>
+      <c r="F24" t="n">
+        <v>23167</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="M24" t="n">
+        <v>26</v>
+      </c>
+      <c r="N24" t="n">
+        <v>74</v>
+      </c>
+      <c r="O24" t="n">
+        <v>5</v>
+      </c>
+      <c r="P24" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>9</v>
+      </c>
+      <c r="S24" t="n">
+        <v>9</v>
+      </c>
+      <c r="T24" t="n">
+        <v>9</v>
+      </c>
+      <c r="U24" t="n">
+        <v>8</v>
+      </c>
+      <c r="V24" t="n">
+        <v>4</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="Y24" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>551</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="n">
+        <v>25.18181818181818</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>185.2727272727273</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>71.36363636363636</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>2945454.545454545</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="n">
+        <v>22.5625</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>180.0625</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1389062.5</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>23.69230769230769</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>183.5384615384615</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>2.307692307692307</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>80.38461538461539</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>42061538.46153846</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>84.76923076923077</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>188</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>64</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>74</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>27</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>165</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>68000000</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
           <t>b15XX7Nt</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B25" s="2" t="n">
         <v>45520.625</v>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t xml:space="preserve">bollengier m 
   fra </t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t xml:space="preserve">stade de roudourou
   guingamp </t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="E25" t="n">
         <v>19060</v>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="n">
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
         <v>4</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H25" t="n">
         <v>0</v>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>QDfKl36E</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>fsfAHubD</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="n">
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
         <v>49</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N25" t="n">
         <v>51</v>
       </c>
-      <c r="O19" t="n">
+      <c r="O25" t="n">
         <v>16</v>
       </c>
-      <c r="P19" t="n">
+      <c r="P25" t="n">
         <v>10</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="Q25" t="n">
         <v>5</v>
       </c>
-      <c r="R19" t="n">
+      <c r="R25" t="n">
         <v>3</v>
       </c>
-      <c r="S19" t="n">
+      <c r="S25" t="n">
         <v>9</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T25" t="n">
         <v>12</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U25" t="n">
         <v>9</v>
       </c>
-      <c r="V19" t="n">
+      <c r="V25" t="n">
         <v>14</v>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>QNSJnsB5</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>4vG8dmrf</t>
         </is>
       </c>
-      <c r="Y19" t="n">
+      <c r="Y25" t="n">
         <v>55</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="Z25" t="n">
         <v>555</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AA25" t="n">
         <v>0</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AB25" t="n">
         <v>20242025</v>
       </c>
-      <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="n">
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="n">
         <v>24.5</v>
       </c>
-      <c r="AF19" t="n">
+      <c r="AF25" t="n">
         <v>179.9</v>
       </c>
-      <c r="AG19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH19" t="n">
+      <c r="AG25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH25" t="n">
         <v>65.2</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AI25" t="n">
         <v>1025000</v>
       </c>
-      <c r="AJ19" t="n">
+      <c r="AJ25" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AK25" t="n">
         <v>27.625</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AL25" t="n">
         <v>177.625</v>
       </c>
-      <c r="AM19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN19" t="n">
+      <c r="AM25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN25" t="n">
         <v>67.375</v>
       </c>
-      <c r="AO19" t="n">
+      <c r="AO25" t="n">
         <v>1275000</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="AP25" t="n">
         <v>70.375</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AQ25" t="n">
         <v>23</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="AR25" t="n">
         <v>179.7</v>
       </c>
-      <c r="AS19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT19" t="n">
+      <c r="AS25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT25" t="n">
         <v>63.3</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="AU25" t="n">
         <v>950000</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="AV25" t="n">
         <v>70.3</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="AW25" t="n">
         <v>20.41666666666667</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="AX25" t="n">
         <v>179.6666666666667</v>
       </c>
-      <c r="AY19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ19" t="n">
+      <c r="AY25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ25" t="n">
         <v>61.75</v>
       </c>
-      <c r="BA19" t="n">
+      <c r="BA25" t="n">
         <v>912500</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BB25" t="n">
         <v>70.91666666666667</v>
       </c>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
-      <c r="BI19" t="inlineStr"/>
-      <c r="BJ19" t="inlineStr"/>
-      <c r="BK19" t="inlineStr"/>
-      <c r="BL19" t="inlineStr"/>
-      <c r="BM19" t="inlineStr"/>
-      <c r="BN19" t="inlineStr"/>
-      <c r="BO19" t="inlineStr"/>
-      <c r="BP19" t="inlineStr"/>
+      <c r="BC25" t="inlineStr"/>
+      <c r="BD25" t="inlineStr"/>
+      <c r="BE25" t="inlineStr"/>
+      <c r="BF25" t="inlineStr"/>
+      <c r="BG25" t="inlineStr"/>
+      <c r="BH25" t="inlineStr"/>
+      <c r="BI25" t="inlineStr"/>
+      <c r="BJ25" t="inlineStr"/>
+      <c r="BK25" t="inlineStr"/>
+      <c r="BL25" t="inlineStr"/>
+      <c r="BM25" t="inlineStr"/>
+      <c r="BN25" t="inlineStr"/>
+      <c r="BO25" t="inlineStr"/>
+      <c r="BP25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>zB0ErWC7</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kubler g 
+  fra </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade marcel tribut
+  dunkerque </t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4933</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>tAAobNse</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>25dB6Eto</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>48</v>
+      </c>
+      <c r="N26" t="n">
+        <v>52</v>
+      </c>
+      <c r="O26" t="n">
+        <v>12</v>
+      </c>
+      <c r="P26" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>6</v>
+      </c>
+      <c r="R26" t="n">
+        <v>4</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="n">
+        <v>15</v>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>SIiBpBrs</t>
+        </is>
+      </c>
+      <c r="Y26" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="n">
+        <v>26.44444444444444</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>182.5555555555555</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>64.55555555555556</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>833333.3333333334</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>67.77777777777777</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>22.83333333333333</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>176.8333333333333</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>63.25</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>804166.6666666666</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>21.66666666666667</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>61.83333333333334</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>708333.3333333334</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>69.33333333333333</v>
+      </c>
+      <c r="BC26" t="inlineStr"/>
+      <c r="BD26" t="inlineStr"/>
+      <c r="BE26" t="inlineStr"/>
+      <c r="BF26" t="inlineStr"/>
+      <c r="BG26" t="inlineStr"/>
+      <c r="BH26" t="inlineStr"/>
+      <c r="BI26" t="inlineStr"/>
+      <c r="BJ26" t="inlineStr"/>
+      <c r="BK26" t="inlineStr"/>
+      <c r="BL26" t="inlineStr"/>
+      <c r="BM26" t="inlineStr"/>
+      <c r="BN26" t="inlineStr"/>
+      <c r="BO26" t="inlineStr"/>
+      <c r="BP26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>6V8cnEDr</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">landry r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade gabriel montpied
+  clermont ferrand </t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>10800</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5582</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>IRuMRua1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>56</v>
+      </c>
+      <c r="N27" t="n">
+        <v>44</v>
+      </c>
+      <c r="O27" t="n">
+        <v>13</v>
+      </c>
+      <c r="P27" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>5</v>
+      </c>
+      <c r="R27" t="n">
+        <v>4</v>
+      </c>
+      <c r="S27" t="n">
+        <v>14</v>
+      </c>
+      <c r="T27" t="n">
+        <v>12</v>
+      </c>
+      <c r="U27" t="n">
+        <v>14</v>
+      </c>
+      <c r="V27" t="n">
+        <v>16</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>4G9MhScS</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>fm0Qb28B</t>
+        </is>
+      </c>
+      <c r="Y27" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="n">
+        <v>23.88888888888889</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>180</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>66.44444444444444</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1436111.111111111</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>73.77777777777777</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>183.7</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>962500</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>20.85714285714286</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>176</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>65.28571428571429</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>1614285.714285714</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>75.28571428571429</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>182.7272727272727</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>64.54545454545455</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>709090.9090909091</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>70.27272727272727</v>
+      </c>
+      <c r="BC27" t="inlineStr"/>
+      <c r="BD27" t="inlineStr"/>
+      <c r="BE27" t="inlineStr"/>
+      <c r="BF27" t="inlineStr"/>
+      <c r="BG27" t="inlineStr"/>
+      <c r="BH27" t="inlineStr"/>
+      <c r="BI27" t="inlineStr"/>
+      <c r="BJ27" t="inlineStr"/>
+      <c r="BK27" t="inlineStr"/>
+      <c r="BL27" t="inlineStr"/>
+      <c r="BM27" t="inlineStr"/>
+      <c r="BN27" t="inlineStr"/>
+      <c r="BO27" t="inlineStr"/>
+      <c r="BP27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>2Hh06Z4E</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rosier e 
+  fra </t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la licorne
+  amiens </t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>12097</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4918</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>lKkBAsxF</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2kM6ufaS</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="n">
+        <v>51</v>
+      </c>
+      <c r="N28" t="n">
+        <v>49</v>
+      </c>
+      <c r="O28" t="n">
+        <v>17</v>
+      </c>
+      <c r="P28" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>6</v>
+      </c>
+      <c r="R28" t="n">
+        <v>3</v>
+      </c>
+      <c r="S28" t="n">
+        <v>11</v>
+      </c>
+      <c r="T28" t="n">
+        <v>13</v>
+      </c>
+      <c r="U28" t="n">
+        <v>11</v>
+      </c>
+      <c r="V28" t="n">
+        <v>13</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>dS1CBple</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>SzfSpYcf</t>
+        </is>
+      </c>
+      <c r="Y28" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1205000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>63.0625</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>751562.5</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>71.4375</v>
+      </c>
+      <c r="AW28" t="inlineStr"/>
+      <c r="AX28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr"/>
+      <c r="BA28" t="inlineStr"/>
+      <c r="BB28" t="inlineStr"/>
+      <c r="BC28" t="inlineStr"/>
+      <c r="BD28" t="inlineStr"/>
+      <c r="BE28" t="inlineStr"/>
+      <c r="BF28" t="inlineStr"/>
+      <c r="BG28" t="inlineStr"/>
+      <c r="BH28" t="inlineStr"/>
+      <c r="BI28" t="inlineStr"/>
+      <c r="BJ28" t="inlineStr"/>
+      <c r="BK28" t="inlineStr"/>
+      <c r="BL28" t="inlineStr"/>
+      <c r="BM28" t="inlineStr"/>
+      <c r="BN28" t="inlineStr"/>
+      <c r="BO28" t="inlineStr"/>
+      <c r="BP28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>EeC5phre</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">valnet a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">michel moretti stadium
+  ajaccio </t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>8470</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2aeoANM8</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0pOdQOCg</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>99</v>
+      </c>
+      <c r="O29" t="n">
+        <v>8</v>
+      </c>
+      <c r="P29" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>8tmnzqxe</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>OQuqpG7i</t>
+        </is>
+      </c>
+      <c r="Y29" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>178.2</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>872500</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1090625</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>26.38888888888889</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>180</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>65.05555555555556</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>751388.8888888889</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>69.61111111111111</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>830000</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>71</v>
+      </c>
+      <c r="BC29" t="inlineStr"/>
+      <c r="BD29" t="inlineStr"/>
+      <c r="BE29" t="inlineStr"/>
+      <c r="BF29" t="inlineStr"/>
+      <c r="BG29" t="inlineStr"/>
+      <c r="BH29" t="inlineStr"/>
+      <c r="BI29" t="inlineStr"/>
+      <c r="BJ29" t="inlineStr"/>
+      <c r="BK29" t="inlineStr"/>
+      <c r="BL29" t="inlineStr"/>
+      <c r="BM29" t="inlineStr"/>
+      <c r="BN29" t="inlineStr"/>
+      <c r="BO29" t="inlineStr"/>
+      <c r="BP29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>dGo94DZQ</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kherradji a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade des alpes
+  grenoble </t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>20068</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>E1wDrLsJ</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="n">
+        <v>6</v>
+      </c>
+      <c r="P30" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Ys1Pb7ws</t>
+        </is>
+      </c>
+      <c r="Y30" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="n">
+        <v>25.72727272727273</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>182.8181818181818</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>67.63636363636364</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1495454.545454545</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>71.36363636363636</v>
+      </c>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="inlineStr"/>
+      <c r="AQ30" t="n">
+        <v>29.66666666666667</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>185.1666666666667</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>1937500</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>24.8125</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>64.3125</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>958750</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>71.3125</v>
+      </c>
+      <c r="BC30" t="inlineStr"/>
+      <c r="BD30" t="inlineStr"/>
+      <c r="BE30" t="inlineStr"/>
+      <c r="BF30" t="inlineStr"/>
+      <c r="BG30" t="inlineStr"/>
+      <c r="BH30" t="inlineStr"/>
+      <c r="BI30" t="inlineStr"/>
+      <c r="BJ30" t="inlineStr"/>
+      <c r="BK30" t="inlineStr"/>
+      <c r="BL30" t="inlineStr"/>
+      <c r="BM30" t="inlineStr"/>
+      <c r="BN30" t="inlineStr"/>
+      <c r="BO30" t="inlineStr"/>
+      <c r="BP30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
+++ b/data/france/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP30"/>
+  <dimension ref="A1:BP35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,28 +772,30 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
+          <t>ObHze1pe</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45528.58333333334</v>
+        <v>45529.5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">kherradji a 
+          <t xml:space="preserve">angoula g 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade pierre mauroy
-  villeneuve d ascq </t>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>50186</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>35322</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30389</v>
+      </c>
       <c r="G2" t="n">
         <v>2</v>
       </c>
@@ -802,54 +804,54 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1.24</v>
+        <v>1.72</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6</v>
+        <v>1.61</v>
       </c>
       <c r="M2" t="n">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="N2" t="n">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="O2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q2" t="n">
         <v>6</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
       </c>
       <c r="T2" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
-          <t>nVS1TlC4</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>6FKPxxgf</t>
+          <t>OpNm82MB</t>
         </is>
       </c>
       <c r="Y2" t="n">
@@ -866,208 +868,206 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>22.625</v>
+        <v>23.9</v>
       </c>
       <c r="AF2" t="n">
-        <v>181.75</v>
+        <v>181.3</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.375</v>
+        <v>1.4</v>
       </c>
       <c r="AH2" t="n">
-        <v>74.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="AI2" t="n">
-        <v>11625000</v>
+        <v>5490000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>81.5</v>
+        <v>77</v>
       </c>
       <c r="AK2" t="n">
-        <v>25.1</v>
+        <v>26.25</v>
       </c>
       <c r="AL2" t="n">
-        <v>185.4</v>
+        <v>182.25</v>
       </c>
       <c r="AM2" t="n">
         <v>1</v>
       </c>
       <c r="AN2" t="n">
-        <v>67.3</v>
+        <v>69.125</v>
       </c>
       <c r="AO2" t="n">
-        <v>1507500</v>
+        <v>1834375</v>
       </c>
       <c r="AP2" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AQ2" t="n">
-        <v>25.07142857142857</v>
+        <v>26.21428571428572</v>
       </c>
       <c r="AR2" t="n">
-        <v>179.3571428571429</v>
+        <v>183</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.357142857142857</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="AT2" t="n">
-        <v>73</v>
+        <v>71.78571428571429</v>
       </c>
       <c r="AU2" t="n">
-        <v>6525000</v>
+        <v>3857142.857142857</v>
       </c>
       <c r="AV2" t="n">
-        <v>78.64285714285714</v>
+        <v>73.92857142857143</v>
       </c>
       <c r="AW2" t="n">
-        <v>25</v>
+        <v>23.90909090909091</v>
       </c>
       <c r="AX2" t="n">
-        <v>181.1739130434783</v>
+        <v>181.2727272727273</v>
       </c>
       <c r="AY2" t="n">
         <v>1</v>
       </c>
       <c r="AZ2" t="n">
-        <v>66.34782608695652</v>
+        <v>64.27272727272727</v>
       </c>
       <c r="BA2" t="n">
-        <v>1292391.304347826</v>
+        <v>1077272.727272727</v>
       </c>
       <c r="BB2" t="n">
-        <v>71.95652173913044</v>
+        <v>71.18181818181819</v>
       </c>
       <c r="BC2" t="n">
-        <v>27.33333333333333</v>
+        <v>25.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>178</v>
+        <v>177.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.666666666666667</v>
+        <v>1.25</v>
       </c>
       <c r="BF2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BG2" t="n">
-        <v>461</v>
+        <v>280</v>
       </c>
       <c r="BH2" t="n">
-        <v>66800000</v>
+        <v>10425000</v>
       </c>
       <c r="BI2" t="n">
-        <v>471</v>
+        <v>293</v>
       </c>
       <c r="BJ2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BK2" t="n">
-        <v>176</v>
+        <v>181.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1</v>
       </c>
       <c r="BM2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BN2" t="n">
-        <v>131</v>
+        <v>322</v>
       </c>
       <c r="BO2" t="n">
-        <v>2325000</v>
+        <v>6050000</v>
       </c>
       <c r="BP2" t="n">
-        <v>144</v>
+        <v>363</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
+          <t>8nivFMyR</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45528.5</v>
+        <v>45529.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">frappart s 
+          <t xml:space="preserve">dechepy b 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">parc olympique lyonnais
-  lyon </t>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>59186</v>
-      </c>
-      <c r="F3" t="n">
-        <v>54392</v>
-      </c>
+        <v>36178</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.44</v>
+        <v>1.27</v>
       </c>
       <c r="L3" t="n">
-        <v>2.82</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="N3" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="P3" t="n">
         <v>15</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T3" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
-          <t>YHU1oFVQ</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>CWxpUrtf</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="Y3" t="n">
@@ -1082,164 +1082,170 @@
       <c r="AB3" t="n">
         <v>20242025</v>
       </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>25</v>
+        <v>23.11111111111111</v>
       </c>
       <c r="AF3" t="n">
-        <v>179.7777777777778</v>
+        <v>183.2222222222222</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.666666666666667</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="AH3" t="n">
-        <v>75.66666666666667</v>
+        <v>74</v>
       </c>
       <c r="AI3" t="n">
-        <v>10300000</v>
+        <v>10166666.66666667</v>
       </c>
       <c r="AJ3" t="n">
-        <v>79.77777777777777</v>
+        <v>79.88888888888889</v>
       </c>
       <c r="AK3" t="n">
-        <v>23.9</v>
+        <v>23.22222222222222</v>
       </c>
       <c r="AL3" t="n">
-        <v>183.4</v>
+        <v>180.6666666666667</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.4</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="AN3" t="n">
-        <v>75.90000000000001</v>
+        <v>72.66666666666667</v>
       </c>
       <c r="AO3" t="n">
-        <v>11600000</v>
+        <v>5355555.555555556</v>
       </c>
       <c r="AP3" t="n">
-        <v>80.8</v>
+        <v>78.22222222222223</v>
       </c>
       <c r="AQ3" t="n">
-        <v>24.95652173913043</v>
+        <v>22.3125</v>
       </c>
       <c r="AR3" t="n">
-        <v>180.7391304347826</v>
+        <v>180.5625</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.739130434782609</v>
+        <v>1</v>
       </c>
       <c r="AT3" t="n">
-        <v>74.39130434782609</v>
+        <v>72.625</v>
       </c>
       <c r="AU3" t="n">
-        <v>7004347.826086956</v>
+        <v>5893750</v>
       </c>
       <c r="AV3" t="n">
-        <v>79.47826086956522</v>
+        <v>78.4375</v>
       </c>
       <c r="AW3" t="n">
-        <v>21.16666666666667</v>
+        <v>24.0625</v>
       </c>
       <c r="AX3" t="n">
-        <v>183.1666666666667</v>
+        <v>179.25</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.222222222222222</v>
+        <v>1</v>
       </c>
       <c r="AZ3" t="n">
-        <v>73.72222222222223</v>
+        <v>70.375</v>
       </c>
       <c r="BA3" t="n">
-        <v>11236111.11111111</v>
+        <v>2862500</v>
       </c>
       <c r="BB3" t="n">
-        <v>82</v>
-      </c>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="n">
-        <v>18</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>173</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>66</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>2200000</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>82</v>
-      </c>
+        <v>75.875</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>179</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>308</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>52500000</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>317</v>
+      </c>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
+      <c r="BO3" t="inlineStr"/>
+      <c r="BP3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2yXIHV57</t>
+          <t>xrJSdNFr</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45528.39583333334</v>
+        <v>45529.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">benchabane f 
+          <t xml:space="preserve">wattellier e 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade du moustoir
-  lorient </t>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>16787</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>26109</v>
+      </c>
+      <c r="F4" t="n">
+        <v>19026</v>
+      </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>jgNAYRGi</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>UgPj1p1N</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.34</v>
+      </c>
       <c r="M4" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="N4" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="O4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="P4" t="n">
         <v>13</v>
@@ -1248,35 +1254,31 @@
         <v>5</v>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T4" t="n">
-        <v>10</v>
-      </c>
-      <c r="U4" t="n">
-        <v>6</v>
-      </c>
-      <c r="V4" t="n">
-        <v>5</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Cp0gM1r4</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>WrQARdPN</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
       <c r="Y4" t="n">
         <v>55</v>
       </c>
       <c r="Z4" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1286,81 +1288,85 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr"/>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
       <c r="AE4" t="n">
-        <v>24.44444444444444</v>
+        <v>21.11111111111111</v>
       </c>
       <c r="AF4" t="n">
-        <v>178.1111111111111</v>
+        <v>184.5555555555555</v>
       </c>
       <c r="AG4" t="n">
         <v>1</v>
       </c>
       <c r="AH4" t="n">
-        <v>71.77777777777777</v>
+        <v>70.55555555555556</v>
       </c>
       <c r="AI4" t="n">
-        <v>4622222.222222222</v>
+        <v>4291666.666666667</v>
       </c>
       <c r="AJ4" t="n">
-        <v>77.11111111111111</v>
+        <v>80.22222222222223</v>
       </c>
       <c r="AK4" t="n">
-        <v>26</v>
+        <v>24.875</v>
       </c>
       <c r="AL4" t="n">
-        <v>182.6363636363636</v>
+        <v>180.25</v>
       </c>
       <c r="AM4" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="AN4" t="n">
-        <v>66.72727272727273</v>
+        <v>75.25</v>
       </c>
       <c r="AO4" t="n">
-        <v>1343181.818181818</v>
+        <v>8725000</v>
       </c>
       <c r="AP4" t="n">
-        <v>70</v>
+        <v>79.375</v>
       </c>
       <c r="AQ4" t="n">
-        <v>20.92857142857143</v>
+        <v>19.84615384615385</v>
       </c>
       <c r="AR4" t="n">
-        <v>178.5714285714286</v>
+        <v>183.0769230769231</v>
       </c>
       <c r="AS4" t="n">
         <v>1</v>
       </c>
       <c r="AT4" t="n">
-        <v>68.28571428571429</v>
+        <v>69.46153846153847</v>
       </c>
       <c r="AU4" t="n">
-        <v>2466071.428571429</v>
+        <v>3638461.538461538</v>
       </c>
       <c r="AV4" t="n">
-        <v>78.42857142857143</v>
+        <v>80.84615384615384</v>
       </c>
       <c r="AW4" t="n">
-        <v>26.38461538461538</v>
+        <v>23.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>184.3076923076923</v>
+        <v>180.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.153846153846154</v>
+        <v>1.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>66.38461538461539</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="BA4" t="n">
-        <v>1365384.615384615</v>
+        <v>7865000</v>
       </c>
       <c r="BB4" t="n">
-        <v>71.69230769230769</v>
+        <v>78.3</v>
       </c>
       <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="inlineStr"/>
@@ -1369,95 +1375,111 @@
       <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr"/>
-      <c r="BO4" t="inlineStr"/>
-      <c r="BP4" t="inlineStr"/>
+      <c r="BJ4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>189</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>72</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ppvl45N8</t>
+          <t>OCd990al</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45527.65625</v>
+        <v>45529.41666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">bollengier m 
+          <t xml:space="preserve">pignard j 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">parc des princes
-  paris </t>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>48229</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>38223</v>
+      </c>
+      <c r="F5" t="n">
+        <v>37435</v>
+      </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>2.94</v>
+        <v>1.95</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="M5" t="n">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="N5" t="n">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="O5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>11</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>8</v>
+      </c>
+      <c r="T5" t="n">
         <v>6</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>10</v>
-      </c>
-      <c r="R5" t="n">
-        <v>3</v>
-      </c>
-      <c r="S5" t="n">
-        <v>9</v>
-      </c>
-      <c r="T5" t="n">
-        <v>16</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
-          <t>8MdrBIUb</t>
+          <t>K6b7RoBp</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>vVQcGxl1</t>
+          <t>0tIbS515</t>
         </is>
       </c>
       <c r="Y5" t="n">
@@ -1472,203 +1494,217 @@
       <c r="AB5" t="n">
         <v>20242025</v>
       </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>182.8</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>76</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>12940000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>79.8</v>
+      </c>
       <c r="AK5" t="n">
-        <v>26.45454545454545</v>
+        <v>27.9</v>
       </c>
       <c r="AL5" t="n">
-        <v>180.2727272727273</v>
+        <v>179.8</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.454545454545455</v>
+        <v>1.4</v>
       </c>
       <c r="AN5" t="n">
-        <v>73.90909090909091</v>
+        <v>74.3</v>
       </c>
       <c r="AO5" t="n">
-        <v>5527272.727272728</v>
+        <v>6200000</v>
       </c>
       <c r="AP5" t="n">
-        <v>77.27272727272727</v>
+        <v>75.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>22.2</v>
+        <v>24.55</v>
       </c>
       <c r="AR5" t="n">
-        <v>184</v>
+        <v>181.7</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.866666666666667</v>
+        <v>1.3</v>
       </c>
       <c r="AT5" t="n">
-        <v>77.93333333333334</v>
+        <v>74.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>27520000</v>
+        <v>7215000</v>
       </c>
       <c r="AV5" t="n">
-        <v>84.33333333333333</v>
+        <v>78.05</v>
       </c>
       <c r="AW5" t="n">
-        <v>25.08333333333333</v>
+        <v>24</v>
       </c>
       <c r="AX5" t="n">
-        <v>181.75</v>
+        <v>181.6666666666667</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.25</v>
+        <v>1.133333333333333</v>
       </c>
       <c r="AZ5" t="n">
-        <v>71.33333333333333</v>
+        <v>69.53333333333333</v>
       </c>
       <c r="BA5" t="n">
-        <v>5383333.333333333</v>
+        <v>3973333.333333333</v>
       </c>
       <c r="BB5" t="n">
-        <v>76.33333333333333</v>
+        <v>74.66666666666667</v>
       </c>
       <c r="BC5" t="n">
-        <v>27.71428571428572</v>
+        <v>25</v>
       </c>
       <c r="BD5" t="n">
-        <v>183.7142857142857</v>
+        <v>179</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.571428571428572</v>
+        <v>1</v>
       </c>
       <c r="BF5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BG5" t="n">
-        <v>563</v>
+        <v>298</v>
       </c>
       <c r="BH5" t="n">
-        <v>162500000</v>
+        <v>28600000</v>
       </c>
       <c r="BI5" t="n">
-        <v>568</v>
+        <v>310</v>
       </c>
       <c r="BJ5" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="BK5" t="n">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="BL5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM5" t="n">
         <v>1</v>
       </c>
       <c r="BN5" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="BO5" t="n">
-        <v>3500000</v>
+        <v>11500000</v>
       </c>
       <c r="BP5" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4rrRVcF7</t>
+          <t>KQAqguF7</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45527.625</v>
+        <v>45528.66666666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">chapapria r 
+          <t xml:space="preserve">batta f 
   fra </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de l aube
-  troyes </t>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>20420</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
+        <v>42000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>16958</v>
+      </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>fsfAHubD</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>IRuMRua1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.24</v>
+      </c>
       <c r="M6" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="N6" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="O6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="P6" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T6" t="n">
-        <v>13</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
-      <c r="V6" t="n">
-        <v>11</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
-          <t>4vG8dmrf</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>4G9MhScS</t>
+          <t>dWZTBmVT</t>
         </is>
       </c>
       <c r="Y6" t="n">
         <v>55</v>
       </c>
       <c r="Z6" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1678,77 +1714,65 @@
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="n">
-        <v>24.22222222222222</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>177.7777777777778</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>64.66666666666667</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1072222.222222222</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>70.66666666666667</v>
-      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="n">
-        <v>24.375</v>
+        <v>24.2</v>
       </c>
       <c r="AL6" t="n">
-        <v>180.625</v>
+        <v>186.9</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.125</v>
+        <v>1</v>
       </c>
       <c r="AN6" t="n">
-        <v>67.5</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="AO6" t="n">
-        <v>1553125</v>
+        <v>3020000</v>
       </c>
       <c r="AP6" t="n">
-        <v>74</v>
+        <v>75.8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>27.05882352941176</v>
+        <v>25.23529411764706</v>
       </c>
       <c r="AR6" t="n">
-        <v>179.3529411764706</v>
+        <v>180.1764705882353</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.176470588235294</v>
+        <v>1</v>
       </c>
       <c r="AT6" t="n">
-        <v>67.35294117647059</v>
+        <v>66.47058823529412</v>
       </c>
       <c r="AU6" t="n">
-        <v>1388235.294117647</v>
+        <v>1260294.117647059</v>
       </c>
       <c r="AV6" t="n">
-        <v>70.70588235294117</v>
+        <v>71.94117647058823</v>
       </c>
       <c r="AW6" t="n">
-        <v>23</v>
+        <v>24.31818181818182</v>
       </c>
       <c r="AX6" t="n">
-        <v>178.625</v>
+        <v>180.5</v>
       </c>
       <c r="AY6" t="n">
         <v>1</v>
       </c>
       <c r="AZ6" t="n">
-        <v>65.625</v>
+        <v>69.40909090909091</v>
       </c>
       <c r="BA6" t="n">
-        <v>1637500</v>
+        <v>2295454.545454545</v>
       </c>
       <c r="BB6" t="n">
-        <v>72.875</v>
+        <v>73.54545454545455</v>
       </c>
       <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="inlineStr"/>
@@ -1757,102 +1781,118 @@
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr"/>
-      <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="inlineStr"/>
-      <c r="BO6" t="inlineStr"/>
-      <c r="BP6" t="inlineStr"/>
+      <c r="BJ6" t="n">
+        <v>19</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>188</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>64</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>UsP4uZcE</t>
+          <t>CKcVGr7E</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45527.625</v>
+        <v>45528.58333333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">landry r 
+          <t xml:space="preserve">kherradji a 
   fra </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade paul lignon
-  rodez </t>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5955</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
+        <v>50186</v>
+      </c>
+      <c r="F7" t="n">
+        <v>36906</v>
+      </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0pOdQOCg</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4v0yqlWc</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.6</v>
+      </c>
       <c r="M7" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="N7" t="n">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="O7" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="P7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T7" t="n">
-        <v>13</v>
-      </c>
-      <c r="U7" t="n">
-        <v>9</v>
-      </c>
-      <c r="V7" t="n">
-        <v>11</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
-          <t>OQuqpG7i</t>
+          <t>nVS1TlC4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>h89kUbu5</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
       <c r="Y7" t="n">
         <v>55</v>
       </c>
       <c r="Z7" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1860,130 +1900,176 @@
       <c r="AB7" t="n">
         <v>20242025</v>
       </c>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="n">
+        <v>22.625</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>11625000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>81.5</v>
+      </c>
       <c r="AK7" t="n">
-        <v>26.81818181818182</v>
+        <v>25.1</v>
       </c>
       <c r="AL7" t="n">
-        <v>176.8181818181818</v>
+        <v>185.4</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.090909090909091</v>
+        <v>1</v>
       </c>
       <c r="AN7" t="n">
-        <v>70.54545454545455</v>
+        <v>67.3</v>
       </c>
       <c r="AO7" t="n">
-        <v>1861363.636363636</v>
+        <v>1507500</v>
       </c>
       <c r="AP7" t="n">
-        <v>73.90909090909091</v>
+        <v>73</v>
       </c>
       <c r="AQ7" t="n">
-        <v>20.9375</v>
+        <v>25.07142857142857</v>
       </c>
       <c r="AR7" t="n">
-        <v>182.75</v>
+        <v>179.3571428571429</v>
       </c>
       <c r="AS7" t="n">
-        <v>1</v>
+        <v>1.357142857142857</v>
       </c>
       <c r="AT7" t="n">
-        <v>62.3125</v>
+        <v>73</v>
       </c>
       <c r="AU7" t="n">
-        <v>829687.5</v>
+        <v>6525000</v>
       </c>
       <c r="AV7" t="n">
-        <v>72.4375</v>
+        <v>78.64285714285714</v>
       </c>
       <c r="AW7" t="n">
-        <v>20.375</v>
+        <v>25</v>
       </c>
       <c r="AX7" t="n">
-        <v>181.25</v>
+        <v>181.1739130434783</v>
       </c>
       <c r="AY7" t="n">
         <v>1</v>
       </c>
       <c r="AZ7" t="n">
-        <v>65.75</v>
+        <v>66.34782608695652</v>
       </c>
       <c r="BA7" t="n">
-        <v>1696875</v>
+        <v>1292391.304347826</v>
       </c>
       <c r="BB7" t="n">
-        <v>77</v>
-      </c>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
-      <c r="BI7" t="inlineStr"/>
-      <c r="BJ7" t="inlineStr"/>
-      <c r="BK7" t="inlineStr"/>
-      <c r="BL7" t="inlineStr"/>
-      <c r="BM7" t="inlineStr"/>
-      <c r="BN7" t="inlineStr"/>
-      <c r="BO7" t="inlineStr"/>
-      <c r="BP7" t="inlineStr"/>
+        <v>71.95652173913044</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>178</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>461</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>66800000</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>471</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>23</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>176</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>131</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>2325000</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>144</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nsErYjjl</t>
+          <t>pSpI7vU0</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45527.625</v>
+        <v>45528.5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">leleu m 
+          <t xml:space="preserve">frappart s 
   fra </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">nouste camp
-  pau </t>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4031</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
+        <v>59186</v>
+      </c>
+      <c r="F8" t="n">
+        <v>54392</v>
+      </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6NOhR4cm</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>GjLn2QoH</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.82</v>
+      </c>
       <c r="M8" t="n">
         <v>32</v>
       </c>
@@ -1991,44 +2077,40 @@
         <v>68</v>
       </c>
       <c r="O8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
         <v>4</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T8" t="n">
-        <v>20</v>
-      </c>
-      <c r="U8" t="n">
-        <v>9</v>
-      </c>
-      <c r="V8" t="n">
-        <v>8</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
-          <t>fm0Qb28B</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Q9EVqFe4</t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
       <c r="Y8" t="n">
         <v>55</v>
       </c>
       <c r="Z8" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -2037,78 +2119,82 @@
         <v>20242025</v>
       </c>
       <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
       <c r="AE8" t="n">
-        <v>23.33333333333333</v>
+        <v>25</v>
       </c>
       <c r="AF8" t="n">
-        <v>185.3333333333333</v>
+        <v>179.7777777777778</v>
       </c>
       <c r="AG8" t="n">
-        <v>1</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AH8" t="n">
-        <v>64.88888888888889</v>
+        <v>75.66666666666667</v>
       </c>
       <c r="AI8" t="n">
-        <v>1066666.666666667</v>
+        <v>10300000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>73</v>
+        <v>79.77777777777777</v>
       </c>
       <c r="AK8" t="n">
-        <v>26.375</v>
+        <v>23.9</v>
       </c>
       <c r="AL8" t="n">
-        <v>180.5</v>
+        <v>183.4</v>
       </c>
       <c r="AM8" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AN8" t="n">
-        <v>68.25</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AO8" t="n">
-        <v>1643750</v>
+        <v>11600000</v>
       </c>
       <c r="AP8" t="n">
-        <v>73.25</v>
+        <v>80.8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>26.84615384615385</v>
+        <v>24.95652173913043</v>
       </c>
       <c r="AR8" t="n">
-        <v>181.3076923076923</v>
+        <v>180.7391304347826</v>
       </c>
       <c r="AS8" t="n">
-        <v>1</v>
+        <v>1.739130434782609</v>
       </c>
       <c r="AT8" t="n">
-        <v>65.46153846153847</v>
+        <v>74.39130434782609</v>
       </c>
       <c r="AU8" t="n">
-        <v>786538.4615384615</v>
+        <v>7004347.826086956</v>
       </c>
       <c r="AV8" t="n">
-        <v>70.92307692307692</v>
+        <v>79.47826086956522</v>
       </c>
       <c r="AW8" t="n">
-        <v>20.23076923076923</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="AX8" t="n">
-        <v>181.4615384615385</v>
+        <v>183.1666666666667</v>
       </c>
       <c r="AY8" t="n">
-        <v>1</v>
+        <v>1.222222222222222</v>
       </c>
       <c r="AZ8" t="n">
-        <v>62.53846153846154</v>
+        <v>73.72222222222223</v>
       </c>
       <c r="BA8" t="n">
-        <v>875000</v>
+        <v>11236111.11111111</v>
       </c>
       <c r="BB8" t="n">
-        <v>75.38461538461539</v>
+        <v>82</v>
       </c>
       <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="inlineStr"/>
@@ -2117,95 +2203,109 @@
       <c r="BG8" t="inlineStr"/>
       <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="inlineStr"/>
-      <c r="BJ8" t="inlineStr"/>
-      <c r="BK8" t="inlineStr"/>
-      <c r="BL8" t="inlineStr"/>
-      <c r="BM8" t="inlineStr"/>
-      <c r="BN8" t="inlineStr"/>
-      <c r="BO8" t="inlineStr"/>
-      <c r="BP8" t="inlineStr"/>
+      <c r="BJ8" t="n">
+        <v>18</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>173</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>66</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>WUmnhCsK</t>
+          <t>2yXIHV57</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45527.625</v>
+        <v>45528.39583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">taleb a 
+          <t xml:space="preserve">benchabane f 
   fra </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la licorne
-  amiens </t>
+          <t xml:space="preserve">stade du moustoir
+  lorient </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>12097</v>
+        <v>16787</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0OEHEprs</t>
+          <t>jgNAYRGi</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>tAAobNse</t>
+          <t>UgPj1p1N</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="N9" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="O9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P9" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>12</v>
+      </c>
+      <c r="T9" t="n">
+        <v>10</v>
+      </c>
+      <c r="U9" t="n">
         <v>6</v>
       </c>
-      <c r="Q9" t="n">
-        <v>4</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2</v>
-      </c>
-      <c r="S9" t="n">
-        <v>8</v>
-      </c>
-      <c r="T9" t="n">
-        <v>17</v>
-      </c>
-      <c r="U9" t="n">
-        <v>14</v>
-      </c>
       <c r="V9" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>zB2j3YvM</t>
+          <t>Cp0gM1r4</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>lb31RXzP</t>
+          <t>WrQARdPN</t>
         </is>
       </c>
       <c r="Y9" t="n">
@@ -2220,67 +2320,83 @@
       <c r="AB9" t="n">
         <v>20242025</v>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="n">
-        <v>24.11111111111111</v>
+        <v>24.44444444444444</v>
       </c>
       <c r="AF9" t="n">
-        <v>178.8888888888889</v>
+        <v>178.1111111111111</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.111111111111111</v>
+        <v>1</v>
       </c>
       <c r="AH9" t="n">
-        <v>67.33333333333333</v>
+        <v>71.77777777777777</v>
       </c>
       <c r="AI9" t="n">
-        <v>1747222.222222222</v>
+        <v>4622222.222222222</v>
       </c>
       <c r="AJ9" t="n">
-        <v>71.66666666666667</v>
-      </c>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
+        <v>77.11111111111111</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>182.6363636363636</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>66.72727272727273</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1343181.818181818</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>70</v>
+      </c>
       <c r="AQ9" t="n">
-        <v>26.17647058823529</v>
+        <v>20.92857142857143</v>
       </c>
       <c r="AR9" t="n">
-        <v>177.1764705882353</v>
+        <v>178.5714285714286</v>
       </c>
       <c r="AS9" t="n">
         <v>1</v>
       </c>
       <c r="AT9" t="n">
-        <v>66.17647058823529</v>
+        <v>68.28571428571429</v>
       </c>
       <c r="AU9" t="n">
-        <v>1182352.941176471</v>
+        <v>2466071.428571429</v>
       </c>
       <c r="AV9" t="n">
-        <v>69.23529411764706</v>
+        <v>78.42857142857143</v>
       </c>
       <c r="AW9" t="n">
-        <v>22.25</v>
+        <v>26.38461538461538</v>
       </c>
       <c r="AX9" t="n">
-        <v>179.5833333333333</v>
+        <v>184.3076923076923</v>
       </c>
       <c r="AY9" t="n">
-        <v>1</v>
+        <v>1.153846153846154</v>
       </c>
       <c r="AZ9" t="n">
-        <v>63.83333333333334</v>
+        <v>66.38461538461539</v>
       </c>
       <c r="BA9" t="n">
-        <v>931250</v>
+        <v>1365384.615384615</v>
       </c>
       <c r="BB9" t="n">
-        <v>72.91666666666667</v>
+        <v>71.69230769230769</v>
       </c>
       <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="inlineStr"/>
@@ -2300,91 +2416,93 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>MaSQpUZg</t>
+          <t>ppvl45N8</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45527.625</v>
+        <v>45527.65625</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">thual o 
+          <t xml:space="preserve">bollengier m 
   fra </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade francis le basser
-  laval </t>
+          <t xml:space="preserve">parc des princes
+  paris </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>11017</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
+        <v>48229</v>
+      </c>
+      <c r="F10" t="n">
+        <v>46000</v>
+      </c>
       <c r="G10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>E1wDrLsJ</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>QDfKl36E</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.4</v>
+      </c>
       <c r="M10" t="n">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="N10" t="n">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="O10" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="P10" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Q10" t="n">
+        <v>10</v>
+      </c>
+      <c r="R10" t="n">
         <v>3</v>
       </c>
-      <c r="R10" t="n">
-        <v>4</v>
-      </c>
       <c r="S10" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="T10" t="n">
         <v>16</v>
       </c>
-      <c r="U10" t="n">
-        <v>11</v>
-      </c>
-      <c r="V10" t="n">
-        <v>19</v>
-      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Ys1Pb7ws</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>QNSJnsB5</t>
+          <t>vVQcGxl1</t>
         </is>
       </c>
       <c r="Y10" t="n">
         <v>55</v>
       </c>
       <c r="Z10" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -2393,98 +2511,118 @@
         <v>20242025</v>
       </c>
       <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>181.125</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>66.75</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1281250</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>72.625</v>
-      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="n">
-        <v>24.11111111111111</v>
+        <v>26.45454545454545</v>
       </c>
       <c r="AL10" t="n">
-        <v>179.8888888888889</v>
+        <v>180.2727272727273</v>
       </c>
       <c r="AM10" t="n">
-        <v>1</v>
+        <v>1.454545454545455</v>
       </c>
       <c r="AN10" t="n">
-        <v>65.33333333333333</v>
+        <v>73.90909090909091</v>
       </c>
       <c r="AO10" t="n">
-        <v>1077777.777777778</v>
+        <v>5527272.727272728</v>
       </c>
       <c r="AP10" t="n">
-        <v>70.44444444444444</v>
+        <v>77.27272727272727</v>
       </c>
       <c r="AQ10" t="n">
-        <v>27.25</v>
+        <v>22.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>177.75</v>
+        <v>184</v>
       </c>
       <c r="AS10" t="n">
-        <v>1</v>
+        <v>1.866666666666667</v>
       </c>
       <c r="AT10" t="n">
-        <v>64.58333333333333</v>
+        <v>77.93333333333334</v>
       </c>
       <c r="AU10" t="n">
-        <v>832500</v>
+        <v>27520000</v>
       </c>
       <c r="AV10" t="n">
-        <v>71</v>
+        <v>84.33333333333333</v>
       </c>
       <c r="AW10" t="n">
-        <v>22.22222222222222</v>
+        <v>25.08333333333333</v>
       </c>
       <c r="AX10" t="n">
-        <v>180.7777777777778</v>
+        <v>181.75</v>
       </c>
       <c r="AY10" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AZ10" t="n">
-        <v>60.33333333333334</v>
+        <v>71.33333333333333</v>
       </c>
       <c r="BA10" t="n">
-        <v>686111.1111111111</v>
+        <v>5383333.333333333</v>
       </c>
       <c r="BB10" t="n">
-        <v>69.77777777777777</v>
-      </c>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
-      <c r="BI10" t="inlineStr"/>
-      <c r="BJ10" t="inlineStr"/>
-      <c r="BK10" t="inlineStr"/>
-      <c r="BL10" t="inlineStr"/>
-      <c r="BM10" t="inlineStr"/>
-      <c r="BN10" t="inlineStr"/>
-      <c r="BO10" t="inlineStr"/>
-      <c r="BP10" t="inlineStr"/>
+        <v>76.33333333333333</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>27.71428571428572</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>183.7142857142857</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>2.571428571428572</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>563</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>162500000</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>568</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>30</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>196</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>74</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>r97iWUK0</t>
+          <t>WUmnhCsK</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2492,76 +2630,78 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">lesage m 
+          <t xml:space="preserve">taleb a 
   fra </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade armand cesari
-  bastia </t>
+          <t xml:space="preserve">stade de la licorne
+  amiens </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>16048</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
+        <v>12097</v>
+      </c>
+      <c r="F11" t="n">
+        <v>608</v>
+      </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AZwK8L6R</t>
+          <t>0OEHEprs</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>lKkBAsxF</t>
+          <t>tAAobNse</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="N11" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="O11" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="P11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q11" t="n">
         <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T11" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="U11" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="V11" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>fo8nHfg4</t>
+          <t>zB2j3YvM</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>dS1CBple</t>
+          <t>lb31RXzP</t>
         </is>
       </c>
       <c r="Y11" t="n">
@@ -2578,65 +2718,65 @@
       </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>181.2</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>67.09999999999999</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1205000</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>71.09999999999999</v>
-      </c>
+      <c r="AE11" t="n">
+        <v>24.11111111111111</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>178.8888888888889</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>67.33333333333333</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1747222.222222222</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="n">
-        <v>24.5</v>
+        <v>26.17647058823529</v>
       </c>
       <c r="AR11" t="n">
-        <v>180.8571428571429</v>
+        <v>177.1764705882353</v>
       </c>
       <c r="AS11" t="n">
         <v>1</v>
       </c>
       <c r="AT11" t="n">
-        <v>63.78571428571428</v>
+        <v>66.17647058823529</v>
       </c>
       <c r="AU11" t="n">
-        <v>832142.8571428572</v>
+        <v>1182352.941176471</v>
       </c>
       <c r="AV11" t="n">
-        <v>67.57142857142857</v>
+        <v>69.23529411764706</v>
       </c>
       <c r="AW11" t="n">
-        <v>24</v>
+        <v>22.25</v>
       </c>
       <c r="AX11" t="n">
-        <v>181.0666666666667</v>
+        <v>179.5833333333333</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AZ11" t="n">
-        <v>62.6</v>
+        <v>63.83333333333334</v>
       </c>
       <c r="BA11" t="n">
-        <v>728333.3333333334</v>
+        <v>931250</v>
       </c>
       <c r="BB11" t="n">
-        <v>71.53333333333333</v>
+        <v>72.91666666666667</v>
       </c>
       <c r="BC11" t="inlineStr"/>
       <c r="BD11" t="inlineStr"/>
@@ -2677,7 +2817,9 @@
       <c r="E12" t="n">
         <v>15660</v>
       </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>7640</v>
+      </c>
       <c r="G12" t="n">
         <v>2</v>
       </c>
@@ -2816,26 +2958,26 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>OA5YizjL</t>
+          <t>4rrRVcF7</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45523.65625</v>
+        <v>45527.625</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">thual o 
+          <t xml:space="preserve">chapapria r 
   fra </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade velodrome
-  marseille </t>
+          <t xml:space="preserve">stade de l aube
+  troyes </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>67394</v>
+        <v>20420</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
@@ -2846,54 +2988,54 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ADl76OZP</t>
+          <t>fsfAHubD</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>jgNAYRGi</t>
+          <t>IRuMRua1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="N13" t="n">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="P13" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T13" t="n">
         <v>13</v>
       </c>
       <c r="U13" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="V13" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>EwpPg8iH</t>
+          <t>4vG8dmrf</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Cp0gM1r4</t>
+          <t>4G9MhScS</t>
         </is>
       </c>
       <c r="Y13" t="n">
@@ -2909,58 +3051,78 @@
         <v>20242025</v>
       </c>
       <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="n">
+        <v>24.22222222222222</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>177.7777777777778</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>64.66666666666667</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1072222.222222222</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>70.66666666666667</v>
+      </c>
       <c r="AK13" t="n">
-        <v>24.44444444444444</v>
+        <v>24.375</v>
       </c>
       <c r="AL13" t="n">
-        <v>178.1111111111111</v>
+        <v>180.625</v>
       </c>
       <c r="AM13" t="n">
-        <v>1</v>
+        <v>1.125</v>
       </c>
       <c r="AN13" t="n">
-        <v>71.77777777777777</v>
+        <v>67.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>4622222.222222222</v>
+        <v>1553125</v>
       </c>
       <c r="AP13" t="n">
-        <v>77.11111111111111</v>
-      </c>
-      <c r="AQ13" t="inlineStr"/>
-      <c r="AR13" t="inlineStr"/>
-      <c r="AS13" t="inlineStr"/>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AU13" t="inlineStr"/>
-      <c r="AV13" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>27.05882352941176</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>179.3529411764706</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.176470588235294</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>67.35294117647059</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1388235.294117647</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>70.70588235294117</v>
+      </c>
       <c r="AW13" t="n">
-        <v>21.73333333333333</v>
+        <v>23</v>
       </c>
       <c r="AX13" t="n">
-        <v>177.4</v>
+        <v>178.625</v>
       </c>
       <c r="AY13" t="n">
         <v>1</v>
       </c>
       <c r="AZ13" t="n">
-        <v>69.06666666666666</v>
+        <v>65.625</v>
       </c>
       <c r="BA13" t="n">
-        <v>2781666.666666667</v>
+        <v>1637500</v>
       </c>
       <c r="BB13" t="n">
-        <v>77.53333333333333</v>
+        <v>72.875</v>
       </c>
       <c r="BC13" t="inlineStr"/>
       <c r="BD13" t="inlineStr"/>
@@ -2980,84 +3142,86 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>lEQmcVR0</t>
+          <t>UsP4uZcE</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45523.65625</v>
+        <v>45527.625</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">petit a 
+          <t xml:space="preserve">landry r 
   fra </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade saint symphorien
-  metz </t>
+          <t xml:space="preserve">stade paul lignon
+  rodez </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>28786</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
+        <v>5955</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4901</v>
+      </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t>0pOdQOCg</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>4v0yqlWc</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>AZwK8L6R</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="N14" t="n">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="O14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S14" t="n">
+        <v>14</v>
+      </c>
+      <c r="T14" t="n">
         <v>13</v>
       </c>
-      <c r="T14" t="n">
-        <v>15</v>
-      </c>
       <c r="U14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="V14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>OQuqpG7i</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
           <t>h89kUbu5</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>fo8nHfg4</t>
         </is>
       </c>
       <c r="Y14" t="n">
@@ -3072,83 +3236,71 @@
       <c r="AB14" t="n">
         <v>20242025</v>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr">
         <is>
           <t>nP6UzIU1</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="n">
-        <v>24.90909090909091</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>177.8181818181818</v>
-      </c>
-      <c r="AG14" t="n">
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="n">
+        <v>26.81818181818182</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>176.8181818181818</v>
+      </c>
+      <c r="AM14" t="n">
         <v>1.090909090909091</v>
       </c>
-      <c r="AH14" t="n">
-        <v>68.90909090909091</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1677272.727272727</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>75.27272727272727</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>25.375</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>179.625</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1</v>
-      </c>
       <c r="AN14" t="n">
-        <v>63.625</v>
+        <v>70.54545454545455</v>
       </c>
       <c r="AO14" t="n">
-        <v>723125</v>
+        <v>1861363.636363636</v>
       </c>
       <c r="AP14" t="n">
-        <v>68.375</v>
+        <v>73.90909090909091</v>
       </c>
       <c r="AQ14" t="n">
-        <v>24</v>
+        <v>20.9375</v>
       </c>
       <c r="AR14" t="n">
-        <v>181.0909090909091</v>
+        <v>182.75</v>
       </c>
       <c r="AS14" t="n">
         <v>1</v>
       </c>
       <c r="AT14" t="n">
-        <v>67.81818181818181</v>
+        <v>62.3125</v>
       </c>
       <c r="AU14" t="n">
-        <v>1718181.818181818</v>
+        <v>829687.5</v>
       </c>
       <c r="AV14" t="n">
-        <v>75</v>
+        <v>72.4375</v>
       </c>
       <c r="AW14" t="n">
-        <v>23.25</v>
+        <v>20.375</v>
       </c>
       <c r="AX14" t="n">
-        <v>180</v>
+        <v>181.25</v>
       </c>
       <c r="AY14" t="n">
         <v>1</v>
       </c>
       <c r="AZ14" t="n">
-        <v>61.5</v>
+        <v>65.75</v>
       </c>
       <c r="BA14" t="n">
-        <v>679166.6666666666</v>
+        <v>1696875</v>
       </c>
       <c r="BB14" t="n">
-        <v>68.16666666666667</v>
+        <v>77</v>
       </c>
       <c r="BC14" t="inlineStr"/>
       <c r="BD14" t="inlineStr"/>
@@ -3168,95 +3320,93 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>nsErYjjl</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45522.65625</v>
+        <v>45527.625</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">millot b 
+          <t xml:space="preserve">leleu m 
   fra </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">roazhon park
-  rennes </t>
+          <t xml:space="preserve">nouste camp
+  pau </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>29778</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
+        <v>4031</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3033</v>
+      </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>6NOhR4cm</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.64</v>
-      </c>
+          <t>GjLn2QoH</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="N15" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="O15" t="n">
+        <v>7</v>
+      </c>
+      <c r="P15" t="n">
         <v>22</v>
       </c>
-      <c r="P15" t="n">
-        <v>16</v>
-      </c>
       <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>12</v>
+      </c>
+      <c r="T15" t="n">
+        <v>20</v>
+      </c>
+      <c r="U15" t="n">
+        <v>9</v>
+      </c>
+      <c r="V15" t="n">
         <v>8</v>
       </c>
-      <c r="R15" t="n">
-        <v>2</v>
-      </c>
-      <c r="S15" t="n">
-        <v>13</v>
-      </c>
-      <c r="T15" t="n">
-        <v>12</v>
-      </c>
-      <c r="U15" t="n">
-        <v>8</v>
-      </c>
-      <c r="V15" t="n">
-        <v>11</v>
-      </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>pCcFFE7M</t>
+          <t>fm0Qb28B</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>YHU1oFVQ</t>
+          <t>Q9EVqFe4</t>
         </is>
       </c>
       <c r="Y15" t="n">
         <v>55</v>
       </c>
       <c r="Z15" t="n">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -3264,153 +3414,121 @@
       <c r="AB15" t="n">
         <v>20242025</v>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
+      <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="n">
-        <v>25.875</v>
+        <v>23.33333333333333</v>
       </c>
       <c r="AF15" t="n">
+        <v>185.3333333333333</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>64.88888888888889</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1066666.666666667</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>73</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>26.375</v>
+      </c>
+      <c r="AL15" t="n">
         <v>180.5</v>
       </c>
-      <c r="AG15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>75.625</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>9475000</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>79.25</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>25.66666666666667</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>182.3333333333333</v>
-      </c>
       <c r="AM15" t="n">
-        <v>1.666666666666667</v>
+        <v>1</v>
       </c>
       <c r="AN15" t="n">
-        <v>76.33333333333333</v>
+        <v>68.25</v>
       </c>
       <c r="AO15" t="n">
-        <v>10111111.11111111</v>
+        <v>1643750</v>
       </c>
       <c r="AP15" t="n">
-        <v>80</v>
+        <v>73.25</v>
       </c>
       <c r="AQ15" t="n">
-        <v>24.23076923076923</v>
+        <v>26.84615384615385</v>
       </c>
       <c r="AR15" t="n">
-        <v>181.9230769230769</v>
+        <v>181.3076923076923</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.538461538461539</v>
+        <v>1</v>
       </c>
       <c r="AT15" t="n">
-        <v>73.07692307692308</v>
+        <v>65.46153846153847</v>
       </c>
       <c r="AU15" t="n">
-        <v>8578846.153846154</v>
+        <v>786538.4615384615</v>
       </c>
       <c r="AV15" t="n">
-        <v>77.53846153846153</v>
+        <v>70.92307692307692</v>
       </c>
       <c r="AW15" t="n">
-        <v>23.81818181818182</v>
+        <v>20.23076923076923</v>
       </c>
       <c r="AX15" t="n">
-        <v>179.5</v>
+        <v>181.4615384615385</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.681818181818182</v>
+        <v>1</v>
       </c>
       <c r="AZ15" t="n">
-        <v>73.18181818181819</v>
+        <v>62.53846153846154</v>
       </c>
       <c r="BA15" t="n">
-        <v>5522727.272727272</v>
+        <v>875000</v>
       </c>
       <c r="BB15" t="n">
-        <v>78.81818181818181</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>189</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>72</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>78</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>31</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>173.5</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>159</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>33000000</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>159</v>
-      </c>
+        <v>75.38461538461539</v>
+      </c>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="inlineStr"/>
+      <c r="BJ15" t="inlineStr"/>
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="inlineStr"/>
+      <c r="BM15" t="inlineStr"/>
+      <c r="BN15" t="inlineStr"/>
+      <c r="BO15" t="inlineStr"/>
+      <c r="BP15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>MaSQpUZg</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45522.5</v>
+        <v>45527.625</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">leonard t 
+          <t xml:space="preserve">thual o 
   fra </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
+          <t xml:space="preserve">stade francis le basser
+  laval </t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>18752</v>
+        <v>11017</v>
       </c>
       <c r="F16" t="n">
-        <v>14811</v>
+        <v>7282</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -3420,65 +3538,61 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>E1wDrLsJ</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.92</v>
-      </c>
+          <t>QDfKl36E</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="N16" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="P16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Q16" t="n">
         <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="T16" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="U16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V16" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>6FKPxxgf</t>
+          <t>Ys1Pb7ws</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>K6b7RoBp</t>
+          <t>QNSJnsB5</t>
         </is>
       </c>
       <c r="Y16" t="n">
         <v>55</v>
       </c>
       <c r="Z16" t="n">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -3487,220 +3601,184 @@
         <v>20242025</v>
       </c>
       <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="n">
-        <v>25.7</v>
+        <v>26.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>184.5</v>
+        <v>181.125</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AH16" t="n">
-        <v>68</v>
+        <v>66.75</v>
       </c>
       <c r="AI16" t="n">
-        <v>1587500</v>
+        <v>1281250</v>
       </c>
       <c r="AJ16" t="n">
-        <v>72.8</v>
+        <v>72.625</v>
       </c>
       <c r="AK16" t="n">
-        <v>27.63636363636364</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="AL16" t="n">
-        <v>179.8181818181818</v>
+        <v>179.8888888888889</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.454545454545455</v>
+        <v>1</v>
       </c>
       <c r="AN16" t="n">
-        <v>77</v>
+        <v>65.33333333333333</v>
       </c>
       <c r="AO16" t="n">
-        <v>12381818.18181818</v>
+        <v>1077777.777777778</v>
       </c>
       <c r="AP16" t="n">
-        <v>78.72727272727273</v>
+        <v>70.44444444444444</v>
       </c>
       <c r="AQ16" t="n">
-        <v>25.7</v>
+        <v>27.25</v>
       </c>
       <c r="AR16" t="n">
-        <v>183.9</v>
+        <v>177.75</v>
       </c>
       <c r="AS16" t="n">
         <v>1</v>
       </c>
       <c r="AT16" t="n">
-        <v>66.45</v>
+        <v>64.58333333333333</v>
       </c>
       <c r="AU16" t="n">
-        <v>1278750</v>
+        <v>832500</v>
       </c>
       <c r="AV16" t="n">
-        <v>71.84999999999999</v>
+        <v>71</v>
       </c>
       <c r="AW16" t="n">
-        <v>23.90909090909091</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="AX16" t="n">
-        <v>179.9545454545455</v>
+        <v>180.7777777777778</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.090909090909091</v>
+        <v>1</v>
       </c>
       <c r="AZ16" t="n">
-        <v>72.90909090909091</v>
+        <v>60.33333333333334</v>
       </c>
       <c r="BA16" t="n">
-        <v>6081818.181818182</v>
+        <v>686111.1111111111</v>
       </c>
       <c r="BB16" t="n">
-        <v>78.13636363636364</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>179.25</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>266</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>5725000</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>290</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>25</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>179</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>4</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>298</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>28600000</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>310</v>
-      </c>
+        <v>69.77777777777777</v>
+      </c>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="inlineStr"/>
+      <c r="BI16" t="inlineStr"/>
+      <c r="BJ16" t="inlineStr"/>
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="inlineStr"/>
+      <c r="BM16" t="inlineStr"/>
+      <c r="BN16" t="inlineStr"/>
+      <c r="BO16" t="inlineStr"/>
+      <c r="BP16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>r97iWUK0</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45522.5</v>
+        <v>45527.625</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">stinat j 
+          <t xml:space="preserve">lesage m 
   fra </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
+          <t xml:space="preserve">stade armand cesari
+  bastia </t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>33150</v>
+        <v>16048</v>
       </c>
       <c r="F17" t="n">
-        <v>25491</v>
+        <v>13500</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>AZwK8L6R</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.33</v>
-      </c>
+          <t>lKkBAsxF</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="N17" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="O17" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="P17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Q17" t="n">
+        <v>4</v>
+      </c>
+      <c r="R17" t="n">
         <v>3</v>
       </c>
-      <c r="R17" t="n">
-        <v>2</v>
-      </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T17" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="U17" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="V17" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>UapruDaf</t>
+          <t>fo8nHfg4</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>YTLwacK1</t>
+          <t>dS1CBple</t>
         </is>
       </c>
       <c r="Y17" t="n">
         <v>55</v>
       </c>
       <c r="Z17" t="n">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -3709,82 +3787,66 @@
         <v>20242025</v>
       </c>
       <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="AE17" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>181.1</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>5200000</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>78.7</v>
-      </c>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
       <c r="AK17" t="n">
-        <v>24.8</v>
+        <v>26.1</v>
       </c>
       <c r="AL17" t="n">
-        <v>182</v>
+        <v>181.2</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AN17" t="n">
-        <v>72.8</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="AO17" t="n">
-        <v>5310000</v>
+        <v>1205000</v>
       </c>
       <c r="AP17" t="n">
-        <v>76.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="AQ17" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>180.8571428571429</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>63.78571428571428</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>832142.8571428572</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>67.57142857142857</v>
+      </c>
+      <c r="AW17" t="n">
         <v>24</v>
       </c>
-      <c r="AR17" t="n">
-        <v>178.375</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>69.8125</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>2631250</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>75.4375</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>25.76470588235294</v>
-      </c>
       <c r="AX17" t="n">
-        <v>182.8235294117647</v>
+        <v>181.0666666666667</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.411764705882353</v>
+        <v>1.2</v>
       </c>
       <c r="AZ17" t="n">
-        <v>71.76470588235294</v>
+        <v>62.6</v>
       </c>
       <c r="BA17" t="n">
-        <v>3450000</v>
+        <v>728333.3333333334</v>
       </c>
       <c r="BB17" t="n">
-        <v>74.58823529411765</v>
+        <v>71.53333333333333</v>
       </c>
       <c r="BC17" t="inlineStr"/>
       <c r="BD17" t="inlineStr"/>
@@ -3804,29 +3866,29 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>lEQmcVR0</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45522.5</v>
+        <v>45523.65625</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">vernice m 
+          <t xml:space="preserve">petit a 
   fra </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la mosson
-  montpellier </t>
+          <t xml:space="preserve">stade saint symphorien
+  metz </t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>20484</v>
+        <v>28786</v>
       </c>
       <c r="F18" t="n">
-        <v>15706</v>
+        <v>18585</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -3836,65 +3898,61 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>4v0yqlWc</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.23</v>
-      </c>
+          <t>AZwK8L6R</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="N18" t="n">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="O18" t="n">
+        <v>18</v>
+      </c>
+      <c r="P18" t="n">
         <v>7</v>
-      </c>
-      <c r="P18" t="n">
-        <v>11</v>
       </c>
       <c r="Q18" t="n">
         <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="T18" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="U18" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="V18" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>vVQcGxl1</t>
+          <t>h89kUbu5</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>4fMAHvLm</t>
+          <t>fo8nHfg4</t>
         </is>
       </c>
       <c r="Y18" t="n">
         <v>55</v>
       </c>
       <c r="Z18" t="n">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -3904,223 +3962,187 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>4v0yqlWc</t>
-        </is>
-      </c>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="n">
-        <v>25.6</v>
+        <v>24.90909090909091</v>
       </c>
       <c r="AF18" t="n">
-        <v>180.5</v>
+        <v>177.8181818181818</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.4</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="AH18" t="n">
-        <v>74.09999999999999</v>
+        <v>68.90909090909091</v>
       </c>
       <c r="AI18" t="n">
-        <v>6330000</v>
+        <v>1677272.727272727</v>
       </c>
       <c r="AJ18" t="n">
-        <v>78.2</v>
+        <v>75.27272727272727</v>
       </c>
       <c r="AK18" t="n">
-        <v>21.22222222222222</v>
+        <v>25.375</v>
       </c>
       <c r="AL18" t="n">
-        <v>185.4444444444445</v>
+        <v>179.625</v>
       </c>
       <c r="AM18" t="n">
         <v>1</v>
       </c>
       <c r="AN18" t="n">
-        <v>70.77777777777777</v>
+        <v>63.625</v>
       </c>
       <c r="AO18" t="n">
-        <v>4402777.777777778</v>
+        <v>723125</v>
       </c>
       <c r="AP18" t="n">
-        <v>79.88888888888889</v>
+        <v>68.375</v>
       </c>
       <c r="AQ18" t="n">
-        <v>23.375</v>
+        <v>24</v>
       </c>
       <c r="AR18" t="n">
-        <v>182</v>
+        <v>181.0909090909091</v>
       </c>
       <c r="AS18" t="n">
         <v>1</v>
       </c>
       <c r="AT18" t="n">
-        <v>70.75</v>
+        <v>67.81818181818181</v>
       </c>
       <c r="AU18" t="n">
-        <v>3787500</v>
+        <v>1718181.818181818</v>
       </c>
       <c r="AV18" t="n">
-        <v>76.625</v>
+        <v>75</v>
       </c>
       <c r="AW18" t="n">
-        <v>21.875</v>
+        <v>23.25</v>
       </c>
       <c r="AX18" t="n">
-        <v>178.75</v>
+        <v>180</v>
       </c>
       <c r="AY18" t="n">
         <v>1</v>
       </c>
       <c r="AZ18" t="n">
-        <v>67.1875</v>
+        <v>61.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>2412500</v>
+        <v>679166.6666666666</v>
       </c>
       <c r="BB18" t="n">
-        <v>76</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>31</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>186</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>147</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>147</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>19</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>176</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>70</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>3800000</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>84</v>
-      </c>
+        <v>68.16666666666667</v>
+      </c>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="inlineStr"/>
+      <c r="BI18" t="inlineStr"/>
+      <c r="BJ18" t="inlineStr"/>
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="inlineStr"/>
+      <c r="BM18" t="inlineStr"/>
+      <c r="BN18" t="inlineStr"/>
+      <c r="BO18" t="inlineStr"/>
+      <c r="BP18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>OA5YizjL</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45522.41666666666</v>
+        <v>45523.65625</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">lissorgue r 
+          <t xml:space="preserve">thual o 
   fra </t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de l abbe deschamps
-  auxerre </t>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>17924</v>
+        <v>67394</v>
       </c>
       <c r="F19" t="n">
-        <v>16354</v>
+        <v>2655</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>ADl76OZP</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.67</v>
-      </c>
+          <t>jgNAYRGi</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="N19" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="O19" t="n">
+        <v>3</v>
+      </c>
+      <c r="P19" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7</v>
+      </c>
+      <c r="S19" t="n">
+        <v>8</v>
+      </c>
+      <c r="T19" t="n">
+        <v>13</v>
+      </c>
+      <c r="U19" t="n">
         <v>16</v>
       </c>
-      <c r="P19" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>7</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2</v>
-      </c>
-      <c r="S19" t="n">
-        <v>11</v>
-      </c>
-      <c r="T19" t="n">
-        <v>17</v>
-      </c>
-      <c r="U19" t="n">
-        <v>7</v>
-      </c>
       <c r="V19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>OpNm82MB</t>
+          <t>EwpPg8iH</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>d0X3cO3I</t>
+          <t>Cp0gM1r4</t>
         </is>
       </c>
       <c r="Y19" t="n">
         <v>55</v>
       </c>
       <c r="Z19" t="n">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -4131,211 +4153,159 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="AE19" t="n">
-        <v>25.66666666666667</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>182.3333333333333</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>68.22222222222223</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1708333.333333333</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>71.66666666666667</v>
-      </c>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
       <c r="AK19" t="n">
-        <v>23.8</v>
+        <v>24.44444444444444</v>
       </c>
       <c r="AL19" t="n">
-        <v>184</v>
+        <v>178.1111111111111</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AN19" t="n">
-        <v>73.7</v>
+        <v>71.77777777777777</v>
       </c>
       <c r="AO19" t="n">
-        <v>9280000</v>
+        <v>4622222.222222222</v>
       </c>
       <c r="AP19" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>25.08333333333333</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>180.8333333333333</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>65.08333333333333</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>1062500</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>69.25</v>
-      </c>
+        <v>77.11111111111111</v>
+      </c>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr"/>
       <c r="AW19" t="n">
-        <v>22.7</v>
+        <v>21.73333333333333</v>
       </c>
       <c r="AX19" t="n">
-        <v>179.5</v>
+        <v>177.4</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AZ19" t="n">
-        <v>72.7</v>
+        <v>69.06666666666666</v>
       </c>
       <c r="BA19" t="n">
-        <v>5470000</v>
+        <v>2781666.666666667</v>
       </c>
       <c r="BB19" t="n">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>192</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>69</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>74</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>23.75</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>177</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>4</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>307</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>53500000</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>321</v>
-      </c>
+        <v>77.53333333333333</v>
+      </c>
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="inlineStr"/>
+      <c r="BI19" t="inlineStr"/>
+      <c r="BJ19" t="inlineStr"/>
+      <c r="BK19" t="inlineStr"/>
+      <c r="BL19" t="inlineStr"/>
+      <c r="BM19" t="inlineStr"/>
+      <c r="BN19" t="inlineStr"/>
+      <c r="BO19" t="inlineStr"/>
+      <c r="BP19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>zkPwWhT1</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45521.66666666666</v>
+        <v>45522.65625</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">turpin c 
+          <t xml:space="preserve">millot b 
   fra </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>18523</v>
+        <v>29778</v>
       </c>
       <c r="F20" t="n">
-        <v>14250</v>
+        <v>26026</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>1.55</v>
+        <v>2.16</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.64</v>
       </c>
       <c r="M20" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="N20" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="O20" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="P20" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S20" t="n">
         <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="U20" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V20" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>CWxpUrtf</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>tAufB9Mi</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
       <c r="Y20" t="n">
@@ -4352,75 +4322,87 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="n">
-        <v>23.9</v>
+        <v>25.875</v>
       </c>
       <c r="AF20" t="n">
-        <v>182.9</v>
+        <v>180.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AH20" t="n">
-        <v>76.2</v>
+        <v>75.625</v>
       </c>
       <c r="AI20" t="n">
-        <v>12650000</v>
+        <v>9475000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="AK20" t="inlineStr"/>
-      <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="inlineStr"/>
-      <c r="AN20" t="inlineStr"/>
-      <c r="AO20" t="inlineStr"/>
-      <c r="AP20" t="inlineStr"/>
+        <v>79.25</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>76.33333333333333</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>10111111.11111111</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>80</v>
+      </c>
       <c r="AQ20" t="n">
-        <v>20.86666666666667</v>
+        <v>24.23076923076923</v>
       </c>
       <c r="AR20" t="n">
-        <v>183.6666666666667</v>
+        <v>181.9230769230769</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.2</v>
+        <v>1.538461538461539</v>
       </c>
       <c r="AT20" t="n">
-        <v>72.73333333333333</v>
+        <v>73.07692307692308</v>
       </c>
       <c r="AU20" t="n">
-        <v>9083333.333333334</v>
+        <v>8578846.153846154</v>
       </c>
       <c r="AV20" t="n">
-        <v>82</v>
+        <v>77.53846153846153</v>
       </c>
       <c r="AW20" t="n">
-        <v>22.72727272727273</v>
+        <v>23.81818181818182</v>
       </c>
       <c r="AX20" t="n">
-        <v>182.1818181818182</v>
+        <v>179.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>1</v>
+        <v>1.681818181818182</v>
       </c>
       <c r="AZ20" t="n">
-        <v>65.81818181818181</v>
+        <v>73.18181818181819</v>
       </c>
       <c r="BA20" t="n">
-        <v>1463636.363636364</v>
+        <v>5522727.272727272</v>
       </c>
       <c r="BB20" t="n">
-        <v>74.27272727272727</v>
+        <v>78.81818181818181</v>
       </c>
       <c r="BC20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BD20" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="BE20" t="n">
         <v>1</v>
@@ -4429,123 +4411,123 @@
         <v>1</v>
       </c>
       <c r="BG20" t="n">
+        <v>72</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="BI20" t="n">
         <v>78</v>
       </c>
-      <c r="BH20" t="n">
-        <v>20500000</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>84</v>
-      </c>
       <c r="BJ20" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="BK20" t="n">
-        <v>176</v>
+        <v>173.5</v>
       </c>
       <c r="BL20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BM20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BN20" t="n">
-        <v>71</v>
+        <v>159</v>
       </c>
       <c r="BO20" t="n">
-        <v>2400000</v>
+        <v>33000000</v>
       </c>
       <c r="BP20" t="n">
-        <v>74</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>2NocJFqd</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45521.58333333334</v>
+        <v>45522.5</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">wattellier e 
+          <t xml:space="preserve">leonard t 
   fra </t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>21029</v>
+        <v>18752</v>
       </c>
       <c r="F21" t="n">
-        <v>14755</v>
+        <v>14811</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>0.06</v>
+        <v>0.26</v>
       </c>
       <c r="L21" t="n">
-        <v>1.66</v>
+        <v>0.92</v>
       </c>
       <c r="M21" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="N21" t="n">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="O21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U21" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V21" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>25Wk0Fko</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>nVS1TlC4</t>
+          <t>K6b7RoBp</t>
         </is>
       </c>
       <c r="Y21" t="n">
@@ -4563,178 +4545,190 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr"/>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr"/>
-      <c r="AJ21" t="inlineStr"/>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="AE21" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>68</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1587500</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>72.8</v>
+      </c>
       <c r="AK21" t="n">
-        <v>24.875</v>
+        <v>27.63636363636364</v>
       </c>
       <c r="AL21" t="n">
-        <v>180.25</v>
+        <v>179.8181818181818</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.25</v>
+        <v>1.454545454545455</v>
       </c>
       <c r="AN21" t="n">
-        <v>75.875</v>
+        <v>77</v>
       </c>
       <c r="AO21" t="n">
-        <v>10312500</v>
+        <v>12381818.18181818</v>
       </c>
       <c r="AP21" t="n">
-        <v>80.5</v>
+        <v>78.72727272727273</v>
       </c>
       <c r="AQ21" t="n">
-        <v>20.25</v>
+        <v>25.7</v>
       </c>
       <c r="AR21" t="n">
-        <v>181.6666666666667</v>
+        <v>183.9</v>
       </c>
       <c r="AS21" t="n">
         <v>1</v>
       </c>
       <c r="AT21" t="n">
-        <v>68</v>
+        <v>66.45</v>
       </c>
       <c r="AU21" t="n">
-        <v>3266666.666666667</v>
+        <v>1278750</v>
       </c>
       <c r="AV21" t="n">
-        <v>78.75</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="AW21" t="n">
-        <v>23.33333333333333</v>
+        <v>23.90909090909091</v>
       </c>
       <c r="AX21" t="n">
-        <v>178.6111111111111</v>
+        <v>179.9545454545455</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.444444444444444</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="AZ21" t="n">
-        <v>72.38888888888889</v>
+        <v>72.90909090909091</v>
       </c>
       <c r="BA21" t="n">
-        <v>8463888.888888888</v>
+        <v>6081818.181818182</v>
       </c>
       <c r="BB21" t="n">
-        <v>79.88888888888889</v>
+        <v>78.13636363636364</v>
       </c>
       <c r="BC21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD21" t="n">
-        <v>182.6666666666667</v>
+        <v>179.25</v>
       </c>
       <c r="BE21" t="n">
         <v>1</v>
       </c>
       <c r="BF21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BG21" t="n">
-        <v>221</v>
+        <v>266</v>
       </c>
       <c r="BH21" t="n">
-        <v>29200000</v>
+        <v>5725000</v>
       </c>
       <c r="BI21" t="n">
-        <v>238</v>
+        <v>290</v>
       </c>
       <c r="BJ21" t="n">
-        <v>28.2</v>
+        <v>25</v>
       </c>
       <c r="BK21" t="n">
-        <v>180.6</v>
+        <v>179</v>
       </c>
       <c r="BL21" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="BM21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BN21" t="n">
-        <v>386</v>
+        <v>298</v>
       </c>
       <c r="BO21" t="n">
-        <v>55800000</v>
+        <v>28600000</v>
       </c>
       <c r="BP21" t="n">
-        <v>389</v>
+        <v>310</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45521.5</v>
+        <v>45522.5</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">bastien b 
+          <t xml:space="preserve">stinat j 
   fra </t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>15220</v>
+        <v>33150</v>
       </c>
       <c r="F22" t="n">
-        <v>14962</v>
+        <v>25491</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="L22" t="n">
-        <v>2.58</v>
+        <v>0.33</v>
       </c>
       <c r="M22" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N22" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="O22" t="n">
         <v>7</v>
       </c>
       <c r="P22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -4743,19 +4737,19 @@
         <v>8</v>
       </c>
       <c r="U22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V22" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0tIbS515</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>pYizckpN</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
       <c r="Y22" t="n">
@@ -4773,200 +4767,190 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>lhUkVMh2</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="AE22" t="n">
-        <v>28.1</v>
+        <v>22.9</v>
       </c>
       <c r="AF22" t="n">
-        <v>181.5</v>
+        <v>181.1</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AH22" t="n">
-        <v>74.09999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AI22" t="n">
-        <v>5460000</v>
+        <v>5200000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr"/>
-      <c r="AN22" t="inlineStr"/>
-      <c r="AO22" t="inlineStr"/>
-      <c r="AP22" t="inlineStr"/>
+        <v>78.7</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>182</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>5310000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>76.2</v>
+      </c>
       <c r="AQ22" t="n">
-        <v>22.78571428571428</v>
+        <v>24</v>
       </c>
       <c r="AR22" t="n">
-        <v>178.1428571428571</v>
+        <v>178.375</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.285714285714286</v>
+        <v>1</v>
       </c>
       <c r="AT22" t="n">
-        <v>67.71428571428571</v>
+        <v>69.8125</v>
       </c>
       <c r="AU22" t="n">
-        <v>4185714.285714286</v>
+        <v>2631250</v>
       </c>
       <c r="AV22" t="n">
-        <v>74.42857142857143</v>
+        <v>75.4375</v>
       </c>
       <c r="AW22" t="n">
-        <v>24.36363636363636</v>
+        <v>25.76470588235294</v>
       </c>
       <c r="AX22" t="n">
-        <v>180.0909090909091</v>
+        <v>182.8235294117647</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.454545454545455</v>
+        <v>1.411764705882353</v>
       </c>
       <c r="AZ22" t="n">
-        <v>75.18181818181819</v>
+        <v>71.76470588235294</v>
       </c>
       <c r="BA22" t="n">
-        <v>10490909.09090909</v>
+        <v>3450000</v>
       </c>
       <c r="BB22" t="n">
-        <v>79.18181818181819</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>172</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>74</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>77</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>23.75</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>183.75</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>4</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>296</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>48000000</v>
-      </c>
-      <c r="BP22" t="n">
-        <v>318</v>
-      </c>
+        <v>74.58823529411765</v>
+      </c>
+      <c r="BC22" t="inlineStr"/>
+      <c r="BD22" t="inlineStr"/>
+      <c r="BE22" t="inlineStr"/>
+      <c r="BF22" t="inlineStr"/>
+      <c r="BG22" t="inlineStr"/>
+      <c r="BH22" t="inlineStr"/>
+      <c r="BI22" t="inlineStr"/>
+      <c r="BJ22" t="inlineStr"/>
+      <c r="BK22" t="inlineStr"/>
+      <c r="BL22" t="inlineStr"/>
+      <c r="BM22" t="inlineStr"/>
+      <c r="BN22" t="inlineStr"/>
+      <c r="BO22" t="inlineStr"/>
+      <c r="BP22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>dvUee9dD</t>
+          <t>M5VGwpVA</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45521.39583333334</v>
+        <v>45522.5</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">gaillouste p 
+          <t xml:space="preserve">vernice m 
   fra </t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade michel d ornano
-  caen </t>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>20300</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
+        <v>20484</v>
+      </c>
+      <c r="F23" t="n">
+        <v>15706</v>
+      </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>GjLn2QoH</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0OEHEprs</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.23</v>
+      </c>
       <c r="M23" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="N23" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="O23" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P23" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q23" t="n">
         <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T23" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="U23" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="V23" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Q9EVqFe4</t>
+          <t>vVQcGxl1</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>zB2j3YvM</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
       <c r="Y23" t="n">
         <v>55</v>
       </c>
       <c r="Z23" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -4974,182 +4958,218 @@
       <c r="AB23" t="n">
         <v>20242025</v>
       </c>
-      <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
       <c r="AE23" t="n">
-        <v>25.44444444444444</v>
+        <v>25.6</v>
       </c>
       <c r="AF23" t="n">
-        <v>181</v>
+        <v>180.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AH23" t="n">
-        <v>67.55555555555556</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AI23" t="n">
-        <v>1638888.888888889</v>
+        <v>6330000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>74</v>
+        <v>78.2</v>
       </c>
       <c r="AK23" t="n">
-        <v>24.66666666666667</v>
+        <v>21.22222222222222</v>
       </c>
       <c r="AL23" t="n">
-        <v>177.8888888888889</v>
+        <v>185.4444444444445</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.111111111111111</v>
+        <v>1</v>
       </c>
       <c r="AN23" t="n">
-        <v>67.22222222222223</v>
+        <v>70.77777777777777</v>
       </c>
       <c r="AO23" t="n">
-        <v>1697222.222222222</v>
+        <v>4402777.777777778</v>
       </c>
       <c r="AP23" t="n">
-        <v>71.55555555555556</v>
+        <v>79.88888888888889</v>
       </c>
       <c r="AQ23" t="n">
-        <v>22.07142857142857</v>
+        <v>23.375</v>
       </c>
       <c r="AR23" t="n">
-        <v>179.7857142857143</v>
+        <v>182</v>
       </c>
       <c r="AS23" t="n">
         <v>1</v>
       </c>
       <c r="AT23" t="n">
-        <v>64.21428571428571</v>
+        <v>70.75</v>
       </c>
       <c r="AU23" t="n">
-        <v>1037500</v>
+        <v>3787500</v>
       </c>
       <c r="AV23" t="n">
-        <v>74.07142857142857</v>
+        <v>76.625</v>
       </c>
       <c r="AW23" t="n">
-        <v>24.95</v>
+        <v>21.875</v>
       </c>
       <c r="AX23" t="n">
-        <v>181.8</v>
+        <v>178.75</v>
       </c>
       <c r="AY23" t="n">
         <v>1</v>
       </c>
       <c r="AZ23" t="n">
-        <v>65.09999999999999</v>
+        <v>67.1875</v>
       </c>
       <c r="BA23" t="n">
-        <v>1083750</v>
+        <v>2412500</v>
       </c>
       <c r="BB23" t="n">
-        <v>69.15000000000001</v>
-      </c>
-      <c r="BC23" t="inlineStr"/>
-      <c r="BD23" t="inlineStr"/>
-      <c r="BE23" t="inlineStr"/>
-      <c r="BF23" t="inlineStr"/>
-      <c r="BG23" t="inlineStr"/>
-      <c r="BH23" t="inlineStr"/>
-      <c r="BI23" t="inlineStr"/>
-      <c r="BJ23" t="inlineStr"/>
-      <c r="BK23" t="inlineStr"/>
-      <c r="BL23" t="inlineStr"/>
-      <c r="BM23" t="inlineStr"/>
-      <c r="BN23" t="inlineStr"/>
-      <c r="BO23" t="inlineStr"/>
-      <c r="BP23" t="inlineStr"/>
+        <v>76</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>31</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>186</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>147</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>147</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>19</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>176</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>70</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>ripawyyS</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45520.65625</v>
+        <v>45522.41666666666</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">lissorgue r 
   fra </t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>25178</v>
+        <v>17924</v>
       </c>
       <c r="F24" t="n">
-        <v>23167</v>
+        <v>16354</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>0.09</v>
+        <v>2.11</v>
       </c>
       <c r="L24" t="n">
-        <v>1.89</v>
+        <v>0.67</v>
       </c>
       <c r="M24" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="N24" t="n">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="O24" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="P24" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Q24" t="n">
+        <v>7</v>
+      </c>
+      <c r="R24" t="n">
         <v>2</v>
       </c>
-      <c r="R24" t="n">
-        <v>9</v>
-      </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T24" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="U24" t="n">
+        <v>7</v>
+      </c>
+      <c r="V24" t="n">
         <v>8</v>
       </c>
-      <c r="V24" t="n">
-        <v>4</v>
-      </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>dWZTBmVT</t>
+          <t>OpNm82MB</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>8MdrBIUb</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
       <c r="Y24" t="n">
@@ -5165,72 +5185,88 @@
         <v>20242025</v>
       </c>
       <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
       <c r="AE24" t="n">
-        <v>25.18181818181818</v>
+        <v>25.66666666666667</v>
       </c>
       <c r="AF24" t="n">
-        <v>185.2727272727273</v>
+        <v>182.3333333333333</v>
       </c>
       <c r="AG24" t="n">
         <v>1</v>
       </c>
       <c r="AH24" t="n">
-        <v>71.36363636363636</v>
+        <v>68.22222222222223</v>
       </c>
       <c r="AI24" t="n">
-        <v>2945454.545454545</v>
+        <v>1708333.333333333</v>
       </c>
       <c r="AJ24" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK24" t="inlineStr"/>
-      <c r="AL24" t="inlineStr"/>
-      <c r="AM24" t="inlineStr"/>
-      <c r="AN24" t="inlineStr"/>
-      <c r="AO24" t="inlineStr"/>
-      <c r="AP24" t="inlineStr"/>
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>184</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>9280000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>78.90000000000001</v>
+      </c>
       <c r="AQ24" t="n">
-        <v>22.5625</v>
+        <v>25.08333333333333</v>
       </c>
       <c r="AR24" t="n">
-        <v>180.0625</v>
+        <v>180.8333333333333</v>
       </c>
       <c r="AS24" t="n">
         <v>1</v>
       </c>
       <c r="AT24" t="n">
-        <v>65.5</v>
+        <v>65.08333333333333</v>
       </c>
       <c r="AU24" t="n">
-        <v>1389062.5</v>
+        <v>1062500</v>
       </c>
       <c r="AV24" t="n">
-        <v>72.75</v>
+        <v>69.25</v>
       </c>
       <c r="AW24" t="n">
-        <v>23.69230769230769</v>
+        <v>22.7</v>
       </c>
       <c r="AX24" t="n">
-        <v>183.5384615384615</v>
+        <v>179.5</v>
       </c>
       <c r="AY24" t="n">
-        <v>2.307692307692307</v>
+        <v>1.1</v>
       </c>
       <c r="AZ24" t="n">
-        <v>80.38461538461539</v>
+        <v>72.7</v>
       </c>
       <c r="BA24" t="n">
-        <v>42061538.46153846</v>
+        <v>5470000</v>
       </c>
       <c r="BB24" t="n">
-        <v>84.76923076923077</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="BC24" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="BD24" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="BE24" t="n">
         <v>1</v>
@@ -5239,124 +5275,130 @@
         <v>1</v>
       </c>
       <c r="BG24" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="BH24" t="n">
-        <v>1300000</v>
+        <v>1800000</v>
       </c>
       <c r="BI24" t="n">
         <v>74</v>
       </c>
       <c r="BJ24" t="n">
-        <v>27</v>
+        <v>23.75</v>
       </c>
       <c r="BK24" t="n">
-        <v>186.5</v>
+        <v>177</v>
       </c>
       <c r="BL24" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="BM24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BN24" t="n">
-        <v>165</v>
+        <v>307</v>
       </c>
       <c r="BO24" t="n">
-        <v>68000000</v>
+        <v>53500000</v>
       </c>
       <c r="BP24" t="n">
-        <v>167</v>
+        <v>321</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>b15XX7Nt</t>
+          <t>fHYrsJy3</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45520.625</v>
+        <v>45521.66666666666</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">bollengier m 
+          <t xml:space="preserve">turpin c 
   fra </t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de roudourou
-  guingamp </t>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>19060</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
+        <v>18523</v>
+      </c>
+      <c r="F25" t="n">
+        <v>14250</v>
+      </c>
       <c r="G25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>QDfKl36E</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>fsfAHubD</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="M25" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="N25" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="O25" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T25" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="U25" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="V25" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>QNSJnsB5</t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>4vG8dmrf</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
       <c r="Y25" t="n">
         <v>55</v>
       </c>
       <c r="Z25" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -5364,120 +5406,142 @@
       <c r="AB25" t="n">
         <v>20242025</v>
       </c>
-      <c r="AC25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="n">
-        <v>24.5</v>
+        <v>23.9</v>
       </c>
       <c r="AF25" t="n">
-        <v>179.9</v>
+        <v>182.9</v>
       </c>
       <c r="AG25" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AH25" t="n">
-        <v>65.2</v>
+        <v>76.2</v>
       </c>
       <c r="AI25" t="n">
-        <v>1025000</v>
+        <v>12650000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>27.625</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>177.625</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>67.375</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>1275000</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>70.375</v>
-      </c>
+        <v>80.8</v>
+      </c>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="n">
-        <v>23</v>
+        <v>20.86666666666667</v>
       </c>
       <c r="AR25" t="n">
-        <v>179.7</v>
+        <v>183.6666666666667</v>
       </c>
       <c r="AS25" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AT25" t="n">
-        <v>63.3</v>
+        <v>72.73333333333333</v>
       </c>
       <c r="AU25" t="n">
-        <v>950000</v>
+        <v>9083333.333333334</v>
       </c>
       <c r="AV25" t="n">
-        <v>70.3</v>
+        <v>82</v>
       </c>
       <c r="AW25" t="n">
-        <v>20.41666666666667</v>
+        <v>22.72727272727273</v>
       </c>
       <c r="AX25" t="n">
-        <v>179.6666666666667</v>
+        <v>182.1818181818182</v>
       </c>
       <c r="AY25" t="n">
         <v>1</v>
       </c>
       <c r="AZ25" t="n">
-        <v>61.75</v>
+        <v>65.81818181818181</v>
       </c>
       <c r="BA25" t="n">
-        <v>912500</v>
+        <v>1463636.363636364</v>
       </c>
       <c r="BB25" t="n">
-        <v>70.91666666666667</v>
-      </c>
-      <c r="BC25" t="inlineStr"/>
-      <c r="BD25" t="inlineStr"/>
-      <c r="BE25" t="inlineStr"/>
-      <c r="BF25" t="inlineStr"/>
-      <c r="BG25" t="inlineStr"/>
-      <c r="BH25" t="inlineStr"/>
-      <c r="BI25" t="inlineStr"/>
-      <c r="BJ25" t="inlineStr"/>
-      <c r="BK25" t="inlineStr"/>
-      <c r="BL25" t="inlineStr"/>
-      <c r="BM25" t="inlineStr"/>
-      <c r="BN25" t="inlineStr"/>
-      <c r="BO25" t="inlineStr"/>
-      <c r="BP25" t="inlineStr"/>
+        <v>74.27272727272727</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>190</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>78</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>20500000</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>84</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>24</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>176</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>71</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>zB0ErWC7</t>
+          <t>jqSiuc6F</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45520.625</v>
+        <v>45521.58333333334</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">kubler g 
+          <t xml:space="preserve">wattellier e 
   fra </t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade marcel tribut
-  dunkerque </t>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4933</v>
-      </c>
-      <c r="F26" t="inlineStr"/>
+        <v>21029</v>
+      </c>
+      <c r="F26" t="n">
+        <v>14755</v>
+      </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
@@ -5486,57 +5550,65 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>tAAobNse</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>25dB6Eto</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.66</v>
+      </c>
       <c r="M26" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="N26" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="O26" t="n">
+        <v>2</v>
+      </c>
+      <c r="P26" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6</v>
+      </c>
+      <c r="S26" t="n">
+        <v>6</v>
+      </c>
+      <c r="T26" t="n">
+        <v>13</v>
+      </c>
+      <c r="U26" t="n">
         <v>12</v>
       </c>
-      <c r="P26" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q26" t="n">
+      <c r="V26" t="n">
         <v>6</v>
       </c>
-      <c r="R26" t="n">
-        <v>4</v>
-      </c>
-      <c r="S26" t="n">
-        <v>15</v>
-      </c>
-      <c r="T26" t="n">
-        <v>15</v>
-      </c>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
-          <t>lb31RXzP</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>SIiBpBrs</t>
+          <t>nVS1TlC4</t>
         </is>
       </c>
       <c r="Y26" t="n">
         <v>55</v>
       </c>
       <c r="Z26" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -5545,7 +5617,11 @@
         <v>20242025</v>
       </c>
       <c r="AC26" t="inlineStr"/>
-      <c r="AD26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr"/>
@@ -5553,164 +5629,196 @@
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="n">
-        <v>26.44444444444444</v>
+        <v>24.875</v>
       </c>
       <c r="AL26" t="n">
-        <v>182.5555555555555</v>
+        <v>180.25</v>
       </c>
       <c r="AM26" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AN26" t="n">
-        <v>64.55555555555556</v>
+        <v>75.875</v>
       </c>
       <c r="AO26" t="n">
-        <v>833333.3333333334</v>
+        <v>10312500</v>
       </c>
       <c r="AP26" t="n">
-        <v>67.77777777777777</v>
+        <v>80.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>22.83333333333333</v>
+        <v>20.25</v>
       </c>
       <c r="AR26" t="n">
-        <v>176.8333333333333</v>
+        <v>181.6666666666667</v>
       </c>
       <c r="AS26" t="n">
         <v>1</v>
       </c>
       <c r="AT26" t="n">
-        <v>63.25</v>
+        <v>68</v>
       </c>
       <c r="AU26" t="n">
-        <v>804166.6666666666</v>
+        <v>3266666.666666667</v>
       </c>
       <c r="AV26" t="n">
-        <v>70.75</v>
+        <v>78.75</v>
       </c>
       <c r="AW26" t="n">
-        <v>21.66666666666667</v>
+        <v>23.33333333333333</v>
       </c>
       <c r="AX26" t="n">
-        <v>180.6666666666667</v>
+        <v>178.6111111111111</v>
       </c>
       <c r="AY26" t="n">
-        <v>1</v>
+        <v>1.444444444444444</v>
       </c>
       <c r="AZ26" t="n">
-        <v>61.83333333333334</v>
+        <v>72.38888888888889</v>
       </c>
       <c r="BA26" t="n">
-        <v>708333.3333333334</v>
+        <v>8463888.888888888</v>
       </c>
       <c r="BB26" t="n">
-        <v>69.33333333333333</v>
-      </c>
-      <c r="BC26" t="inlineStr"/>
-      <c r="BD26" t="inlineStr"/>
-      <c r="BE26" t="inlineStr"/>
-      <c r="BF26" t="inlineStr"/>
-      <c r="BG26" t="inlineStr"/>
-      <c r="BH26" t="inlineStr"/>
-      <c r="BI26" t="inlineStr"/>
-      <c r="BJ26" t="inlineStr"/>
-      <c r="BK26" t="inlineStr"/>
-      <c r="BL26" t="inlineStr"/>
-      <c r="BM26" t="inlineStr"/>
-      <c r="BN26" t="inlineStr"/>
-      <c r="BO26" t="inlineStr"/>
-      <c r="BP26" t="inlineStr"/>
+        <v>79.88888888888889</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>182.6666666666667</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>221</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>29200000</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>238</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>180.6</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>386</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>55800000</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>389</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>6V8cnEDr</t>
+          <t>0js8u60b</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45520.625</v>
+        <v>45521.5</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">landry r 
+          <t xml:space="preserve">bastien b 
   fra </t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade gabriel montpied
-  clermont ferrand </t>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>10800</v>
+        <v>15220</v>
       </c>
       <c r="F27" t="n">
-        <v>5582</v>
+        <v>14962</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>IRuMRua1</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>6NOhR4cm</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L27" t="n">
+        <v>2.58</v>
+      </c>
       <c r="M27" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="N27" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="O27" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="P27" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q27" t="n">
         <v>5</v>
       </c>
       <c r="R27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S27" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T27" t="n">
+        <v>8</v>
+      </c>
+      <c r="U27" t="n">
+        <v>10</v>
+      </c>
+      <c r="V27" t="n">
         <v>12</v>
       </c>
-      <c r="U27" t="n">
-        <v>14</v>
-      </c>
-      <c r="V27" t="n">
-        <v>16</v>
-      </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>4G9MhScS</t>
+          <t>0tIbS515</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>fm0Qb28B</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="Y27" t="n">
         <v>55</v>
       </c>
       <c r="Z27" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -5719,177 +5827,197 @@
         <v>20242025</v>
       </c>
       <c r="AC27" t="inlineStr"/>
-      <c r="AD27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
       <c r="AE27" t="n">
-        <v>23.88888888888889</v>
+        <v>28.1</v>
       </c>
       <c r="AF27" t="n">
-        <v>180</v>
+        <v>181.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.111111111111111</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>66.44444444444444</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AI27" t="n">
-        <v>1436111.111111111</v>
+        <v>5460000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>73.77777777777777</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>183.7</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>962500</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>70.7</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="n">
-        <v>20.85714285714286</v>
+        <v>22.78571428571428</v>
       </c>
       <c r="AR27" t="n">
-        <v>176</v>
+        <v>178.1428571428571</v>
       </c>
       <c r="AS27" t="n">
-        <v>1</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="AT27" t="n">
-        <v>65.28571428571429</v>
+        <v>67.71428571428571</v>
       </c>
       <c r="AU27" t="n">
-        <v>1614285.714285714</v>
+        <v>4185714.285714286</v>
       </c>
       <c r="AV27" t="n">
-        <v>75.28571428571429</v>
+        <v>74.42857142857143</v>
       </c>
       <c r="AW27" t="n">
-        <v>26</v>
+        <v>24.36363636363636</v>
       </c>
       <c r="AX27" t="n">
-        <v>182.7272727272727</v>
+        <v>180.0909090909091</v>
       </c>
       <c r="AY27" t="n">
-        <v>1</v>
+        <v>1.454545454545455</v>
       </c>
       <c r="AZ27" t="n">
-        <v>64.54545454545455</v>
+        <v>75.18181818181819</v>
       </c>
       <c r="BA27" t="n">
-        <v>709090.9090909091</v>
+        <v>10490909.09090909</v>
       </c>
       <c r="BB27" t="n">
-        <v>70.27272727272727</v>
-      </c>
-      <c r="BC27" t="inlineStr"/>
-      <c r="BD27" t="inlineStr"/>
-      <c r="BE27" t="inlineStr"/>
-      <c r="BF27" t="inlineStr"/>
-      <c r="BG27" t="inlineStr"/>
-      <c r="BH27" t="inlineStr"/>
-      <c r="BI27" t="inlineStr"/>
-      <c r="BJ27" t="inlineStr"/>
-      <c r="BK27" t="inlineStr"/>
-      <c r="BL27" t="inlineStr"/>
-      <c r="BM27" t="inlineStr"/>
-      <c r="BN27" t="inlineStr"/>
-      <c r="BO27" t="inlineStr"/>
-      <c r="BP27" t="inlineStr"/>
+        <v>79.18181818181819</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>172</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>74</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>77</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>183.75</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>296</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>318</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2Hh06Z4E</t>
+          <t>dvUee9dD</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45520.625</v>
+        <v>45521.39583333334</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">rosier e 
+          <t xml:space="preserve">gaillouste p 
   fra </t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la licorne
-  amiens </t>
+          <t xml:space="preserve">stade michel d ornano
+  caen </t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>12097</v>
+        <v>20300</v>
       </c>
       <c r="F28" t="n">
-        <v>4918</v>
+        <v>16639</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>lKkBAsxF</t>
+          <t>GjLn2QoH</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2kM6ufaS</t>
+          <t>0OEHEprs</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="N28" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="O28" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="P28" t="n">
         <v>13</v>
       </c>
       <c r="Q28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T28" t="n">
         <v>13</v>
       </c>
       <c r="U28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V28" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>dS1CBple</t>
+          <t>Q9EVqFe4</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>SzfSpYcf</t>
+          <t>zB2j3YvM</t>
         </is>
       </c>
       <c r="Y28" t="n">
@@ -5907,53 +6035,77 @@
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="n">
-        <v>26.1</v>
+        <v>25.44444444444444</v>
       </c>
       <c r="AF28" t="n">
-        <v>181.2</v>
+        <v>181</v>
       </c>
       <c r="AG28" t="n">
         <v>1</v>
       </c>
       <c r="AH28" t="n">
-        <v>67.09999999999999</v>
+        <v>67.55555555555556</v>
       </c>
       <c r="AI28" t="n">
-        <v>1205000</v>
+        <v>1638888.888888889</v>
       </c>
       <c r="AJ28" t="n">
-        <v>71.09999999999999</v>
-      </c>
-      <c r="AK28" t="inlineStr"/>
-      <c r="AL28" t="inlineStr"/>
-      <c r="AM28" t="inlineStr"/>
-      <c r="AN28" t="inlineStr"/>
-      <c r="AO28" t="inlineStr"/>
-      <c r="AP28" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>177.8888888888889</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>67.22222222222223</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1697222.222222222</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>71.55555555555556</v>
+      </c>
       <c r="AQ28" t="n">
-        <v>24.5</v>
+        <v>22.07142857142857</v>
       </c>
       <c r="AR28" t="n">
-        <v>180.75</v>
+        <v>179.7857142857143</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.1875</v>
+        <v>1</v>
       </c>
       <c r="AT28" t="n">
-        <v>63.0625</v>
+        <v>64.21428571428571</v>
       </c>
       <c r="AU28" t="n">
-        <v>751562.5</v>
+        <v>1037500</v>
       </c>
       <c r="AV28" t="n">
-        <v>71.4375</v>
-      </c>
-      <c r="AW28" t="inlineStr"/>
-      <c r="AX28" t="inlineStr"/>
-      <c r="AY28" t="inlineStr"/>
-      <c r="AZ28" t="inlineStr"/>
-      <c r="BA28" t="inlineStr"/>
-      <c r="BB28" t="inlineStr"/>
+        <v>74.07142857142857</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>181.8</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>1083750</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>69.15000000000001</v>
+      </c>
       <c r="BC28" t="inlineStr"/>
       <c r="BD28" t="inlineStr"/>
       <c r="BE28" t="inlineStr"/>
@@ -5972,87 +6124,97 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>EeC5phre</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45520.625</v>
+        <v>45520.65625</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">valnet a 
+          <t xml:space="preserve">delajod w 
   fra </t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">michel moretti stadium
-  ajaccio </t>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>8470</v>
-      </c>
-      <c r="F29" t="inlineStr"/>
+        <v>25178</v>
+      </c>
+      <c r="F29" t="n">
+        <v>23167</v>
+      </c>
       <c r="G29" t="n">
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2aeoANM8</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0pOdQOCg</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.89</v>
+      </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="N29" t="n">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="O29" t="n">
+        <v>5</v>
+      </c>
+      <c r="P29" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2</v>
+      </c>
+      <c r="R29" t="n">
+        <v>9</v>
+      </c>
+      <c r="S29" t="n">
+        <v>9</v>
+      </c>
+      <c r="T29" t="n">
+        <v>9</v>
+      </c>
+      <c r="U29" t="n">
         <v>8</v>
       </c>
-      <c r="P29" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q29" t="n">
+      <c r="V29" t="n">
         <v>4</v>
       </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
-          <t>8tmnzqxe</t>
+          <t>dWZTBmVT</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>OQuqpG7i</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
       <c r="Y29" t="n">
         <v>55</v>
       </c>
       <c r="Z29" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -6063,96 +6225,112 @@
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="n">
-        <v>24.9</v>
+        <v>25.18181818181818</v>
       </c>
       <c r="AF29" t="n">
-        <v>178.2</v>
+        <v>185.2727272727273</v>
       </c>
       <c r="AG29" t="n">
         <v>1</v>
       </c>
       <c r="AH29" t="n">
-        <v>64.40000000000001</v>
+        <v>71.36363636363636</v>
       </c>
       <c r="AI29" t="n">
-        <v>872500</v>
+        <v>2945454.545454545</v>
       </c>
       <c r="AJ29" t="n">
-        <v>70.3</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>182.5</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>64.75</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>1090625</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>70.75</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
       <c r="AQ29" t="n">
-        <v>26.38888888888889</v>
+        <v>22.5625</v>
       </c>
       <c r="AR29" t="n">
-        <v>180</v>
+        <v>180.0625</v>
       </c>
       <c r="AS29" t="n">
         <v>1</v>
       </c>
       <c r="AT29" t="n">
-        <v>65.05555555555556</v>
+        <v>65.5</v>
       </c>
       <c r="AU29" t="n">
-        <v>751388.8888888889</v>
+        <v>1389062.5</v>
       </c>
       <c r="AV29" t="n">
-        <v>69.61111111111111</v>
+        <v>72.75</v>
       </c>
       <c r="AW29" t="n">
-        <v>22</v>
+        <v>23.69230769230769</v>
       </c>
       <c r="AX29" t="n">
-        <v>182.2</v>
+        <v>183.5384615384615</v>
       </c>
       <c r="AY29" t="n">
-        <v>1</v>
+        <v>2.307692307692307</v>
       </c>
       <c r="AZ29" t="n">
-        <v>62.7</v>
+        <v>80.38461538461539</v>
       </c>
       <c r="BA29" t="n">
-        <v>830000</v>
+        <v>42061538.46153846</v>
       </c>
       <c r="BB29" t="n">
-        <v>71</v>
-      </c>
-      <c r="BC29" t="inlineStr"/>
-      <c r="BD29" t="inlineStr"/>
-      <c r="BE29" t="inlineStr"/>
-      <c r="BF29" t="inlineStr"/>
-      <c r="BG29" t="inlineStr"/>
-      <c r="BH29" t="inlineStr"/>
-      <c r="BI29" t="inlineStr"/>
-      <c r="BJ29" t="inlineStr"/>
-      <c r="BK29" t="inlineStr"/>
-      <c r="BL29" t="inlineStr"/>
-      <c r="BM29" t="inlineStr"/>
-      <c r="BN29" t="inlineStr"/>
-      <c r="BO29" t="inlineStr"/>
-      <c r="BP29" t="inlineStr"/>
+        <v>84.76923076923077</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>188</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>64</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>74</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>27</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>165</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>68000000</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>167</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>dGo94DZQ</t>
+          <t>EeC5phre</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -6160,54 +6338,60 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">kherradji a 
+          <t xml:space="preserve">valnet a 
   fra </t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade des alpes
-  grenoble </t>
+          <t xml:space="preserve">michel moretti stadium
+  ajaccio </t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>20068</v>
-      </c>
-      <c r="F30" t="inlineStr"/>
+        <v>8470</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3315</v>
+      </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>UgPj1p1N</t>
+          <t>2aeoANM8</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>E1wDrLsJ</t>
+          <t>0pOdQOCg</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>99</v>
+      </c>
       <c r="O30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P30" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q30" t="n">
         <v>4</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T30" t="n">
         <v>0</v>
@@ -6216,12 +6400,12 @@
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
-          <t>WrQARdPN</t>
+          <t>8tmnzqxe</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ys1Pb7ws</t>
+          <t>OQuqpG7i</t>
         </is>
       </c>
       <c r="Y30" t="n">
@@ -6239,64 +6423,76 @@
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr"/>
       <c r="AE30" t="n">
-        <v>25.72727272727273</v>
+        <v>24.9</v>
       </c>
       <c r="AF30" t="n">
-        <v>182.8181818181818</v>
+        <v>178.2</v>
       </c>
       <c r="AG30" t="n">
         <v>1</v>
       </c>
       <c r="AH30" t="n">
-        <v>67.63636363636364</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AI30" t="n">
-        <v>1495454.545454545</v>
+        <v>872500</v>
       </c>
       <c r="AJ30" t="n">
-        <v>71.36363636363636</v>
-      </c>
-      <c r="AK30" t="inlineStr"/>
-      <c r="AL30" t="inlineStr"/>
-      <c r="AM30" t="inlineStr"/>
-      <c r="AN30" t="inlineStr"/>
-      <c r="AO30" t="inlineStr"/>
-      <c r="AP30" t="inlineStr"/>
+        <v>70.3</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1090625</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>70.75</v>
+      </c>
       <c r="AQ30" t="n">
-        <v>29.66666666666667</v>
+        <v>26.38888888888889</v>
       </c>
       <c r="AR30" t="n">
-        <v>185.1666666666667</v>
+        <v>180</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AT30" t="n">
-        <v>70.5</v>
+        <v>65.05555555555556</v>
       </c>
       <c r="AU30" t="n">
-        <v>1937500</v>
+        <v>751388.8888888889</v>
       </c>
       <c r="AV30" t="n">
-        <v>72.5</v>
+        <v>69.61111111111111</v>
       </c>
       <c r="AW30" t="n">
-        <v>24.8125</v>
+        <v>22</v>
       </c>
       <c r="AX30" t="n">
-        <v>181.5</v>
+        <v>182.2</v>
       </c>
       <c r="AY30" t="n">
         <v>1</v>
       </c>
       <c r="AZ30" t="n">
-        <v>64.3125</v>
+        <v>62.7</v>
       </c>
       <c r="BA30" t="n">
-        <v>958750</v>
+        <v>830000</v>
       </c>
       <c r="BB30" t="n">
-        <v>71.3125</v>
+        <v>71</v>
       </c>
       <c r="BC30" t="inlineStr"/>
       <c r="BD30" t="inlineStr"/>
@@ -6313,6 +6509,876 @@
       <c r="BO30" t="inlineStr"/>
       <c r="BP30" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>2Hh06Z4E</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rosier e 
+  fra </t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la licorne
+  amiens </t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>12097</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4918</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>lKkBAsxF</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2kM6ufaS</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>51</v>
+      </c>
+      <c r="N31" t="n">
+        <v>49</v>
+      </c>
+      <c r="O31" t="n">
+        <v>17</v>
+      </c>
+      <c r="P31" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>6</v>
+      </c>
+      <c r="R31" t="n">
+        <v>3</v>
+      </c>
+      <c r="S31" t="n">
+        <v>11</v>
+      </c>
+      <c r="T31" t="n">
+        <v>13</v>
+      </c>
+      <c r="U31" t="n">
+        <v>11</v>
+      </c>
+      <c r="V31" t="n">
+        <v>13</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>dS1CBple</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>SzfSpYcf</t>
+        </is>
+      </c>
+      <c r="Y31" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1205000</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="inlineStr"/>
+      <c r="AQ31" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>63.0625</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>751562.5</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>71.4375</v>
+      </c>
+      <c r="AW31" t="inlineStr"/>
+      <c r="AX31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr"/>
+      <c r="BA31" t="inlineStr"/>
+      <c r="BB31" t="inlineStr"/>
+      <c r="BC31" t="inlineStr"/>
+      <c r="BD31" t="inlineStr"/>
+      <c r="BE31" t="inlineStr"/>
+      <c r="BF31" t="inlineStr"/>
+      <c r="BG31" t="inlineStr"/>
+      <c r="BH31" t="inlineStr"/>
+      <c r="BI31" t="inlineStr"/>
+      <c r="BJ31" t="inlineStr"/>
+      <c r="BK31" t="inlineStr"/>
+      <c r="BL31" t="inlineStr"/>
+      <c r="BM31" t="inlineStr"/>
+      <c r="BN31" t="inlineStr"/>
+      <c r="BO31" t="inlineStr"/>
+      <c r="BP31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>6V8cnEDr</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">landry r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade gabriel montpied
+  clermont ferrand </t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>10800</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5582</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>IRuMRua1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="n">
+        <v>56</v>
+      </c>
+      <c r="N32" t="n">
+        <v>44</v>
+      </c>
+      <c r="O32" t="n">
+        <v>13</v>
+      </c>
+      <c r="P32" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>5</v>
+      </c>
+      <c r="R32" t="n">
+        <v>4</v>
+      </c>
+      <c r="S32" t="n">
+        <v>14</v>
+      </c>
+      <c r="T32" t="n">
+        <v>12</v>
+      </c>
+      <c r="U32" t="n">
+        <v>14</v>
+      </c>
+      <c r="V32" t="n">
+        <v>16</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>4G9MhScS</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>fm0Qb28B</t>
+        </is>
+      </c>
+      <c r="Y32" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="n">
+        <v>23.88888888888889</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>180</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>66.44444444444444</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1436111.111111111</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>73.77777777777777</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>183.7</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>962500</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>20.85714285714286</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>176</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>65.28571428571429</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>1614285.714285714</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>75.28571428571429</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>182.7272727272727</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>64.54545454545455</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>709090.9090909091</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>70.27272727272727</v>
+      </c>
+      <c r="BC32" t="inlineStr"/>
+      <c r="BD32" t="inlineStr"/>
+      <c r="BE32" t="inlineStr"/>
+      <c r="BF32" t="inlineStr"/>
+      <c r="BG32" t="inlineStr"/>
+      <c r="BH32" t="inlineStr"/>
+      <c r="BI32" t="inlineStr"/>
+      <c r="BJ32" t="inlineStr"/>
+      <c r="BK32" t="inlineStr"/>
+      <c r="BL32" t="inlineStr"/>
+      <c r="BM32" t="inlineStr"/>
+      <c r="BN32" t="inlineStr"/>
+      <c r="BO32" t="inlineStr"/>
+      <c r="BP32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>zB0ErWC7</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kubler g 
+  fra </t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade marcel tribut
+  dunkerque </t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>4933</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3333</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>tAAobNse</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>25dB6Eto</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="n">
+        <v>48</v>
+      </c>
+      <c r="N33" t="n">
+        <v>52</v>
+      </c>
+      <c r="O33" t="n">
+        <v>12</v>
+      </c>
+      <c r="P33" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>6</v>
+      </c>
+      <c r="R33" t="n">
+        <v>4</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="n">
+        <v>15</v>
+      </c>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>SIiBpBrs</t>
+        </is>
+      </c>
+      <c r="Y33" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="n">
+        <v>26.44444444444444</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>182.5555555555555</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>64.55555555555556</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>833333.3333333334</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>67.77777777777777</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>22.83333333333333</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>176.8333333333333</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>63.25</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>804166.6666666666</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>21.66666666666667</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>61.83333333333334</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>708333.3333333334</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>69.33333333333333</v>
+      </c>
+      <c r="BC33" t="inlineStr"/>
+      <c r="BD33" t="inlineStr"/>
+      <c r="BE33" t="inlineStr"/>
+      <c r="BF33" t="inlineStr"/>
+      <c r="BG33" t="inlineStr"/>
+      <c r="BH33" t="inlineStr"/>
+      <c r="BI33" t="inlineStr"/>
+      <c r="BJ33" t="inlineStr"/>
+      <c r="BK33" t="inlineStr"/>
+      <c r="BL33" t="inlineStr"/>
+      <c r="BM33" t="inlineStr"/>
+      <c r="BN33" t="inlineStr"/>
+      <c r="BO33" t="inlineStr"/>
+      <c r="BP33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>dGo94DZQ</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kherradji a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade des alpes
+  grenoble </t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>20068</v>
+      </c>
+      <c r="F34" t="n">
+        <v>4008</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>E1wDrLsJ</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="n">
+        <v>6</v>
+      </c>
+      <c r="P34" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>4</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Ys1Pb7ws</t>
+        </is>
+      </c>
+      <c r="Y34" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="n">
+        <v>25.72727272727273</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>182.8181818181818</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>67.63636363636364</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1495454.545454545</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>71.36363636363636</v>
+      </c>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="inlineStr"/>
+      <c r="AQ34" t="n">
+        <v>29.66666666666667</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>185.1666666666667</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>1937500</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>24.8125</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>64.3125</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>958750</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>71.3125</v>
+      </c>
+      <c r="BC34" t="inlineStr"/>
+      <c r="BD34" t="inlineStr"/>
+      <c r="BE34" t="inlineStr"/>
+      <c r="BF34" t="inlineStr"/>
+      <c r="BG34" t="inlineStr"/>
+      <c r="BH34" t="inlineStr"/>
+      <c r="BI34" t="inlineStr"/>
+      <c r="BJ34" t="inlineStr"/>
+      <c r="BK34" t="inlineStr"/>
+      <c r="BL34" t="inlineStr"/>
+      <c r="BM34" t="inlineStr"/>
+      <c r="BN34" t="inlineStr"/>
+      <c r="BO34" t="inlineStr"/>
+      <c r="BP34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>b15XX7Nt</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de roudourou
+  guingamp </t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>19060</v>
+      </c>
+      <c r="F35" t="n">
+        <v>6052</v>
+      </c>
+      <c r="G35" t="n">
+        <v>4</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>QDfKl36E</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fsfAHubD</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="n">
+        <v>49</v>
+      </c>
+      <c r="N35" t="n">
+        <v>51</v>
+      </c>
+      <c r="O35" t="n">
+        <v>16</v>
+      </c>
+      <c r="P35" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>5</v>
+      </c>
+      <c r="R35" t="n">
+        <v>3</v>
+      </c>
+      <c r="S35" t="n">
+        <v>9</v>
+      </c>
+      <c r="T35" t="n">
+        <v>12</v>
+      </c>
+      <c r="U35" t="n">
+        <v>9</v>
+      </c>
+      <c r="V35" t="n">
+        <v>14</v>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>QNSJnsB5</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>4vG8dmrf</t>
+        </is>
+      </c>
+      <c r="Y35" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>179.9</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1025000</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>27.625</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>177.625</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>67.375</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>1275000</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>70.375</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>179.7</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>950000</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>20.41666666666667</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>179.6666666666667</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>912500</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>70.91666666666667</v>
+      </c>
+      <c r="BC35" t="inlineStr"/>
+      <c r="BD35" t="inlineStr"/>
+      <c r="BE35" t="inlineStr"/>
+      <c r="BF35" t="inlineStr"/>
+      <c r="BG35" t="inlineStr"/>
+      <c r="BH35" t="inlineStr"/>
+      <c r="BI35" t="inlineStr"/>
+      <c r="BJ35" t="inlineStr"/>
+      <c r="BK35" t="inlineStr"/>
+      <c r="BL35" t="inlineStr"/>
+      <c r="BM35" t="inlineStr"/>
+      <c r="BN35" t="inlineStr"/>
+      <c r="BO35" t="inlineStr"/>
+      <c r="BP35" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
+++ b/data/france/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP35"/>
+  <dimension ref="A1:BP37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,93 +772,93 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ObHze1pe</t>
+          <t>0pvInj5s</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45529.5</v>
+        <v>45530.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">angoula g 
+          <t xml:space="preserve">bouille t 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la beaujoire
-  nantes </t>
+          <t xml:space="preserve">stade bauer
+  paris   saint ouen </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>35322</v>
+        <v>10000</v>
       </c>
       <c r="F2" t="n">
-        <v>30389</v>
+        <v>4560</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>2kM6ufaS</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.61</v>
-      </c>
+          <t>2aeoANM8</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N2" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="O2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S2" t="n">
+        <v>15</v>
+      </c>
+      <c r="T2" t="n">
+        <v>15</v>
+      </c>
+      <c r="U2" t="n">
+        <v>13</v>
+      </c>
+      <c r="V2" t="n">
         <v>8</v>
       </c>
-      <c r="P2" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>6</v>
-      </c>
-      <c r="R2" t="n">
-        <v>3</v>
-      </c>
-      <c r="S2" t="n">
-        <v>9</v>
-      </c>
-      <c r="T2" t="n">
-        <v>6</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
-          <t>YTLwacK1</t>
+          <t>SzfSpYcf</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>OpNm82MB</t>
+          <t>8tmnzqxe</t>
         </is>
       </c>
       <c r="Y2" t="n">
         <v>55</v>
       </c>
       <c r="Z2" t="n">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -866,208 +866,166 @@
       <c r="AB2" t="n">
         <v>20242025</v>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>181.3</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>72.90000000000001</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>5490000</v>
-      </c>
-      <c r="AJ2" t="n">
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>176.4444444444445</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>65.11111111111111</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>722222.2222222222</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>68.55555555555556</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>187</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>66</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1687500</v>
+      </c>
+      <c r="AV2" t="n">
         <v>77</v>
       </c>
-      <c r="AK2" t="n">
-        <v>26.25</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>182.25</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>69.125</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1834375</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>72</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>26.21428571428572</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>183</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1.428571428571429</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>71.78571428571429</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3857142.857142857</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>73.92857142857143</v>
-      </c>
       <c r="AW2" t="n">
-        <v>23.90909090909091</v>
+        <v>24.52380952380953</v>
       </c>
       <c r="AX2" t="n">
-        <v>181.2727272727273</v>
+        <v>182.4761904761905</v>
       </c>
       <c r="AY2" t="n">
         <v>1</v>
       </c>
       <c r="AZ2" t="n">
-        <v>64.27272727272727</v>
+        <v>65.76190476190476</v>
       </c>
       <c r="BA2" t="n">
-        <v>1077272.727272727</v>
+        <v>1139285.714285714</v>
       </c>
       <c r="BB2" t="n">
-        <v>71.18181818181819</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>177.5</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>280</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>10425000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>293</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>22</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>181.6</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>322</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>6050000</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>363</v>
-      </c>
+        <v>71.57142857142857</v>
+      </c>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8nivFMyR</t>
+          <t>hhlQ5IbD</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45529.5</v>
+        <v>45529.65625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">dechepy b 
+          <t xml:space="preserve">ben el hadj salem h 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz riviera
-  nice </t>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>36178</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>67394</v>
+      </c>
+      <c r="F3" t="n">
+        <v>63841</v>
+      </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1.27</v>
+        <v>2.66</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="M3" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="N3" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="O3" t="n">
+        <v>16</v>
+      </c>
+      <c r="P3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q3" t="n">
         <v>10</v>
-      </c>
-      <c r="P3" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>4</v>
       </c>
       <c r="R3" t="n">
         <v>3</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T3" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
-          <t>d0X3cO3I</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>UapruDaf</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
       <c r="Y3" t="n">
@@ -1084,115 +1042,105 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>lhUkVMh2</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="n">
-        <v>23.11111111111111</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>183.2222222222222</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.111111111111111</v>
-      </c>
-      <c r="AH3" t="n">
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>178</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>11320000</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>183.9333333333333</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.066666666666667</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>67.86666666666666</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>3386666.666666667</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>77.86666666666666</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>182</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>135</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>5700000</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>153</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>180</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN3" t="n">
         <v>74</v>
       </c>
-      <c r="AI3" t="n">
-        <v>10166666.66666667</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>79.88888888888889</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>23.22222222222222</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>180.6666666666667</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.111111111111111</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>72.66666666666667</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>5355555.555555556</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>78.22222222222223</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>22.3125</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>180.5625</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>72.625</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>5893750</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>78.4375</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>24.0625</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>179.25</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>70.375</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>2862500</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>75.875</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>179</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>308</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>52500000</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>317</v>
-      </c>
-      <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="inlineStr"/>
-      <c r="BN3" t="inlineStr"/>
-      <c r="BO3" t="inlineStr"/>
-      <c r="BP3" t="inlineStr"/>
+      <c r="BO3" t="n">
+        <v>9500000</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>xrJSdNFr</t>
+          <t>8nivFMyR</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -1200,78 +1148,76 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">wattellier e 
+          <t xml:space="preserve">dechepy b 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la meinau
-  strasbourg </t>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>26109</v>
-      </c>
-      <c r="F4" t="n">
-        <v>19026</v>
-      </c>
+        <v>36178</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>56</v>
+      </c>
+      <c r="N4" t="n">
+        <v>44</v>
+      </c>
+      <c r="O4" t="n">
+        <v>10</v>
+      </c>
+      <c r="P4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R4" t="n">
         <v>3</v>
       </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M4" t="n">
-        <v>59</v>
-      </c>
-      <c r="N4" t="n">
-        <v>41</v>
-      </c>
-      <c r="O4" t="n">
-        <v>9</v>
-      </c>
-      <c r="P4" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>5</v>
-      </c>
-      <c r="R4" t="n">
-        <v>5</v>
-      </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
-          <t>4fMAHvLm</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>pCcFFE7M</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="Y4" t="n">
@@ -1288,141 +1234,137 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>4v0yqlWc</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>21.11111111111111</v>
+        <v>23.11111111111111</v>
       </c>
       <c r="AF4" t="n">
-        <v>184.5555555555555</v>
+        <v>183.2222222222222</v>
       </c>
       <c r="AG4" t="n">
-        <v>1</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="AH4" t="n">
-        <v>70.55555555555556</v>
+        <v>74</v>
       </c>
       <c r="AI4" t="n">
-        <v>4291666.666666667</v>
+        <v>10166666.66666667</v>
       </c>
       <c r="AJ4" t="n">
-        <v>80.22222222222223</v>
+        <v>79.88888888888889</v>
       </c>
       <c r="AK4" t="n">
-        <v>24.875</v>
+        <v>23.22222222222222</v>
       </c>
       <c r="AL4" t="n">
-        <v>180.25</v>
+        <v>180.6666666666667</v>
       </c>
       <c r="AM4" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>72.66666666666667</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>5355555.555555556</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>78.22222222222223</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>22.3125</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>180.5625</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>72.625</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>5893750</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>78.4375</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>24.0625</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>179.25</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>70.375</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>2862500</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>75.875</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>179</v>
+      </c>
+      <c r="BE4" t="n">
         <v>1.75</v>
       </c>
-      <c r="AN4" t="n">
-        <v>75.25</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>8725000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>79.375</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>19.84615384615385</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>183.0769230769231</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>69.46153846153847</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3638461.538461538</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>80.84615384615384</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>180.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>73.40000000000001</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>7865000</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="n">
-        <v>20</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>189</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>72</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>78</v>
-      </c>
+      <c r="BF4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>308</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>52500000</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>317</v>
+      </c>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
+      <c r="BO4" t="inlineStr"/>
+      <c r="BP4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>OCd990al</t>
+          <t>ObHze1pe</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45529.41666666666</v>
+        <v>45529.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">pignard j 
+          <t xml:space="preserve">angoula g 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade bollaert delelis
-  lens </t>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>38223</v>
+        <v>35322</v>
       </c>
       <c r="F5" t="n">
-        <v>37435</v>
+        <v>30389</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
@@ -1432,40 +1374,40 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="L5" t="n">
-        <v>0.67</v>
+        <v>1.61</v>
       </c>
       <c r="M5" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="N5" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="O5" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="P5" t="n">
         <v>10</v>
       </c>
       <c r="Q5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T5" t="n">
         <v>6</v>
@@ -1474,12 +1416,12 @@
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
-          <t>K6b7RoBp</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0tIbS515</t>
+          <t>OpNm82MB</t>
         </is>
       </c>
       <c r="Y5" t="n">
@@ -1496,185 +1438,185 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>25.9</v>
+        <v>23.9</v>
       </c>
       <c r="AF5" t="n">
-        <v>182.8</v>
+        <v>181.3</v>
       </c>
       <c r="AG5" t="n">
         <v>1.4</v>
       </c>
       <c r="AH5" t="n">
-        <v>76</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="AI5" t="n">
-        <v>12940000</v>
+        <v>5490000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>79.8</v>
+        <v>77</v>
       </c>
       <c r="AK5" t="n">
-        <v>27.9</v>
+        <v>26.25</v>
       </c>
       <c r="AL5" t="n">
-        <v>179.8</v>
+        <v>182.25</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AN5" t="n">
-        <v>74.3</v>
+        <v>69.125</v>
       </c>
       <c r="AO5" t="n">
-        <v>6200000</v>
+        <v>1834375</v>
       </c>
       <c r="AP5" t="n">
-        <v>75.5</v>
+        <v>72</v>
       </c>
       <c r="AQ5" t="n">
-        <v>24.55</v>
+        <v>26.21428571428572</v>
       </c>
       <c r="AR5" t="n">
-        <v>181.7</v>
+        <v>183</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.3</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="AT5" t="n">
-        <v>74.2</v>
+        <v>71.78571428571429</v>
       </c>
       <c r="AU5" t="n">
-        <v>7215000</v>
+        <v>3857142.857142857</v>
       </c>
       <c r="AV5" t="n">
-        <v>78.05</v>
+        <v>73.92857142857143</v>
       </c>
       <c r="AW5" t="n">
-        <v>24</v>
+        <v>23.90909090909091</v>
       </c>
       <c r="AX5" t="n">
-        <v>181.6666666666667</v>
+        <v>181.2727272727273</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.133333333333333</v>
+        <v>1</v>
       </c>
       <c r="AZ5" t="n">
-        <v>69.53333333333333</v>
+        <v>64.27272727272727</v>
       </c>
       <c r="BA5" t="n">
-        <v>3973333.333333333</v>
+        <v>1077272.727272727</v>
       </c>
       <c r="BB5" t="n">
-        <v>74.66666666666667</v>
+        <v>71.18181818181819</v>
       </c>
       <c r="BC5" t="n">
-        <v>25</v>
+        <v>25.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>179</v>
+        <v>177.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="BF5" t="n">
         <v>4</v>
       </c>
       <c r="BG5" t="n">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="BH5" t="n">
-        <v>28600000</v>
+        <v>10425000</v>
       </c>
       <c r="BI5" t="n">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="BJ5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BK5" t="n">
-        <v>180</v>
+        <v>181.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BN5" t="n">
-        <v>76</v>
+        <v>322</v>
       </c>
       <c r="BO5" t="n">
-        <v>11500000</v>
+        <v>6050000</v>
       </c>
       <c r="BP5" t="n">
-        <v>82</v>
+        <v>363</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>KQAqguF7</t>
+          <t>xrJSdNFr</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45528.66666666666</v>
+        <v>45529.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">batta f 
+          <t xml:space="preserve">wattellier e 
   fra </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade geoffroy guichard
-  saint etienne </t>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>42000</v>
+        <v>26109</v>
       </c>
       <c r="F6" t="n">
-        <v>16958</v>
+        <v>19026</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1.31</v>
+        <v>0.9</v>
       </c>
       <c r="L6" t="n">
-        <v>2.24</v>
+        <v>1.34</v>
       </c>
       <c r="M6" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O6" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="P6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
@@ -1683,21 +1625,21 @@
         <v>5</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T6" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
-          <t>tAufB9Mi</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>dWZTBmVT</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
       <c r="Y6" t="n">
@@ -1712,67 +1654,87 @@
       <c r="AB6" t="n">
         <v>20242025</v>
       </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>21.11111111111111</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>184.5555555555555</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>70.55555555555556</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>4291666.666666667</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>80.22222222222223</v>
+      </c>
       <c r="AK6" t="n">
-        <v>24.2</v>
+        <v>24.875</v>
       </c>
       <c r="AL6" t="n">
-        <v>186.9</v>
+        <v>180.25</v>
       </c>
       <c r="AM6" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="AN6" t="n">
-        <v>71.09999999999999</v>
+        <v>75.25</v>
       </c>
       <c r="AO6" t="n">
-        <v>3020000</v>
+        <v>8725000</v>
       </c>
       <c r="AP6" t="n">
-        <v>75.8</v>
+        <v>79.375</v>
       </c>
       <c r="AQ6" t="n">
-        <v>25.23529411764706</v>
+        <v>19.84615384615385</v>
       </c>
       <c r="AR6" t="n">
-        <v>180.1764705882353</v>
+        <v>183.0769230769231</v>
       </c>
       <c r="AS6" t="n">
         <v>1</v>
       </c>
       <c r="AT6" t="n">
-        <v>66.47058823529412</v>
+        <v>69.46153846153847</v>
       </c>
       <c r="AU6" t="n">
-        <v>1260294.117647059</v>
+        <v>3638461.538461538</v>
       </c>
       <c r="AV6" t="n">
-        <v>71.94117647058823</v>
+        <v>80.84615384615384</v>
       </c>
       <c r="AW6" t="n">
-        <v>24.31818181818182</v>
+        <v>23.2</v>
       </c>
       <c r="AX6" t="n">
         <v>180.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>69.40909090909091</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="BA6" t="n">
-        <v>2295454.545454545</v>
+        <v>7865000</v>
       </c>
       <c r="BB6" t="n">
-        <v>73.54545454545455</v>
+        <v>78.3</v>
       </c>
       <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="inlineStr"/>
@@ -1782,10 +1744,10 @@
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr"/>
       <c r="BJ6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BK6" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BL6" t="n">
         <v>1</v>
@@ -1794,41 +1756,41 @@
         <v>1</v>
       </c>
       <c r="BN6" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="BO6" t="n">
-        <v>1300000</v>
+        <v>2900000</v>
       </c>
       <c r="BP6" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
+          <t>OCd990al</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45528.58333333334</v>
+        <v>45529.41666666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">kherradji a 
+          <t xml:space="preserve">pignard j 
   fra </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade pierre mauroy
-  villeneuve d ascq </t>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>50186</v>
+        <v>38223</v>
       </c>
       <c r="F7" t="n">
-        <v>36906</v>
+        <v>37435</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
@@ -1838,54 +1800,54 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1.24</v>
+        <v>1.95</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="M7" t="n">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="N7" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="O7" t="n">
+        <v>22</v>
+      </c>
+      <c r="P7" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q7" t="n">
         <v>11</v>
-      </c>
-      <c r="P7" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>6</v>
       </c>
       <c r="R7" t="n">
         <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T7" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
-          <t>nVS1TlC4</t>
+          <t>K6b7RoBp</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>6FKPxxgf</t>
+          <t>0tIbS515</t>
         </is>
       </c>
       <c r="Y7" t="n">
@@ -1902,151 +1864,151 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="n">
-        <v>22.625</v>
+        <v>25.9</v>
       </c>
       <c r="AF7" t="n">
-        <v>181.75</v>
+        <v>182.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.375</v>
+        <v>1.4</v>
       </c>
       <c r="AH7" t="n">
-        <v>74.5</v>
+        <v>76</v>
       </c>
       <c r="AI7" t="n">
-        <v>11625000</v>
+        <v>12940000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>81.5</v>
+        <v>79.8</v>
       </c>
       <c r="AK7" t="n">
-        <v>25.1</v>
+        <v>27.9</v>
       </c>
       <c r="AL7" t="n">
-        <v>185.4</v>
+        <v>179.8</v>
       </c>
       <c r="AM7" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AN7" t="n">
-        <v>67.3</v>
+        <v>74.3</v>
       </c>
       <c r="AO7" t="n">
-        <v>1507500</v>
+        <v>6200000</v>
       </c>
       <c r="AP7" t="n">
-        <v>73</v>
+        <v>75.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>25.07142857142857</v>
+        <v>24.55</v>
       </c>
       <c r="AR7" t="n">
-        <v>179.3571428571429</v>
+        <v>181.7</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.357142857142857</v>
+        <v>1.3</v>
       </c>
       <c r="AT7" t="n">
-        <v>73</v>
+        <v>74.2</v>
       </c>
       <c r="AU7" t="n">
-        <v>6525000</v>
+        <v>7215000</v>
       </c>
       <c r="AV7" t="n">
-        <v>78.64285714285714</v>
+        <v>78.05</v>
       </c>
       <c r="AW7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>181.6666666666667</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.133333333333333</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>69.53333333333333</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>3973333.333333333</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>74.66666666666667</v>
+      </c>
+      <c r="BC7" t="n">
         <v>25</v>
       </c>
-      <c r="AX7" t="n">
-        <v>181.1739130434783</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>66.34782608695652</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1292391.304347826</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>71.95652173913044</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>27.33333333333333</v>
-      </c>
       <c r="BD7" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.666666666666667</v>
+        <v>1</v>
       </c>
       <c r="BF7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BG7" t="n">
-        <v>461</v>
+        <v>298</v>
       </c>
       <c r="BH7" t="n">
-        <v>66800000</v>
+        <v>28600000</v>
       </c>
       <c r="BI7" t="n">
-        <v>471</v>
+        <v>310</v>
       </c>
       <c r="BJ7" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BK7" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BL7" t="n">
         <v>1</v>
       </c>
       <c r="BM7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BN7" t="n">
-        <v>131</v>
+        <v>76</v>
       </c>
       <c r="BO7" t="n">
-        <v>2325000</v>
+        <v>11500000</v>
       </c>
       <c r="BP7" t="n">
-        <v>144</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
+          <t>KQAqguF7</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45528.5</v>
+        <v>45528.66666666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">frappart s 
+          <t xml:space="preserve">batta f 
   fra </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">parc olympique lyonnais
-  lyon </t>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>59186</v>
+        <v>42000</v>
       </c>
       <c r="F8" t="n">
-        <v>54392</v>
+        <v>16958</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -2056,54 +2018,54 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0.44</v>
+        <v>1.31</v>
       </c>
       <c r="L8" t="n">
-        <v>2.82</v>
+        <v>2.24</v>
       </c>
       <c r="M8" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="N8" t="n">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="P8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
-          <t>YHU1oFVQ</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>CWxpUrtf</t>
+          <t>dWZTBmVT</t>
         </is>
       </c>
       <c r="Y8" t="n">
@@ -2119,82 +2081,66 @@
         <v>20242025</v>
       </c>
       <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="AE8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>179.7777777777778</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>75.66666666666667</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>10300000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>79.77777777777777</v>
-      </c>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="n">
-        <v>23.9</v>
+        <v>24.2</v>
       </c>
       <c r="AL8" t="n">
-        <v>183.4</v>
+        <v>186.9</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AN8" t="n">
-        <v>75.90000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="AO8" t="n">
-        <v>11600000</v>
+        <v>3020000</v>
       </c>
       <c r="AP8" t="n">
-        <v>80.8</v>
+        <v>75.8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>24.95652173913043</v>
+        <v>25.23529411764706</v>
       </c>
       <c r="AR8" t="n">
-        <v>180.7391304347826</v>
+        <v>180.1764705882353</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.739130434782609</v>
+        <v>1</v>
       </c>
       <c r="AT8" t="n">
-        <v>74.39130434782609</v>
+        <v>66.47058823529412</v>
       </c>
       <c r="AU8" t="n">
-        <v>7004347.826086956</v>
+        <v>1260294.117647059</v>
       </c>
       <c r="AV8" t="n">
-        <v>79.47826086956522</v>
+        <v>71.94117647058823</v>
       </c>
       <c r="AW8" t="n">
-        <v>21.16666666666667</v>
+        <v>24.31818181818182</v>
       </c>
       <c r="AX8" t="n">
-        <v>183.1666666666667</v>
+        <v>180.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.222222222222222</v>
+        <v>1</v>
       </c>
       <c r="AZ8" t="n">
-        <v>73.72222222222223</v>
+        <v>69.40909090909091</v>
       </c>
       <c r="BA8" t="n">
-        <v>11236111.11111111</v>
+        <v>2295454.545454545</v>
       </c>
       <c r="BB8" t="n">
-        <v>82</v>
+        <v>73.54545454545455</v>
       </c>
       <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="inlineStr"/>
@@ -2204,10 +2150,10 @@
       <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="inlineStr"/>
       <c r="BJ8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BK8" t="n">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="BL8" t="n">
         <v>1</v>
@@ -2216,40 +2162,42 @@
         <v>1</v>
       </c>
       <c r="BN8" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="BO8" t="n">
-        <v>2200000</v>
+        <v>1300000</v>
       </c>
       <c r="BP8" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2yXIHV57</t>
+          <t>CKcVGr7E</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45528.39583333334</v>
+        <v>45528.58333333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">benchabane f 
+          <t xml:space="preserve">kherradji a 
   fra </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade du moustoir
-  lorient </t>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>16787</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
+        <v>50186</v>
+      </c>
+      <c r="F9" t="n">
+        <v>36906</v>
+      </c>
       <c r="G9" t="n">
         <v>2</v>
       </c>
@@ -2258,61 +2206,61 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>jgNAYRGi</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>UgPj1p1N</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="M9" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="N9" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="O9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P9" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T9" t="n">
-        <v>10</v>
-      </c>
-      <c r="U9" t="n">
-        <v>6</v>
-      </c>
-      <c r="V9" t="n">
-        <v>5</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Cp0gM1r4</t>
+          <t>nVS1TlC4</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>WrQARdPN</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
       <c r="Y9" t="n">
         <v>55</v>
       </c>
       <c r="Z9" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -2322,180 +2270,208 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="n">
-        <v>24.44444444444444</v>
+        <v>22.625</v>
       </c>
       <c r="AF9" t="n">
-        <v>178.1111111111111</v>
+        <v>181.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>1</v>
+        <v>1.375</v>
       </c>
       <c r="AH9" t="n">
-        <v>71.77777777777777</v>
+        <v>74.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>4622222.222222222</v>
+        <v>11625000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>77.11111111111111</v>
+        <v>81.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>26</v>
+        <v>25.1</v>
       </c>
       <c r="AL9" t="n">
-        <v>182.6363636363636</v>
+        <v>185.4</v>
       </c>
       <c r="AM9" t="n">
         <v>1</v>
       </c>
       <c r="AN9" t="n">
-        <v>66.72727272727273</v>
+        <v>67.3</v>
       </c>
       <c r="AO9" t="n">
-        <v>1343181.818181818</v>
+        <v>1507500</v>
       </c>
       <c r="AP9" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AQ9" t="n">
-        <v>20.92857142857143</v>
+        <v>25.07142857142857</v>
       </c>
       <c r="AR9" t="n">
-        <v>178.5714285714286</v>
+        <v>179.3571428571429</v>
       </c>
       <c r="AS9" t="n">
-        <v>1</v>
+        <v>1.357142857142857</v>
       </c>
       <c r="AT9" t="n">
-        <v>68.28571428571429</v>
+        <v>73</v>
       </c>
       <c r="AU9" t="n">
-        <v>2466071.428571429</v>
+        <v>6525000</v>
       </c>
       <c r="AV9" t="n">
-        <v>78.42857142857143</v>
+        <v>78.64285714285714</v>
       </c>
       <c r="AW9" t="n">
-        <v>26.38461538461538</v>
+        <v>25</v>
       </c>
       <c r="AX9" t="n">
-        <v>184.3076923076923</v>
+        <v>181.1739130434783</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.153846153846154</v>
+        <v>1</v>
       </c>
       <c r="AZ9" t="n">
-        <v>66.38461538461539</v>
+        <v>66.34782608695652</v>
       </c>
       <c r="BA9" t="n">
-        <v>1365384.615384615</v>
+        <v>1292391.304347826</v>
       </c>
       <c r="BB9" t="n">
-        <v>71.69230769230769</v>
-      </c>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
-      <c r="BI9" t="inlineStr"/>
-      <c r="BJ9" t="inlineStr"/>
-      <c r="BK9" t="inlineStr"/>
-      <c r="BL9" t="inlineStr"/>
-      <c r="BM9" t="inlineStr"/>
-      <c r="BN9" t="inlineStr"/>
-      <c r="BO9" t="inlineStr"/>
-      <c r="BP9" t="inlineStr"/>
+        <v>71.95652173913044</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>178</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>461</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>66800000</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>471</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>23</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>176</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>131</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>2325000</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>144</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>ppvl45N8</t>
+          <t>pSpI7vU0</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45527.65625</v>
+        <v>45528.5</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">bollengier m 
+          <t xml:space="preserve">frappart s 
   fra </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">parc des princes
-  paris </t>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>48229</v>
+        <v>59186</v>
       </c>
       <c r="F10" t="n">
-        <v>46000</v>
+        <v>54392</v>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>2.94</v>
+        <v>0.44</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4</v>
+        <v>2.82</v>
       </c>
       <c r="M10" t="n">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="N10" t="n">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="O10" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>4</v>
+      </c>
+      <c r="S10" t="n">
         <v>10</v>
       </c>
-      <c r="R10" t="n">
-        <v>3</v>
-      </c>
-      <c r="S10" t="n">
-        <v>9</v>
-      </c>
       <c r="T10" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
-          <t>8MdrBIUb</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>vVQcGxl1</t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
       <c r="Y10" t="n">
@@ -2513,195 +2489,191 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="AE10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>179.7777777777778</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>75.66666666666667</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>10300000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>79.77777777777777</v>
+      </c>
       <c r="AK10" t="n">
-        <v>26.45454545454545</v>
+        <v>23.9</v>
       </c>
       <c r="AL10" t="n">
-        <v>180.2727272727273</v>
+        <v>183.4</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.454545454545455</v>
+        <v>1.4</v>
       </c>
       <c r="AN10" t="n">
-        <v>73.90909090909091</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AO10" t="n">
-        <v>5527272.727272728</v>
+        <v>11600000</v>
       </c>
       <c r="AP10" t="n">
-        <v>77.27272727272727</v>
+        <v>80.8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>22.2</v>
+        <v>24.95652173913043</v>
       </c>
       <c r="AR10" t="n">
-        <v>184</v>
+        <v>180.7391304347826</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.866666666666667</v>
+        <v>1.739130434782609</v>
       </c>
       <c r="AT10" t="n">
-        <v>77.93333333333334</v>
+        <v>74.39130434782609</v>
       </c>
       <c r="AU10" t="n">
-        <v>27520000</v>
+        <v>7004347.826086956</v>
       </c>
       <c r="AV10" t="n">
-        <v>84.33333333333333</v>
+        <v>79.47826086956522</v>
       </c>
       <c r="AW10" t="n">
-        <v>25.08333333333333</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="AX10" t="n">
-        <v>181.75</v>
+        <v>183.1666666666667</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.25</v>
+        <v>1.222222222222222</v>
       </c>
       <c r="AZ10" t="n">
-        <v>71.33333333333333</v>
+        <v>73.72222222222223</v>
       </c>
       <c r="BA10" t="n">
-        <v>5383333.333333333</v>
+        <v>11236111.11111111</v>
       </c>
       <c r="BB10" t="n">
-        <v>76.33333333333333</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>27.71428571428572</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>183.7142857142857</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>2.571428571428572</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>563</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>162500000</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>568</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
       <c r="BJ10" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="BK10" t="n">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="BL10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM10" t="n">
         <v>1</v>
       </c>
       <c r="BN10" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="BO10" t="n">
-        <v>3500000</v>
+        <v>2200000</v>
       </c>
       <c r="BP10" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>WUmnhCsK</t>
+          <t>2yXIHV57</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45527.625</v>
+        <v>45528.39583333334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">taleb a 
+          <t xml:space="preserve">benchabane f 
   fra </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la licorne
-  amiens </t>
+          <t xml:space="preserve">stade du moustoir
+  lorient </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>12097</v>
-      </c>
-      <c r="F11" t="n">
-        <v>608</v>
-      </c>
+        <v>16787</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0OEHEprs</t>
+          <t>jgNAYRGi</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>tAAobNse</t>
+          <t>UgPj1p1N</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="N11" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="O11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P11" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S11" t="n">
+        <v>12</v>
+      </c>
+      <c r="T11" t="n">
+        <v>10</v>
+      </c>
+      <c r="U11" t="n">
         <v>6</v>
       </c>
-      <c r="Q11" t="n">
-        <v>4</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>8</v>
-      </c>
-      <c r="T11" t="n">
-        <v>17</v>
-      </c>
-      <c r="U11" t="n">
-        <v>14</v>
-      </c>
       <c r="V11" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>zB2j3YvM</t>
+          <t>Cp0gM1r4</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>lb31RXzP</t>
+          <t>WrQARdPN</t>
         </is>
       </c>
       <c r="Y11" t="n">
@@ -2716,67 +2688,83 @@
       <c r="AB11" t="n">
         <v>20242025</v>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="n">
-        <v>24.11111111111111</v>
+        <v>24.44444444444444</v>
       </c>
       <c r="AF11" t="n">
-        <v>178.8888888888889</v>
+        <v>178.1111111111111</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.111111111111111</v>
+        <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>67.33333333333333</v>
+        <v>71.77777777777777</v>
       </c>
       <c r="AI11" t="n">
-        <v>1747222.222222222</v>
+        <v>4622222.222222222</v>
       </c>
       <c r="AJ11" t="n">
-        <v>71.66666666666667</v>
-      </c>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
+        <v>77.11111111111111</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>182.6363636363636</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>66.72727272727273</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1343181.818181818</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>70</v>
+      </c>
       <c r="AQ11" t="n">
-        <v>26.17647058823529</v>
+        <v>20.92857142857143</v>
       </c>
       <c r="AR11" t="n">
-        <v>177.1764705882353</v>
+        <v>178.5714285714286</v>
       </c>
       <c r="AS11" t="n">
         <v>1</v>
       </c>
       <c r="AT11" t="n">
-        <v>66.17647058823529</v>
+        <v>68.28571428571429</v>
       </c>
       <c r="AU11" t="n">
-        <v>1182352.941176471</v>
+        <v>2466071.428571429</v>
       </c>
       <c r="AV11" t="n">
-        <v>69.23529411764706</v>
+        <v>78.42857142857143</v>
       </c>
       <c r="AW11" t="n">
-        <v>22.25</v>
+        <v>26.38461538461538</v>
       </c>
       <c r="AX11" t="n">
-        <v>179.5833333333333</v>
+        <v>184.3076923076923</v>
       </c>
       <c r="AY11" t="n">
-        <v>1</v>
+        <v>1.153846153846154</v>
       </c>
       <c r="AZ11" t="n">
-        <v>63.83333333333334</v>
+        <v>66.38461538461539</v>
       </c>
       <c r="BA11" t="n">
-        <v>931250</v>
+        <v>1365384.615384615</v>
       </c>
       <c r="BB11" t="n">
-        <v>72.91666666666667</v>
+        <v>71.69230769230769</v>
       </c>
       <c r="BC11" t="inlineStr"/>
       <c r="BD11" t="inlineStr"/>
@@ -2796,93 +2784,93 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>GM5aU8kD</t>
+          <t>ppvl45N8</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45527.625</v>
+        <v>45527.65625</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">bastien b 
+          <t xml:space="preserve">bollengier m 
   fra </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">parc des sports
-  annecy </t>
+          <t xml:space="preserve">parc des princes
+  paris </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>15660</v>
+        <v>48229</v>
       </c>
       <c r="F12" t="n">
-        <v>7640</v>
+        <v>46000</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>25dB6Eto</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>ADl76OZP</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.4</v>
+      </c>
       <c r="M12" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="N12" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="O12" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="P12" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q12" t="n">
         <v>10</v>
       </c>
-      <c r="Q12" t="n">
-        <v>7</v>
-      </c>
       <c r="R12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T12" t="n">
-        <v>13</v>
-      </c>
-      <c r="U12" t="n">
-        <v>8</v>
-      </c>
-      <c r="V12" t="n">
-        <v>20</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
-          <t>SIiBpBrs</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>EwpPg8iH</t>
+          <t>vVQcGxl1</t>
         </is>
       </c>
       <c r="Y12" t="n">
         <v>55</v>
       </c>
       <c r="Z12" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2891,69 +2879,113 @@
         <v>20242025</v>
       </c>
       <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>182</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>64.44444444444444</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>841666.6666666666</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>68.11111111111111</v>
-      </c>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="n">
+        <v>26.45454545454545</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>180.2727272727273</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>73.90909090909091</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>5527272.727272728</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>77.27272727272727</v>
+      </c>
       <c r="AQ12" t="n">
-        <v>24.81818181818182</v>
+        <v>22.2</v>
       </c>
       <c r="AR12" t="n">
-        <v>181.2727272727273</v>
+        <v>184</v>
       </c>
       <c r="AS12" t="n">
-        <v>1</v>
+        <v>1.866666666666667</v>
       </c>
       <c r="AT12" t="n">
-        <v>64.36363636363636</v>
+        <v>77.93333333333334</v>
       </c>
       <c r="AU12" t="n">
-        <v>881818.1818181818</v>
+        <v>27520000</v>
       </c>
       <c r="AV12" t="n">
-        <v>70.36363636363636</v>
-      </c>
-      <c r="AW12" t="inlineStr"/>
-      <c r="AX12" t="inlineStr"/>
-      <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr"/>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
-      <c r="BI12" t="inlineStr"/>
-      <c r="BJ12" t="inlineStr"/>
-      <c r="BK12" t="inlineStr"/>
-      <c r="BL12" t="inlineStr"/>
-      <c r="BM12" t="inlineStr"/>
-      <c r="BN12" t="inlineStr"/>
-      <c r="BO12" t="inlineStr"/>
-      <c r="BP12" t="inlineStr"/>
+        <v>84.33333333333333</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>25.08333333333333</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>71.33333333333333</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>5383333.333333333</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>76.33333333333333</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>27.71428571428572</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>183.7142857142857</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>2.571428571428572</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>563</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>162500000</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>568</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>30</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>196</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>74</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -3506,7 +3538,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>MaSQpUZg</t>
+          <t>WUmnhCsK</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -3514,78 +3546,78 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">thual o 
+          <t xml:space="preserve">taleb a 
   fra </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade francis le basser
-  laval </t>
+          <t xml:space="preserve">stade de la licorne
+  amiens </t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>11017</v>
+        <v>12097</v>
       </c>
       <c r="F16" t="n">
-        <v>7282</v>
+        <v>608</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>E1wDrLsJ</t>
+          <t>0OEHEprs</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>QDfKl36E</t>
+          <t>tAAobNse</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="N16" t="n">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="O16" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="P16" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="T16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U16" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="V16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Ys1Pb7ws</t>
+          <t>zB2j3YvM</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>QNSJnsB5</t>
+          <t>lb31RXzP</t>
         </is>
       </c>
       <c r="Y16" t="n">
@@ -3603,76 +3635,64 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="n">
-        <v>26.5</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="AF16" t="n">
-        <v>181.125</v>
+        <v>178.8888888888889</v>
       </c>
       <c r="AG16" t="n">
-        <v>1</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="AH16" t="n">
-        <v>66.75</v>
+        <v>67.33333333333333</v>
       </c>
       <c r="AI16" t="n">
-        <v>1281250</v>
+        <v>1747222.222222222</v>
       </c>
       <c r="AJ16" t="n">
-        <v>72.625</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>24.11111111111111</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>179.8888888888889</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>65.33333333333333</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>1077777.777777778</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>70.44444444444444</v>
-      </c>
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="n">
-        <v>27.25</v>
+        <v>26.17647058823529</v>
       </c>
       <c r="AR16" t="n">
-        <v>177.75</v>
+        <v>177.1764705882353</v>
       </c>
       <c r="AS16" t="n">
         <v>1</v>
       </c>
       <c r="AT16" t="n">
-        <v>64.58333333333333</v>
+        <v>66.17647058823529</v>
       </c>
       <c r="AU16" t="n">
-        <v>832500</v>
+        <v>1182352.941176471</v>
       </c>
       <c r="AV16" t="n">
-        <v>71</v>
+        <v>69.23529411764706</v>
       </c>
       <c r="AW16" t="n">
-        <v>22.22222222222222</v>
+        <v>22.25</v>
       </c>
       <c r="AX16" t="n">
-        <v>180.7777777777778</v>
+        <v>179.5833333333333</v>
       </c>
       <c r="AY16" t="n">
         <v>1</v>
       </c>
       <c r="AZ16" t="n">
-        <v>60.33333333333334</v>
+        <v>63.83333333333334</v>
       </c>
       <c r="BA16" t="n">
-        <v>686111.1111111111</v>
+        <v>931250</v>
       </c>
       <c r="BB16" t="n">
-        <v>69.77777777777777</v>
+        <v>72.91666666666667</v>
       </c>
       <c r="BC16" t="inlineStr"/>
       <c r="BD16" t="inlineStr"/>
@@ -3866,86 +3886,86 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>lEQmcVR0</t>
+          <t>MaSQpUZg</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45523.65625</v>
+        <v>45527.625</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">petit a 
+          <t xml:space="preserve">thual o 
   fra </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade saint symphorien
-  metz </t>
+          <t xml:space="preserve">stade francis le basser
+  laval </t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>28786</v>
+        <v>11017</v>
       </c>
       <c r="F18" t="n">
-        <v>18585</v>
+        <v>7282</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4v0yqlWc</t>
+          <t>E1wDrLsJ</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>AZwK8L6R</t>
+          <t>QDfKl36E</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="N18" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="O18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P18" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S18" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="T18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>h89kUbu5</t>
+          <t>Ys1Pb7ws</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>fo8nHfg4</t>
+          <t>QNSJnsB5</t>
         </is>
       </c>
       <c r="Y18" t="n">
@@ -3960,83 +3980,79 @@
       <c r="AB18" t="n">
         <v>20242025</v>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
+      <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="n">
-        <v>24.90909090909091</v>
+        <v>26.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>177.8181818181818</v>
+        <v>181.125</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.090909090909091</v>
+        <v>1</v>
       </c>
       <c r="AH18" t="n">
-        <v>68.90909090909091</v>
+        <v>66.75</v>
       </c>
       <c r="AI18" t="n">
-        <v>1677272.727272727</v>
+        <v>1281250</v>
       </c>
       <c r="AJ18" t="n">
-        <v>75.27272727272727</v>
+        <v>72.625</v>
       </c>
       <c r="AK18" t="n">
-        <v>25.375</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="AL18" t="n">
-        <v>179.625</v>
+        <v>179.8888888888889</v>
       </c>
       <c r="AM18" t="n">
         <v>1</v>
       </c>
       <c r="AN18" t="n">
-        <v>63.625</v>
+        <v>65.33333333333333</v>
       </c>
       <c r="AO18" t="n">
-        <v>723125</v>
+        <v>1077777.777777778</v>
       </c>
       <c r="AP18" t="n">
-        <v>68.375</v>
+        <v>70.44444444444444</v>
       </c>
       <c r="AQ18" t="n">
-        <v>24</v>
+        <v>27.25</v>
       </c>
       <c r="AR18" t="n">
-        <v>181.0909090909091</v>
+        <v>177.75</v>
       </c>
       <c r="AS18" t="n">
         <v>1</v>
       </c>
       <c r="AT18" t="n">
-        <v>67.81818181818181</v>
+        <v>64.58333333333333</v>
       </c>
       <c r="AU18" t="n">
-        <v>1718181.818181818</v>
+        <v>832500</v>
       </c>
       <c r="AV18" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="AW18" t="n">
-        <v>23.25</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="AX18" t="n">
-        <v>180</v>
+        <v>180.7777777777778</v>
       </c>
       <c r="AY18" t="n">
         <v>1</v>
       </c>
       <c r="AZ18" t="n">
-        <v>61.5</v>
+        <v>60.33333333333334</v>
       </c>
       <c r="BA18" t="n">
-        <v>679166.6666666666</v>
+        <v>686111.1111111111</v>
       </c>
       <c r="BB18" t="n">
-        <v>68.16666666666667</v>
+        <v>69.77777777777777</v>
       </c>
       <c r="BC18" t="inlineStr"/>
       <c r="BD18" t="inlineStr"/>
@@ -4056,86 +4072,86 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>OA5YizjL</t>
+          <t>GM5aU8kD</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45523.65625</v>
+        <v>45527.625</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">thual o 
+          <t xml:space="preserve">bastien b 
   fra </t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade velodrome
-  marseille </t>
+          <t xml:space="preserve">parc des sports
+  annecy </t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>67394</v>
+        <v>15660</v>
       </c>
       <c r="F19" t="n">
-        <v>2655</v>
+        <v>7640</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
+          <t>25dB6Eto</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>ADl76OZP</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>jgNAYRGi</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="N19" t="n">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="P19" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T19" t="n">
         <v>13</v>
       </c>
       <c r="U19" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="V19" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
+          <t>SIiBpBrs</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
           <t>EwpPg8iH</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>Cp0gM1r4</t>
         </is>
       </c>
       <c r="Y19" t="n">
@@ -4151,59 +4167,55 @@
         <v>20242025</v>
       </c>
       <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr"/>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="n">
-        <v>24.44444444444444</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>178.1111111111111</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>71.77777777777777</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>4622222.222222222</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>77.11111111111111</v>
-      </c>
-      <c r="AQ19" t="inlineStr"/>
-      <c r="AR19" t="inlineStr"/>
-      <c r="AS19" t="inlineStr"/>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AU19" t="inlineStr"/>
-      <c r="AV19" t="inlineStr"/>
-      <c r="AW19" t="n">
-        <v>21.73333333333333</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>177.4</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>69.06666666666666</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>2781666.666666667</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>77.53333333333333</v>
-      </c>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>182</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>64.44444444444444</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>841666.6666666666</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>68.11111111111111</v>
+      </c>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="n">
+        <v>24.81818181818182</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>181.2727272727273</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>64.36363636363636</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>881818.1818181818</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>70.36363636363636</v>
+      </c>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="inlineStr"/>
       <c r="BC19" t="inlineStr"/>
       <c r="BD19" t="inlineStr"/>
       <c r="BE19" t="inlineStr"/>
@@ -4222,97 +4234,93 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>OA5YizjL</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45522.65625</v>
+        <v>45523.65625</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">millot b 
+          <t xml:space="preserve">thual o 
   fra </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">roazhon park
-  rennes </t>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>29778</v>
+        <v>67394</v>
       </c>
       <c r="F20" t="n">
-        <v>26026</v>
+        <v>2655</v>
       </c>
       <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ADl76OZP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>jgNAYRGi</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>33</v>
+      </c>
+      <c r="N20" t="n">
+        <v>67</v>
+      </c>
+      <c r="O20" t="n">
         <v>3</v>
       </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="M20" t="n">
-        <v>48</v>
-      </c>
-      <c r="N20" t="n">
-        <v>52</v>
-      </c>
-      <c r="O20" t="n">
-        <v>22</v>
-      </c>
       <c r="P20" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7</v>
+      </c>
+      <c r="S20" t="n">
+        <v>8</v>
+      </c>
+      <c r="T20" t="n">
+        <v>13</v>
+      </c>
+      <c r="U20" t="n">
         <v>16</v>
       </c>
-      <c r="Q20" t="n">
-        <v>8</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2</v>
-      </c>
-      <c r="S20" t="n">
-        <v>13</v>
-      </c>
-      <c r="T20" t="n">
-        <v>12</v>
-      </c>
-      <c r="U20" t="n">
-        <v>8</v>
-      </c>
       <c r="V20" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>pCcFFE7M</t>
+          <t>EwpPg8iH</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>YHU1oFVQ</t>
+          <t>Cp0gM1r4</t>
         </is>
       </c>
       <c r="Y20" t="n">
         <v>55</v>
       </c>
       <c r="Z20" t="n">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -4320,221 +4328,165 @@
       <c r="AB20" t="n">
         <v>20242025</v>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr"/>
-      <c r="AE20" t="n">
-        <v>25.875</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>180.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>75.625</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>9475000</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>79.25</v>
-      </c>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
       <c r="AK20" t="n">
-        <v>25.66666666666667</v>
+        <v>24.44444444444444</v>
       </c>
       <c r="AL20" t="n">
-        <v>182.3333333333333</v>
+        <v>178.1111111111111</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.666666666666667</v>
+        <v>1</v>
       </c>
       <c r="AN20" t="n">
-        <v>76.33333333333333</v>
+        <v>71.77777777777777</v>
       </c>
       <c r="AO20" t="n">
-        <v>10111111.11111111</v>
+        <v>4622222.222222222</v>
       </c>
       <c r="AP20" t="n">
-        <v>80</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>24.23076923076923</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>181.9230769230769</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>1.538461538461539</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>73.07692307692308</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>8578846.153846154</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>77.53846153846153</v>
-      </c>
+        <v>77.11111111111111</v>
+      </c>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
       <c r="AW20" t="n">
-        <v>23.81818181818182</v>
+        <v>21.73333333333333</v>
       </c>
       <c r="AX20" t="n">
-        <v>179.5</v>
+        <v>177.4</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.681818181818182</v>
+        <v>1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>73.18181818181819</v>
+        <v>69.06666666666666</v>
       </c>
       <c r="BA20" t="n">
-        <v>5522727.272727272</v>
+        <v>2781666.666666667</v>
       </c>
       <c r="BB20" t="n">
-        <v>78.81818181818181</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>189</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>72</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>78</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>31</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>173.5</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>159</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>33000000</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>159</v>
-      </c>
+        <v>77.53333333333333</v>
+      </c>
+      <c r="BC20" t="inlineStr"/>
+      <c r="BD20" t="inlineStr"/>
+      <c r="BE20" t="inlineStr"/>
+      <c r="BF20" t="inlineStr"/>
+      <c r="BG20" t="inlineStr"/>
+      <c r="BH20" t="inlineStr"/>
+      <c r="BI20" t="inlineStr"/>
+      <c r="BJ20" t="inlineStr"/>
+      <c r="BK20" t="inlineStr"/>
+      <c r="BL20" t="inlineStr"/>
+      <c r="BM20" t="inlineStr"/>
+      <c r="BN20" t="inlineStr"/>
+      <c r="BO20" t="inlineStr"/>
+      <c r="BP20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>lEQmcVR0</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45522.5</v>
+        <v>45523.65625</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">leonard t 
+          <t xml:space="preserve">petit a 
   fra </t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
+          <t xml:space="preserve">stade saint symphorien
+  metz </t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>18752</v>
+        <v>28786</v>
       </c>
       <c r="F21" t="n">
-        <v>14811</v>
+        <v>18585</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>4v0yqlWc</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.92</v>
-      </c>
+          <t>AZwK8L6R</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="N21" t="n">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="P21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q21" t="n">
+        <v>5</v>
+      </c>
+      <c r="R21" t="n">
         <v>3</v>
       </c>
-      <c r="R21" t="n">
-        <v>5</v>
-      </c>
       <c r="S21" t="n">
+        <v>13</v>
+      </c>
+      <c r="T21" t="n">
+        <v>15</v>
+      </c>
+      <c r="U21" t="n">
         <v>12</v>
       </c>
-      <c r="T21" t="n">
-        <v>14</v>
-      </c>
-      <c r="U21" t="n">
-        <v>10</v>
-      </c>
       <c r="V21" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>6FKPxxgf</t>
+          <t>h89kUbu5</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>K6b7RoBp</t>
+          <t>fo8nHfg4</t>
         </is>
       </c>
       <c r="Y21" t="n">
         <v>55</v>
       </c>
       <c r="Z21" t="n">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -4542,214 +4494,186 @@
       <c r="AB21" t="n">
         <v>20242025</v>
       </c>
-      <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="n">
-        <v>25.7</v>
+        <v>24.90909090909091</v>
       </c>
       <c r="AF21" t="n">
-        <v>184.5</v>
+        <v>177.8181818181818</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.1</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="AH21" t="n">
-        <v>68</v>
+        <v>68.90909090909091</v>
       </c>
       <c r="AI21" t="n">
-        <v>1587500</v>
+        <v>1677272.727272727</v>
       </c>
       <c r="AJ21" t="n">
-        <v>72.8</v>
+        <v>75.27272727272727</v>
       </c>
       <c r="AK21" t="n">
-        <v>27.63636363636364</v>
+        <v>25.375</v>
       </c>
       <c r="AL21" t="n">
-        <v>179.8181818181818</v>
+        <v>179.625</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.454545454545455</v>
+        <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>77</v>
+        <v>63.625</v>
       </c>
       <c r="AO21" t="n">
-        <v>12381818.18181818</v>
+        <v>723125</v>
       </c>
       <c r="AP21" t="n">
-        <v>78.72727272727273</v>
+        <v>68.375</v>
       </c>
       <c r="AQ21" t="n">
-        <v>25.7</v>
+        <v>24</v>
       </c>
       <c r="AR21" t="n">
-        <v>183.9</v>
+        <v>181.0909090909091</v>
       </c>
       <c r="AS21" t="n">
         <v>1</v>
       </c>
       <c r="AT21" t="n">
-        <v>66.45</v>
+        <v>67.81818181818181</v>
       </c>
       <c r="AU21" t="n">
-        <v>1278750</v>
+        <v>1718181.818181818</v>
       </c>
       <c r="AV21" t="n">
-        <v>71.84999999999999</v>
+        <v>75</v>
       </c>
       <c r="AW21" t="n">
-        <v>23.90909090909091</v>
+        <v>23.25</v>
       </c>
       <c r="AX21" t="n">
-        <v>179.9545454545455</v>
+        <v>180</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.090909090909091</v>
+        <v>1</v>
       </c>
       <c r="AZ21" t="n">
-        <v>72.90909090909091</v>
+        <v>61.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>6081818.181818182</v>
+        <v>679166.6666666666</v>
       </c>
       <c r="BB21" t="n">
-        <v>78.13636363636364</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>179.25</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>266</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>5725000</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>290</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>25</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>179</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>4</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>298</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>28600000</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>310</v>
-      </c>
+        <v>68.16666666666667</v>
+      </c>
+      <c r="BC21" t="inlineStr"/>
+      <c r="BD21" t="inlineStr"/>
+      <c r="BE21" t="inlineStr"/>
+      <c r="BF21" t="inlineStr"/>
+      <c r="BG21" t="inlineStr"/>
+      <c r="BH21" t="inlineStr"/>
+      <c r="BI21" t="inlineStr"/>
+      <c r="BJ21" t="inlineStr"/>
+      <c r="BK21" t="inlineStr"/>
+      <c r="BL21" t="inlineStr"/>
+      <c r="BM21" t="inlineStr"/>
+      <c r="BN21" t="inlineStr"/>
+      <c r="BO21" t="inlineStr"/>
+      <c r="BP21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>zkPwWhT1</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45522.5</v>
+        <v>45522.65625</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">stinat j 
+          <t xml:space="preserve">millot b 
   fra </t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>33150</v>
+        <v>29778</v>
       </c>
       <c r="F22" t="n">
-        <v>25491</v>
+        <v>26026</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="L22" t="n">
-        <v>0.33</v>
+        <v>1.64</v>
       </c>
       <c r="M22" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N22" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="O22" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="P22" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="R22" t="n">
         <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T22" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="U22" t="n">
         <v>8</v>
       </c>
       <c r="V22" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>UapruDaf</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>YTLwacK1</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
       <c r="Y22" t="n">
@@ -4764,103 +4688,131 @@
       <c r="AB22" t="n">
         <v>20242025</v>
       </c>
-      <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="n">
-        <v>22.9</v>
+        <v>25.875</v>
       </c>
       <c r="AF22" t="n">
-        <v>181.1</v>
+        <v>180.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.1</v>
+        <v>1.75</v>
       </c>
       <c r="AH22" t="n">
-        <v>72.40000000000001</v>
+        <v>75.625</v>
       </c>
       <c r="AI22" t="n">
-        <v>5200000</v>
+        <v>9475000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>78.7</v>
+        <v>79.25</v>
       </c>
       <c r="AK22" t="n">
-        <v>24.8</v>
+        <v>25.66666666666667</v>
       </c>
       <c r="AL22" t="n">
-        <v>182</v>
+        <v>182.3333333333333</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.4</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AN22" t="n">
-        <v>72.8</v>
+        <v>76.33333333333333</v>
       </c>
       <c r="AO22" t="n">
-        <v>5310000</v>
+        <v>10111111.11111111</v>
       </c>
       <c r="AP22" t="n">
-        <v>76.2</v>
+        <v>80</v>
       </c>
       <c r="AQ22" t="n">
-        <v>24</v>
+        <v>24.23076923076923</v>
       </c>
       <c r="AR22" t="n">
-        <v>178.375</v>
+        <v>181.9230769230769</v>
       </c>
       <c r="AS22" t="n">
-        <v>1</v>
+        <v>1.538461538461539</v>
       </c>
       <c r="AT22" t="n">
-        <v>69.8125</v>
+        <v>73.07692307692308</v>
       </c>
       <c r="AU22" t="n">
-        <v>2631250</v>
+        <v>8578846.153846154</v>
       </c>
       <c r="AV22" t="n">
-        <v>75.4375</v>
+        <v>77.53846153846153</v>
       </c>
       <c r="AW22" t="n">
-        <v>25.76470588235294</v>
+        <v>23.81818181818182</v>
       </c>
       <c r="AX22" t="n">
-        <v>182.8235294117647</v>
+        <v>179.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.411764705882353</v>
+        <v>1.681818181818182</v>
       </c>
       <c r="AZ22" t="n">
-        <v>71.76470588235294</v>
+        <v>73.18181818181819</v>
       </c>
       <c r="BA22" t="n">
-        <v>3450000</v>
+        <v>5522727.272727272</v>
       </c>
       <c r="BB22" t="n">
-        <v>74.58823529411765</v>
-      </c>
-      <c r="BC22" t="inlineStr"/>
-      <c r="BD22" t="inlineStr"/>
-      <c r="BE22" t="inlineStr"/>
-      <c r="BF22" t="inlineStr"/>
-      <c r="BG22" t="inlineStr"/>
-      <c r="BH22" t="inlineStr"/>
-      <c r="BI22" t="inlineStr"/>
-      <c r="BJ22" t="inlineStr"/>
-      <c r="BK22" t="inlineStr"/>
-      <c r="BL22" t="inlineStr"/>
-      <c r="BM22" t="inlineStr"/>
-      <c r="BN22" t="inlineStr"/>
-      <c r="BO22" t="inlineStr"/>
-      <c r="BP22" t="inlineStr"/>
+        <v>78.81818181818181</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>189</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>72</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>78</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>31</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>173.5</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>159</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>33000000</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
@@ -4868,82 +4820,82 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">vernice m 
+          <t xml:space="preserve">stinat j 
   fra </t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la mosson
-  montpellier </t>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>20484</v>
+        <v>33150</v>
       </c>
       <c r="F23" t="n">
-        <v>15706</v>
+        <v>25491</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="L23" t="n">
-        <v>1.23</v>
+        <v>0.33</v>
       </c>
       <c r="M23" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="N23" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="O23" t="n">
         <v>7</v>
       </c>
       <c r="P23" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="U23" t="n">
+        <v>8</v>
+      </c>
+      <c r="V23" t="n">
         <v>3</v>
       </c>
-      <c r="V23" t="n">
-        <v>9</v>
-      </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>vVQcGxl1</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>4fMAHvLm</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
       <c r="Y23" t="n">
@@ -4958,218 +4910,186 @@
       <c r="AB23" t="n">
         <v>20242025</v>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
+      <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>4v0yqlWc</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="AE23" t="n">
-        <v>25.6</v>
+        <v>22.9</v>
       </c>
       <c r="AF23" t="n">
-        <v>180.5</v>
+        <v>181.1</v>
       </c>
       <c r="AG23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>182</v>
+      </c>
+      <c r="AM23" t="n">
         <v>1.4</v>
       </c>
-      <c r="AH23" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>6330000</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>21.22222222222222</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>185.4444444444445</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1</v>
-      </c>
       <c r="AN23" t="n">
-        <v>70.77777777777777</v>
+        <v>72.8</v>
       </c>
       <c r="AO23" t="n">
-        <v>4402777.777777778</v>
+        <v>5310000</v>
       </c>
       <c r="AP23" t="n">
-        <v>79.88888888888889</v>
+        <v>76.2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>23.375</v>
+        <v>24</v>
       </c>
       <c r="AR23" t="n">
-        <v>182</v>
+        <v>178.375</v>
       </c>
       <c r="AS23" t="n">
         <v>1</v>
       </c>
       <c r="AT23" t="n">
-        <v>70.75</v>
+        <v>69.8125</v>
       </c>
       <c r="AU23" t="n">
-        <v>3787500</v>
+        <v>2631250</v>
       </c>
       <c r="AV23" t="n">
-        <v>76.625</v>
+        <v>75.4375</v>
       </c>
       <c r="AW23" t="n">
-        <v>21.875</v>
+        <v>25.76470588235294</v>
       </c>
       <c r="AX23" t="n">
-        <v>178.75</v>
+        <v>182.8235294117647</v>
       </c>
       <c r="AY23" t="n">
-        <v>1</v>
+        <v>1.411764705882353</v>
       </c>
       <c r="AZ23" t="n">
-        <v>67.1875</v>
+        <v>71.76470588235294</v>
       </c>
       <c r="BA23" t="n">
-        <v>2412500</v>
+        <v>3450000</v>
       </c>
       <c r="BB23" t="n">
-        <v>76</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>31</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>186</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>147</v>
-      </c>
-      <c r="BH23" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="BI23" t="n">
-        <v>147</v>
-      </c>
-      <c r="BJ23" t="n">
-        <v>19</v>
-      </c>
-      <c r="BK23" t="n">
-        <v>176</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN23" t="n">
-        <v>70</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>3800000</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>84</v>
-      </c>
+        <v>74.58823529411765</v>
+      </c>
+      <c r="BC23" t="inlineStr"/>
+      <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr"/>
+      <c r="BF23" t="inlineStr"/>
+      <c r="BG23" t="inlineStr"/>
+      <c r="BH23" t="inlineStr"/>
+      <c r="BI23" t="inlineStr"/>
+      <c r="BJ23" t="inlineStr"/>
+      <c r="BK23" t="inlineStr"/>
+      <c r="BL23" t="inlineStr"/>
+      <c r="BM23" t="inlineStr"/>
+      <c r="BN23" t="inlineStr"/>
+      <c r="BO23" t="inlineStr"/>
+      <c r="BP23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>M5VGwpVA</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45522.41666666666</v>
+        <v>45522.5</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">lissorgue r 
+          <t xml:space="preserve">vernice m 
   fra </t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de l abbe deschamps
-  auxerre </t>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>17924</v>
+        <v>20484</v>
       </c>
       <c r="F24" t="n">
-        <v>16354</v>
+        <v>15706</v>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
         <v>1</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>2.11</v>
+        <v>1.5</v>
       </c>
       <c r="L24" t="n">
-        <v>0.67</v>
+        <v>1.23</v>
       </c>
       <c r="M24" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="N24" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O24" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="P24" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="n">
+        <v>18</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
+      </c>
+      <c r="V24" t="n">
         <v>9</v>
       </c>
-      <c r="Q24" t="n">
-        <v>7</v>
-      </c>
-      <c r="R24" t="n">
-        <v>2</v>
-      </c>
-      <c r="S24" t="n">
-        <v>11</v>
-      </c>
-      <c r="T24" t="n">
-        <v>17</v>
-      </c>
-      <c r="U24" t="n">
-        <v>7</v>
-      </c>
-      <c r="V24" t="n">
-        <v>8</v>
-      </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>OpNm82MB</t>
+          <t>vVQcGxl1</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>d0X3cO3I</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
       <c r="Y24" t="n">
@@ -5184,214 +5104,218 @@
       <c r="AB24" t="n">
         <v>20242025</v>
       </c>
-      <c r="AC24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>4v0yqlWc</t>
         </is>
       </c>
       <c r="AE24" t="n">
-        <v>25.66666666666667</v>
+        <v>25.6</v>
       </c>
       <c r="AF24" t="n">
-        <v>182.3333333333333</v>
+        <v>180.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AH24" t="n">
-        <v>68.22222222222223</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AI24" t="n">
-        <v>1708333.333333333</v>
+        <v>6330000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>71.66666666666667</v>
+        <v>78.2</v>
       </c>
       <c r="AK24" t="n">
-        <v>23.8</v>
+        <v>21.22222222222222</v>
       </c>
       <c r="AL24" t="n">
-        <v>184</v>
+        <v>185.4444444444445</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AN24" t="n">
-        <v>73.7</v>
+        <v>70.77777777777777</v>
       </c>
       <c r="AO24" t="n">
-        <v>9280000</v>
+        <v>4402777.777777778</v>
       </c>
       <c r="AP24" t="n">
-        <v>78.90000000000001</v>
+        <v>79.88888888888889</v>
       </c>
       <c r="AQ24" t="n">
-        <v>25.08333333333333</v>
+        <v>23.375</v>
       </c>
       <c r="AR24" t="n">
-        <v>180.8333333333333</v>
+        <v>182</v>
       </c>
       <c r="AS24" t="n">
         <v>1</v>
       </c>
       <c r="AT24" t="n">
-        <v>65.08333333333333</v>
+        <v>70.75</v>
       </c>
       <c r="AU24" t="n">
-        <v>1062500</v>
+        <v>3787500</v>
       </c>
       <c r="AV24" t="n">
-        <v>69.25</v>
+        <v>76.625</v>
       </c>
       <c r="AW24" t="n">
-        <v>22.7</v>
+        <v>21.875</v>
       </c>
       <c r="AX24" t="n">
-        <v>179.5</v>
+        <v>178.75</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AZ24" t="n">
-        <v>72.7</v>
+        <v>67.1875</v>
       </c>
       <c r="BA24" t="n">
-        <v>5470000</v>
+        <v>2412500</v>
       </c>
       <c r="BB24" t="n">
-        <v>78.09999999999999</v>
+        <v>76</v>
       </c>
       <c r="BC24" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="BD24" t="n">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="BE24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BF24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BG24" t="n">
-        <v>69</v>
+        <v>147</v>
       </c>
       <c r="BH24" t="n">
-        <v>1800000</v>
+        <v>6000000</v>
       </c>
       <c r="BI24" t="n">
-        <v>74</v>
+        <v>147</v>
       </c>
       <c r="BJ24" t="n">
-        <v>23.75</v>
+        <v>19</v>
       </c>
       <c r="BK24" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="BL24" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="BM24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BN24" t="n">
-        <v>307</v>
+        <v>70</v>
       </c>
       <c r="BO24" t="n">
-        <v>53500000</v>
+        <v>3800000</v>
       </c>
       <c r="BP24" t="n">
-        <v>321</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>2NocJFqd</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45521.66666666666</v>
+        <v>45522.5</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">turpin c 
+          <t xml:space="preserve">leonard t 
   fra </t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>18523</v>
+        <v>18752</v>
       </c>
       <c r="F25" t="n">
-        <v>14250</v>
+        <v>14811</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>1.55</v>
+        <v>0.26</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="M25" t="n">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="N25" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="O25" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="P25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q25" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T25" t="n">
         <v>14</v>
       </c>
       <c r="U25" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="V25" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>CWxpUrtf</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>tAufB9Mi</t>
+          <t>K6b7RoBp</t>
         </is>
       </c>
       <c r="Y25" t="n">
@@ -5406,202 +5330,214 @@
       <c r="AB25" t="n">
         <v>20242025</v>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="AD25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
       <c r="AE25" t="n">
-        <v>23.9</v>
+        <v>25.7</v>
       </c>
       <c r="AF25" t="n">
-        <v>182.9</v>
+        <v>184.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="AH25" t="n">
-        <v>76.2</v>
+        <v>68</v>
       </c>
       <c r="AI25" t="n">
-        <v>12650000</v>
+        <v>1587500</v>
       </c>
       <c r="AJ25" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="AK25" t="inlineStr"/>
-      <c r="AL25" t="inlineStr"/>
-      <c r="AM25" t="inlineStr"/>
-      <c r="AN25" t="inlineStr"/>
-      <c r="AO25" t="inlineStr"/>
-      <c r="AP25" t="inlineStr"/>
+        <v>72.8</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>27.63636363636364</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>179.8181818181818</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>77</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>12381818.18181818</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>78.72727272727273</v>
+      </c>
       <c r="AQ25" t="n">
-        <v>20.86666666666667</v>
+        <v>25.7</v>
       </c>
       <c r="AR25" t="n">
-        <v>183.6666666666667</v>
+        <v>183.9</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AT25" t="n">
-        <v>72.73333333333333</v>
+        <v>66.45</v>
       </c>
       <c r="AU25" t="n">
-        <v>9083333.333333334</v>
+        <v>1278750</v>
       </c>
       <c r="AV25" t="n">
-        <v>82</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="AW25" t="n">
-        <v>22.72727272727273</v>
+        <v>23.90909090909091</v>
       </c>
       <c r="AX25" t="n">
-        <v>182.1818181818182</v>
+        <v>179.9545454545455</v>
       </c>
       <c r="AY25" t="n">
-        <v>1</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="AZ25" t="n">
-        <v>65.81818181818181</v>
+        <v>72.90909090909091</v>
       </c>
       <c r="BA25" t="n">
-        <v>1463636.363636364</v>
+        <v>6081818.181818182</v>
       </c>
       <c r="BB25" t="n">
-        <v>74.27272727272727</v>
+        <v>78.13636363636364</v>
       </c>
       <c r="BC25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD25" t="n">
-        <v>190</v>
+        <v>179.25</v>
       </c>
       <c r="BE25" t="n">
         <v>1</v>
       </c>
       <c r="BF25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BG25" t="n">
-        <v>78</v>
+        <v>266</v>
       </c>
       <c r="BH25" t="n">
-        <v>20500000</v>
+        <v>5725000</v>
       </c>
       <c r="BI25" t="n">
-        <v>84</v>
+        <v>290</v>
       </c>
       <c r="BJ25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BK25" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BL25" t="n">
         <v>1</v>
       </c>
       <c r="BM25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BN25" t="n">
-        <v>71</v>
+        <v>298</v>
       </c>
       <c r="BO25" t="n">
-        <v>2400000</v>
+        <v>28600000</v>
       </c>
       <c r="BP25" t="n">
-        <v>74</v>
+        <v>310</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>ripawyyS</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45521.58333333334</v>
+        <v>45522.41666666666</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">wattellier e 
+          <t xml:space="preserve">lissorgue r 
   fra </t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>21029</v>
+        <v>17924</v>
       </c>
       <c r="F26" t="n">
-        <v>14755</v>
+        <v>16354</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M26" t="n">
+        <v>46</v>
+      </c>
+      <c r="N26" t="n">
+        <v>54</v>
+      </c>
+      <c r="O26" t="n">
+        <v>16</v>
+      </c>
+      <c r="P26" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>7</v>
+      </c>
+      <c r="R26" t="n">
         <v>2</v>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="M26" t="n">
-        <v>29</v>
-      </c>
-      <c r="N26" t="n">
-        <v>71</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2</v>
-      </c>
-      <c r="P26" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>6</v>
-      </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T26" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="U26" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="V26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>25Wk0Fko</t>
+          <t>OpNm82MB</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>nVS1TlC4</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
       <c r="Y26" t="n">
@@ -5619,199 +5555,211 @@
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr"/>
-      <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="inlineStr"/>
-      <c r="AH26" t="inlineStr"/>
-      <c r="AI26" t="inlineStr"/>
-      <c r="AJ26" t="inlineStr"/>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="AE26" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>68.22222222222223</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1708333.333333333</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>71.66666666666667</v>
+      </c>
       <c r="AK26" t="n">
-        <v>24.875</v>
+        <v>23.8</v>
       </c>
       <c r="AL26" t="n">
-        <v>180.25</v>
+        <v>184</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AN26" t="n">
-        <v>75.875</v>
+        <v>73.7</v>
       </c>
       <c r="AO26" t="n">
-        <v>10312500</v>
+        <v>9280000</v>
       </c>
       <c r="AP26" t="n">
-        <v>80.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="AQ26" t="n">
-        <v>20.25</v>
+        <v>25.08333333333333</v>
       </c>
       <c r="AR26" t="n">
-        <v>181.6666666666667</v>
+        <v>180.8333333333333</v>
       </c>
       <c r="AS26" t="n">
         <v>1</v>
       </c>
       <c r="AT26" t="n">
-        <v>68</v>
+        <v>65.08333333333333</v>
       </c>
       <c r="AU26" t="n">
-        <v>3266666.666666667</v>
+        <v>1062500</v>
       </c>
       <c r="AV26" t="n">
-        <v>78.75</v>
+        <v>69.25</v>
       </c>
       <c r="AW26" t="n">
-        <v>23.33333333333333</v>
+        <v>22.7</v>
       </c>
       <c r="AX26" t="n">
-        <v>178.6111111111111</v>
+        <v>179.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.444444444444444</v>
+        <v>1.1</v>
       </c>
       <c r="AZ26" t="n">
-        <v>72.38888888888889</v>
+        <v>72.7</v>
       </c>
       <c r="BA26" t="n">
-        <v>8463888.888888888</v>
+        <v>5470000</v>
       </c>
       <c r="BB26" t="n">
-        <v>79.88888888888889</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="BC26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD26" t="n">
-        <v>182.6666666666667</v>
+        <v>192</v>
       </c>
       <c r="BE26" t="n">
         <v>1</v>
       </c>
       <c r="BF26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BG26" t="n">
-        <v>221</v>
+        <v>69</v>
       </c>
       <c r="BH26" t="n">
-        <v>29200000</v>
+        <v>1800000</v>
       </c>
       <c r="BI26" t="n">
-        <v>238</v>
+        <v>74</v>
       </c>
       <c r="BJ26" t="n">
-        <v>28.2</v>
+        <v>23.75</v>
       </c>
       <c r="BK26" t="n">
-        <v>180.6</v>
+        <v>177</v>
       </c>
       <c r="BL26" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="BM26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BN26" t="n">
-        <v>386</v>
+        <v>307</v>
       </c>
       <c r="BO26" t="n">
-        <v>55800000</v>
+        <v>53500000</v>
       </c>
       <c r="BP26" t="n">
-        <v>389</v>
+        <v>321</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>fHYrsJy3</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45521.5</v>
+        <v>45521.66666666666</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">bastien b 
+          <t xml:space="preserve">turpin c 
   fra </t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>15220</v>
+        <v>18523</v>
       </c>
       <c r="F27" t="n">
-        <v>14962</v>
+        <v>14250</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>1.18</v>
+        <v>1.55</v>
       </c>
       <c r="L27" t="n">
-        <v>2.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="N27" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="O27" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="P27" t="n">
         <v>7</v>
       </c>
       <c r="Q27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T27" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="U27" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="V27" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>0tIbS515</t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>pYizckpN</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
       <c r="Y27" t="n">
@@ -5826,29 +5774,29 @@
       <c r="AB27" t="n">
         <v>20242025</v>
       </c>
-      <c r="AC27" t="inlineStr"/>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>lhUkVMh2</t>
-        </is>
-      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="n">
-        <v>28.1</v>
+        <v>23.9</v>
       </c>
       <c r="AF27" t="n">
-        <v>181.5</v>
+        <v>182.9</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AH27" t="n">
-        <v>74.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="AI27" t="n">
-        <v>5460000</v>
+        <v>12650000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>75</v>
+        <v>80.8</v>
       </c>
       <c r="AK27" t="inlineStr"/>
       <c r="AL27" t="inlineStr"/>
@@ -5857,46 +5805,46 @@
       <c r="AO27" t="inlineStr"/>
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="n">
-        <v>22.78571428571428</v>
+        <v>20.86666666666667</v>
       </c>
       <c r="AR27" t="n">
-        <v>178.1428571428571</v>
+        <v>183.6666666666667</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.285714285714286</v>
+        <v>1.2</v>
       </c>
       <c r="AT27" t="n">
-        <v>67.71428571428571</v>
+        <v>72.73333333333333</v>
       </c>
       <c r="AU27" t="n">
-        <v>4185714.285714286</v>
+        <v>9083333.333333334</v>
       </c>
       <c r="AV27" t="n">
-        <v>74.42857142857143</v>
+        <v>82</v>
       </c>
       <c r="AW27" t="n">
-        <v>24.36363636363636</v>
+        <v>22.72727272727273</v>
       </c>
       <c r="AX27" t="n">
-        <v>180.0909090909091</v>
+        <v>182.1818181818182</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.454545454545455</v>
+        <v>1</v>
       </c>
       <c r="AZ27" t="n">
-        <v>75.18181818181819</v>
+        <v>65.81818181818181</v>
       </c>
       <c r="BA27" t="n">
-        <v>10490909.09090909</v>
+        <v>1463636.363636364</v>
       </c>
       <c r="BB27" t="n">
-        <v>79.18181818181819</v>
+        <v>74.27272727272727</v>
       </c>
       <c r="BC27" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BD27" t="n">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="BE27" t="n">
         <v>1</v>
@@ -5905,62 +5853,62 @@
         <v>1</v>
       </c>
       <c r="BG27" t="n">
+        <v>78</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>20500000</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>84</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>24</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>176</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>71</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="BP27" t="n">
         <v>74</v>
-      </c>
-      <c r="BH27" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="BI27" t="n">
-        <v>77</v>
-      </c>
-      <c r="BJ27" t="n">
-        <v>23.75</v>
-      </c>
-      <c r="BK27" t="n">
-        <v>183.75</v>
-      </c>
-      <c r="BL27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BM27" t="n">
-        <v>4</v>
-      </c>
-      <c r="BN27" t="n">
-        <v>296</v>
-      </c>
-      <c r="BO27" t="n">
-        <v>48000000</v>
-      </c>
-      <c r="BP27" t="n">
-        <v>318</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>dvUee9dD</t>
+          <t>jqSiuc6F</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45521.39583333334</v>
+        <v>45521.58333333334</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">gaillouste p 
+          <t xml:space="preserve">wattellier e 
   fra </t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade michel d ornano
-  caen </t>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>20300</v>
+        <v>21029</v>
       </c>
       <c r="F28" t="n">
-        <v>16639</v>
+        <v>14755</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -5970,61 +5918,65 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>GjLn2QoH</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0OEHEprs</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.66</v>
+      </c>
       <c r="M28" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="N28" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="O28" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="Q28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T28" t="n">
         <v>13</v>
       </c>
       <c r="U28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V28" t="n">
         <v>6</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Q9EVqFe4</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>zB2j3YvM</t>
+          <t>nVS1TlC4</t>
         </is>
       </c>
       <c r="Y28" t="n">
         <v>55</v>
       </c>
       <c r="Z28" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -6033,181 +5985,201 @@
         <v>20242025</v>
       </c>
       <c r="AC28" t="inlineStr"/>
-      <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="n">
-        <v>25.44444444444444</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>181</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>67.55555555555556</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1638888.888888889</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>74</v>
-      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
       <c r="AK28" t="n">
-        <v>24.66666666666667</v>
+        <v>24.875</v>
       </c>
       <c r="AL28" t="n">
-        <v>177.8888888888889</v>
+        <v>180.25</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.111111111111111</v>
+        <v>1.25</v>
       </c>
       <c r="AN28" t="n">
-        <v>67.22222222222223</v>
+        <v>75.875</v>
       </c>
       <c r="AO28" t="n">
-        <v>1697222.222222222</v>
+        <v>10312500</v>
       </c>
       <c r="AP28" t="n">
-        <v>71.55555555555556</v>
+        <v>80.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>22.07142857142857</v>
+        <v>20.25</v>
       </c>
       <c r="AR28" t="n">
-        <v>179.7857142857143</v>
+        <v>181.6666666666667</v>
       </c>
       <c r="AS28" t="n">
         <v>1</v>
       </c>
       <c r="AT28" t="n">
-        <v>64.21428571428571</v>
+        <v>68</v>
       </c>
       <c r="AU28" t="n">
-        <v>1037500</v>
+        <v>3266666.666666667</v>
       </c>
       <c r="AV28" t="n">
-        <v>74.07142857142857</v>
+        <v>78.75</v>
       </c>
       <c r="AW28" t="n">
-        <v>24.95</v>
+        <v>23.33333333333333</v>
       </c>
       <c r="AX28" t="n">
-        <v>181.8</v>
+        <v>178.6111111111111</v>
       </c>
       <c r="AY28" t="n">
-        <v>1</v>
+        <v>1.444444444444444</v>
       </c>
       <c r="AZ28" t="n">
-        <v>65.09999999999999</v>
+        <v>72.38888888888889</v>
       </c>
       <c r="BA28" t="n">
-        <v>1083750</v>
+        <v>8463888.888888888</v>
       </c>
       <c r="BB28" t="n">
-        <v>69.15000000000001</v>
-      </c>
-      <c r="BC28" t="inlineStr"/>
-      <c r="BD28" t="inlineStr"/>
-      <c r="BE28" t="inlineStr"/>
-      <c r="BF28" t="inlineStr"/>
-      <c r="BG28" t="inlineStr"/>
-      <c r="BH28" t="inlineStr"/>
-      <c r="BI28" t="inlineStr"/>
-      <c r="BJ28" t="inlineStr"/>
-      <c r="BK28" t="inlineStr"/>
-      <c r="BL28" t="inlineStr"/>
-      <c r="BM28" t="inlineStr"/>
-      <c r="BN28" t="inlineStr"/>
-      <c r="BO28" t="inlineStr"/>
-      <c r="BP28" t="inlineStr"/>
+        <v>79.88888888888889</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>182.6666666666667</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>221</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>29200000</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>238</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>180.6</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>386</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>55800000</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>389</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>0js8u60b</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45520.65625</v>
+        <v>45521.5</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">bastien b 
   fra </t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>25178</v>
+        <v>15220</v>
       </c>
       <c r="F29" t="n">
-        <v>23167</v>
+        <v>14962</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>0.09</v>
+        <v>1.18</v>
       </c>
       <c r="L29" t="n">
-        <v>1.89</v>
+        <v>2.58</v>
       </c>
       <c r="M29" t="n">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="N29" t="n">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="O29" t="n">
+        <v>7</v>
+      </c>
+      <c r="P29" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q29" t="n">
         <v>5</v>
       </c>
-      <c r="P29" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2</v>
-      </c>
       <c r="R29" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V29" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>dWZTBmVT</t>
+          <t>0tIbS515</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>8MdrBIUb</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="Y29" t="n">
@@ -6223,21 +6195,25 @@
         <v>20242025</v>
       </c>
       <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
       <c r="AE29" t="n">
-        <v>25.18181818181818</v>
+        <v>28.1</v>
       </c>
       <c r="AF29" t="n">
-        <v>185.2727272727273</v>
+        <v>181.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>71.36363636363636</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AI29" t="n">
-        <v>2945454.545454545</v>
+        <v>5460000</v>
       </c>
       <c r="AJ29" t="n">
         <v>75</v>
@@ -6249,46 +6225,46 @@
       <c r="AO29" t="inlineStr"/>
       <c r="AP29" t="inlineStr"/>
       <c r="AQ29" t="n">
-        <v>22.5625</v>
+        <v>22.78571428571428</v>
       </c>
       <c r="AR29" t="n">
-        <v>180.0625</v>
+        <v>178.1428571428571</v>
       </c>
       <c r="AS29" t="n">
-        <v>1</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="AT29" t="n">
-        <v>65.5</v>
+        <v>67.71428571428571</v>
       </c>
       <c r="AU29" t="n">
-        <v>1389062.5</v>
+        <v>4185714.285714286</v>
       </c>
       <c r="AV29" t="n">
-        <v>72.75</v>
+        <v>74.42857142857143</v>
       </c>
       <c r="AW29" t="n">
-        <v>23.69230769230769</v>
+        <v>24.36363636363636</v>
       </c>
       <c r="AX29" t="n">
-        <v>183.5384615384615</v>
+        <v>180.0909090909091</v>
       </c>
       <c r="AY29" t="n">
-        <v>2.307692307692307</v>
+        <v>1.454545454545455</v>
       </c>
       <c r="AZ29" t="n">
-        <v>80.38461538461539</v>
+        <v>75.18181818181819</v>
       </c>
       <c r="BA29" t="n">
-        <v>42061538.46153846</v>
+        <v>10490909.09090909</v>
       </c>
       <c r="BB29" t="n">
-        <v>84.76923076923077</v>
+        <v>79.18181818181819</v>
       </c>
       <c r="BC29" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="BD29" t="n">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="BE29" t="n">
         <v>1</v>
@@ -6297,115 +6273,119 @@
         <v>1</v>
       </c>
       <c r="BG29" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="BH29" t="n">
-        <v>1300000</v>
+        <v>5000000</v>
       </c>
       <c r="BI29" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="BJ29" t="n">
-        <v>27</v>
+        <v>23.75</v>
       </c>
       <c r="BK29" t="n">
-        <v>186.5</v>
+        <v>183.75</v>
       </c>
       <c r="BL29" t="n">
-        <v>3</v>
+        <v>1.25</v>
       </c>
       <c r="BM29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BN29" t="n">
-        <v>165</v>
+        <v>296</v>
       </c>
       <c r="BO29" t="n">
-        <v>68000000</v>
+        <v>48000000</v>
       </c>
       <c r="BP29" t="n">
-        <v>167</v>
+        <v>318</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>EeC5phre</t>
+          <t>dvUee9dD</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45520.625</v>
+        <v>45521.39583333334</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">valnet a 
+          <t xml:space="preserve">gaillouste p 
   fra </t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">michel moretti stadium
-  ajaccio </t>
+          <t xml:space="preserve">stade michel d ornano
+  caen </t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>8470</v>
+        <v>20300</v>
       </c>
       <c r="F30" t="n">
-        <v>3315</v>
+        <v>16639</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2aeoANM8</t>
+          <t>GjLn2QoH</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0pOdQOCg</t>
+          <t>0OEHEprs</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="N30" t="n">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="O30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P30" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q30" t="n">
         <v>5</v>
       </c>
-      <c r="Q30" t="n">
-        <v>4</v>
-      </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="U30" t="n">
+        <v>10</v>
+      </c>
+      <c r="V30" t="n">
+        <v>6</v>
+      </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>8tmnzqxe</t>
+          <t>Q9EVqFe4</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>OQuqpG7i</t>
+          <t>zB2j3YvM</t>
         </is>
       </c>
       <c r="Y30" t="n">
@@ -6423,76 +6403,76 @@
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr"/>
       <c r="AE30" t="n">
-        <v>24.9</v>
+        <v>25.44444444444444</v>
       </c>
       <c r="AF30" t="n">
-        <v>178.2</v>
+        <v>181</v>
       </c>
       <c r="AG30" t="n">
         <v>1</v>
       </c>
       <c r="AH30" t="n">
-        <v>64.40000000000001</v>
+        <v>67.55555555555556</v>
       </c>
       <c r="AI30" t="n">
-        <v>872500</v>
+        <v>1638888.888888889</v>
       </c>
       <c r="AJ30" t="n">
-        <v>70.3</v>
+        <v>74</v>
       </c>
       <c r="AK30" t="n">
-        <v>22.5</v>
+        <v>24.66666666666667</v>
       </c>
       <c r="AL30" t="n">
-        <v>182.5</v>
+        <v>177.8888888888889</v>
       </c>
       <c r="AM30" t="n">
-        <v>1</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="AN30" t="n">
-        <v>64.75</v>
+        <v>67.22222222222223</v>
       </c>
       <c r="AO30" t="n">
-        <v>1090625</v>
+        <v>1697222.222222222</v>
       </c>
       <c r="AP30" t="n">
-        <v>70.75</v>
+        <v>71.55555555555556</v>
       </c>
       <c r="AQ30" t="n">
-        <v>26.38888888888889</v>
+        <v>22.07142857142857</v>
       </c>
       <c r="AR30" t="n">
-        <v>180</v>
+        <v>179.7857142857143</v>
       </c>
       <c r="AS30" t="n">
         <v>1</v>
       </c>
       <c r="AT30" t="n">
-        <v>65.05555555555556</v>
+        <v>64.21428571428571</v>
       </c>
       <c r="AU30" t="n">
-        <v>751388.8888888889</v>
+        <v>1037500</v>
       </c>
       <c r="AV30" t="n">
-        <v>69.61111111111111</v>
+        <v>74.07142857142857</v>
       </c>
       <c r="AW30" t="n">
-        <v>22</v>
+        <v>24.95</v>
       </c>
       <c r="AX30" t="n">
-        <v>182.2</v>
+        <v>181.8</v>
       </c>
       <c r="AY30" t="n">
         <v>1</v>
       </c>
       <c r="AZ30" t="n">
-        <v>62.7</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="BA30" t="n">
-        <v>830000</v>
+        <v>1083750</v>
       </c>
       <c r="BB30" t="n">
-        <v>71</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="BC30" t="inlineStr"/>
       <c r="BD30" t="inlineStr"/>
@@ -6512,93 +6492,97 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2Hh06Z4E</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45520.625</v>
+        <v>45520.65625</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">rosier e 
+          <t xml:space="preserve">delajod w 
   fra </t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la licorne
-  amiens </t>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>12097</v>
+        <v>25178</v>
       </c>
       <c r="F31" t="n">
-        <v>4918</v>
+        <v>23167</v>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>lKkBAsxF</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2kM6ufaS</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.89</v>
+      </c>
       <c r="M31" t="n">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N31" t="n">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="O31" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="P31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q31" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R31" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T31" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="U31" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="V31" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>dS1CBple</t>
+          <t>dWZTBmVT</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>SzfSpYcf</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
       <c r="Y31" t="n">
         <v>55</v>
       </c>
       <c r="Z31" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -6609,22 +6593,22 @@
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="n">
-        <v>26.1</v>
+        <v>25.18181818181818</v>
       </c>
       <c r="AF31" t="n">
-        <v>181.2</v>
+        <v>185.2727272727273</v>
       </c>
       <c r="AG31" t="n">
         <v>1</v>
       </c>
       <c r="AH31" t="n">
-        <v>67.09999999999999</v>
+        <v>71.36363636363636</v>
       </c>
       <c r="AI31" t="n">
-        <v>1205000</v>
+        <v>2945454.545454545</v>
       </c>
       <c r="AJ31" t="n">
-        <v>71.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="inlineStr"/>
@@ -6633,48 +6617,88 @@
       <c r="AO31" t="inlineStr"/>
       <c r="AP31" t="inlineStr"/>
       <c r="AQ31" t="n">
-        <v>24.5</v>
+        <v>22.5625</v>
       </c>
       <c r="AR31" t="n">
-        <v>180.75</v>
+        <v>180.0625</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.1875</v>
+        <v>1</v>
       </c>
       <c r="AT31" t="n">
-        <v>63.0625</v>
+        <v>65.5</v>
       </c>
       <c r="AU31" t="n">
-        <v>751562.5</v>
+        <v>1389062.5</v>
       </c>
       <c r="AV31" t="n">
-        <v>71.4375</v>
-      </c>
-      <c r="AW31" t="inlineStr"/>
-      <c r="AX31" t="inlineStr"/>
-      <c r="AY31" t="inlineStr"/>
-      <c r="AZ31" t="inlineStr"/>
-      <c r="BA31" t="inlineStr"/>
-      <c r="BB31" t="inlineStr"/>
-      <c r="BC31" t="inlineStr"/>
-      <c r="BD31" t="inlineStr"/>
-      <c r="BE31" t="inlineStr"/>
-      <c r="BF31" t="inlineStr"/>
-      <c r="BG31" t="inlineStr"/>
-      <c r="BH31" t="inlineStr"/>
-      <c r="BI31" t="inlineStr"/>
-      <c r="BJ31" t="inlineStr"/>
-      <c r="BK31" t="inlineStr"/>
-      <c r="BL31" t="inlineStr"/>
-      <c r="BM31" t="inlineStr"/>
-      <c r="BN31" t="inlineStr"/>
-      <c r="BO31" t="inlineStr"/>
-      <c r="BP31" t="inlineStr"/>
+        <v>72.75</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>23.69230769230769</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>183.5384615384615</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>2.307692307692307</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>80.38461538461539</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>42061538.46153846</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>84.76923076923077</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>188</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>64</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>74</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>27</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>165</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>68000000</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>167</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>6V8cnEDr</t>
+          <t>EeC5phre</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -6682,78 +6706,74 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">landry r 
+          <t xml:space="preserve">valnet a 
   fra </t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade gabriel montpied
-  clermont ferrand </t>
+          <t xml:space="preserve">michel moretti stadium
+  ajaccio </t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>10800</v>
+        <v>8470</v>
       </c>
       <c r="F32" t="n">
-        <v>5582</v>
+        <v>3315</v>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>IRuMRua1</t>
+          <t>2aeoANM8</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>6NOhR4cm</t>
+          <t>0pOdQOCg</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="N32" t="n">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="O32" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="P32" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Q32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="T32" t="n">
-        <v>12</v>
-      </c>
-      <c r="U32" t="n">
-        <v>14</v>
-      </c>
-      <c r="V32" t="n">
-        <v>16</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
-          <t>4G9MhScS</t>
+          <t>8tmnzqxe</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>fm0Qb28B</t>
+          <t>OQuqpG7i</t>
         </is>
       </c>
       <c r="Y32" t="n">
@@ -6771,76 +6791,76 @@
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="n">
-        <v>23.88888888888889</v>
+        <v>24.9</v>
       </c>
       <c r="AF32" t="n">
+        <v>178.2</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>872500</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1090625</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>26.38888888888889</v>
+      </c>
+      <c r="AR32" t="n">
         <v>180</v>
       </c>
-      <c r="AG32" t="n">
-        <v>1.111111111111111</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>66.44444444444444</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1436111.111111111</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>73.77777777777777</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>183.7</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>962500</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>70.7</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>20.85714285714286</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>176</v>
-      </c>
       <c r="AS32" t="n">
         <v>1</v>
       </c>
       <c r="AT32" t="n">
-        <v>65.28571428571429</v>
+        <v>65.05555555555556</v>
       </c>
       <c r="AU32" t="n">
-        <v>1614285.714285714</v>
+        <v>751388.8888888889</v>
       </c>
       <c r="AV32" t="n">
-        <v>75.28571428571429</v>
+        <v>69.61111111111111</v>
       </c>
       <c r="AW32" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AX32" t="n">
-        <v>182.7272727272727</v>
+        <v>182.2</v>
       </c>
       <c r="AY32" t="n">
         <v>1</v>
       </c>
       <c r="AZ32" t="n">
-        <v>64.54545454545455</v>
+        <v>62.7</v>
       </c>
       <c r="BA32" t="n">
-        <v>709090.9090909091</v>
+        <v>830000</v>
       </c>
       <c r="BB32" t="n">
-        <v>70.27272727272727</v>
+        <v>71</v>
       </c>
       <c r="BC32" t="inlineStr"/>
       <c r="BD32" t="inlineStr"/>
@@ -6860,7 +6880,7 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>zB0ErWC7</t>
+          <t>2Hh06Z4E</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
@@ -6868,48 +6888,48 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">kubler g 
+          <t xml:space="preserve">rosier e 
   fra </t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade marcel tribut
-  dunkerque </t>
+          <t xml:space="preserve">stade de la licorne
+  amiens </t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4933</v>
+        <v>12097</v>
       </c>
       <c r="F33" t="n">
-        <v>3333</v>
+        <v>4918</v>
       </c>
       <c r="G33" t="n">
+        <v>3</v>
+      </c>
+      <c r="H33" t="n">
         <v>0</v>
       </c>
-      <c r="H33" t="n">
-        <v>2</v>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>tAAobNse</t>
+          <t>lKkBAsxF</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>25dB6Eto</t>
+          <t>2kM6ufaS</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="N33" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="O33" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="P33" t="n">
         <v>13</v>
@@ -6918,24 +6938,28 @@
         <v>6</v>
       </c>
       <c r="R33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T33" t="n">
-        <v>15</v>
-      </c>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="U33" t="n">
+        <v>11</v>
+      </c>
+      <c r="V33" t="n">
+        <v>13</v>
+      </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>lb31RXzP</t>
+          <t>dS1CBple</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>SIiBpBrs</t>
+          <t>SzfSpYcf</t>
         </is>
       </c>
       <c r="Y33" t="n">
@@ -6952,66 +6976,54 @@
       </c>
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr"/>
-      <c r="AE33" t="inlineStr"/>
-      <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="inlineStr"/>
-      <c r="AH33" t="inlineStr"/>
-      <c r="AI33" t="inlineStr"/>
-      <c r="AJ33" t="inlineStr"/>
-      <c r="AK33" t="n">
-        <v>26.44444444444444</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>182.5555555555555</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>64.55555555555556</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>833333.3333333334</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>67.77777777777777</v>
-      </c>
+      <c r="AE33" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1205000</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="inlineStr"/>
       <c r="AQ33" t="n">
-        <v>22.83333333333333</v>
+        <v>24.5</v>
       </c>
       <c r="AR33" t="n">
-        <v>176.8333333333333</v>
+        <v>180.75</v>
       </c>
       <c r="AS33" t="n">
-        <v>1</v>
+        <v>1.1875</v>
       </c>
       <c r="AT33" t="n">
-        <v>63.25</v>
+        <v>63.0625</v>
       </c>
       <c r="AU33" t="n">
-        <v>804166.6666666666</v>
+        <v>751562.5</v>
       </c>
       <c r="AV33" t="n">
-        <v>70.75</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>21.66666666666667</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>180.6666666666667</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>61.83333333333334</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>708333.3333333334</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>69.33333333333333</v>
-      </c>
+        <v>71.4375</v>
+      </c>
+      <c r="AW33" t="inlineStr"/>
+      <c r="AX33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr"/>
+      <c r="BA33" t="inlineStr"/>
+      <c r="BB33" t="inlineStr"/>
       <c r="BC33" t="inlineStr"/>
       <c r="BD33" t="inlineStr"/>
       <c r="BE33" t="inlineStr"/>
@@ -7030,7 +7042,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>dGo94DZQ</t>
+          <t>6V8cnEDr</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -7038,70 +7050,78 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">kherradji a 
+          <t xml:space="preserve">landry r 
   fra </t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade des alpes
-  grenoble </t>
+          <t xml:space="preserve">stade gabriel montpied
+  clermont ferrand </t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>20068</v>
+        <v>10800</v>
       </c>
       <c r="F34" t="n">
-        <v>4008</v>
+        <v>5582</v>
       </c>
       <c r="G34" t="n">
         <v>2</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>UgPj1p1N</t>
+          <t>IRuMRua1</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>E1wDrLsJ</t>
+          <t>6NOhR4cm</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="M34" t="n">
+        <v>56</v>
+      </c>
+      <c r="N34" t="n">
+        <v>44</v>
+      </c>
       <c r="O34" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="P34" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q34" t="n">
+        <v>5</v>
+      </c>
+      <c r="R34" t="n">
         <v>4</v>
       </c>
-      <c r="R34" t="n">
-        <v>1</v>
-      </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="U34" t="n">
+        <v>14</v>
+      </c>
+      <c r="V34" t="n">
+        <v>16</v>
+      </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>WrQARdPN</t>
+          <t>4G9MhScS</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ys1Pb7ws</t>
+          <t>fm0Qb28B</t>
         </is>
       </c>
       <c r="Y34" t="n">
@@ -7119,64 +7139,76 @@
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr"/>
       <c r="AE34" t="n">
-        <v>25.72727272727273</v>
+        <v>23.88888888888889</v>
       </c>
       <c r="AF34" t="n">
-        <v>182.8181818181818</v>
+        <v>180</v>
       </c>
       <c r="AG34" t="n">
-        <v>1</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="AH34" t="n">
-        <v>67.63636363636364</v>
+        <v>66.44444444444444</v>
       </c>
       <c r="AI34" t="n">
-        <v>1495454.545454545</v>
+        <v>1436111.111111111</v>
       </c>
       <c r="AJ34" t="n">
-        <v>71.36363636363636</v>
-      </c>
-      <c r="AK34" t="inlineStr"/>
-      <c r="AL34" t="inlineStr"/>
-      <c r="AM34" t="inlineStr"/>
-      <c r="AN34" t="inlineStr"/>
-      <c r="AO34" t="inlineStr"/>
-      <c r="AP34" t="inlineStr"/>
+        <v>73.77777777777777</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>183.7</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>962500</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>70.7</v>
+      </c>
       <c r="AQ34" t="n">
-        <v>29.66666666666667</v>
+        <v>20.85714285714286</v>
       </c>
       <c r="AR34" t="n">
-        <v>185.1666666666667</v>
+        <v>176</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AT34" t="n">
-        <v>70.5</v>
+        <v>65.28571428571429</v>
       </c>
       <c r="AU34" t="n">
-        <v>1937500</v>
+        <v>1614285.714285714</v>
       </c>
       <c r="AV34" t="n">
-        <v>72.5</v>
+        <v>75.28571428571429</v>
       </c>
       <c r="AW34" t="n">
-        <v>24.8125</v>
+        <v>26</v>
       </c>
       <c r="AX34" t="n">
-        <v>181.5</v>
+        <v>182.7272727272727</v>
       </c>
       <c r="AY34" t="n">
         <v>1</v>
       </c>
       <c r="AZ34" t="n">
-        <v>64.3125</v>
+        <v>64.54545454545455</v>
       </c>
       <c r="BA34" t="n">
-        <v>958750</v>
+        <v>709090.9090909091</v>
       </c>
       <c r="BB34" t="n">
-        <v>71.3125</v>
+        <v>70.27272727272727</v>
       </c>
       <c r="BC34" t="inlineStr"/>
       <c r="BD34" t="inlineStr"/>
@@ -7196,7 +7228,7 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>b15XX7Nt</t>
+          <t>zB0ErWC7</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
@@ -7204,78 +7236,74 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">bollengier m 
+          <t xml:space="preserve">kubler g 
   fra </t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de roudourou
-  guingamp </t>
+          <t xml:space="preserve">stade marcel tribut
+  dunkerque </t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>19060</v>
+        <v>4933</v>
       </c>
       <c r="F35" t="n">
-        <v>6052</v>
+        <v>3333</v>
       </c>
       <c r="G35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>QDfKl36E</t>
+          <t>tAAobNse</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>fsfAHubD</t>
+          <t>25dB6Eto</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N35" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O35" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P35" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T35" t="n">
-        <v>12</v>
-      </c>
-      <c r="U35" t="n">
-        <v>9</v>
-      </c>
-      <c r="V35" t="n">
-        <v>14</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr">
         <is>
-          <t>QNSJnsB5</t>
+          <t>lb31RXzP</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>4vG8dmrf</t>
+          <t>SIiBpBrs</t>
         </is>
       </c>
       <c r="Y35" t="n">
@@ -7292,77 +7320,65 @@
       </c>
       <c r="AC35" t="inlineStr"/>
       <c r="AD35" t="inlineStr"/>
-      <c r="AE35" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>179.9</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1025000</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>69.90000000000001</v>
-      </c>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
       <c r="AK35" t="n">
-        <v>27.625</v>
+        <v>26.44444444444444</v>
       </c>
       <c r="AL35" t="n">
-        <v>177.625</v>
+        <v>182.5555555555555</v>
       </c>
       <c r="AM35" t="n">
         <v>1</v>
       </c>
       <c r="AN35" t="n">
-        <v>67.375</v>
+        <v>64.55555555555556</v>
       </c>
       <c r="AO35" t="n">
-        <v>1275000</v>
+        <v>833333.3333333334</v>
       </c>
       <c r="AP35" t="n">
-        <v>70.375</v>
+        <v>67.77777777777777</v>
       </c>
       <c r="AQ35" t="n">
-        <v>23</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="AR35" t="n">
-        <v>179.7</v>
+        <v>176.8333333333333</v>
       </c>
       <c r="AS35" t="n">
         <v>1</v>
       </c>
       <c r="AT35" t="n">
-        <v>63.3</v>
+        <v>63.25</v>
       </c>
       <c r="AU35" t="n">
-        <v>950000</v>
+        <v>804166.6666666666</v>
       </c>
       <c r="AV35" t="n">
-        <v>70.3</v>
+        <v>70.75</v>
       </c>
       <c r="AW35" t="n">
-        <v>20.41666666666667</v>
+        <v>21.66666666666667</v>
       </c>
       <c r="AX35" t="n">
-        <v>179.6666666666667</v>
+        <v>180.6666666666667</v>
       </c>
       <c r="AY35" t="n">
         <v>1</v>
       </c>
       <c r="AZ35" t="n">
-        <v>61.75</v>
+        <v>61.83333333333334</v>
       </c>
       <c r="BA35" t="n">
-        <v>912500</v>
+        <v>708333.3333333334</v>
       </c>
       <c r="BB35" t="n">
-        <v>70.91666666666667</v>
+        <v>69.33333333333333</v>
       </c>
       <c r="BC35" t="inlineStr"/>
       <c r="BD35" t="inlineStr"/>
@@ -7379,6 +7395,358 @@
       <c r="BO35" t="inlineStr"/>
       <c r="BP35" t="inlineStr"/>
     </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>dGo94DZQ</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kherradji a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade des alpes
+  grenoble </t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>20068</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4008</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>E1wDrLsJ</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="n">
+        <v>6</v>
+      </c>
+      <c r="P36" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>4</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Ys1Pb7ws</t>
+        </is>
+      </c>
+      <c r="Y36" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="n">
+        <v>25.72727272727273</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>182.8181818181818</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>67.63636363636364</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1495454.545454545</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>71.36363636363636</v>
+      </c>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr"/>
+      <c r="AP36" t="inlineStr"/>
+      <c r="AQ36" t="n">
+        <v>29.66666666666667</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>185.1666666666667</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>1937500</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>24.8125</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>64.3125</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>958750</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>71.3125</v>
+      </c>
+      <c r="BC36" t="inlineStr"/>
+      <c r="BD36" t="inlineStr"/>
+      <c r="BE36" t="inlineStr"/>
+      <c r="BF36" t="inlineStr"/>
+      <c r="BG36" t="inlineStr"/>
+      <c r="BH36" t="inlineStr"/>
+      <c r="BI36" t="inlineStr"/>
+      <c r="BJ36" t="inlineStr"/>
+      <c r="BK36" t="inlineStr"/>
+      <c r="BL36" t="inlineStr"/>
+      <c r="BM36" t="inlineStr"/>
+      <c r="BN36" t="inlineStr"/>
+      <c r="BO36" t="inlineStr"/>
+      <c r="BP36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>b15XX7Nt</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de roudourou
+  guingamp </t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>19060</v>
+      </c>
+      <c r="F37" t="n">
+        <v>6052</v>
+      </c>
+      <c r="G37" t="n">
+        <v>4</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>QDfKl36E</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fsfAHubD</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="n">
+        <v>49</v>
+      </c>
+      <c r="N37" t="n">
+        <v>51</v>
+      </c>
+      <c r="O37" t="n">
+        <v>16</v>
+      </c>
+      <c r="P37" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>5</v>
+      </c>
+      <c r="R37" t="n">
+        <v>3</v>
+      </c>
+      <c r="S37" t="n">
+        <v>9</v>
+      </c>
+      <c r="T37" t="n">
+        <v>12</v>
+      </c>
+      <c r="U37" t="n">
+        <v>9</v>
+      </c>
+      <c r="V37" t="n">
+        <v>14</v>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>QNSJnsB5</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>4vG8dmrf</t>
+        </is>
+      </c>
+      <c r="Y37" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>555</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>179.9</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1025000</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>27.625</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>177.625</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>67.375</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1275000</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>70.375</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>179.7</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>950000</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>20.41666666666667</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>179.6666666666667</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>912500</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>70.91666666666667</v>
+      </c>
+      <c r="BC37" t="inlineStr"/>
+      <c r="BD37" t="inlineStr"/>
+      <c r="BE37" t="inlineStr"/>
+      <c r="BF37" t="inlineStr"/>
+      <c r="BG37" t="inlineStr"/>
+      <c r="BH37" t="inlineStr"/>
+      <c r="BI37" t="inlineStr"/>
+      <c r="BJ37" t="inlineStr"/>
+      <c r="BK37" t="inlineStr"/>
+      <c r="BL37" t="inlineStr"/>
+      <c r="BM37" t="inlineStr"/>
+      <c r="BN37" t="inlineStr"/>
+      <c r="BO37" t="inlineStr"/>
+      <c r="BP37" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
+++ b/data/france/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
@@ -873,58 +873,58 @@
       </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>23.3</v>
+        <v>24</v>
       </c>
       <c r="AF2" t="n">
-        <v>181.5</v>
+        <v>181.7272727272727</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.1</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="AH2" t="n">
-        <v>75.5</v>
+        <v>75.54545454545455</v>
       </c>
       <c r="AI2" t="n">
-        <v>11030000</v>
+        <v>10481818.18181818</v>
       </c>
       <c r="AJ2" t="n">
-        <v>81.2</v>
+        <v>80.72727272727273</v>
       </c>
       <c r="AK2" t="n">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="AL2" t="n">
-        <v>181.875</v>
+        <v>182.4</v>
       </c>
       <c r="AM2" t="n">
-        <v>2.125</v>
+        <v>2.1</v>
       </c>
       <c r="AN2" t="n">
-        <v>81.75</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="AO2" t="n">
-        <v>47000000</v>
+        <v>47600000</v>
       </c>
       <c r="AP2" t="n">
-        <v>86.75</v>
+        <v>86.7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>25.81818181818182</v>
+        <v>27.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>176.3636363636364</v>
+        <v>180</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.818181818181818</v>
+        <v>2</v>
       </c>
       <c r="AT2" t="n">
-        <v>75.45454545454545</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="AU2" t="n">
-        <v>12288636.36363636</v>
+        <v>10445000</v>
       </c>
       <c r="AV2" t="n">
-        <v>79.18181818181819</v>
+        <v>78.33333333333333</v>
       </c>
       <c r="AW2" t="n">
         <v>22.5</v>
@@ -945,25 +945,25 @@
         <v>83.72222222222223</v>
       </c>
       <c r="BC2" t="n">
-        <v>29.5</v>
+        <v>28.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>179.75</v>
+        <v>180.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BG2" t="n">
-        <v>307</v>
+        <v>380</v>
       </c>
       <c r="BH2" t="n">
-        <v>32800000</v>
+        <v>37100000</v>
       </c>
       <c r="BI2" t="n">
-        <v>307</v>
+        <v>385</v>
       </c>
       <c r="BJ2" t="n">
         <v>27</v>
@@ -990,7 +990,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -998,62 +998,64 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">vernice m 
+          <t xml:space="preserve">stinat j 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>21029</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>18752</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9168</v>
+      </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1.66</v>
+        <v>1.47</v>
       </c>
       <c r="L3" t="n">
-        <v>1.18</v>
+        <v>2.56</v>
       </c>
       <c r="M3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="P3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q3" t="n">
         <v>7</v>
       </c>
       <c r="R3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T3" t="n">
         <v>13</v>
@@ -1062,12 +1064,12 @@
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
-          <t>25Wk0Fko</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>pCcFFE7M</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
       <c r="Y3" t="n">
@@ -1085,98 +1087,122 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1687500</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>23.09090909090909</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>182.2727272727273</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>73.45454545454545</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>10377272.72727273</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>79.18181818181819</v>
+      </c>
       <c r="AQ3" t="n">
-        <v>23.88235294117647</v>
+        <v>27.65</v>
       </c>
       <c r="AR3" t="n">
-        <v>183.1176470588235</v>
+        <v>181.15</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.058823529411765</v>
+        <v>1.05</v>
       </c>
       <c r="AT3" t="n">
-        <v>71.82352941176471</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="AU3" t="n">
-        <v>6541176.470588235</v>
+        <v>1565000</v>
       </c>
       <c r="AV3" t="n">
-        <v>77.70588235294117</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AW3" t="n">
-        <v>24.14285714285714</v>
+        <v>23.38888888888889</v>
       </c>
       <c r="AX3" t="n">
-        <v>179.7142857142857</v>
+        <v>182.2777777777778</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.428571428571429</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="AZ3" t="n">
-        <v>72.92857142857143</v>
+        <v>73.22222222222223</v>
       </c>
       <c r="BA3" t="n">
-        <v>6760714.285714285</v>
+        <v>7956944.444444444</v>
       </c>
       <c r="BB3" t="n">
-        <v>78.14285714285714</v>
+        <v>78.44444444444444</v>
       </c>
       <c r="BC3" t="n">
-        <v>23</v>
+        <v>25.66666666666667</v>
       </c>
       <c r="BD3" t="n">
-        <v>177.5</v>
+        <v>177.6666666666667</v>
       </c>
       <c r="BE3" t="n">
         <v>1</v>
       </c>
       <c r="BF3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BG3" t="n">
-        <v>149</v>
+        <v>200</v>
       </c>
       <c r="BH3" t="n">
-        <v>16000000</v>
+        <v>3300000</v>
       </c>
       <c r="BI3" t="n">
-        <v>159</v>
+        <v>213</v>
       </c>
       <c r="BJ3" t="n">
-        <v>20</v>
+        <v>24.8</v>
       </c>
       <c r="BK3" t="n">
-        <v>189</v>
+        <v>180.4</v>
       </c>
       <c r="BL3" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="BM3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BN3" t="n">
-        <v>72</v>
+        <v>373</v>
       </c>
       <c r="BO3" t="n">
-        <v>2900000</v>
+        <v>50400000</v>
       </c>
       <c r="BP3" t="n">
-        <v>78</v>
+        <v>393</v>
       </c>
     </row>
     <row r="4">
@@ -1296,12 +1322,24 @@
       <c r="AJ4" t="n">
         <v>74.90909090909091</v>
       </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
+      <c r="AK4" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>2897500</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>73.8</v>
+      </c>
       <c r="AQ4" t="n">
         <v>23.53333333333333</v>
       </c>
@@ -1321,22 +1359,22 @@
         <v>74.59999999999999</v>
       </c>
       <c r="AW4" t="n">
-        <v>22.80952380952381</v>
+        <v>22.86363636363636</v>
       </c>
       <c r="AX4" t="n">
-        <v>181.5238095238095</v>
+        <v>181.6818181818182</v>
       </c>
       <c r="AY4" t="n">
         <v>1</v>
       </c>
       <c r="AZ4" t="n">
-        <v>64.9047619047619</v>
+        <v>65.13636363636364</v>
       </c>
       <c r="BA4" t="n">
-        <v>1511904.761904762</v>
+        <v>1579545.454545455</v>
       </c>
       <c r="BB4" t="n">
-        <v>71.9047619047619</v>
+        <v>72.13636363636364</v>
       </c>
       <c r="BC4" t="n">
         <v>19</v>
@@ -1384,7 +1422,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -1392,64 +1430,64 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stinat j 
+          <t xml:space="preserve">vernice m 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>18752</v>
+        <v>21029</v>
       </c>
       <c r="F5" t="n">
-        <v>9168</v>
+        <v>12856</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="L5" t="n">
-        <v>2.56</v>
+        <v>1.18</v>
       </c>
       <c r="M5" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="P5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q5" t="n">
         <v>7</v>
       </c>
       <c r="R5" t="n">
+        <v>5</v>
+      </c>
+      <c r="S5" t="n">
         <v>9</v>
-      </c>
-      <c r="S5" t="n">
-        <v>14</v>
       </c>
       <c r="T5" t="n">
         <v>13</v>
@@ -1458,12 +1496,12 @@
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
-          <t>6FKPxxgf</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>d0X3cO3I</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
       <c r="Y5" t="n">
@@ -1481,122 +1519,110 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="AE5" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>183.2</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>67.8</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1687500</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>72.7</v>
-      </c>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="n">
-        <v>22.77777777777778</v>
+        <v>25.3</v>
       </c>
       <c r="AL5" t="n">
-        <v>181.5555555555555</v>
+        <v>180.9</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.111111111111111</v>
+        <v>1.9</v>
       </c>
       <c r="AN5" t="n">
-        <v>74.22222222222223</v>
+        <v>76</v>
       </c>
       <c r="AO5" t="n">
-        <v>10655555.55555556</v>
+        <v>9080000</v>
       </c>
       <c r="AP5" t="n">
-        <v>80.22222222222223</v>
+        <v>78.7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>27.65</v>
+        <v>24.28571428571428</v>
       </c>
       <c r="AR5" t="n">
-        <v>181.15</v>
+        <v>184</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.05</v>
+        <v>1.047619047619048</v>
       </c>
       <c r="AT5" t="n">
-        <v>68.40000000000001</v>
+        <v>72.28571428571429</v>
       </c>
       <c r="AU5" t="n">
-        <v>1565000</v>
+        <v>6209523.80952381</v>
       </c>
       <c r="AV5" t="n">
-        <v>72.40000000000001</v>
+        <v>77.19047619047619</v>
       </c>
       <c r="AW5" t="n">
-        <v>23.5625</v>
+        <v>23.33333333333333</v>
       </c>
       <c r="AX5" t="n">
-        <v>182.5625</v>
+        <v>179</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.0625</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="AZ5" t="n">
-        <v>72.6875</v>
+        <v>72.61904761904762</v>
       </c>
       <c r="BA5" t="n">
-        <v>6451562.5</v>
+        <v>6211904.761904762</v>
       </c>
       <c r="BB5" t="n">
-        <v>77.8125</v>
+        <v>78.57142857142857</v>
       </c>
       <c r="BC5" t="n">
-        <v>25.66666666666667</v>
+        <v>23</v>
       </c>
       <c r="BD5" t="n">
-        <v>177.6666666666667</v>
+        <v>177.5</v>
       </c>
       <c r="BE5" t="n">
         <v>1</v>
       </c>
       <c r="BF5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BG5" t="n">
-        <v>200</v>
+        <v>149</v>
       </c>
       <c r="BH5" t="n">
-        <v>3300000</v>
+        <v>16000000</v>
       </c>
       <c r="BI5" t="n">
-        <v>213</v>
+        <v>159</v>
       </c>
       <c r="BJ5" t="n">
-        <v>24.8</v>
+        <v>20</v>
       </c>
       <c r="BK5" t="n">
-        <v>180.4</v>
+        <v>189</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BN5" t="n">
-        <v>373</v>
+        <v>72</v>
       </c>
       <c r="BO5" t="n">
-        <v>50400000</v>
+        <v>2900000</v>
       </c>
       <c r="BP5" t="n">
-        <v>393</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6">
@@ -1710,37 +1736,37 @@
         <v>21.6</v>
       </c>
       <c r="AF6" t="n">
-        <v>183</v>
+        <v>183.3</v>
       </c>
       <c r="AG6" t="n">
         <v>1.1</v>
       </c>
       <c r="AH6" t="n">
-        <v>74.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="AI6" t="n">
-        <v>11330000</v>
+        <v>12630000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>82.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="AK6" t="n">
-        <v>26.2</v>
+        <v>25.81818181818182</v>
       </c>
       <c r="AL6" t="n">
-        <v>181.1</v>
+        <v>180.3636363636364</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.3</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="AN6" t="n">
-        <v>76</v>
+        <v>75.81818181818181</v>
       </c>
       <c r="AO6" t="n">
-        <v>11000000</v>
+        <v>10863636.36363636</v>
       </c>
       <c r="AP6" t="n">
-        <v>79.3</v>
+        <v>79.63636363636364</v>
       </c>
       <c r="AQ6" t="n">
         <v>23.45</v>
@@ -1752,31 +1778,31 @@
         <v>1.8</v>
       </c>
       <c r="AT6" t="n">
-        <v>75.65000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="AU6" t="n">
-        <v>13997500</v>
+        <v>14672500</v>
       </c>
       <c r="AV6" t="n">
-        <v>80.75</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>25</v>
+        <v>24.85714285714286</v>
       </c>
       <c r="AX6" t="n">
-        <v>177.6111111111111</v>
+        <v>178.1904761904762</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.277777777777778</v>
+        <v>1.238095238095238</v>
       </c>
       <c r="AZ6" t="n">
-        <v>73</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="BA6" t="n">
-        <v>6472777.777777778</v>
+        <v>7071904.761904762</v>
       </c>
       <c r="BB6" t="n">
-        <v>77.16666666666667</v>
+        <v>77.57142857142857</v>
       </c>
       <c r="BC6" t="n">
         <v>18</v>
@@ -1925,64 +1951,76 @@
         </is>
       </c>
       <c r="AE7" t="n">
-        <v>23.55555555555556</v>
+        <v>23.2</v>
       </c>
       <c r="AF7" t="n">
-        <v>180.7777777777778</v>
+        <v>181.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.111111111111111</v>
+        <v>1.1</v>
       </c>
       <c r="AH7" t="n">
-        <v>73.11111111111111</v>
+        <v>72.8</v>
       </c>
       <c r="AI7" t="n">
-        <v>5388888.888888889</v>
+        <v>5180000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>78.11111111111111</v>
-      </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
+        <v>78.40000000000001</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>182.4444444444445</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>76.77777777777777</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>16122222.22222222</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>80.66666666666667</v>
+      </c>
       <c r="AQ7" t="n">
-        <v>23.4</v>
+        <v>23.1875</v>
       </c>
       <c r="AR7" t="n">
-        <v>179.0666666666667</v>
+        <v>179.8125</v>
       </c>
       <c r="AS7" t="n">
         <v>1</v>
       </c>
       <c r="AT7" t="n">
-        <v>70.46666666666667</v>
+        <v>70.4375</v>
       </c>
       <c r="AU7" t="n">
-        <v>3353333.333333333</v>
+        <v>3350000</v>
       </c>
       <c r="AV7" t="n">
-        <v>76.53333333333333</v>
+        <v>76.8125</v>
       </c>
       <c r="AW7" t="n">
-        <v>25.75</v>
+        <v>24.33333333333333</v>
       </c>
       <c r="AX7" t="n">
-        <v>178.625</v>
+        <v>179.3333333333333</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.75</v>
+        <v>1.466666666666667</v>
       </c>
       <c r="AZ7" t="n">
-        <v>77.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="BA7" t="n">
-        <v>15137500</v>
+        <v>11460000</v>
       </c>
       <c r="BB7" t="n">
-        <v>79.5</v>
+        <v>79.73333333333333</v>
       </c>
       <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="inlineStr"/>
@@ -1995,22 +2033,22 @@
         <v>21</v>
       </c>
       <c r="BK7" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="BL7" t="n">
         <v>1</v>
       </c>
       <c r="BM7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BN7" t="n">
-        <v>135</v>
+        <v>206</v>
       </c>
       <c r="BO7" t="n">
-        <v>5700000</v>
+        <v>9900000</v>
       </c>
       <c r="BP7" t="n">
-        <v>153</v>
+        <v>233</v>
       </c>
     </row>
     <row r="8">
@@ -2037,7 +2075,9 @@
       <c r="E8" t="n">
         <v>20484</v>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>13000</v>
+      </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
@@ -2061,28 +2101,28 @@
         <v>1.7</v>
       </c>
       <c r="M8" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="N8" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S8" t="n">
         <v>11</v>
       </c>
       <c r="T8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
@@ -2137,28 +2177,28 @@
         <v>77.59999999999999</v>
       </c>
       <c r="AK8" t="n">
-        <v>24.9</v>
+        <v>24.81818181818182</v>
       </c>
       <c r="AL8" t="n">
-        <v>183</v>
+        <v>183.1818181818182</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.4</v>
+        <v>1.363636363636364</v>
       </c>
       <c r="AN8" t="n">
-        <v>72.2</v>
+        <v>72.18181818181819</v>
       </c>
       <c r="AO8" t="n">
-        <v>4532500</v>
+        <v>4411363.636363637</v>
       </c>
       <c r="AP8" t="n">
-        <v>75.90000000000001</v>
+        <v>75.81818181818181</v>
       </c>
       <c r="AQ8" t="n">
         <v>23.71428571428572</v>
       </c>
       <c r="AR8" t="n">
-        <v>178.2142857142857</v>
+        <v>179.5</v>
       </c>
       <c r="AS8" t="n">
         <v>1.285714285714286</v>
@@ -2173,22 +2213,22 @@
         <v>76.78571428571429</v>
       </c>
       <c r="AW8" t="n">
-        <v>24.73333333333333</v>
+        <v>24.6875</v>
       </c>
       <c r="AX8" t="n">
-        <v>180.5333333333333</v>
+        <v>180.8125</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.266666666666667</v>
+        <v>1.25</v>
       </c>
       <c r="AZ8" t="n">
-        <v>72.13333333333334</v>
+        <v>72.125</v>
       </c>
       <c r="BA8" t="n">
-        <v>4318333.333333333</v>
+        <v>4248437.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>75.2</v>
+        <v>75.1875</v>
       </c>
       <c r="BC8" t="n">
         <v>24.8</v>
@@ -2257,7 +2297,9 @@
       <c r="E9" t="n">
         <v>15220</v>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>14885</v>
+      </c>
       <c r="G9" t="n">
         <v>4</v>
       </c>
@@ -2281,28 +2323,28 @@
         <v>0.31</v>
       </c>
       <c r="M9" t="n">
+        <v>47</v>
+      </c>
+      <c r="N9" t="n">
         <v>53</v>
       </c>
-      <c r="N9" t="n">
-        <v>47</v>
-      </c>
       <c r="O9" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T9" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
@@ -2331,22 +2373,22 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="n">
-        <v>27.33333333333333</v>
+        <v>27.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>179.3333333333333</v>
+        <v>181.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.333333333333333</v>
+        <v>1.4</v>
       </c>
       <c r="AH9" t="n">
-        <v>74.55555555555556</v>
+        <v>74.7</v>
       </c>
       <c r="AI9" t="n">
-        <v>6755555.555555556</v>
+        <v>6830000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>75.88888888888889</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AK9" t="n">
         <v>25.375</v>
@@ -2367,22 +2409,22 @@
         <v>74.875</v>
       </c>
       <c r="AQ9" t="n">
-        <v>24.52941176470588</v>
+        <v>23.7</v>
       </c>
       <c r="AR9" t="n">
-        <v>178.2352941176471</v>
+        <v>180</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.294117647058824</v>
+        <v>1.25</v>
       </c>
       <c r="AT9" t="n">
-        <v>68.52941176470588</v>
+        <v>68</v>
       </c>
       <c r="AU9" t="n">
-        <v>3258823.529411765</v>
+        <v>3010000</v>
       </c>
       <c r="AV9" t="n">
-        <v>73.41176470588235</v>
+        <v>73.95</v>
       </c>
       <c r="AW9" t="n">
         <v>26.27272727272727</v>
@@ -2576,7 +2618,7 @@
         <v>21.3</v>
       </c>
       <c r="AR10" t="n">
-        <v>181.3</v>
+        <v>181</v>
       </c>
       <c r="AS10" t="n">
         <v>1</v>
@@ -2837,7 +2879,9 @@
       <c r="E12" t="n">
         <v>59186</v>
       </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>43805</v>
+      </c>
       <c r="G12" t="n">
         <v>4</v>
       </c>
@@ -2861,25 +2905,25 @@
         <v>2.24</v>
       </c>
       <c r="M12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N12" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T12" t="n">
         <v>6</v>
@@ -2915,22 +2959,22 @@
         </is>
       </c>
       <c r="AE12" t="n">
-        <v>27.22222222222222</v>
+        <v>27.2</v>
       </c>
       <c r="AF12" t="n">
-        <v>183.2222222222222</v>
+        <v>183.6</v>
       </c>
       <c r="AG12" t="n">
         <v>2</v>
       </c>
       <c r="AH12" t="n">
-        <v>76.55555555555556</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="AI12" t="n">
-        <v>9666666.666666666</v>
+        <v>9800000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>78.77777777777777</v>
+        <v>78.8</v>
       </c>
       <c r="AK12" t="n">
         <v>20.9</v>
@@ -2951,40 +2995,40 @@
         <v>80.3</v>
       </c>
       <c r="AQ12" t="n">
-        <v>23.15384615384615</v>
+        <v>22.75</v>
       </c>
       <c r="AR12" t="n">
-        <v>181.0769230769231</v>
+        <v>182.375</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.307692307692308</v>
+        <v>1.25</v>
       </c>
       <c r="AT12" t="n">
-        <v>73.30769230769231</v>
+        <v>72.875</v>
       </c>
       <c r="AU12" t="n">
-        <v>6023076.923076923</v>
+        <v>5643750</v>
       </c>
       <c r="AV12" t="n">
-        <v>80.30769230769231</v>
+        <v>80.4375</v>
       </c>
       <c r="AW12" t="n">
-        <v>20.75</v>
+        <v>19.85714285714286</v>
       </c>
       <c r="AX12" t="n">
-        <v>182.1666666666667</v>
+        <v>181.0952380952381</v>
       </c>
       <c r="AY12" t="n">
         <v>1</v>
       </c>
       <c r="AZ12" t="n">
-        <v>67.5</v>
+        <v>67.42857142857143</v>
       </c>
       <c r="BA12" t="n">
-        <v>2800000</v>
+        <v>2714285.714285714</v>
       </c>
       <c r="BB12" t="n">
-        <v>77.33333333333333</v>
+        <v>78.47619047619048</v>
       </c>
       <c r="BC12" t="n">
         <v>24.5</v>
@@ -3018,7 +3062,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>QiPssnZI</t>
+          <t>06FhaTlm</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -3026,76 +3070,78 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">landry r 
+          <t xml:space="preserve">rosier e 
   fra </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade velodrome
-  marseille </t>
+          <t xml:space="preserve">stade marcel tribut
+  dunkerque </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>67394</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
+        <v>4933</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3123</v>
+      </c>
       <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ADl76OZP</t>
+          <t>tAAobNse</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>AZwK8L6R</t>
+          <t>0pOdQOCg</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
+        <v>52</v>
+      </c>
+      <c r="N13" t="n">
         <v>48</v>
-      </c>
-      <c r="N13" t="n">
-        <v>52</v>
       </c>
       <c r="O13" t="n">
         <v>13</v>
       </c>
       <c r="P13" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
         <v>9</v>
       </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>4</v>
-      </c>
-      <c r="S13" t="n">
-        <v>22</v>
-      </c>
       <c r="T13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="V13" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>EwpPg8iH</t>
+          <t>lb31RXzP</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>fo8nHfg4</t>
+          <t>OQuqpG7i</t>
         </is>
       </c>
       <c r="Y13" t="n">
@@ -3124,29 +3170,41 @@
       <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="inlineStr"/>
       <c r="AP13" t="inlineStr"/>
-      <c r="AQ13" t="inlineStr"/>
-      <c r="AR13" t="inlineStr"/>
-      <c r="AS13" t="inlineStr"/>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AU13" t="inlineStr"/>
-      <c r="AV13" t="inlineStr"/>
+      <c r="AQ13" t="n">
+        <v>22.92307692307692</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>175.8461538461538</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>64.30769230769231</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1073076.923076923</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>73.23076923076923</v>
+      </c>
       <c r="AW13" t="n">
-        <v>26.3</v>
+        <v>21.30769230769231</v>
       </c>
       <c r="AX13" t="n">
-        <v>179.5</v>
+        <v>184.0769230769231</v>
       </c>
       <c r="AY13" t="n">
         <v>1</v>
       </c>
       <c r="AZ13" t="n">
-        <v>65.5</v>
+        <v>62</v>
       </c>
       <c r="BA13" t="n">
-        <v>967500</v>
+        <v>726923.0769230769</v>
       </c>
       <c r="BB13" t="n">
-        <v>67</v>
+        <v>71.30769230769231</v>
       </c>
       <c r="BC13" t="inlineStr"/>
       <c r="BD13" t="inlineStr"/>
@@ -3166,7 +3224,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>8WI0c7Ja</t>
+          <t>QiPssnZI</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -3174,76 +3232,76 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">chapapria r 
+          <t xml:space="preserve">landry r 
   fra </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de roudourou
-  guingamp </t>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>19060</v>
+        <v>67394</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>QDfKl36E</t>
+          <t>ADl76OZP</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2kM6ufaS</t>
+          <t>AZwK8L6R</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="N14" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="O14" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="P14" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="Q14" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="S14" t="n">
+        <v>22</v>
+      </c>
+      <c r="T14" t="n">
+        <v>16</v>
+      </c>
+      <c r="U14" t="n">
         <v>12</v>
       </c>
-      <c r="T14" t="n">
+      <c r="V14" t="n">
         <v>10</v>
       </c>
-      <c r="U14" t="n">
-        <v>2</v>
-      </c>
-      <c r="V14" t="n">
-        <v>12</v>
-      </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>QNSJnsB5</t>
+          <t>EwpPg8iH</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>SzfSpYcf</t>
+          <t>fo8nHfg4</t>
         </is>
       </c>
       <c r="Y14" t="n">
@@ -3260,54 +3318,42 @@
       </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="n">
-        <v>24.11111111111111</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>179.8888888888889</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>65.33333333333333</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1077777.777777778</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>70.44444444444444</v>
-      </c>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="inlineStr"/>
       <c r="AM14" t="inlineStr"/>
       <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="inlineStr"/>
       <c r="AP14" t="inlineStr"/>
-      <c r="AQ14" t="n">
-        <v>22.92857142857143</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>180.4285714285714</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>61.57142857142857</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>760714.2857142857</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="AW14" t="inlineStr"/>
-      <c r="AX14" t="inlineStr"/>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr"/>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="n">
+        <v>25.72727272727273</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>179.0909090909091</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>65.63636363636364</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1079545.454545455</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>67.90909090909091</v>
+      </c>
       <c r="BC14" t="inlineStr"/>
       <c r="BD14" t="inlineStr"/>
       <c r="BE14" t="inlineStr"/>
@@ -3326,7 +3372,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>UPVYr846</t>
+          <t>8WI0c7Ja</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -3334,76 +3380,78 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">lesage m 
+          <t xml:space="preserve">chapapria r 
   fra </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade des alpes
-  grenoble </t>
+          <t xml:space="preserve">stade de roudourou
+  guingamp </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>20068</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
+        <v>19060</v>
+      </c>
+      <c r="F15" t="n">
+        <v>7872</v>
+      </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>UgPj1p1N</t>
+          <t>QDfKl36E</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>6NOhR4cm</t>
+          <t>2kM6ufaS</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="N15" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="O15" t="n">
+        <v>21</v>
+      </c>
+      <c r="P15" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q15" t="n">
         <v>7</v>
       </c>
-      <c r="P15" t="n">
+      <c r="R15" t="n">
+        <v>7</v>
+      </c>
+      <c r="S15" t="n">
         <v>12</v>
       </c>
-      <c r="Q15" t="n">
-        <v>4</v>
-      </c>
-      <c r="R15" t="n">
-        <v>5</v>
-      </c>
-      <c r="S15" t="n">
-        <v>8</v>
-      </c>
       <c r="T15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U15" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="V15" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>WrQARdPN</t>
+          <t>QNSJnsB5</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>fm0Qb28B</t>
+          <t>SzfSpYcf</t>
         </is>
       </c>
       <c r="Y15" t="n">
@@ -3421,77 +3469,53 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="n">
-        <v>26.8</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="AF15" t="n">
-        <v>185.7</v>
+        <v>179.8888888888889</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AH15" t="n">
-        <v>68.2</v>
+        <v>65.33333333333333</v>
       </c>
       <c r="AI15" t="n">
-        <v>1597500</v>
+        <v>1077777.777777778</v>
       </c>
       <c r="AJ15" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>23.44444444444444</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>182.2222222222222</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>64.11111111111111</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>975000</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>71.88888888888889</v>
-      </c>
+        <v>70.44444444444444</v>
+      </c>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="n">
-        <v>25.64285714285714</v>
+        <v>22.92857142857143</v>
       </c>
       <c r="AR15" t="n">
-        <v>181</v>
+        <v>180.4285714285714</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.142857142857143</v>
+        <v>1</v>
       </c>
       <c r="AT15" t="n">
-        <v>67.71428571428571</v>
+        <v>61.57142857142857</v>
       </c>
       <c r="AU15" t="n">
-        <v>1848214.285714286</v>
+        <v>760714.2857142857</v>
       </c>
       <c r="AV15" t="n">
-        <v>73.42857142857143</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>27.88888888888889</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>177.6666666666667</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>65.33333333333333</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>736111.1111111111</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>69</v>
-      </c>
+        <v>69.5</v>
+      </c>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="inlineStr"/>
       <c r="BD15" t="inlineStr"/>
       <c r="BE15" t="inlineStr"/>
@@ -3510,7 +3534,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>06FhaTlm</t>
+          <t>UPVYr846</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -3518,76 +3542,78 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">rosier e 
+          <t xml:space="preserve">lesage m 
   fra </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade marcel tribut
-  dunkerque </t>
+          <t xml:space="preserve">stade des alpes
+  grenoble </t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4933</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
+        <v>20068</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4087</v>
+      </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>tAAobNse</t>
+          <t>UgPj1p1N</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0pOdQOCg</t>
+          <t>6NOhR4cm</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="N16" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="O16" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="P16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T16" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="U16" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="V16" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>lb31RXzP</t>
+          <t>WrQARdPN</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>OQuqpG7i</t>
+          <t>fm0Qb28B</t>
         </is>
       </c>
       <c r="Y16" t="n">
@@ -3604,53 +3630,77 @@
       </c>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="inlineStr"/>
-      <c r="AM16" t="inlineStr"/>
-      <c r="AN16" t="inlineStr"/>
-      <c r="AO16" t="inlineStr"/>
-      <c r="AP16" t="inlineStr"/>
+      <c r="AE16" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>185</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1597500</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>23.44444444444444</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>182.2222222222222</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>64.11111111111111</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>975000</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>71.88888888888889</v>
+      </c>
       <c r="AQ16" t="n">
-        <v>22.92307692307692</v>
+        <v>25.64285714285714</v>
       </c>
       <c r="AR16" t="n">
-        <v>175.8461538461538</v>
+        <v>181</v>
       </c>
       <c r="AS16" t="n">
-        <v>1</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="AT16" t="n">
-        <v>64.30769230769231</v>
+        <v>67.71428571428571</v>
       </c>
       <c r="AU16" t="n">
-        <v>1073076.923076923</v>
+        <v>1848214.285714286</v>
       </c>
       <c r="AV16" t="n">
-        <v>73.23076923076923</v>
+        <v>73.42857142857143</v>
       </c>
       <c r="AW16" t="n">
-        <v>21.30769230769231</v>
+        <v>27.88888888888889</v>
       </c>
       <c r="AX16" t="n">
-        <v>184.0769230769231</v>
+        <v>177.6666666666667</v>
       </c>
       <c r="AY16" t="n">
         <v>1</v>
       </c>
       <c r="AZ16" t="n">
-        <v>62</v>
+        <v>65.33333333333333</v>
       </c>
       <c r="BA16" t="n">
-        <v>726923.0769230769</v>
+        <v>736111.1111111111</v>
       </c>
       <c r="BB16" t="n">
-        <v>71.30769230769231</v>
+        <v>69</v>
       </c>
       <c r="BC16" t="inlineStr"/>
       <c r="BD16" t="inlineStr"/>
@@ -3691,7 +3741,9 @@
       <c r="E17" t="n">
         <v>10800</v>
       </c>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>5421</v>
+      </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
@@ -3768,7 +3820,7 @@
         <v>24.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>181.875</v>
+        <v>181.75</v>
       </c>
       <c r="AG17" t="n">
         <v>1.125</v>
@@ -3875,7 +3927,9 @@
       <c r="E18" t="n">
         <v>20300</v>
       </c>
-      <c r="F18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>13076</v>
+      </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
@@ -3949,22 +4003,22 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="n">
-        <v>23.25</v>
+        <v>24.33333333333333</v>
       </c>
       <c r="AF18" t="n">
-        <v>181.5</v>
+        <v>181.5555555555555</v>
       </c>
       <c r="AG18" t="n">
-        <v>1</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="AH18" t="n">
-        <v>65.625</v>
+        <v>66.77777777777777</v>
       </c>
       <c r="AI18" t="n">
-        <v>1428125</v>
+        <v>1680555.555555556</v>
       </c>
       <c r="AJ18" t="n">
-        <v>74.625</v>
+        <v>74.77777777777777</v>
       </c>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="inlineStr"/>
@@ -4047,7 +4101,9 @@
       <c r="E19" t="n">
         <v>8470</v>
       </c>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>3398</v>
+      </c>
       <c r="G19" t="n">
         <v>2</v>
       </c>
@@ -4121,58 +4177,58 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="n">
-        <v>24.22222222222222</v>
+        <v>24.1</v>
       </c>
       <c r="AF19" t="n">
-        <v>182</v>
+        <v>182.3</v>
       </c>
       <c r="AG19" t="n">
         <v>1</v>
       </c>
       <c r="AH19" t="n">
-        <v>64.66666666666667</v>
+        <v>64.8</v>
       </c>
       <c r="AI19" t="n">
-        <v>1016666.666666667</v>
+        <v>1035000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>70.55555555555556</v>
+        <v>70.7</v>
       </c>
       <c r="AK19" t="n">
-        <v>24.5</v>
+        <v>24.55555555555556</v>
       </c>
       <c r="AL19" t="n">
-        <v>176.375</v>
+        <v>177.2222222222222</v>
       </c>
       <c r="AM19" t="n">
         <v>1</v>
       </c>
       <c r="AN19" t="n">
-        <v>65.125</v>
+        <v>65.77777777777777</v>
       </c>
       <c r="AO19" t="n">
-        <v>1168750</v>
+        <v>1294444.444444444</v>
       </c>
       <c r="AP19" t="n">
-        <v>70.875</v>
+        <v>71.22222222222223</v>
       </c>
       <c r="AQ19" t="n">
-        <v>28.5</v>
+        <v>28.17647058823529</v>
       </c>
       <c r="AR19" t="n">
-        <v>176.1875</v>
+        <v>176.7058823529412</v>
       </c>
       <c r="AS19" t="n">
         <v>1</v>
       </c>
       <c r="AT19" t="n">
-        <v>65.8125</v>
+        <v>65.82352941176471</v>
       </c>
       <c r="AU19" t="n">
-        <v>715625</v>
+        <v>744117.6470588235</v>
       </c>
       <c r="AV19" t="n">
-        <v>70.0625</v>
+        <v>70.17647058823529</v>
       </c>
       <c r="AW19" t="n">
         <v>27.6875</v>
@@ -4313,22 +4369,22 @@
       <c r="AI20" t="inlineStr"/>
       <c r="AJ20" t="inlineStr"/>
       <c r="AK20" t="n">
-        <v>27.66666666666667</v>
+        <v>27.2</v>
       </c>
       <c r="AL20" t="n">
-        <v>176.4444444444445</v>
+        <v>177.3</v>
       </c>
       <c r="AM20" t="n">
         <v>1</v>
       </c>
       <c r="AN20" t="n">
-        <v>65.11111111111111</v>
+        <v>65.2</v>
       </c>
       <c r="AO20" t="n">
-        <v>722222.2222222222</v>
+        <v>770000</v>
       </c>
       <c r="AP20" t="n">
-        <v>68.55555555555556</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AQ20" t="n">
         <v>22.5</v>
@@ -4349,22 +4405,22 @@
         <v>77</v>
       </c>
       <c r="AW20" t="n">
-        <v>24.52380952380953</v>
+        <v>24.45454545454545</v>
       </c>
       <c r="AX20" t="n">
-        <v>182.4761904761905</v>
+        <v>182.5909090909091</v>
       </c>
       <c r="AY20" t="n">
         <v>1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>65.76190476190476</v>
+        <v>65.77272727272727</v>
       </c>
       <c r="BA20" t="n">
-        <v>1139285.714285714</v>
+        <v>1142045.454545455</v>
       </c>
       <c r="BB20" t="n">
-        <v>71.57142857142857</v>
+        <v>71.59090909090909</v>
       </c>
       <c r="BC20" t="inlineStr"/>
       <c r="BD20" t="inlineStr"/>
@@ -4484,12 +4540,24 @@
         </is>
       </c>
       <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="inlineStr"/>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr"/>
-      <c r="AJ21" t="inlineStr"/>
+      <c r="AE21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>183</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>15960000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>80.8</v>
+      </c>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="inlineStr"/>
       <c r="AM21" t="inlineStr"/>
@@ -4497,61 +4565,61 @@
       <c r="AO21" t="inlineStr"/>
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="n">
-        <v>23.8</v>
+        <v>21.625</v>
       </c>
       <c r="AR21" t="n">
-        <v>178</v>
+        <v>180.625</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.6</v>
+        <v>1.375</v>
       </c>
       <c r="AT21" t="n">
-        <v>74.2</v>
+        <v>70.375</v>
       </c>
       <c r="AU21" t="n">
-        <v>11320000</v>
+        <v>7675000</v>
       </c>
       <c r="AV21" t="n">
-        <v>78.8</v>
+        <v>80.75</v>
       </c>
       <c r="AW21" t="n">
-        <v>21.2</v>
+        <v>22</v>
       </c>
       <c r="AX21" t="n">
-        <v>183.9333333333333</v>
+        <v>185.4444444444445</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.066666666666667</v>
+        <v>1.055555555555556</v>
       </c>
       <c r="AZ21" t="n">
-        <v>67.86666666666666</v>
+        <v>68.88888888888889</v>
       </c>
       <c r="BA21" t="n">
-        <v>3386666.666666667</v>
+        <v>3555555.555555556</v>
       </c>
       <c r="BB21" t="n">
-        <v>77.86666666666666</v>
+        <v>77.38888888888889</v>
       </c>
       <c r="BC21" t="n">
         <v>21</v>
       </c>
       <c r="BD21" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="BE21" t="n">
         <v>1</v>
       </c>
       <c r="BF21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BG21" t="n">
-        <v>135</v>
+        <v>206</v>
       </c>
       <c r="BH21" t="n">
-        <v>5700000</v>
+        <v>9900000</v>
       </c>
       <c r="BI21" t="n">
-        <v>153</v>
+        <v>233</v>
       </c>
       <c r="BJ21" t="n">
         <v>21</v>
@@ -4599,7 +4667,9 @@
       <c r="E22" t="n">
         <v>36178</v>
       </c>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>21656</v>
+      </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
@@ -4677,58 +4747,58 @@
       </c>
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="n">
-        <v>23.11111111111111</v>
+        <v>23.36363636363636</v>
       </c>
       <c r="AF22" t="n">
-        <v>183.2222222222222</v>
+        <v>183.6363636363636</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.111111111111111</v>
+        <v>1.181818181818182</v>
       </c>
       <c r="AH22" t="n">
-        <v>74</v>
+        <v>73.27272727272727</v>
       </c>
       <c r="AI22" t="n">
-        <v>10166666.66666667</v>
+        <v>9977272.727272727</v>
       </c>
       <c r="AJ22" t="n">
-        <v>79.88888888888889</v>
+        <v>78.90909090909091</v>
       </c>
       <c r="AK22" t="n">
-        <v>23.22222222222222</v>
+        <v>22.9</v>
       </c>
       <c r="AL22" t="n">
-        <v>180.6666666666667</v>
+        <v>181.7</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.111111111111111</v>
+        <v>1.1</v>
       </c>
       <c r="AN22" t="n">
-        <v>72.66666666666667</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AO22" t="n">
-        <v>5355555.555555556</v>
+        <v>5150000</v>
       </c>
       <c r="AP22" t="n">
-        <v>78.22222222222223</v>
+        <v>78.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>22.3125</v>
+        <v>22.52941176470588</v>
       </c>
       <c r="AR22" t="n">
-        <v>180.5625</v>
+        <v>180.5882352941177</v>
       </c>
       <c r="AS22" t="n">
-        <v>1</v>
+        <v>1.058823529411765</v>
       </c>
       <c r="AT22" t="n">
-        <v>72.625</v>
+        <v>72.94117647058823</v>
       </c>
       <c r="AU22" t="n">
-        <v>5893750</v>
+        <v>6576470.588235294</v>
       </c>
       <c r="AV22" t="n">
-        <v>78.4375</v>
+        <v>78.52941176470588</v>
       </c>
       <c r="AW22" t="n">
         <v>24.0625</v>
@@ -4881,76 +4951,76 @@
       </c>
       <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="n">
-        <v>23.9</v>
+        <v>23.90909090909091</v>
       </c>
       <c r="AF23" t="n">
-        <v>181.3</v>
+        <v>181.6363636363636</v>
       </c>
       <c r="AG23" t="n">
+        <v>1.363636363636364</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>72.81818181818181</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>5281818.181818182</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>76.81818181818181</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>69</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1987500</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>26.06666666666667</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>183.1333333333333</v>
+      </c>
+      <c r="AS23" t="n">
         <v>1.4</v>
       </c>
-      <c r="AH23" t="n">
-        <v>72.90000000000001</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>5490000</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>77</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>26.25</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>182.25</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>69.125</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1834375</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>72</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>26.21428571428572</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>183</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>1.428571428571429</v>
-      </c>
       <c r="AT23" t="n">
-        <v>71.78571428571429</v>
+        <v>71.8</v>
       </c>
       <c r="AU23" t="n">
-        <v>3857142.857142857</v>
+        <v>3813333.333333333</v>
       </c>
       <c r="AV23" t="n">
-        <v>73.92857142857143</v>
+        <v>74</v>
       </c>
       <c r="AW23" t="n">
-        <v>23.90909090909091</v>
+        <v>23.66666666666667</v>
       </c>
       <c r="AX23" t="n">
-        <v>181.2727272727273</v>
+        <v>181.3333333333333</v>
       </c>
       <c r="AY23" t="n">
         <v>1</v>
       </c>
       <c r="AZ23" t="n">
-        <v>64.27272727272727</v>
+        <v>64.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>1077272.727272727</v>
+        <v>1170833.333333333</v>
       </c>
       <c r="BB23" t="n">
-        <v>71.18181818181819</v>
+        <v>71.58333333333333</v>
       </c>
       <c r="BC23" t="n">
         <v>25.5</v>
@@ -5103,76 +5173,76 @@
         </is>
       </c>
       <c r="AE24" t="n">
-        <v>21.11111111111111</v>
+        <v>20.54545454545455</v>
       </c>
       <c r="AF24" t="n">
-        <v>184.5555555555555</v>
+        <v>183.3636363636364</v>
       </c>
       <c r="AG24" t="n">
         <v>1</v>
       </c>
       <c r="AH24" t="n">
-        <v>70.55555555555556</v>
+        <v>69.72727272727273</v>
       </c>
       <c r="AI24" t="n">
-        <v>4291666.666666667</v>
+        <v>3902272.727272727</v>
       </c>
       <c r="AJ24" t="n">
-        <v>80.22222222222223</v>
+        <v>80.18181818181819</v>
       </c>
       <c r="AK24" t="n">
-        <v>24.875</v>
+        <v>24.9</v>
       </c>
       <c r="AL24" t="n">
-        <v>180.25</v>
+        <v>180.3</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AN24" t="n">
-        <v>75.25</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="AO24" t="n">
-        <v>8725000</v>
+        <v>8230000</v>
       </c>
       <c r="AP24" t="n">
-        <v>79.375</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="AQ24" t="n">
-        <v>19.84615384615385</v>
+        <v>19.66666666666667</v>
       </c>
       <c r="AR24" t="n">
-        <v>183.0769230769231</v>
+        <v>182.5</v>
       </c>
       <c r="AS24" t="n">
         <v>1</v>
       </c>
       <c r="AT24" t="n">
-        <v>69.46153846153847</v>
+        <v>69.16666666666667</v>
       </c>
       <c r="AU24" t="n">
-        <v>3638461.538461538</v>
+        <v>3450000</v>
       </c>
       <c r="AV24" t="n">
-        <v>80.84615384615384</v>
+        <v>80.61111111111111</v>
       </c>
       <c r="AW24" t="n">
-        <v>23.2</v>
+        <v>23.11764705882353</v>
       </c>
       <c r="AX24" t="n">
-        <v>180.5</v>
+        <v>180.3529411764706</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.5</v>
+        <v>1.647058823529412</v>
       </c>
       <c r="AZ24" t="n">
-        <v>73.40000000000001</v>
+        <v>72.64705882352941</v>
       </c>
       <c r="BA24" t="n">
-        <v>7865000</v>
+        <v>6985294.117647059</v>
       </c>
       <c r="BB24" t="n">
-        <v>78.3</v>
+        <v>78.11764705882354</v>
       </c>
       <c r="BC24" t="inlineStr"/>
       <c r="BD24" t="inlineStr"/>
@@ -5307,76 +5377,76 @@
       </c>
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="n">
-        <v>25.9</v>
+        <v>25.54545454545455</v>
       </c>
       <c r="AF25" t="n">
-        <v>182.8</v>
+        <v>181.9090909090909</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.4</v>
+        <v>1.363636363636364</v>
       </c>
       <c r="AH25" t="n">
-        <v>76</v>
+        <v>75.81818181818181</v>
       </c>
       <c r="AI25" t="n">
-        <v>12940000</v>
+        <v>12627272.72727273</v>
       </c>
       <c r="AJ25" t="n">
-        <v>79.8</v>
+        <v>80.09090909090909</v>
       </c>
       <c r="AK25" t="n">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="AL25" t="n">
-        <v>179.8</v>
+        <v>181.3636363636364</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.4</v>
+        <v>1.454545454545455</v>
       </c>
       <c r="AN25" t="n">
-        <v>74.3</v>
+        <v>74.45454545454545</v>
       </c>
       <c r="AO25" t="n">
-        <v>6200000</v>
+        <v>6318181.818181818</v>
       </c>
       <c r="AP25" t="n">
-        <v>75.5</v>
+        <v>75.54545454545455</v>
       </c>
       <c r="AQ25" t="n">
-        <v>24.55</v>
+        <v>24.40909090909091</v>
       </c>
       <c r="AR25" t="n">
-        <v>181.7</v>
+        <v>181.5909090909091</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.3</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="AT25" t="n">
-        <v>74.2</v>
+        <v>74.18181818181819</v>
       </c>
       <c r="AU25" t="n">
-        <v>7215000</v>
+        <v>7240909.090909091</v>
       </c>
       <c r="AV25" t="n">
-        <v>78.05</v>
+        <v>78.27272727272727</v>
       </c>
       <c r="AW25" t="n">
-        <v>24</v>
+        <v>24.3125</v>
       </c>
       <c r="AX25" t="n">
-        <v>181.6666666666667</v>
+        <v>182.625</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.133333333333333</v>
+        <v>1.1875</v>
       </c>
       <c r="AZ25" t="n">
-        <v>69.53333333333333</v>
+        <v>69.9375</v>
       </c>
       <c r="BA25" t="n">
-        <v>3973333.333333333</v>
+        <v>4193750</v>
       </c>
       <c r="BB25" t="n">
-        <v>74.66666666666667</v>
+        <v>74.75</v>
       </c>
       <c r="BC25" t="n">
         <v>25</v>
@@ -5713,22 +5783,22 @@
       </c>
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="n">
-        <v>22.625</v>
+        <v>24.3</v>
       </c>
       <c r="AF27" t="n">
-        <v>181.75</v>
+        <v>182.9</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.375</v>
+        <v>1.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>74.5</v>
+        <v>74.8</v>
       </c>
       <c r="AI27" t="n">
-        <v>11625000</v>
+        <v>10350000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>81.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="AK27" t="n">
         <v>25.1</v>
@@ -5749,22 +5819,22 @@
         <v>73</v>
       </c>
       <c r="AQ27" t="n">
-        <v>25.07142857142857</v>
+        <v>25.46666666666667</v>
       </c>
       <c r="AR27" t="n">
-        <v>179.3571428571429</v>
+        <v>180.2666666666667</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.357142857142857</v>
+        <v>1.466666666666667</v>
       </c>
       <c r="AT27" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="AU27" t="n">
-        <v>6525000</v>
+        <v>6456666.666666667</v>
       </c>
       <c r="AV27" t="n">
-        <v>78.64285714285714</v>
+        <v>78.46666666666667</v>
       </c>
       <c r="AW27" t="n">
         <v>25</v>
@@ -5931,28 +6001,28 @@
         </is>
       </c>
       <c r="AE28" t="n">
-        <v>25</v>
+        <v>25.2</v>
       </c>
       <c r="AF28" t="n">
-        <v>179.7777777777778</v>
+        <v>180.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.666666666666667</v>
+        <v>1.7</v>
       </c>
       <c r="AH28" t="n">
-        <v>75.66666666666667</v>
+        <v>75.8</v>
       </c>
       <c r="AI28" t="n">
-        <v>10300000</v>
+        <v>10370000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>79.77777777777777</v>
+        <v>79.7</v>
       </c>
       <c r="AK28" t="n">
         <v>23.9</v>
       </c>
       <c r="AL28" t="n">
-        <v>183.4</v>
+        <v>183.7</v>
       </c>
       <c r="AM28" t="n">
         <v>1.4</v>
@@ -5961,10 +6031,10 @@
         <v>75.90000000000001</v>
       </c>
       <c r="AO28" t="n">
-        <v>11600000</v>
+        <v>11650000</v>
       </c>
       <c r="AP28" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AQ28" t="n">
         <v>24.95652173913043</v>
@@ -5979,28 +6049,28 @@
         <v>74.39130434782609</v>
       </c>
       <c r="AU28" t="n">
-        <v>7004347.826086956</v>
+        <v>7026086.956521739</v>
       </c>
       <c r="AV28" t="n">
-        <v>79.47826086956522</v>
+        <v>79.52173913043478</v>
       </c>
       <c r="AW28" t="n">
         <v>21.16666666666667</v>
       </c>
       <c r="AX28" t="n">
-        <v>183.1666666666667</v>
+        <v>183.3333333333333</v>
       </c>
       <c r="AY28" t="n">
         <v>1.222222222222222</v>
       </c>
       <c r="AZ28" t="n">
-        <v>73.72222222222223</v>
+        <v>73.77777777777777</v>
       </c>
       <c r="BA28" t="n">
-        <v>11236111.11111111</v>
+        <v>11958333.33333333</v>
       </c>
       <c r="BB28" t="n">
-        <v>82</v>
+        <v>82.11111111111111</v>
       </c>
       <c r="BC28" t="inlineStr"/>
       <c r="BD28" t="inlineStr"/>
@@ -6055,7 +6125,9 @@
       <c r="E29" t="n">
         <v>16787</v>
       </c>
-      <c r="F29" t="inlineStr"/>
+      <c r="F29" t="n">
+        <v>10798</v>
+      </c>
       <c r="G29" t="n">
         <v>2</v>
       </c>
@@ -6322,17 +6394,29 @@
           <t>SblU3Hee</t>
         </is>
       </c>
-      <c r="AE30" t="inlineStr"/>
-      <c r="AF30" t="inlineStr"/>
-      <c r="AG30" t="inlineStr"/>
-      <c r="AH30" t="inlineStr"/>
-      <c r="AI30" t="inlineStr"/>
-      <c r="AJ30" t="inlineStr"/>
+      <c r="AE30" t="n">
+        <v>23.44444444444444</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>182.4444444444445</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>2.222222222222222</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>82.66666666666667</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>51611111.11111111</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>86.77777777777777</v>
+      </c>
       <c r="AK30" t="n">
         <v>26.45454545454545</v>
       </c>
       <c r="AL30" t="n">
-        <v>180.2727272727273</v>
+        <v>180.8181818181818</v>
       </c>
       <c r="AM30" t="n">
         <v>1.454545454545455</v>
@@ -6368,7 +6452,7 @@
         <v>25.08333333333333</v>
       </c>
       <c r="AX30" t="n">
-        <v>181.75</v>
+        <v>182.25</v>
       </c>
       <c r="AY30" t="n">
         <v>1.25</v>
@@ -6428,7 +6512,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>nsErYjjl</t>
+          <t>MaSQpUZg</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
@@ -6436,78 +6520,78 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">leleu m 
+          <t xml:space="preserve">thual o 
   fra </t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">nouste camp
-  pau </t>
+          <t xml:space="preserve">stade francis le basser
+  laval </t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4031</v>
+        <v>11017</v>
       </c>
       <c r="F31" t="n">
-        <v>3033</v>
+        <v>7282</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>6NOhR4cm</t>
+          <t>E1wDrLsJ</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>GjLn2QoH</t>
+          <t>QDfKl36E</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="N31" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="O31" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="P31" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R31" t="n">
         <v>4</v>
       </c>
       <c r="S31" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="T31" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="U31" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="V31" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>fm0Qb28B</t>
+          <t>Ys1Pb7ws</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Q9EVqFe4</t>
+          <t>QNSJnsB5</t>
         </is>
       </c>
       <c r="Y31" t="n">
@@ -6525,76 +6609,76 @@
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="n">
-        <v>23.33333333333333</v>
+        <v>26.5</v>
       </c>
       <c r="AF31" t="n">
-        <v>185.3333333333333</v>
+        <v>181.125</v>
       </c>
       <c r="AG31" t="n">
         <v>1</v>
       </c>
       <c r="AH31" t="n">
-        <v>64.88888888888889</v>
+        <v>66.75</v>
       </c>
       <c r="AI31" t="n">
-        <v>1066666.666666667</v>
+        <v>1281250</v>
       </c>
       <c r="AJ31" t="n">
-        <v>73</v>
+        <v>72.625</v>
       </c>
       <c r="AK31" t="n">
-        <v>26.375</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="AL31" t="n">
-        <v>180.5</v>
+        <v>179.8888888888889</v>
       </c>
       <c r="AM31" t="n">
         <v>1</v>
       </c>
       <c r="AN31" t="n">
-        <v>68.25</v>
+        <v>65.33333333333333</v>
       </c>
       <c r="AO31" t="n">
-        <v>1643750</v>
+        <v>1077777.777777778</v>
       </c>
       <c r="AP31" t="n">
-        <v>73.25</v>
+        <v>70.44444444444444</v>
       </c>
       <c r="AQ31" t="n">
-        <v>26.84615384615385</v>
+        <v>27.25</v>
       </c>
       <c r="AR31" t="n">
-        <v>181.3076923076923</v>
+        <v>177.75</v>
       </c>
       <c r="AS31" t="n">
         <v>1</v>
       </c>
       <c r="AT31" t="n">
-        <v>65.46153846153847</v>
+        <v>64.58333333333333</v>
       </c>
       <c r="AU31" t="n">
-        <v>786538.4615384615</v>
+        <v>832500</v>
       </c>
       <c r="AV31" t="n">
-        <v>70.92307692307692</v>
+        <v>71</v>
       </c>
       <c r="AW31" t="n">
-        <v>20.23076923076923</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="AX31" t="n">
-        <v>181.4615384615385</v>
+        <v>180.7777777777778</v>
       </c>
       <c r="AY31" t="n">
         <v>1</v>
       </c>
       <c r="AZ31" t="n">
-        <v>62.53846153846154</v>
+        <v>60.33333333333334</v>
       </c>
       <c r="BA31" t="n">
-        <v>875000</v>
+        <v>686111.1111111111</v>
       </c>
       <c r="BB31" t="n">
-        <v>75.38461538461539</v>
+        <v>69.77777777777777</v>
       </c>
       <c r="BC31" t="inlineStr"/>
       <c r="BD31" t="inlineStr"/>
@@ -6614,7 +6698,7 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>UsP4uZcE</t>
+          <t>r97iWUK0</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -6622,78 +6706,78 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">landry r 
+          <t xml:space="preserve">lesage m 
   fra </t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade paul lignon
-  rodez </t>
+          <t xml:space="preserve">stade armand cesari
+  bastia </t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5955</v>
+        <v>16048</v>
       </c>
       <c r="F32" t="n">
-        <v>4901</v>
+        <v>13500</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0pOdQOCg</t>
+          <t>AZwK8L6R</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>4v0yqlWc</t>
+          <t>lKkBAsxF</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="n">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="N32" t="n">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="O32" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P32" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q32" t="n">
         <v>4</v>
       </c>
       <c r="R32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S32" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T32" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="U32" t="n">
+        <v>17</v>
+      </c>
+      <c r="V32" t="n">
         <v>9</v>
       </c>
-      <c r="V32" t="n">
-        <v>11</v>
-      </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>OQuqpG7i</t>
+          <t>fo8nHfg4</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>h89kUbu5</t>
+          <t>dS1CBple</t>
         </is>
       </c>
       <c r="Y32" t="n">
@@ -6709,11 +6793,7 @@
         <v>20242025</v>
       </c>
       <c r="AC32" t="inlineStr"/>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
+      <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr"/>
@@ -6721,58 +6801,58 @@
       <c r="AI32" t="inlineStr"/>
       <c r="AJ32" t="inlineStr"/>
       <c r="AK32" t="n">
-        <v>26.81818181818182</v>
+        <v>26.1</v>
       </c>
       <c r="AL32" t="n">
-        <v>176.8181818181818</v>
+        <v>181.2</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.090909090909091</v>
+        <v>1</v>
       </c>
       <c r="AN32" t="n">
-        <v>70.54545454545455</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="AO32" t="n">
-        <v>1861363.636363636</v>
+        <v>1205000</v>
       </c>
       <c r="AP32" t="n">
-        <v>73.90909090909091</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="AQ32" t="n">
-        <v>20.9375</v>
+        <v>24.2</v>
       </c>
       <c r="AR32" t="n">
-        <v>182.75</v>
+        <v>180.4666666666667</v>
       </c>
       <c r="AS32" t="n">
         <v>1</v>
       </c>
       <c r="AT32" t="n">
-        <v>62.3125</v>
+        <v>64</v>
       </c>
       <c r="AU32" t="n">
-        <v>829687.5</v>
+        <v>923333.3333333334</v>
       </c>
       <c r="AV32" t="n">
-        <v>72.4375</v>
+        <v>68.2</v>
       </c>
       <c r="AW32" t="n">
-        <v>20.375</v>
+        <v>24</v>
       </c>
       <c r="AX32" t="n">
-        <v>181.25</v>
+        <v>181.0666666666667</v>
       </c>
       <c r="AY32" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AZ32" t="n">
-        <v>65.75</v>
+        <v>62.6</v>
       </c>
       <c r="BA32" t="n">
-        <v>1696875</v>
+        <v>728333.3333333334</v>
       </c>
       <c r="BB32" t="n">
-        <v>77</v>
+        <v>71.53333333333333</v>
       </c>
       <c r="BC32" t="inlineStr"/>
       <c r="BD32" t="inlineStr"/>
@@ -6792,7 +6872,7 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>GM5aU8kD</t>
+          <t>UsP4uZcE</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
@@ -6800,78 +6880,78 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">bastien b 
+          <t xml:space="preserve">landry r 
   fra </t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">parc des sports
-  annecy </t>
+          <t xml:space="preserve">stade paul lignon
+  rodez </t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>15660</v>
+        <v>5955</v>
       </c>
       <c r="F33" t="n">
-        <v>7640</v>
+        <v>4901</v>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>25dB6Eto</t>
+          <t>0pOdQOCg</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>ADl76OZP</t>
+          <t>4v0yqlWc</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="n">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="N33" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="O33" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="P33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q33" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S33" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T33" t="n">
         <v>13</v>
       </c>
       <c r="U33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V33" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>SIiBpBrs</t>
+          <t>OQuqpG7i</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>EwpPg8iH</t>
+          <t>h89kUbu5</t>
         </is>
       </c>
       <c r="Y33" t="n">
@@ -6887,55 +6967,71 @@
         <v>20242025</v>
       </c>
       <c r="AC33" t="inlineStr"/>
-      <c r="AD33" t="inlineStr"/>
-      <c r="AE33" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>182</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>64.44444444444444</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>841666.6666666666</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>68.11111111111111</v>
-      </c>
-      <c r="AK33" t="inlineStr"/>
-      <c r="AL33" t="inlineStr"/>
-      <c r="AM33" t="inlineStr"/>
-      <c r="AN33" t="inlineStr"/>
-      <c r="AO33" t="inlineStr"/>
-      <c r="AP33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="n">
+        <v>26.81818181818182</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>176.8181818181818</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>70.54545454545455</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1861363.636363636</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>73.90909090909091</v>
+      </c>
       <c r="AQ33" t="n">
-        <v>24.81818181818182</v>
+        <v>20.9375</v>
       </c>
       <c r="AR33" t="n">
-        <v>181.2727272727273</v>
+        <v>182.75</v>
       </c>
       <c r="AS33" t="n">
         <v>1</v>
       </c>
       <c r="AT33" t="n">
-        <v>64.36363636363636</v>
+        <v>62.3125</v>
       </c>
       <c r="AU33" t="n">
-        <v>881818.1818181818</v>
+        <v>829687.5</v>
       </c>
       <c r="AV33" t="n">
-        <v>70.36363636363636</v>
-      </c>
-      <c r="AW33" t="inlineStr"/>
-      <c r="AX33" t="inlineStr"/>
-      <c r="AY33" t="inlineStr"/>
-      <c r="AZ33" t="inlineStr"/>
-      <c r="BA33" t="inlineStr"/>
-      <c r="BB33" t="inlineStr"/>
+        <v>72.4375</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>20.375</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>65.75</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>1696875</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>77</v>
+      </c>
       <c r="BC33" t="inlineStr"/>
       <c r="BD33" t="inlineStr"/>
       <c r="BE33" t="inlineStr"/>
@@ -6954,7 +7050,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>r97iWUK0</t>
+          <t>GM5aU8kD</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -6962,36 +7058,36 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">lesage m 
+          <t xml:space="preserve">bastien b 
   fra </t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade armand cesari
-  bastia </t>
+          <t xml:space="preserve">parc des sports
+  annecy </t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>16048</v>
+        <v>15660</v>
       </c>
       <c r="F34" t="n">
-        <v>13500</v>
+        <v>7640</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>AZwK8L6R</t>
+          <t>25dB6Eto</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>lKkBAsxF</t>
+          <t>ADl76OZP</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -7003,37 +7099,37 @@
         <v>41</v>
       </c>
       <c r="O34" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="P34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q34" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S34" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T34" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="U34" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="V34" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>fo8nHfg4</t>
+          <t>SIiBpBrs</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>dS1CBple</t>
+          <t>EwpPg8iH</t>
         </is>
       </c>
       <c r="Y34" t="n">
@@ -7050,66 +7146,54 @@
       </c>
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr"/>
-      <c r="AE34" t="inlineStr"/>
-      <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="inlineStr"/>
-      <c r="AH34" t="inlineStr"/>
-      <c r="AI34" t="inlineStr"/>
-      <c r="AJ34" t="inlineStr"/>
-      <c r="AK34" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>181.2</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>67.09999999999999</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>1205000</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>71.09999999999999</v>
-      </c>
+      <c r="AE34" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>182</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>64.44444444444444</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>841666.6666666666</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>68.11111111111111</v>
+      </c>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="inlineStr"/>
       <c r="AQ34" t="n">
-        <v>24.5</v>
+        <v>24.81818181818182</v>
       </c>
       <c r="AR34" t="n">
-        <v>180.8571428571429</v>
+        <v>181.2727272727273</v>
       </c>
       <c r="AS34" t="n">
         <v>1</v>
       </c>
       <c r="AT34" t="n">
-        <v>63.78571428571428</v>
+        <v>64.36363636363636</v>
       </c>
       <c r="AU34" t="n">
-        <v>832142.8571428572</v>
+        <v>881818.1818181818</v>
       </c>
       <c r="AV34" t="n">
-        <v>67.57142857142857</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>181.0666666666667</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>62.6</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>728333.3333333334</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>71.53333333333333</v>
-      </c>
+        <v>70.36363636363636</v>
+      </c>
+      <c r="AW34" t="inlineStr"/>
+      <c r="AX34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr"/>
+      <c r="BA34" t="inlineStr"/>
+      <c r="BB34" t="inlineStr"/>
       <c r="BC34" t="inlineStr"/>
       <c r="BD34" t="inlineStr"/>
       <c r="BE34" t="inlineStr"/>
@@ -7128,7 +7212,7 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>MaSQpUZg</t>
+          <t>nsErYjjl</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
@@ -7136,78 +7220,78 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">thual o 
+          <t xml:space="preserve">leleu m 
   fra </t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade francis le basser
-  laval </t>
+          <t xml:space="preserve">nouste camp
+  pau </t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>11017</v>
+        <v>4031</v>
       </c>
       <c r="F35" t="n">
-        <v>7282</v>
+        <v>3033</v>
       </c>
       <c r="G35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" t="n">
         <v>0</v>
       </c>
-      <c r="H35" t="n">
-        <v>1</v>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>E1wDrLsJ</t>
+          <t>6NOhR4cm</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>QDfKl36E</t>
+          <t>GjLn2QoH</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="N35" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="O35" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="P35" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R35" t="n">
         <v>4</v>
       </c>
       <c r="S35" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="T35" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="U35" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="V35" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Ys1Pb7ws</t>
+          <t>fm0Qb28B</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>QNSJnsB5</t>
+          <t>Q9EVqFe4</t>
         </is>
       </c>
       <c r="Y35" t="n">
@@ -7225,76 +7309,76 @@
       <c r="AC35" t="inlineStr"/>
       <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="n">
-        <v>26.5</v>
+        <v>23.33333333333333</v>
       </c>
       <c r="AF35" t="n">
-        <v>181.125</v>
+        <v>185.3333333333333</v>
       </c>
       <c r="AG35" t="n">
         <v>1</v>
       </c>
       <c r="AH35" t="n">
-        <v>66.75</v>
+        <v>64.88888888888889</v>
       </c>
       <c r="AI35" t="n">
-        <v>1281250</v>
+        <v>1066666.666666667</v>
       </c>
       <c r="AJ35" t="n">
-        <v>72.625</v>
+        <v>73</v>
       </c>
       <c r="AK35" t="n">
-        <v>24.11111111111111</v>
+        <v>27.11111111111111</v>
       </c>
       <c r="AL35" t="n">
-        <v>179.8888888888889</v>
+        <v>180.6666666666667</v>
       </c>
       <c r="AM35" t="n">
-        <v>1</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="AN35" t="n">
-        <v>65.33333333333333</v>
+        <v>69.11111111111111</v>
       </c>
       <c r="AO35" t="n">
-        <v>1077777.777777778</v>
+        <v>1872222.222222222</v>
       </c>
       <c r="AP35" t="n">
-        <v>70.44444444444444</v>
+        <v>73.55555555555556</v>
       </c>
       <c r="AQ35" t="n">
-        <v>27.25</v>
+        <v>26.84615384615385</v>
       </c>
       <c r="AR35" t="n">
-        <v>177.75</v>
+        <v>181.3076923076923</v>
       </c>
       <c r="AS35" t="n">
         <v>1</v>
       </c>
       <c r="AT35" t="n">
-        <v>64.58333333333333</v>
+        <v>65.46153846153847</v>
       </c>
       <c r="AU35" t="n">
-        <v>832500</v>
+        <v>786538.4615384615</v>
       </c>
       <c r="AV35" t="n">
-        <v>71</v>
+        <v>70.92307692307692</v>
       </c>
       <c r="AW35" t="n">
-        <v>22.22222222222222</v>
+        <v>20.23076923076923</v>
       </c>
       <c r="AX35" t="n">
-        <v>180.7777777777778</v>
+        <v>181.4615384615385</v>
       </c>
       <c r="AY35" t="n">
         <v>1</v>
       </c>
       <c r="AZ35" t="n">
-        <v>60.33333333333334</v>
+        <v>62.53846153846154</v>
       </c>
       <c r="BA35" t="n">
-        <v>686111.1111111111</v>
+        <v>875000</v>
       </c>
       <c r="BB35" t="n">
-        <v>69.77777777777777</v>
+        <v>75.38461538461539</v>
       </c>
       <c r="BC35" t="inlineStr"/>
       <c r="BD35" t="inlineStr"/>
@@ -7314,7 +7398,7 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>WUmnhCsK</t>
+          <t>4rrRVcF7</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -7322,78 +7406,76 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">taleb a 
+          <t xml:space="preserve">chapapria r 
   fra </t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la licorne
-  amiens </t>
+          <t xml:space="preserve">stade de l aube
+  troyes </t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>12097</v>
-      </c>
-      <c r="F36" t="n">
-        <v>608</v>
-      </c>
+        <v>20420</v>
+      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0OEHEprs</t>
+          <t>fsfAHubD</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>tAAobNse</t>
+          <t>IRuMRua1</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="N36" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="O36" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="P36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T36" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="U36" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="V36" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>zB2j3YvM</t>
+          <t>4vG8dmrf</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>lb31RXzP</t>
+          <t>4G9MhScS</t>
         </is>
       </c>
       <c r="Y36" t="n">
@@ -7411,64 +7493,76 @@
       <c r="AC36" t="inlineStr"/>
       <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="n">
-        <v>24.11111111111111</v>
+        <v>24.22222222222222</v>
       </c>
       <c r="AF36" t="n">
-        <v>178.8888888888889</v>
+        <v>177.7777777777778</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.111111111111111</v>
+        <v>1</v>
       </c>
       <c r="AH36" t="n">
-        <v>67.33333333333333</v>
+        <v>64.66666666666667</v>
       </c>
       <c r="AI36" t="n">
-        <v>1747222.222222222</v>
+        <v>1072222.222222222</v>
       </c>
       <c r="AJ36" t="n">
-        <v>71.66666666666667</v>
-      </c>
-      <c r="AK36" t="inlineStr"/>
-      <c r="AL36" t="inlineStr"/>
-      <c r="AM36" t="inlineStr"/>
-      <c r="AN36" t="inlineStr"/>
-      <c r="AO36" t="inlineStr"/>
-      <c r="AP36" t="inlineStr"/>
+        <v>70.66666666666667</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>24.375</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>1553125</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>74</v>
+      </c>
       <c r="AQ36" t="n">
-        <v>26.17647058823529</v>
+        <v>27.05882352941176</v>
       </c>
       <c r="AR36" t="n">
-        <v>177.1764705882353</v>
+        <v>179.3529411764706</v>
       </c>
       <c r="AS36" t="n">
-        <v>1</v>
+        <v>1.176470588235294</v>
       </c>
       <c r="AT36" t="n">
-        <v>66.17647058823529</v>
+        <v>67.35294117647059</v>
       </c>
       <c r="AU36" t="n">
-        <v>1182352.941176471</v>
+        <v>1388235.294117647</v>
       </c>
       <c r="AV36" t="n">
-        <v>69.23529411764706</v>
+        <v>70.70588235294117</v>
       </c>
       <c r="AW36" t="n">
-        <v>22.25</v>
+        <v>23</v>
       </c>
       <c r="AX36" t="n">
-        <v>179.5833333333333</v>
+        <v>178.625</v>
       </c>
       <c r="AY36" t="n">
         <v>1</v>
       </c>
       <c r="AZ36" t="n">
-        <v>63.83333333333334</v>
+        <v>65.625</v>
       </c>
       <c r="BA36" t="n">
-        <v>931250</v>
+        <v>1637500</v>
       </c>
       <c r="BB36" t="n">
-        <v>72.91666666666667</v>
+        <v>72.875</v>
       </c>
       <c r="BC36" t="inlineStr"/>
       <c r="BD36" t="inlineStr"/>
@@ -7488,7 +7582,7 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>4rrRVcF7</t>
+          <t>WUmnhCsK</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
@@ -7496,76 +7590,78 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">chapapria r 
+          <t xml:space="preserve">taleb a 
   fra </t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de l aube
-  troyes </t>
+          <t xml:space="preserve">stade de la licorne
+  amiens </t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>20420</v>
-      </c>
-      <c r="F37" t="inlineStr"/>
+        <v>12097</v>
+      </c>
+      <c r="F37" t="n">
+        <v>608</v>
+      </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>fsfAHubD</t>
+          <t>0OEHEprs</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>IRuMRua1</t>
+          <t>tAAobNse</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="N37" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="O37" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="P37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T37" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="U37" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="V37" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>4vG8dmrf</t>
+          <t>zB2j3YvM</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>4G9MhScS</t>
+          <t>lb31RXzP</t>
         </is>
       </c>
       <c r="Y37" t="n">
@@ -7583,76 +7679,64 @@
       <c r="AC37" t="inlineStr"/>
       <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="n">
-        <v>24.22222222222222</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="AF37" t="n">
-        <v>177.7777777777778</v>
+        <v>178.8888888888889</v>
       </c>
       <c r="AG37" t="n">
-        <v>1</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="AH37" t="n">
-        <v>64.66666666666667</v>
+        <v>67.33333333333333</v>
       </c>
       <c r="AI37" t="n">
-        <v>1072222.222222222</v>
+        <v>1747222.222222222</v>
       </c>
       <c r="AJ37" t="n">
-        <v>70.66666666666667</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>24.375</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>180.625</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>1553125</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>74</v>
-      </c>
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr"/>
+      <c r="AP37" t="inlineStr"/>
       <c r="AQ37" t="n">
-        <v>27.05882352941176</v>
+        <v>26.17647058823529</v>
       </c>
       <c r="AR37" t="n">
-        <v>179.3529411764706</v>
+        <v>177.1764705882353</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.176470588235294</v>
+        <v>1</v>
       </c>
       <c r="AT37" t="n">
-        <v>67.35294117647059</v>
+        <v>66.17647058823529</v>
       </c>
       <c r="AU37" t="n">
-        <v>1388235.294117647</v>
+        <v>1182352.941176471</v>
       </c>
       <c r="AV37" t="n">
-        <v>70.70588235294117</v>
+        <v>69.23529411764706</v>
       </c>
       <c r="AW37" t="n">
-        <v>23</v>
+        <v>22.25</v>
       </c>
       <c r="AX37" t="n">
-        <v>178.625</v>
+        <v>179.5833333333333</v>
       </c>
       <c r="AY37" t="n">
         <v>1</v>
       </c>
       <c r="AZ37" t="n">
-        <v>65.625</v>
+        <v>63.83333333333334</v>
       </c>
       <c r="BA37" t="n">
-        <v>1637500</v>
+        <v>931250</v>
       </c>
       <c r="BB37" t="n">
-        <v>72.875</v>
+        <v>72.91666666666667</v>
       </c>
       <c r="BC37" t="inlineStr"/>
       <c r="BD37" t="inlineStr"/>
@@ -7672,7 +7756,7 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>lEQmcVR0</t>
+          <t>OA5YizjL</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -7680,78 +7764,78 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">petit a 
+          <t xml:space="preserve">thual o 
   fra </t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade saint symphorien
-  metz </t>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>28786</v>
+        <v>67394</v>
       </c>
       <c r="F38" t="n">
-        <v>18585</v>
+        <v>2655</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
         <v>1</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>4v0yqlWc</t>
+          <t>ADl76OZP</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>AZwK8L6R</t>
+          <t>jgNAYRGi</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="n">
+        <v>33</v>
+      </c>
+      <c r="N38" t="n">
         <v>67</v>
       </c>
-      <c r="N38" t="n">
-        <v>33</v>
-      </c>
       <c r="O38" t="n">
+        <v>3</v>
+      </c>
+      <c r="P38" t="n">
         <v>18</v>
       </c>
-      <c r="P38" t="n">
+      <c r="Q38" t="n">
+        <v>1</v>
+      </c>
+      <c r="R38" t="n">
         <v>7</v>
       </c>
-      <c r="Q38" t="n">
-        <v>5</v>
-      </c>
-      <c r="R38" t="n">
-        <v>3</v>
-      </c>
       <c r="S38" t="n">
+        <v>8</v>
+      </c>
+      <c r="T38" t="n">
         <v>13</v>
       </c>
-      <c r="T38" t="n">
-        <v>15</v>
-      </c>
       <c r="U38" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V38" t="n">
         <v>6</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>h89kUbu5</t>
+          <t>EwpPg8iH</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>fo8nHfg4</t>
+          <t>Cp0gM1r4</t>
         </is>
       </c>
       <c r="Y38" t="n">
@@ -7766,83 +7850,59 @@
       <c r="AB38" t="n">
         <v>20242025</v>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="AD38" t="inlineStr"/>
-      <c r="AE38" t="n">
-        <v>24.90909090909091</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>177.8181818181818</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.090909090909091</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>68.90909090909091</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>1677272.727272727</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>75.27272727272727</v>
-      </c>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr"/>
+      <c r="AJ38" t="inlineStr"/>
       <c r="AK38" t="n">
-        <v>25.375</v>
+        <v>24.44444444444444</v>
       </c>
       <c r="AL38" t="n">
-        <v>179.625</v>
+        <v>178.1111111111111</v>
       </c>
       <c r="AM38" t="n">
         <v>1</v>
       </c>
       <c r="AN38" t="n">
-        <v>63.625</v>
+        <v>71.77777777777777</v>
       </c>
       <c r="AO38" t="n">
-        <v>723125</v>
+        <v>4622222.222222222</v>
       </c>
       <c r="AP38" t="n">
-        <v>68.375</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>24</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>181.0909090909091</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>67.81818181818181</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>1718181.818181818</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>75</v>
-      </c>
+        <v>77.11111111111111</v>
+      </c>
+      <c r="AQ38" t="inlineStr"/>
+      <c r="AR38" t="inlineStr"/>
+      <c r="AS38" t="inlineStr"/>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AU38" t="inlineStr"/>
+      <c r="AV38" t="inlineStr"/>
       <c r="AW38" t="n">
-        <v>23.25</v>
+        <v>21.73333333333333</v>
       </c>
       <c r="AX38" t="n">
-        <v>180</v>
+        <v>177.4</v>
       </c>
       <c r="AY38" t="n">
         <v>1</v>
       </c>
       <c r="AZ38" t="n">
-        <v>61.5</v>
+        <v>69.06666666666666</v>
       </c>
       <c r="BA38" t="n">
-        <v>679166.6666666666</v>
+        <v>2781666.666666667</v>
       </c>
       <c r="BB38" t="n">
-        <v>68.16666666666667</v>
+        <v>77.53333333333333</v>
       </c>
       <c r="BC38" t="inlineStr"/>
       <c r="BD38" t="inlineStr"/>
@@ -7862,7 +7922,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>OA5YizjL</t>
+          <t>lEQmcVR0</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
@@ -7870,78 +7930,78 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">thual o 
+          <t xml:space="preserve">petit a 
   fra </t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade velodrome
-  marseille </t>
+          <t xml:space="preserve">stade saint symphorien
+  metz </t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>67394</v>
+        <v>28786</v>
       </c>
       <c r="F39" t="n">
-        <v>2655</v>
+        <v>18585</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
         <v>1</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>ADl76OZP</t>
+          <t>4v0yqlWc</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>jgNAYRGi</t>
+          <t>AZwK8L6R</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="n">
+        <v>67</v>
+      </c>
+      <c r="N39" t="n">
         <v>33</v>
       </c>
-      <c r="N39" t="n">
-        <v>67</v>
-      </c>
       <c r="O39" t="n">
+        <v>18</v>
+      </c>
+      <c r="P39" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>5</v>
+      </c>
+      <c r="R39" t="n">
         <v>3</v>
       </c>
-      <c r="P39" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>1</v>
-      </c>
-      <c r="R39" t="n">
-        <v>7</v>
-      </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="U39" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="V39" t="n">
         <v>6</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>EwpPg8iH</t>
+          <t>h89kUbu5</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Cp0gM1r4</t>
+          <t>fo8nHfg4</t>
         </is>
       </c>
       <c r="Y39" t="n">
@@ -7956,59 +8016,83 @@
       <c r="AB39" t="n">
         <v>20242025</v>
       </c>
-      <c r="AC39" t="inlineStr"/>
-      <c r="AD39" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="AE39" t="inlineStr"/>
-      <c r="AF39" t="inlineStr"/>
-      <c r="AG39" t="inlineStr"/>
-      <c r="AH39" t="inlineStr"/>
-      <c r="AI39" t="inlineStr"/>
-      <c r="AJ39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="n">
+        <v>24.90909090909091</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>177.8181818181818</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>68.90909090909091</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1677272.727272727</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>75.27272727272727</v>
+      </c>
       <c r="AK39" t="n">
-        <v>24.44444444444444</v>
+        <v>25.375</v>
       </c>
       <c r="AL39" t="n">
-        <v>178.1111111111111</v>
+        <v>179.625</v>
       </c>
       <c r="AM39" t="n">
         <v>1</v>
       </c>
       <c r="AN39" t="n">
-        <v>71.77777777777777</v>
+        <v>63.625</v>
       </c>
       <c r="AO39" t="n">
-        <v>4622222.222222222</v>
+        <v>723125</v>
       </c>
       <c r="AP39" t="n">
-        <v>77.11111111111111</v>
-      </c>
-      <c r="AQ39" t="inlineStr"/>
-      <c r="AR39" t="inlineStr"/>
-      <c r="AS39" t="inlineStr"/>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AU39" t="inlineStr"/>
-      <c r="AV39" t="inlineStr"/>
+        <v>68.375</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>181.0909090909091</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>67.81818181818181</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>1718181.818181818</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>75</v>
+      </c>
       <c r="AW39" t="n">
-        <v>21.73333333333333</v>
+        <v>22.6</v>
       </c>
       <c r="AX39" t="n">
-        <v>177.4</v>
+        <v>179</v>
       </c>
       <c r="AY39" t="n">
         <v>1</v>
       </c>
       <c r="AZ39" t="n">
-        <v>69.06666666666666</v>
+        <v>62.6</v>
       </c>
       <c r="BA39" t="n">
-        <v>2781666.666666667</v>
+        <v>983333.3333333334</v>
       </c>
       <c r="BB39" t="n">
-        <v>77.53333333333333</v>
+        <v>69.93333333333334</v>
       </c>
       <c r="BC39" t="inlineStr"/>
       <c r="BD39" t="inlineStr"/>
@@ -8133,64 +8217,64 @@
       </c>
       <c r="AD40" t="inlineStr"/>
       <c r="AE40" t="n">
-        <v>25.875</v>
+        <v>25.7</v>
       </c>
       <c r="AF40" t="n">
         <v>180.5</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AH40" t="n">
-        <v>75.625</v>
+        <v>75.7</v>
       </c>
       <c r="AI40" t="n">
-        <v>9475000</v>
+        <v>8830000</v>
       </c>
       <c r="AJ40" t="n">
-        <v>79.25</v>
+        <v>79</v>
       </c>
       <c r="AK40" t="n">
-        <v>25.66666666666667</v>
+        <v>25.8</v>
       </c>
       <c r="AL40" t="n">
-        <v>182.3333333333333</v>
+        <v>183.1</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.666666666666667</v>
+        <v>1.7</v>
       </c>
       <c r="AN40" t="n">
-        <v>76.33333333333333</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="AO40" t="n">
-        <v>10111111.11111111</v>
+        <v>10250000</v>
       </c>
       <c r="AP40" t="n">
         <v>80</v>
       </c>
       <c r="AQ40" t="n">
-        <v>24.23076923076923</v>
+        <v>24.70588235294118</v>
       </c>
       <c r="AR40" t="n">
-        <v>181.9230769230769</v>
+        <v>182.2352941176471</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.538461538461539</v>
+        <v>1.764705882352941</v>
       </c>
       <c r="AT40" t="n">
-        <v>73.07692307692308</v>
+        <v>73.58823529411765</v>
       </c>
       <c r="AU40" t="n">
-        <v>8578846.153846154</v>
+        <v>8513235.294117646</v>
       </c>
       <c r="AV40" t="n">
-        <v>77.53846153846153</v>
+        <v>77.52941176470588</v>
       </c>
       <c r="AW40" t="n">
         <v>23.81818181818182</v>
       </c>
       <c r="AX40" t="n">
-        <v>179.5</v>
+        <v>179.0909090909091</v>
       </c>
       <c r="AY40" t="n">
         <v>1.681818181818182</v>
@@ -8199,10 +8283,10 @@
         <v>73.18181818181819</v>
       </c>
       <c r="BA40" t="n">
-        <v>5522727.272727272</v>
+        <v>5545454.545454546</v>
       </c>
       <c r="BB40" t="n">
-        <v>78.81818181818181</v>
+        <v>78.86363636363636</v>
       </c>
       <c r="BC40" t="n">
         <v>20</v>
@@ -8250,7 +8334,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>2NocJFqd</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
@@ -8258,82 +8342,82 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">stinat j 
+          <t xml:space="preserve">leonard t 
   fra </t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>33150</v>
+        <v>18752</v>
       </c>
       <c r="F41" t="n">
-        <v>25491</v>
+        <v>14811</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>1.01</v>
+        <v>0.26</v>
       </c>
       <c r="L41" t="n">
-        <v>0.33</v>
+        <v>0.92</v>
       </c>
       <c r="M41" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="N41" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="O41" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P41" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q41" t="n">
         <v>3</v>
       </c>
       <c r="R41" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S41" t="n">
+        <v>12</v>
+      </c>
+      <c r="T41" t="n">
+        <v>14</v>
+      </c>
+      <c r="U41" t="n">
         <v>10</v>
       </c>
-      <c r="T41" t="n">
-        <v>8</v>
-      </c>
-      <c r="U41" t="n">
-        <v>8</v>
-      </c>
       <c r="V41" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>UapruDaf</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>YTLwacK1</t>
+          <t>K6b7RoBp</t>
         </is>
       </c>
       <c r="Y41" t="n">
@@ -8351,95 +8435,123 @@
       <c r="AC41" t="inlineStr"/>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="AE41" t="n">
-        <v>22.9</v>
+        <v>25.7</v>
       </c>
       <c r="AF41" t="n">
-        <v>181.1</v>
+        <v>184.5</v>
       </c>
       <c r="AG41" t="n">
         <v>1.1</v>
       </c>
       <c r="AH41" t="n">
-        <v>72.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="AI41" t="n">
-        <v>5200000</v>
+        <v>1587500</v>
       </c>
       <c r="AJ41" t="n">
-        <v>78.7</v>
+        <v>72.8</v>
       </c>
       <c r="AK41" t="n">
-        <v>24.8</v>
+        <v>27.63636363636364</v>
       </c>
       <c r="AL41" t="n">
-        <v>182</v>
+        <v>179.2727272727273</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.4</v>
+        <v>1.454545454545455</v>
       </c>
       <c r="AN41" t="n">
-        <v>72.8</v>
+        <v>77</v>
       </c>
       <c r="AO41" t="n">
-        <v>5310000</v>
+        <v>12381818.18181818</v>
       </c>
       <c r="AP41" t="n">
-        <v>76.2</v>
+        <v>78.72727272727273</v>
       </c>
       <c r="AQ41" t="n">
-        <v>24</v>
+        <v>25.7</v>
       </c>
       <c r="AR41" t="n">
-        <v>178.375</v>
+        <v>183.9</v>
       </c>
       <c r="AS41" t="n">
         <v>1</v>
       </c>
       <c r="AT41" t="n">
-        <v>69.8125</v>
+        <v>66.45</v>
       </c>
       <c r="AU41" t="n">
-        <v>2631250</v>
+        <v>1278750</v>
       </c>
       <c r="AV41" t="n">
-        <v>75.4375</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="AW41" t="n">
-        <v>25.76470588235294</v>
+        <v>23.91304347826087</v>
       </c>
       <c r="AX41" t="n">
-        <v>182.8235294117647</v>
+        <v>180.1304347826087</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.411764705882353</v>
+        <v>1.08695652173913</v>
       </c>
       <c r="AZ41" t="n">
-        <v>71.76470588235294</v>
+        <v>72.95652173913044</v>
       </c>
       <c r="BA41" t="n">
-        <v>3450000</v>
+        <v>6056521.739130435</v>
       </c>
       <c r="BB41" t="n">
-        <v>74.58823529411765</v>
-      </c>
-      <c r="BC41" t="inlineStr"/>
-      <c r="BD41" t="inlineStr"/>
-      <c r="BE41" t="inlineStr"/>
-      <c r="BF41" t="inlineStr"/>
-      <c r="BG41" t="inlineStr"/>
-      <c r="BH41" t="inlineStr"/>
-      <c r="BI41" t="inlineStr"/>
-      <c r="BJ41" t="inlineStr"/>
-      <c r="BK41" t="inlineStr"/>
-      <c r="BL41" t="inlineStr"/>
-      <c r="BM41" t="inlineStr"/>
-      <c r="BN41" t="inlineStr"/>
-      <c r="BO41" t="inlineStr"/>
-      <c r="BP41" t="inlineStr"/>
+        <v>78.1304347826087</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>179.25</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>266</v>
+      </c>
+      <c r="BH41" t="n">
+        <v>5725000</v>
+      </c>
+      <c r="BI41" t="n">
+        <v>290</v>
+      </c>
+      <c r="BJ41" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="BK41" t="n">
+        <v>180.2</v>
+      </c>
+      <c r="BL41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM41" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN41" t="n">
+        <v>376</v>
+      </c>
+      <c r="BO41" t="n">
+        <v>45600000</v>
+      </c>
+      <c r="BP41" t="n">
+        <v>389</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -8571,22 +8683,22 @@
         <v>78.2</v>
       </c>
       <c r="AK42" t="n">
-        <v>21.22222222222222</v>
+        <v>20.9</v>
       </c>
       <c r="AL42" t="n">
-        <v>185.4444444444445</v>
+        <v>184.7</v>
       </c>
       <c r="AM42" t="n">
         <v>1</v>
       </c>
       <c r="AN42" t="n">
-        <v>70.77777777777777</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="AO42" t="n">
-        <v>4402777.777777778</v>
+        <v>4112500</v>
       </c>
       <c r="AP42" t="n">
-        <v>79.88888888888889</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="AQ42" t="n">
         <v>23.375</v>
@@ -8607,28 +8719,28 @@
         <v>76.625</v>
       </c>
       <c r="AW42" t="n">
-        <v>21.875</v>
+        <v>21.1</v>
       </c>
       <c r="AX42" t="n">
-        <v>178.75</v>
+        <v>178.6</v>
       </c>
       <c r="AY42" t="n">
         <v>1</v>
       </c>
       <c r="AZ42" t="n">
-        <v>67.1875</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="BA42" t="n">
-        <v>2412500</v>
+        <v>2425000</v>
       </c>
       <c r="BB42" t="n">
-        <v>76</v>
+        <v>76.8</v>
       </c>
       <c r="BC42" t="n">
         <v>31</v>
       </c>
       <c r="BD42" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="BE42" t="n">
         <v>2</v>
@@ -8670,7 +8782,7 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
@@ -8678,82 +8790,82 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">leonard t 
+          <t xml:space="preserve">stinat j 
   fra </t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>18752</v>
+        <v>33150</v>
       </c>
       <c r="F43" t="n">
-        <v>14811</v>
+        <v>25491</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>0.26</v>
+        <v>1.01</v>
       </c>
       <c r="L43" t="n">
-        <v>0.92</v>
+        <v>0.33</v>
       </c>
       <c r="M43" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="N43" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="O43" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P43" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q43" t="n">
         <v>3</v>
       </c>
       <c r="R43" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S43" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T43" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="U43" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V43" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>6FKPxxgf</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>K6b7RoBp</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
       <c r="Y43" t="n">
@@ -8771,123 +8883,95 @@
       <c r="AC43" t="inlineStr"/>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="AE43" t="n">
-        <v>25.7</v>
+        <v>22.63636363636364</v>
       </c>
       <c r="AF43" t="n">
-        <v>184.5</v>
+        <v>182</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.1</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="AH43" t="n">
-        <v>68</v>
+        <v>72.18181818181819</v>
       </c>
       <c r="AI43" t="n">
-        <v>1587500</v>
+        <v>5027272.727272728</v>
       </c>
       <c r="AJ43" t="n">
-        <v>72.8</v>
+        <v>78.90909090909091</v>
       </c>
       <c r="AK43" t="n">
-        <v>27.63636363636364</v>
+        <v>24.72727272727273</v>
       </c>
       <c r="AL43" t="n">
-        <v>179.8181818181818</v>
+        <v>182.2727272727273</v>
       </c>
       <c r="AM43" t="n">
-        <v>1.454545454545455</v>
+        <v>1.363636363636364</v>
       </c>
       <c r="AN43" t="n">
-        <v>77</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="AO43" t="n">
-        <v>12381818.18181818</v>
+        <v>5118181.818181818</v>
       </c>
       <c r="AP43" t="n">
-        <v>78.72727272727273</v>
+        <v>76.09090909090909</v>
       </c>
       <c r="AQ43" t="n">
-        <v>25.7</v>
+        <v>24</v>
       </c>
       <c r="AR43" t="n">
-        <v>183.9</v>
+        <v>178.375</v>
       </c>
       <c r="AS43" t="n">
         <v>1</v>
       </c>
       <c r="AT43" t="n">
-        <v>66.45</v>
+        <v>69.8125</v>
       </c>
       <c r="AU43" t="n">
-        <v>1278750</v>
+        <v>2631250</v>
       </c>
       <c r="AV43" t="n">
-        <v>71.84999999999999</v>
+        <v>75.4375</v>
       </c>
       <c r="AW43" t="n">
-        <v>23.90909090909091</v>
+        <v>25.66666666666667</v>
       </c>
       <c r="AX43" t="n">
-        <v>179.9545454545455</v>
+        <v>182.9444444444445</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.090909090909091</v>
+        <v>1.388888888888889</v>
       </c>
       <c r="AZ43" t="n">
-        <v>72.90909090909091</v>
+        <v>71.77777777777777</v>
       </c>
       <c r="BA43" t="n">
-        <v>6081818.181818182</v>
+        <v>3436111.111111111</v>
       </c>
       <c r="BB43" t="n">
-        <v>78.13636363636364</v>
-      </c>
-      <c r="BC43" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD43" t="n">
-        <v>179.25</v>
-      </c>
-      <c r="BE43" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF43" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG43" t="n">
-        <v>266</v>
-      </c>
-      <c r="BH43" t="n">
-        <v>5725000</v>
-      </c>
-      <c r="BI43" t="n">
-        <v>290</v>
-      </c>
-      <c r="BJ43" t="n">
-        <v>25</v>
-      </c>
-      <c r="BK43" t="n">
-        <v>179</v>
-      </c>
-      <c r="BL43" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM43" t="n">
-        <v>4</v>
-      </c>
-      <c r="BN43" t="n">
-        <v>298</v>
-      </c>
-      <c r="BO43" t="n">
-        <v>28600000</v>
-      </c>
-      <c r="BP43" t="n">
-        <v>310</v>
-      </c>
+        <v>74.61111111111111</v>
+      </c>
+      <c r="BC43" t="inlineStr"/>
+      <c r="BD43" t="inlineStr"/>
+      <c r="BE43" t="inlineStr"/>
+      <c r="BF43" t="inlineStr"/>
+      <c r="BG43" t="inlineStr"/>
+      <c r="BH43" t="inlineStr"/>
+      <c r="BI43" t="inlineStr"/>
+      <c r="BJ43" t="inlineStr"/>
+      <c r="BK43" t="inlineStr"/>
+      <c r="BL43" t="inlineStr"/>
+      <c r="BM43" t="inlineStr"/>
+      <c r="BN43" t="inlineStr"/>
+      <c r="BO43" t="inlineStr"/>
+      <c r="BP43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -8997,40 +9081,40 @@
         </is>
       </c>
       <c r="AE44" t="n">
-        <v>25.66666666666667</v>
+        <v>25.5</v>
       </c>
       <c r="AF44" t="n">
-        <v>182.3333333333333</v>
+        <v>182.6</v>
       </c>
       <c r="AG44" t="n">
         <v>1</v>
       </c>
       <c r="AH44" t="n">
-        <v>68.22222222222223</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="AI44" t="n">
-        <v>1708333.333333333</v>
+        <v>1837500</v>
       </c>
       <c r="AJ44" t="n">
-        <v>71.66666666666667</v>
+        <v>72.2</v>
       </c>
       <c r="AK44" t="n">
-        <v>23.8</v>
+        <v>24</v>
       </c>
       <c r="AL44" t="n">
-        <v>184</v>
+        <v>183.7272727272727</v>
       </c>
       <c r="AM44" t="n">
-        <v>1.2</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="AN44" t="n">
-        <v>73.7</v>
+        <v>74.09090909090909</v>
       </c>
       <c r="AO44" t="n">
-        <v>9280000</v>
+        <v>10027272.72727273</v>
       </c>
       <c r="AP44" t="n">
-        <v>78.90000000000001</v>
+        <v>79</v>
       </c>
       <c r="AQ44" t="n">
         <v>25.08333333333333</v>
@@ -9051,22 +9135,22 @@
         <v>69.25</v>
       </c>
       <c r="AW44" t="n">
-        <v>22.7</v>
+        <v>23</v>
       </c>
       <c r="AX44" t="n">
-        <v>179.5</v>
+        <v>179.6363636363636</v>
       </c>
       <c r="AY44" t="n">
-        <v>1.1</v>
+        <v>1.181818181818182</v>
       </c>
       <c r="AZ44" t="n">
-        <v>72.7</v>
+        <v>73.18181818181819</v>
       </c>
       <c r="BA44" t="n">
-        <v>5470000</v>
+        <v>6563636.363636363</v>
       </c>
       <c r="BB44" t="n">
-        <v>78.09999999999999</v>
+        <v>78.27272727272727</v>
       </c>
       <c r="BC44" t="n">
         <v>25</v>
@@ -9222,19 +9306,19 @@
         <v>23.9</v>
       </c>
       <c r="AF45" t="n">
-        <v>182.9</v>
+        <v>183.2</v>
       </c>
       <c r="AG45" t="n">
         <v>1.4</v>
       </c>
       <c r="AH45" t="n">
-        <v>76.2</v>
+        <v>76.3</v>
       </c>
       <c r="AI45" t="n">
-        <v>12650000</v>
+        <v>14000000</v>
       </c>
       <c r="AJ45" t="n">
-        <v>80.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="AK45" t="inlineStr"/>
       <c r="AL45" t="inlineStr"/>
@@ -9246,19 +9330,19 @@
         <v>20.86666666666667</v>
       </c>
       <c r="AR45" t="n">
-        <v>183.6666666666667</v>
+        <v>183.7333333333333</v>
       </c>
       <c r="AS45" t="n">
         <v>1.2</v>
       </c>
       <c r="AT45" t="n">
-        <v>72.73333333333333</v>
+        <v>72.8</v>
       </c>
       <c r="AU45" t="n">
-        <v>9083333.333333334</v>
+        <v>9950000</v>
       </c>
       <c r="AV45" t="n">
-        <v>82</v>
+        <v>82.13333333333334</v>
       </c>
       <c r="AW45" t="n">
         <v>22.72727272727273</v>
@@ -9435,58 +9519,58 @@
       <c r="AI46" t="inlineStr"/>
       <c r="AJ46" t="inlineStr"/>
       <c r="AK46" t="n">
-        <v>24.875</v>
+        <v>25.55555555555556</v>
       </c>
       <c r="AL46" t="n">
-        <v>180.25</v>
+        <v>180.7777777777778</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.25</v>
+        <v>1.222222222222222</v>
       </c>
       <c r="AN46" t="n">
-        <v>75.875</v>
+        <v>75.88888888888889</v>
       </c>
       <c r="AO46" t="n">
-        <v>10312500</v>
+        <v>9722222.222222222</v>
       </c>
       <c r="AP46" t="n">
-        <v>80.5</v>
+        <v>80</v>
       </c>
       <c r="AQ46" t="n">
-        <v>20.25</v>
+        <v>20.69230769230769</v>
       </c>
       <c r="AR46" t="n">
-        <v>181.6666666666667</v>
+        <v>182.5384615384615</v>
       </c>
       <c r="AS46" t="n">
         <v>1</v>
       </c>
       <c r="AT46" t="n">
-        <v>68</v>
+        <v>68.46153846153847</v>
       </c>
       <c r="AU46" t="n">
-        <v>3266666.666666667</v>
+        <v>3353846.153846154</v>
       </c>
       <c r="AV46" t="n">
-        <v>78.75</v>
+        <v>78.46153846153847</v>
       </c>
       <c r="AW46" t="n">
-        <v>23.33333333333333</v>
+        <v>24.72727272727273</v>
       </c>
       <c r="AX46" t="n">
-        <v>178.6111111111111</v>
+        <v>180.5454545454545</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.444444444444444</v>
+        <v>1.636363636363636</v>
       </c>
       <c r="AZ46" t="n">
-        <v>72.38888888888889</v>
+        <v>73.04545454545455</v>
       </c>
       <c r="BA46" t="n">
-        <v>8463888.888888888</v>
+        <v>7902272.727272728</v>
       </c>
       <c r="BB46" t="n">
-        <v>79.88888888888889</v>
+        <v>79.18181818181819</v>
       </c>
       <c r="BC46" t="n">
         <v>24</v>
@@ -9639,46 +9723,58 @@
         </is>
       </c>
       <c r="AE47" t="n">
-        <v>28.1</v>
+        <v>28.18181818181818</v>
       </c>
       <c r="AF47" t="n">
-        <v>181.5</v>
+        <v>182.9090909090909</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.3</v>
+        <v>1.363636363636364</v>
       </c>
       <c r="AH47" t="n">
-        <v>74.09999999999999</v>
+        <v>74.27272727272727</v>
       </c>
       <c r="AI47" t="n">
-        <v>5460000</v>
+        <v>5645454.545454546</v>
       </c>
       <c r="AJ47" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK47" t="inlineStr"/>
-      <c r="AL47" t="inlineStr"/>
-      <c r="AM47" t="inlineStr"/>
-      <c r="AN47" t="inlineStr"/>
-      <c r="AO47" t="inlineStr"/>
-      <c r="AP47" t="inlineStr"/>
+        <v>75.09090909090909</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>23.55555555555556</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>182.1111111111111</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>75.88888888888889</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>14111111.11111111</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>80</v>
+      </c>
       <c r="AQ47" t="n">
-        <v>22.78571428571428</v>
+        <v>23.2</v>
       </c>
       <c r="AR47" t="n">
-        <v>178.1428571428571</v>
+        <v>179.4</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.285714285714286</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AT47" t="n">
-        <v>67.71428571428571</v>
+        <v>68.26666666666667</v>
       </c>
       <c r="AU47" t="n">
-        <v>4185714.285714286</v>
+        <v>4406666.666666667</v>
       </c>
       <c r="AV47" t="n">
-        <v>74.42857142857143</v>
+        <v>74.53333333333333</v>
       </c>
       <c r="AW47" t="n">
         <v>24.36363636363636</v>
@@ -9720,25 +9816,25 @@
         <v>77</v>
       </c>
       <c r="BJ47" t="n">
-        <v>23.75</v>
+        <v>22.33333333333333</v>
       </c>
       <c r="BK47" t="n">
-        <v>183.75</v>
+        <v>184.6666666666667</v>
       </c>
       <c r="BL47" t="n">
-        <v>1.25</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="BM47" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BN47" t="n">
-        <v>296</v>
+        <v>431</v>
       </c>
       <c r="BO47" t="n">
-        <v>48000000</v>
+        <v>53800000</v>
       </c>
       <c r="BP47" t="n">
-        <v>318</v>
+        <v>482</v>
       </c>
     </row>
     <row r="48">
@@ -9877,22 +9973,22 @@
         <v>71.55555555555556</v>
       </c>
       <c r="AQ48" t="n">
-        <v>22.07142857142857</v>
+        <v>24</v>
       </c>
       <c r="AR48" t="n">
-        <v>179.7857142857143</v>
+        <v>180.1764705882353</v>
       </c>
       <c r="AS48" t="n">
-        <v>1</v>
+        <v>1.176470588235294</v>
       </c>
       <c r="AT48" t="n">
-        <v>64.21428571428571</v>
+        <v>66.29411764705883</v>
       </c>
       <c r="AU48" t="n">
-        <v>1037500</v>
+        <v>1507352.941176471</v>
       </c>
       <c r="AV48" t="n">
-        <v>74.07142857142857</v>
+        <v>74.41176470588235</v>
       </c>
       <c r="AW48" t="n">
         <v>24.95</v>
@@ -10073,22 +10169,22 @@
         <v>72.75</v>
       </c>
       <c r="AW49" t="n">
-        <v>23.69230769230769</v>
+        <v>24.6875</v>
       </c>
       <c r="AX49" t="n">
-        <v>183.5384615384615</v>
+        <v>183.4375</v>
       </c>
       <c r="AY49" t="n">
-        <v>2.307692307692307</v>
+        <v>2.4375</v>
       </c>
       <c r="AZ49" t="n">
-        <v>80.38461538461539</v>
+        <v>81.625</v>
       </c>
       <c r="BA49" t="n">
-        <v>42061538.46153846</v>
+        <v>47956250</v>
       </c>
       <c r="BB49" t="n">
-        <v>84.76923076923077</v>
+        <v>85.375</v>
       </c>
       <c r="BC49" t="n">
         <v>19</v>
@@ -10136,7 +10232,7 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>b15XX7Nt</t>
+          <t>EeC5phre</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -10144,78 +10240,74 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">bollengier m 
+          <t xml:space="preserve">valnet a 
   fra </t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de roudourou
-  guingamp </t>
+          <t xml:space="preserve">michel moretti stadium
+  ajaccio </t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>19060</v>
+        <v>8470</v>
       </c>
       <c r="F50" t="n">
-        <v>6052</v>
+        <v>3315</v>
       </c>
       <c r="G50" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>QDfKl36E</t>
+          <t>2aeoANM8</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>fsfAHubD</t>
+          <t>0pOdQOCg</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="N50" t="n">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="O50" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="P50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="T50" t="n">
-        <v>12</v>
-      </c>
-      <c r="U50" t="n">
-        <v>9</v>
-      </c>
-      <c r="V50" t="n">
-        <v>14</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr">
         <is>
-          <t>QNSJnsB5</t>
+          <t>8tmnzqxe</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>4vG8dmrf</t>
+          <t>OQuqpG7i</t>
         </is>
       </c>
       <c r="Y50" t="n">
@@ -10233,76 +10325,76 @@
       <c r="AC50" t="inlineStr"/>
       <c r="AD50" t="inlineStr"/>
       <c r="AE50" t="n">
-        <v>24.5</v>
+        <v>24.9</v>
       </c>
       <c r="AF50" t="n">
-        <v>179.9</v>
+        <v>178.2</v>
       </c>
       <c r="AG50" t="n">
         <v>1</v>
       </c>
       <c r="AH50" t="n">
-        <v>65.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AI50" t="n">
-        <v>1025000</v>
+        <v>872500</v>
       </c>
       <c r="AJ50" t="n">
-        <v>69.90000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="AK50" t="n">
-        <v>27.625</v>
+        <v>22.5</v>
       </c>
       <c r="AL50" t="n">
-        <v>177.625</v>
+        <v>182.5</v>
       </c>
       <c r="AM50" t="n">
         <v>1</v>
       </c>
       <c r="AN50" t="n">
-        <v>67.375</v>
+        <v>64.75</v>
       </c>
       <c r="AO50" t="n">
-        <v>1275000</v>
+        <v>1090625</v>
       </c>
       <c r="AP50" t="n">
-        <v>70.375</v>
+        <v>70.75</v>
       </c>
       <c r="AQ50" t="n">
-        <v>23</v>
+        <v>26.38888888888889</v>
       </c>
       <c r="AR50" t="n">
-        <v>179.7</v>
+        <v>180</v>
       </c>
       <c r="AS50" t="n">
         <v>1</v>
       </c>
       <c r="AT50" t="n">
-        <v>63.3</v>
+        <v>65.05555555555556</v>
       </c>
       <c r="AU50" t="n">
-        <v>950000</v>
+        <v>751388.8888888889</v>
       </c>
       <c r="AV50" t="n">
-        <v>70.3</v>
+        <v>69.61111111111111</v>
       </c>
       <c r="AW50" t="n">
-        <v>20.41666666666667</v>
+        <v>22</v>
       </c>
       <c r="AX50" t="n">
-        <v>179.6666666666667</v>
+        <v>182.2</v>
       </c>
       <c r="AY50" t="n">
         <v>1</v>
       </c>
       <c r="AZ50" t="n">
-        <v>61.75</v>
+        <v>62.7</v>
       </c>
       <c r="BA50" t="n">
-        <v>912500</v>
+        <v>830000</v>
       </c>
       <c r="BB50" t="n">
-        <v>70.91666666666667</v>
+        <v>71</v>
       </c>
       <c r="BC50" t="inlineStr"/>
       <c r="BD50" t="inlineStr"/>
@@ -10322,7 +10414,7 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>dGo94DZQ</t>
+          <t>2Hh06Z4E</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
@@ -10330,70 +10422,78 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">kherradji a 
+          <t xml:space="preserve">rosier e 
   fra </t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade des alpes
-  grenoble </t>
+          <t xml:space="preserve">stade de la licorne
+  amiens </t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>20068</v>
+        <v>12097</v>
       </c>
       <c r="F51" t="n">
-        <v>4008</v>
+        <v>4918</v>
       </c>
       <c r="G51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>UgPj1p1N</t>
+          <t>lKkBAsxF</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>E1wDrLsJ</t>
+          <t>2kM6ufaS</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="M51" t="n">
+        <v>51</v>
+      </c>
+      <c r="N51" t="n">
+        <v>49</v>
+      </c>
       <c r="O51" t="n">
+        <v>17</v>
+      </c>
+      <c r="P51" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q51" t="n">
         <v>6</v>
       </c>
-      <c r="P51" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>4</v>
-      </c>
       <c r="R51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="U51" t="n">
+        <v>11</v>
+      </c>
+      <c r="V51" t="n">
+        <v>13</v>
+      </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>WrQARdPN</t>
+          <t>dS1CBple</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ys1Pb7ws</t>
+          <t>SzfSpYcf</t>
         </is>
       </c>
       <c r="Y51" t="n">
@@ -10411,22 +10511,22 @@
       <c r="AC51" t="inlineStr"/>
       <c r="AD51" t="inlineStr"/>
       <c r="AE51" t="n">
-        <v>25.72727272727273</v>
+        <v>26.1</v>
       </c>
       <c r="AF51" t="n">
-        <v>182.8181818181818</v>
+        <v>181.2</v>
       </c>
       <c r="AG51" t="n">
         <v>1</v>
       </c>
       <c r="AH51" t="n">
-        <v>67.63636363636364</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="AI51" t="n">
-        <v>1495454.545454545</v>
+        <v>1205000</v>
       </c>
       <c r="AJ51" t="n">
-        <v>71.36363636363636</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="AK51" t="inlineStr"/>
       <c r="AL51" t="inlineStr"/>
@@ -10435,41 +10535,29 @@
       <c r="AO51" t="inlineStr"/>
       <c r="AP51" t="inlineStr"/>
       <c r="AQ51" t="n">
-        <v>29.66666666666667</v>
+        <v>24.5</v>
       </c>
       <c r="AR51" t="n">
-        <v>185.1666666666667</v>
+        <v>180.75</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.5</v>
+        <v>1.1875</v>
       </c>
       <c r="AT51" t="n">
-        <v>70.5</v>
+        <v>63.0625</v>
       </c>
       <c r="AU51" t="n">
-        <v>1937500</v>
+        <v>751562.5</v>
       </c>
       <c r="AV51" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>24.8125</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>181.5</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>64.3125</v>
-      </c>
-      <c r="BA51" t="n">
-        <v>958750</v>
-      </c>
-      <c r="BB51" t="n">
-        <v>71.3125</v>
-      </c>
+        <v>71.4375</v>
+      </c>
+      <c r="AW51" t="inlineStr"/>
+      <c r="AX51" t="inlineStr"/>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr"/>
+      <c r="BA51" t="inlineStr"/>
+      <c r="BB51" t="inlineStr"/>
       <c r="BC51" t="inlineStr"/>
       <c r="BD51" t="inlineStr"/>
       <c r="BE51" t="inlineStr"/>
@@ -10488,7 +10576,7 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>zB0ErWC7</t>
+          <t>6V8cnEDr</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -10496,74 +10584,78 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">kubler g 
+          <t xml:space="preserve">landry r 
   fra </t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade marcel tribut
-  dunkerque </t>
+          <t xml:space="preserve">stade gabriel montpied
+  clermont ferrand </t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4933</v>
+        <v>10800</v>
       </c>
       <c r="F52" t="n">
-        <v>3333</v>
+        <v>5582</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H52" t="n">
         <v>2</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>tAAobNse</t>
+          <t>IRuMRua1</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>25dB6Eto</t>
+          <t>6NOhR4cm</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="N52" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="O52" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P52" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R52" t="n">
         <v>4</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T52" t="n">
-        <v>15</v>
-      </c>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="U52" t="n">
+        <v>14</v>
+      </c>
+      <c r="V52" t="n">
+        <v>16</v>
+      </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>lb31RXzP</t>
+          <t>4G9MhScS</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>SIiBpBrs</t>
+          <t>fm0Qb28B</t>
         </is>
       </c>
       <c r="Y52" t="n">
@@ -10580,65 +10672,77 @@
       </c>
       <c r="AC52" t="inlineStr"/>
       <c r="AD52" t="inlineStr"/>
-      <c r="AE52" t="inlineStr"/>
-      <c r="AF52" t="inlineStr"/>
-      <c r="AG52" t="inlineStr"/>
-      <c r="AH52" t="inlineStr"/>
-      <c r="AI52" t="inlineStr"/>
-      <c r="AJ52" t="inlineStr"/>
+      <c r="AE52" t="n">
+        <v>23.88888888888889</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>179.8888888888889</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>66.44444444444444</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>1436111.111111111</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>73.77777777777777</v>
+      </c>
       <c r="AK52" t="n">
-        <v>26.44444444444444</v>
+        <v>25.4</v>
       </c>
       <c r="AL52" t="n">
-        <v>182.5555555555555</v>
+        <v>183.7</v>
       </c>
       <c r="AM52" t="n">
         <v>1</v>
       </c>
       <c r="AN52" t="n">
-        <v>64.55555555555556</v>
+        <v>65.5</v>
       </c>
       <c r="AO52" t="n">
-        <v>833333.3333333334</v>
+        <v>962500</v>
       </c>
       <c r="AP52" t="n">
-        <v>67.77777777777777</v>
+        <v>70.7</v>
       </c>
       <c r="AQ52" t="n">
-        <v>22.83333333333333</v>
+        <v>20.85714285714286</v>
       </c>
       <c r="AR52" t="n">
-        <v>176.8333333333333</v>
+        <v>176</v>
       </c>
       <c r="AS52" t="n">
         <v>1</v>
       </c>
       <c r="AT52" t="n">
-        <v>63.25</v>
+        <v>65.28571428571429</v>
       </c>
       <c r="AU52" t="n">
-        <v>804166.6666666666</v>
+        <v>1614285.714285714</v>
       </c>
       <c r="AV52" t="n">
-        <v>70.75</v>
+        <v>75.28571428571429</v>
       </c>
       <c r="AW52" t="n">
-        <v>21.66666666666667</v>
+        <v>26</v>
       </c>
       <c r="AX52" t="n">
-        <v>180.6666666666667</v>
+        <v>182.7272727272727</v>
       </c>
       <c r="AY52" t="n">
         <v>1</v>
       </c>
       <c r="AZ52" t="n">
-        <v>61.83333333333334</v>
+        <v>64.54545454545455</v>
       </c>
       <c r="BA52" t="n">
-        <v>708333.3333333334</v>
+        <v>709090.9090909091</v>
       </c>
       <c r="BB52" t="n">
-        <v>69.33333333333333</v>
+        <v>70.27272727272727</v>
       </c>
       <c r="BC52" t="inlineStr"/>
       <c r="BD52" t="inlineStr"/>
@@ -10658,7 +10762,7 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>6V8cnEDr</t>
+          <t>zB0ErWC7</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
@@ -10666,78 +10770,74 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">landry r 
+          <t xml:space="preserve">kubler g 
   fra </t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade gabriel montpied
-  clermont ferrand </t>
+          <t xml:space="preserve">stade marcel tribut
+  dunkerque </t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>10800</v>
+        <v>4933</v>
       </c>
       <c r="F53" t="n">
-        <v>5582</v>
+        <v>3333</v>
       </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
         <v>2</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>IRuMRua1</t>
+          <t>tAAobNse</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>6NOhR4cm</t>
+          <t>25dB6Eto</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="N53" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="O53" t="n">
+        <v>12</v>
+      </c>
+      <c r="P53" t="n">
         <v>13</v>
       </c>
-      <c r="P53" t="n">
-        <v>11</v>
-      </c>
       <c r="Q53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R53" t="n">
         <v>4</v>
       </c>
       <c r="S53" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T53" t="n">
-        <v>12</v>
-      </c>
-      <c r="U53" t="n">
-        <v>14</v>
-      </c>
-      <c r="V53" t="n">
-        <v>16</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
         <is>
-          <t>4G9MhScS</t>
+          <t>lb31RXzP</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>fm0Qb28B</t>
+          <t>SIiBpBrs</t>
         </is>
       </c>
       <c r="Y53" t="n">
@@ -10754,77 +10854,65 @@
       </c>
       <c r="AC53" t="inlineStr"/>
       <c r="AD53" t="inlineStr"/>
-      <c r="AE53" t="n">
-        <v>23.88888888888889</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>180</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>1.111111111111111</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>66.44444444444444</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>1436111.111111111</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>73.77777777777777</v>
-      </c>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr"/>
+      <c r="AJ53" t="inlineStr"/>
       <c r="AK53" t="n">
-        <v>25.4</v>
+        <v>26.44444444444444</v>
       </c>
       <c r="AL53" t="n">
-        <v>183.7</v>
+        <v>182.5555555555555</v>
       </c>
       <c r="AM53" t="n">
         <v>1</v>
       </c>
       <c r="AN53" t="n">
-        <v>65.5</v>
+        <v>64.55555555555556</v>
       </c>
       <c r="AO53" t="n">
-        <v>962500</v>
+        <v>833333.3333333334</v>
       </c>
       <c r="AP53" t="n">
-        <v>70.7</v>
+        <v>67.77777777777777</v>
       </c>
       <c r="AQ53" t="n">
-        <v>20.85714285714286</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="AR53" t="n">
-        <v>176</v>
+        <v>176.8333333333333</v>
       </c>
       <c r="AS53" t="n">
         <v>1</v>
       </c>
       <c r="AT53" t="n">
-        <v>65.28571428571429</v>
+        <v>63.25</v>
       </c>
       <c r="AU53" t="n">
-        <v>1614285.714285714</v>
+        <v>804166.6666666666</v>
       </c>
       <c r="AV53" t="n">
-        <v>75.28571428571429</v>
+        <v>70.75</v>
       </c>
       <c r="AW53" t="n">
-        <v>26</v>
+        <v>21.66666666666667</v>
       </c>
       <c r="AX53" t="n">
-        <v>182.7272727272727</v>
+        <v>180.6666666666667</v>
       </c>
       <c r="AY53" t="n">
         <v>1</v>
       </c>
       <c r="AZ53" t="n">
-        <v>64.54545454545455</v>
+        <v>61.83333333333334</v>
       </c>
       <c r="BA53" t="n">
-        <v>709090.9090909091</v>
+        <v>708333.3333333334</v>
       </c>
       <c r="BB53" t="n">
-        <v>70.27272727272727</v>
+        <v>69.33333333333333</v>
       </c>
       <c r="BC53" t="inlineStr"/>
       <c r="BD53" t="inlineStr"/>
@@ -10844,7 +10932,7 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2Hh06Z4E</t>
+          <t>dGo94DZQ</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -10852,78 +10940,70 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">rosier e 
+          <t xml:space="preserve">kherradji a 
   fra </t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la licorne
-  amiens </t>
+          <t xml:space="preserve">stade des alpes
+  grenoble </t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>12097</v>
+        <v>20068</v>
       </c>
       <c r="F54" t="n">
-        <v>4918</v>
+        <v>4008</v>
       </c>
       <c r="G54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>lKkBAsxF</t>
+          <t>UgPj1p1N</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2kM6ufaS</t>
+          <t>E1wDrLsJ</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="n">
-        <v>51</v>
-      </c>
-      <c r="N54" t="n">
-        <v>49</v>
-      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="P54" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Q54" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S54" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="T54" t="n">
-        <v>13</v>
-      </c>
-      <c r="U54" t="n">
-        <v>11</v>
-      </c>
-      <c r="V54" t="n">
-        <v>13</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
         <is>
-          <t>dS1CBple</t>
+          <t>WrQARdPN</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>SzfSpYcf</t>
+          <t>Ys1Pb7ws</t>
         </is>
       </c>
       <c r="Y54" t="n">
@@ -10941,22 +11021,22 @@
       <c r="AC54" t="inlineStr"/>
       <c r="AD54" t="inlineStr"/>
       <c r="AE54" t="n">
-        <v>26.1</v>
+        <v>25.72727272727273</v>
       </c>
       <c r="AF54" t="n">
-        <v>181.2</v>
+        <v>182.1818181818182</v>
       </c>
       <c r="AG54" t="n">
         <v>1</v>
       </c>
       <c r="AH54" t="n">
-        <v>67.09999999999999</v>
+        <v>67.63636363636364</v>
       </c>
       <c r="AI54" t="n">
-        <v>1205000</v>
+        <v>1495454.545454545</v>
       </c>
       <c r="AJ54" t="n">
-        <v>71.09999999999999</v>
+        <v>71.36363636363636</v>
       </c>
       <c r="AK54" t="inlineStr"/>
       <c r="AL54" t="inlineStr"/>
@@ -10965,29 +11045,41 @@
       <c r="AO54" t="inlineStr"/>
       <c r="AP54" t="inlineStr"/>
       <c r="AQ54" t="n">
-        <v>24.5</v>
+        <v>29.66666666666667</v>
       </c>
       <c r="AR54" t="n">
-        <v>180.75</v>
+        <v>185.1666666666667</v>
       </c>
       <c r="AS54" t="n">
-        <v>1.1875</v>
+        <v>1.5</v>
       </c>
       <c r="AT54" t="n">
-        <v>63.0625</v>
+        <v>70.5</v>
       </c>
       <c r="AU54" t="n">
-        <v>751562.5</v>
+        <v>1937500</v>
       </c>
       <c r="AV54" t="n">
-        <v>71.4375</v>
-      </c>
-      <c r="AW54" t="inlineStr"/>
-      <c r="AX54" t="inlineStr"/>
-      <c r="AY54" t="inlineStr"/>
-      <c r="AZ54" t="inlineStr"/>
-      <c r="BA54" t="inlineStr"/>
-      <c r="BB54" t="inlineStr"/>
+        <v>72.5</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>24.8125</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>64.3125</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>958750</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>71.3125</v>
+      </c>
       <c r="BC54" t="inlineStr"/>
       <c r="BD54" t="inlineStr"/>
       <c r="BE54" t="inlineStr"/>
@@ -11006,7 +11098,7 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>EeC5phre</t>
+          <t>b15XX7Nt</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
@@ -11014,74 +11106,78 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">valnet a 
+          <t xml:space="preserve">bollengier m 
   fra </t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">michel moretti stadium
-  ajaccio </t>
+          <t xml:space="preserve">stade de roudourou
+  guingamp </t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>8470</v>
+        <v>19060</v>
       </c>
       <c r="F55" t="n">
-        <v>3315</v>
+        <v>6052</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2aeoANM8</t>
+          <t>QDfKl36E</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>0pOdQOCg</t>
+          <t>fsfAHubD</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="N55" t="n">
-        <v>99</v>
+        <v>51</v>
       </c>
       <c r="O55" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P55" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q55" t="n">
         <v>5</v>
       </c>
-      <c r="Q55" t="n">
-        <v>4</v>
-      </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S55" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="U55" t="n">
+        <v>9</v>
+      </c>
+      <c r="V55" t="n">
+        <v>14</v>
+      </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>8tmnzqxe</t>
+          <t>QNSJnsB5</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>OQuqpG7i</t>
+          <t>4vG8dmrf</t>
         </is>
       </c>
       <c r="Y55" t="n">
@@ -11099,76 +11195,76 @@
       <c r="AC55" t="inlineStr"/>
       <c r="AD55" t="inlineStr"/>
       <c r="AE55" t="n">
-        <v>24.9</v>
+        <v>24.5</v>
       </c>
       <c r="AF55" t="n">
-        <v>178.2</v>
+        <v>179.9</v>
       </c>
       <c r="AG55" t="n">
         <v>1</v>
       </c>
       <c r="AH55" t="n">
-        <v>64.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="AI55" t="n">
-        <v>872500</v>
+        <v>1025000</v>
       </c>
       <c r="AJ55" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>27.625</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>177.625</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>67.375</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>1275000</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>70.375</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>179.7</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>950000</v>
+      </c>
+      <c r="AV55" t="n">
         <v>70.3</v>
       </c>
-      <c r="AK55" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>182.5</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>64.75</v>
-      </c>
-      <c r="AO55" t="n">
-        <v>1090625</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>70.75</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>26.38888888888889</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>180</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>65.05555555555556</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>751388.8888888889</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>69.61111111111111</v>
-      </c>
       <c r="AW55" t="n">
-        <v>22</v>
+        <v>20.41666666666667</v>
       </c>
       <c r="AX55" t="n">
-        <v>182.2</v>
+        <v>179.6666666666667</v>
       </c>
       <c r="AY55" t="n">
         <v>1</v>
       </c>
       <c r="AZ55" t="n">
-        <v>62.7</v>
+        <v>61.75</v>
       </c>
       <c r="BA55" t="n">
-        <v>830000</v>
+        <v>912500</v>
       </c>
       <c r="BB55" t="n">
-        <v>71</v>
+        <v>70.91666666666667</v>
       </c>
       <c r="BC55" t="inlineStr"/>
       <c r="BD55" t="inlineStr"/>
